--- a/estimates_PS2026.xlsx
+++ b/estimates_PS2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\GitHub\tibor-pal.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F01DABD-F926-4932-9CF9-690ADD91D984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE17497E-8B44-4E4A-BE09-56144D211C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{898E4DB8-E74C-49BD-9493-76D0D230C2FB}"/>
   </bookViews>
@@ -796,22 +796,22 @@
         <v>0.68202628184472758</v>
       </c>
       <c r="AF2" s="6">
-        <v>0.106991581580998</v>
+        <v>0.105076808074302</v>
       </c>
       <c r="AG2" s="6">
-        <v>0.17357256548469399</v>
+        <v>0.158248776402827</v>
       </c>
       <c r="AH2" s="6">
-        <v>0.13008024620085201</v>
+        <v>0.12338968605319101</v>
       </c>
       <c r="AI2" s="6">
-        <v>9.3889666058376106E-2</v>
+        <v>9.8498378117968299E-2</v>
       </c>
       <c r="AJ2" s="6">
-        <v>5.03153516152723E-2</v>
+        <v>4.9224327290621699E-2</v>
       </c>
       <c r="AK2" s="6">
-        <v>0.118969375785445</v>
+        <v>0.114200790307074</v>
       </c>
       <c r="AL2" s="6"/>
       <c r="AM2" s="6"/>
@@ -912,22 +912,22 @@
         <v>1.3108781333286856</v>
       </c>
       <c r="AF3" s="6">
-        <v>0.10927933196898799</v>
+        <v>0.10631038726976701</v>
       </c>
       <c r="AG3" s="6">
-        <v>0.194113370202951</v>
+        <v>0.16738473978888099</v>
       </c>
       <c r="AH3" s="6">
-        <v>0.120217815230222</v>
+        <v>0.11618855859225601</v>
       </c>
       <c r="AI3" s="6">
-        <v>8.5202055590456793E-2</v>
+        <v>9.3134528332838598E-2</v>
       </c>
       <c r="AJ3" s="6">
-        <v>4.9095306948347198E-2</v>
+        <v>4.85080910015767E-2</v>
       </c>
       <c r="AK3" s="6">
-        <v>0.11936868831632499</v>
+        <v>0.113342504305152</v>
       </c>
       <c r="AL3" s="6"/>
       <c r="AM3" s="6"/>
@@ -1028,22 +1028,22 @@
         <v>1.7356833581507303</v>
       </c>
       <c r="AF4" s="6">
-        <v>0.11097225341336101</v>
+        <v>0.107211555399974</v>
       </c>
       <c r="AG4" s="6">
-        <v>0.210288167510253</v>
+        <v>0.174246224495479</v>
       </c>
       <c r="AH4" s="6">
-        <v>0.147416959421942</v>
+        <v>0.13063200417924101</v>
       </c>
       <c r="AI4" s="6">
-        <v>9.1426523527864303E-2</v>
+        <v>9.7289535576220998E-2</v>
       </c>
       <c r="AJ4" s="6">
-        <v>4.8181770253346398E-2</v>
+        <v>4.7994434928294298E-2</v>
       </c>
       <c r="AK4" s="6">
-        <v>0.13182627447926801</v>
+        <v>0.119781518780938</v>
       </c>
       <c r="AL4" s="6"/>
       <c r="AM4" s="6"/>
@@ -1144,22 +1144,22 @@
         <v>0.95553907752421452</v>
       </c>
       <c r="AF5" s="6">
-        <v>0.111855742447036</v>
+        <v>0.107692691174126</v>
       </c>
       <c r="AG5" s="6">
-        <v>0.219717728329066</v>
+        <v>0.178013929446657</v>
       </c>
       <c r="AH5" s="6">
-        <v>0.169756394470545</v>
+        <v>0.14108671291720901</v>
       </c>
       <c r="AI5" s="6">
-        <v>9.3510031103343105E-2</v>
+        <v>9.7987383609731193E-2</v>
       </c>
       <c r="AJ5" s="6">
-        <v>4.7707558157831301E-2</v>
+        <v>4.7715887285492302E-2</v>
       </c>
       <c r="AK5" s="6">
-        <v>0.140195815908782</v>
+        <v>0.123557233939373</v>
       </c>
       <c r="AL5" s="6"/>
       <c r="AM5" s="6"/>
@@ -1260,22 +1260,22 @@
         <v>1.4782286312740922</v>
       </c>
       <c r="AF6" s="6">
-        <v>0.11187812096703301</v>
+        <v>0.10694221673716101</v>
       </c>
       <c r="AG6" s="6">
-        <v>0.20363257652382599</v>
+        <v>0.16526210560972601</v>
       </c>
       <c r="AH6" s="6">
-        <v>0.15101693711375699</v>
+        <v>0.13423632938104901</v>
       </c>
       <c r="AI6" s="6">
-        <v>9.2082486095588501E-2</v>
+        <v>9.7111741841987204E-2</v>
       </c>
       <c r="AJ6" s="6">
-        <v>4.7747157434528897E-2</v>
+        <v>4.7698110345238097E-2</v>
       </c>
       <c r="AK6" s="6">
-        <v>0.13138168461442001</v>
+        <v>0.118412522633945</v>
       </c>
       <c r="AL6" s="6"/>
       <c r="AM6" s="6"/>
@@ -1376,22 +1376,22 @@
         <v>1.5381172948124799</v>
       </c>
       <c r="AF7" s="6">
-        <v>0.11124875696970001</v>
+        <v>0.10671659128658401</v>
       </c>
       <c r="AG7" s="6">
-        <v>0.19795803879017601</v>
+        <v>0.16362522638209601</v>
       </c>
       <c r="AH7" s="6">
-        <v>0.148570125128998</v>
+        <v>0.13324142313095</v>
       </c>
       <c r="AI7" s="6">
-        <v>9.3068975231830095E-2</v>
+        <v>9.7709939744775598E-2</v>
       </c>
       <c r="AJ7" s="6">
-        <v>4.8048385316200301E-2</v>
+        <v>4.78441538736172E-2</v>
       </c>
       <c r="AK7" s="6">
-        <v>0.12960346127828101</v>
+        <v>0.11789046860003601</v>
       </c>
       <c r="AL7" s="6"/>
       <c r="AM7" s="6"/>
@@ -1492,22 +1492,22 @@
         <v>1.3125323859656035</v>
       </c>
       <c r="AF8" s="6">
-        <v>0.110741480796731</v>
+        <v>0.106540890767089</v>
       </c>
       <c r="AG8" s="6">
-        <v>0.193650982534709</v>
+        <v>0.16241883936754101</v>
       </c>
       <c r="AH8" s="6">
-        <v>0.14534069085661599</v>
+        <v>0.13195428332386799</v>
       </c>
       <c r="AI8" s="6">
-        <v>9.3557700155974505E-2</v>
+        <v>9.7933508493593904E-2</v>
       </c>
       <c r="AJ8" s="6">
-        <v>4.8300638280529197E-2</v>
+        <v>4.7964340272376497E-2</v>
       </c>
       <c r="AK8" s="6">
-        <v>0.127841420259832</v>
+        <v>0.117313602006532</v>
       </c>
       <c r="AL8" s="6"/>
       <c r="AM8" s="6"/>
@@ -1608,22 +1608,22 @@
         <v>0.74808933823362622</v>
       </c>
       <c r="AF9" s="6">
-        <v>0.11012526374399299</v>
+        <v>0.106300750865667</v>
       </c>
       <c r="AG9" s="6">
-        <v>0.188197267756291</v>
+        <v>0.16067414889784101</v>
       </c>
       <c r="AH9" s="6">
-        <v>0.14251610785641</v>
+        <v>0.13064334788208601</v>
       </c>
       <c r="AI9" s="6">
-        <v>9.4565531299371397E-2</v>
+        <v>9.8466039188470106E-2</v>
       </c>
       <c r="AJ9" s="6">
-        <v>4.86018482967666E-2</v>
+        <v>4.8117228455105299E-2</v>
       </c>
       <c r="AK9" s="6">
-        <v>0.12601754238347601</v>
+        <v>0.11666596045717501</v>
       </c>
       <c r="AL9" s="6"/>
       <c r="AM9" s="6"/>
@@ -1724,22 +1724,22 @@
         <v>1.321993518747</v>
       </c>
       <c r="AF10" s="6">
-        <v>0.108951907524191</v>
+        <v>0.106096579345689</v>
       </c>
       <c r="AG10" s="6">
-        <v>0.16759825125084399</v>
+        <v>0.153413503948544</v>
       </c>
       <c r="AH10" s="6">
-        <v>0.13340023154372399</v>
+        <v>0.12598663342187499</v>
       </c>
       <c r="AI10" s="6">
-        <v>9.3640871418923993E-2</v>
+        <v>9.7870817200975402E-2</v>
       </c>
       <c r="AJ10" s="6">
-        <v>4.8623664026187799E-2</v>
+        <v>4.8109638430665E-2</v>
       </c>
       <c r="AK10" s="6">
-        <v>0.118350135561479</v>
+        <v>0.113532006673795</v>
       </c>
       <c r="AL10" s="6"/>
       <c r="AM10" s="6"/>
@@ -1840,22 +1840,22 @@
         <v>1.5112808287716106</v>
       </c>
       <c r="AF11" s="6">
-        <v>0.108995804936291</v>
+        <v>0.106153230519673</v>
       </c>
       <c r="AG11" s="6">
-        <v>0.16875736005126199</v>
+        <v>0.1542089770566</v>
       </c>
       <c r="AH11" s="6">
-        <v>0.13716750505414399</v>
+        <v>0.12823474750867001</v>
       </c>
       <c r="AI11" s="6">
-        <v>0.10071326913798601</v>
+        <v>0.101048656359659</v>
       </c>
       <c r="AJ11" s="6">
-        <v>4.9198484430561198E-2</v>
+        <v>4.8192256681084497E-2</v>
       </c>
       <c r="AK11" s="6">
-        <v>0.121343403751087</v>
+        <v>0.11505334009052599</v>
       </c>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6"/>
@@ -1956,22 +1956,22 @@
         <v>1.537735749143998</v>
       </c>
       <c r="AF12" s="6">
-        <v>0.10900282413823401</v>
+        <v>0.106188460013406</v>
       </c>
       <c r="AG12" s="6">
-        <v>0.16972943202222401</v>
+        <v>0.15490061141536601</v>
       </c>
       <c r="AH12" s="6">
-        <v>0.13963997722184701</v>
+        <v>0.12943259353627601</v>
       </c>
       <c r="AI12" s="6">
-        <v>9.9507362026689999E-2</v>
+        <v>0.100430357638902</v>
       </c>
       <c r="AJ12" s="6">
-        <v>4.9183245975832998E-2</v>
+        <v>4.8191187101512697E-2</v>
       </c>
       <c r="AK12" s="6">
-        <v>0.121921799370707</v>
+        <v>0.115393238124986</v>
       </c>
       <c r="AL12" s="6"/>
       <c r="AM12" s="6"/>
@@ -2072,22 +2072,22 @@
         <v>1.9238899590684255</v>
       </c>
       <c r="AF13" s="6">
-        <v>0.108208834967953</v>
+        <v>0.105799609965169</v>
       </c>
       <c r="AG13" s="6">
-        <v>0.16395410687072501</v>
+        <v>0.15244477102096399</v>
       </c>
       <c r="AH13" s="6">
-        <v>0.136441373020083</v>
+        <v>0.12733476790522899</v>
       </c>
       <c r="AI13" s="6">
-        <v>0.10147288804299601</v>
+        <v>0.10155866541886099</v>
       </c>
       <c r="AJ13" s="6">
-        <v>4.9586978029997897E-2</v>
+        <v>4.8425795308995899E-2</v>
       </c>
       <c r="AK13" s="6">
-        <v>0.120110496827368</v>
+        <v>0.114491531972875</v>
       </c>
       <c r="AL13" s="6"/>
       <c r="AM13" s="6"/>
@@ -2188,22 +2188,22 @@
         <v>1.6917730954455479</v>
       </c>
       <c r="AF14" s="6">
-        <v>0.10779330611210799</v>
+        <v>0.10560178255915401</v>
       </c>
       <c r="AG14" s="6">
-        <v>0.16142410036048599</v>
+        <v>0.15140679980670799</v>
       </c>
       <c r="AH14" s="6">
-        <v>0.13384774331583901</v>
+        <v>0.12606572365886701</v>
       </c>
       <c r="AI14" s="6">
-        <v>0.101859617227696</v>
+        <v>0.101853078780743</v>
       </c>
       <c r="AJ14" s="6">
-        <v>4.9801183122049099E-2</v>
+        <v>4.8554564272175998E-2</v>
       </c>
       <c r="AK14" s="6">
-        <v>0.11889485735697999</v>
+        <v>0.113968357916492</v>
       </c>
       <c r="AL14" s="6"/>
       <c r="AM14" s="6"/>
@@ -2304,22 +2304,22 @@
         <v>1.1847619757674011</v>
       </c>
       <c r="AF15" s="6">
-        <v>0.10669292682286299</v>
+        <v>0.10503163809586701</v>
       </c>
       <c r="AG15" s="6">
-        <v>0.15346193958110901</v>
+        <v>0.14764648142619999</v>
       </c>
       <c r="AH15" s="6">
-        <v>0.13476085177684499</v>
+        <v>0.12641418955504299</v>
       </c>
       <c r="AI15" s="6">
-        <v>0.105669131359427</v>
+        <v>0.104020387005752</v>
       </c>
       <c r="AJ15" s="6">
-        <v>5.03965045355372E-2</v>
+        <v>4.88969368953995E-2</v>
       </c>
       <c r="AK15" s="6">
-        <v>0.11798736105396899</v>
+        <v>0.113599106040513</v>
       </c>
       <c r="AL15" s="6"/>
       <c r="AM15" s="6"/>
@@ -2420,22 +2420,22 @@
         <v>1.1100106231305418</v>
       </c>
       <c r="AF16" s="6">
-        <v>0.10766197650336</v>
+        <v>0.105329272396224</v>
       </c>
       <c r="AG16" s="6">
-        <v>0.17230440101833699</v>
+        <v>0.15671519716773599</v>
       </c>
       <c r="AH16" s="6">
-        <v>0.14205398757329901</v>
+        <v>0.13024892270086599</v>
       </c>
       <c r="AI16" s="6">
-        <v>0.109137398000739</v>
+        <v>0.105927600245299</v>
       </c>
       <c r="AJ16" s="6">
-        <v>5.0960403826676201E-2</v>
+        <v>4.9221753598774599E-2</v>
       </c>
       <c r="AK16" s="6">
-        <v>0.12547052002835099</v>
+        <v>0.117331362131496</v>
       </c>
       <c r="AL16" s="6"/>
       <c r="AM16" s="6"/>
@@ -2536,22 +2536,22 @@
         <v>1.0200758723504677</v>
       </c>
       <c r="AF17" s="6">
-        <v>0.106224625230775</v>
+        <v>0.104596591822177</v>
       </c>
       <c r="AG17" s="6">
-        <v>0.15960671742266899</v>
+        <v>0.15096395846713201</v>
       </c>
       <c r="AH17" s="6">
-        <v>0.13858869302912599</v>
+        <v>0.12846643719125</v>
       </c>
       <c r="AI17" s="6">
-        <v>0.11469921472160299</v>
+        <v>0.108928126394609</v>
       </c>
       <c r="AJ17" s="6">
-        <v>5.1687507672269498E-2</v>
+        <v>4.9635378031372003E-2</v>
       </c>
       <c r="AK17" s="6">
-        <v>0.12265459207068199</v>
+        <v>0.116096675671313</v>
       </c>
       <c r="AL17" s="6"/>
       <c r="AM17" s="6"/>
@@ -2652,22 +2652,22 @@
         <v>1.5055836632347663</v>
       </c>
       <c r="AF18" s="6">
-        <v>0.10547896011423499</v>
+        <v>0.104213155271101</v>
       </c>
       <c r="AG18" s="6">
-        <v>0.15623408535525299</v>
+        <v>0.14918887954281901</v>
       </c>
       <c r="AH18" s="6">
-        <v>0.144753031740394</v>
+        <v>0.13136525100024099</v>
       </c>
       <c r="AI18" s="6">
-        <v>0.116811081825952</v>
+        <v>0.110112269633034</v>
       </c>
       <c r="AJ18" s="6">
-        <v>5.20496478713341E-2</v>
+        <v>4.9851032836263097E-2</v>
       </c>
       <c r="AK18" s="6">
-        <v>0.123837167327659</v>
+        <v>0.116659230177608</v>
       </c>
       <c r="AL18" s="6"/>
       <c r="AM18" s="6"/>
@@ -2768,22 +2768,22 @@
         <v>1.2411879791372371</v>
       </c>
       <c r="AF19" s="6">
-        <v>0.10392576976463901</v>
+        <v>0.10337723565909</v>
       </c>
       <c r="AG19" s="6">
-        <v>0.144890991870433</v>
+        <v>0.14338190774585699</v>
       </c>
       <c r="AH19" s="6">
-        <v>0.121888970903531</v>
+        <v>0.119866859176296</v>
       </c>
       <c r="AI19" s="6">
-        <v>9.4043497593796294E-2</v>
+        <v>9.9848739272189402E-2</v>
       </c>
       <c r="AJ19" s="6">
-        <v>5.19132725441541E-2</v>
+        <v>5.0045786930137601E-2</v>
       </c>
       <c r="AK19" s="6">
-        <v>0.109735560724743</v>
+        <v>0.109855568826041</v>
       </c>
       <c r="AL19" s="6"/>
       <c r="AM19" s="6"/>
@@ -2884,22 +2884,22 @@
         <v>1.2373485207907819</v>
       </c>
       <c r="AF20" s="6">
-        <v>0.103795463682727</v>
+        <v>0.10311197066779799</v>
       </c>
       <c r="AG20" s="6">
-        <v>0.17606631651674101</v>
+        <v>0.15833887329808899</v>
       </c>
       <c r="AH20" s="6">
-        <v>0.140023499272772</v>
+        <v>0.12993720754555199</v>
       </c>
       <c r="AI20" s="6">
-        <v>0.101052406603667</v>
+        <v>0.10383268773316599</v>
       </c>
       <c r="AJ20" s="6">
-        <v>5.28746755317357E-2</v>
+        <v>5.0582087697999399E-2</v>
       </c>
       <c r="AK20" s="6">
-        <v>0.12370310475561699</v>
+        <v>0.11706436325724399</v>
       </c>
       <c r="AL20" s="6"/>
       <c r="AM20" s="6"/>
@@ -3000,22 +3000,22 @@
         <v>1.3270635306140477</v>
       </c>
       <c r="AF21" s="6">
-        <v>0.101489650117961</v>
+        <v>0.101867660317355</v>
       </c>
       <c r="AG21" s="6">
-        <v>0.152286082799409</v>
+        <v>0.14727878433931499</v>
       </c>
       <c r="AH21" s="6">
-        <v>0.11383158684109999</v>
+        <v>0.118427007739872</v>
       </c>
       <c r="AI21" s="6">
-        <v>0.11098061688505099</v>
+        <v>0.109897369035535</v>
       </c>
       <c r="AJ21" s="6">
-        <v>5.4337067103316303E-2</v>
+        <v>5.1371894374191603E-2</v>
       </c>
       <c r="AK21" s="6">
-        <v>0.113214937667591</v>
+        <v>0.112643495034424</v>
       </c>
       <c r="AL21" s="6"/>
       <c r="AM21" s="6"/>
@@ -3116,22 +3116,22 @@
         <v>1.9978857770267311</v>
       </c>
       <c r="AF22" s="6">
-        <v>9.8755923827193101E-2</v>
+        <v>0.100318051899775</v>
       </c>
       <c r="AG22" s="6">
-        <v>0.15838766533651</v>
+        <v>0.14314757946252499</v>
       </c>
       <c r="AH22" s="6">
-        <v>0.16235416476109699</v>
+        <v>0.14258339685263299</v>
       </c>
       <c r="AI22" s="6">
-        <v>0.12595896520709601</v>
+        <v>0.11823500094554799</v>
       </c>
       <c r="AJ22" s="6">
-        <v>5.6418483398249099E-2</v>
+        <v>5.2464328546471997E-2</v>
       </c>
       <c r="AK22" s="6">
-        <v>0.13070994546272</v>
+        <v>0.119729293646317</v>
       </c>
       <c r="AL22" s="6"/>
       <c r="AM22" s="6"/>
@@ -3232,22 +3232,22 @@
         <v>3.2436993539228354</v>
       </c>
       <c r="AF23" s="6">
-        <v>9.55663142616196E-2</v>
+        <v>9.8468172059748796E-2</v>
       </c>
       <c r="AG23" s="6">
-        <v>0.129561795512323</v>
+        <v>0.13009347208322999</v>
       </c>
       <c r="AH23" s="6">
-        <v>0.102972147282726</v>
+        <v>0.113832083128544</v>
       </c>
       <c r="AI23" s="6">
-        <v>5.3289743806995298E-2</v>
+        <v>7.5084486622640598E-2</v>
       </c>
       <c r="AJ23" s="6">
-        <v>2.3374736985924301E-2</v>
+        <v>4.33652757001717E-2</v>
       </c>
       <c r="AK23" s="6">
-        <v>8.6393669284478697E-2</v>
+        <v>9.7594366538378399E-2</v>
       </c>
       <c r="AL23" s="6"/>
       <c r="AM23" s="6"/>
@@ -3348,22 +3348,22 @@
         <v>3.2862730925906192</v>
       </c>
       <c r="AF24" s="6">
-        <v>9.3349404923900495E-2</v>
+        <v>9.7088913044482694E-2</v>
       </c>
       <c r="AG24" s="6">
-        <v>0.11321999736819301</v>
+        <v>0.120920110249694</v>
       </c>
       <c r="AH24" s="6">
-        <v>8.1221066296487898E-2</v>
+        <v>9.8362748160522095E-2</v>
       </c>
       <c r="AI24" s="6">
-        <v>4.2213088869967601E-2</v>
+        <v>5.9836483775925403E-2</v>
       </c>
       <c r="AJ24" s="6">
-        <v>2.15646412930901E-2</v>
+        <v>3.4893221195057E-2</v>
       </c>
       <c r="AK24" s="6">
-        <v>7.3697436665299806E-2</v>
+        <v>8.6434232176735903E-2</v>
       </c>
       <c r="AL24" s="6"/>
       <c r="AM24" s="6"/>
@@ -3464,22 +3464,22 @@
         <v>3.4410611294228843</v>
       </c>
       <c r="AF25" s="6">
-        <v>9.1610035792772396E-2</v>
+        <v>9.5943850840720907E-2</v>
       </c>
       <c r="AG25" s="6">
-        <v>0.101576252975392</v>
+        <v>0.11296255291779</v>
       </c>
       <c r="AH25" s="6">
-        <v>7.6494036983593902E-2</v>
+        <v>0.10162853059139799</v>
       </c>
       <c r="AI25" s="6">
-        <v>4.8350100649903298E-2</v>
+        <v>6.5605892062962204E-2</v>
       </c>
       <c r="AJ25" s="6">
-        <v>2.3457706976959501E-2</v>
+        <v>3.62866592529714E-2</v>
       </c>
       <c r="AK25" s="6">
-        <v>7.1153313925393494E-2</v>
+        <v>8.6693450826414095E-2</v>
       </c>
       <c r="AL25" s="6"/>
       <c r="AM25" s="6"/>
@@ -3580,22 +3580,22 @@
         <v>2.1949687837057752</v>
       </c>
       <c r="AF26" s="6">
-        <v>9.0265946476331793E-2</v>
+        <v>9.5011247688139594E-2</v>
       </c>
       <c r="AG26" s="6">
-        <v>9.4262720130062302E-2</v>
+        <v>0.107807322214874</v>
       </c>
       <c r="AH26" s="6">
-        <v>6.4316395546391902E-2</v>
+        <v>8.7640493844146197E-2</v>
       </c>
       <c r="AI26" s="6">
-        <v>5.09003878047838E-2</v>
+        <v>6.7110156752779301E-2</v>
       </c>
       <c r="AJ26" s="6">
-        <v>2.5448354798763902E-2</v>
+        <v>3.7741145667066801E-2</v>
       </c>
       <c r="AK26" s="6">
-        <v>6.6776052670715499E-2</v>
+        <v>8.2370767341815601E-2</v>
       </c>
       <c r="AL26" s="6"/>
       <c r="AM26" s="6"/>
@@ -3696,22 +3696,22 @@
         <v>2.6689756779388674</v>
       </c>
       <c r="AF27" s="6">
-        <v>0.177720504190927</v>
+        <v>0.144486338470737</v>
       </c>
       <c r="AG27" s="6">
-        <v>0.15134110594414499</v>
+        <v>0.13879945144566799</v>
       </c>
       <c r="AH27" s="6">
-        <v>8.0198253855686602E-2</v>
+        <v>9.7593339224943801E-2</v>
       </c>
       <c r="AI27" s="6">
-        <v>5.72859502809311E-2</v>
+        <v>7.2611192564029703E-2</v>
       </c>
       <c r="AJ27" s="6">
-        <v>2.7397577631566201E-2</v>
+        <v>3.9054603381092602E-2</v>
       </c>
       <c r="AK27" s="6">
-        <v>9.7681817556646802E-2</v>
+        <v>0.100139444906046</v>
       </c>
       <c r="AL27" s="6"/>
       <c r="AM27" s="6"/>
@@ -3812,22 +3812,22 @@
         <v>3.6150873681068063</v>
       </c>
       <c r="AF28" s="6">
-        <v>0.164064190573771</v>
+        <v>0.13859406828901699</v>
       </c>
       <c r="AG28" s="6">
-        <v>0.134265109473724</v>
+        <v>0.13218380880846001</v>
       </c>
       <c r="AH28" s="6">
-        <v>7.2969929563898903E-2</v>
+        <v>9.0968977580913296E-2</v>
       </c>
       <c r="AI28" s="6">
-        <v>6.3224307012329006E-2</v>
+        <v>7.7262975897774103E-2</v>
       </c>
       <c r="AJ28" s="6">
-        <v>2.9256594453662001E-2</v>
+        <v>4.0209524366080197E-2</v>
       </c>
       <c r="AK28" s="6">
-        <v>9.1325817491335406E-2</v>
+        <v>9.7233083773239401E-2</v>
       </c>
       <c r="AL28" s="6"/>
       <c r="AM28" s="6"/>
@@ -3928,22 +3928,22 @@
         <v>4.0154692025668126</v>
       </c>
       <c r="AF29" s="6">
-        <v>0.15316769324888799</v>
+        <v>0.133543184181417</v>
       </c>
       <c r="AG29" s="6">
-        <v>0.12251807505611199</v>
+        <v>0.12707180931304199</v>
       </c>
       <c r="AH29" s="6">
-        <v>6.92357940166346E-2</v>
+        <v>8.6434454781022296E-2</v>
       </c>
       <c r="AI29" s="6">
-        <v>5.2635385768585403E-2</v>
+        <v>6.7229034716918504E-2</v>
       </c>
       <c r="AJ29" s="6">
-        <v>2.72363944885602E-2</v>
+        <v>3.70645658545724E-2</v>
       </c>
       <c r="AK29" s="6">
-        <v>8.3439088552159493E-2</v>
+        <v>9.1418690336137406E-2</v>
       </c>
       <c r="AL29" s="6"/>
       <c r="AM29" s="6"/>
@@ -4044,22 +4044,22 @@
         <v>4.5340719456142153</v>
       </c>
       <c r="AF30" s="6">
-        <v>0.144615290798111</v>
+        <v>0.12932955904946999</v>
       </c>
       <c r="AG30" s="6">
-        <v>0.114634026769488</v>
+        <v>0.123292592548188</v>
       </c>
       <c r="AH30" s="6">
-        <v>6.3928488885421603E-2</v>
+        <v>8.0525921687074994E-2</v>
       </c>
       <c r="AI30" s="6">
-        <v>5.56236087273385E-2</v>
+        <v>6.9281965115656E-2</v>
       </c>
       <c r="AJ30" s="6">
-        <v>2.90438518747787E-2</v>
+        <v>3.8222086583701298E-2</v>
       </c>
       <c r="AK30" s="6">
-        <v>7.9899543044313001E-2</v>
+        <v>8.8975795848219297E-2</v>
       </c>
       <c r="AL30" s="6"/>
       <c r="AM30" s="6"/>
@@ -4160,22 +4160,22 @@
         <v>4.6265784409410315</v>
       </c>
       <c r="AF31" s="6">
-        <v>0.136344697269485</v>
+        <v>0.125029081518827</v>
       </c>
       <c r="AG31" s="6">
-        <v>0.105958281185719</v>
+        <v>0.118683162258759</v>
       </c>
       <c r="AH31" s="6">
-        <v>5.87295488039008E-2</v>
+        <v>7.4646631527392204E-2</v>
       </c>
       <c r="AI31" s="6">
-        <v>5.1752166796037599E-2</v>
+        <v>6.5276228685030802E-2</v>
       </c>
       <c r="AJ31" s="6">
-        <v>3.0793290197709801E-2</v>
+        <v>3.93030323489491E-2</v>
       </c>
       <c r="AK31" s="6">
-        <v>7.4693365967278796E-2</v>
+        <v>8.4946253107674993E-2</v>
       </c>
       <c r="AL31" s="6"/>
       <c r="AM31" s="6"/>
@@ -4276,22 +4276,22 @@
         <v>4.4461527613668395</v>
       </c>
       <c r="AF32" s="6">
-        <v>0.128848709465477</v>
+        <v>0.120906542435416</v>
       </c>
       <c r="AG32" s="6">
-        <v>9.7963148262669303E-2</v>
+        <v>0.113980992007488</v>
       </c>
       <c r="AH32" s="6">
-        <v>5.4439892934081503E-2</v>
+        <v>7.0181009943087805E-2</v>
       </c>
       <c r="AI32" s="6">
-        <v>5.78240062368E-2</v>
+        <v>7.0396247203902806E-2</v>
       </c>
       <c r="AJ32" s="6">
-        <v>3.2769624429159303E-2</v>
+        <v>4.05765588993003E-2</v>
       </c>
       <c r="AK32" s="6">
-        <v>7.2270481153462102E-2</v>
+        <v>8.3348010349002397E-2</v>
       </c>
       <c r="AL32" s="6"/>
       <c r="AM32" s="6"/>
@@ -4392,22 +4392,22 @@
         <v>4.6284826785427668</v>
       </c>
       <c r="AF33" s="6">
-        <v>0.122890127754825</v>
+        <v>0.11744825688504</v>
       </c>
       <c r="AG33" s="6">
-        <v>9.2556788665914394E-2</v>
+        <v>0.110507605214843</v>
       </c>
       <c r="AH33" s="6">
-        <v>5.7638110390480599E-2</v>
+        <v>7.2163971408063701E-2</v>
       </c>
       <c r="AI33" s="6">
-        <v>6.4979506178130503E-2</v>
+        <v>7.5852465860949E-2</v>
       </c>
       <c r="AJ33" s="6">
-        <v>3.4702538357943902E-2</v>
+        <v>4.1779619475585401E-2</v>
       </c>
       <c r="AK33" s="6">
-        <v>7.2996577382578504E-2</v>
+        <v>8.4105651493777994E-2</v>
       </c>
       <c r="AL33" s="6"/>
       <c r="AM33" s="6"/>
@@ -4508,22 +4508,22 @@
         <v>4.3469602313372491</v>
       </c>
       <c r="AF34" s="6">
-        <v>0.118454436131786</v>
+        <v>0.114747908730971</v>
       </c>
       <c r="AG34" s="6">
-        <v>8.9504772663328194E-2</v>
+        <v>0.108341990085246</v>
       </c>
       <c r="AH34" s="6">
-        <v>5.5232187519295602E-2</v>
+        <v>6.9140767252738697E-2</v>
       </c>
       <c r="AI34" s="6">
-        <v>6.9254069547158903E-2</v>
+        <v>7.8798280869200904E-2</v>
       </c>
       <c r="AJ34" s="6">
-        <v>3.64998940209482E-2</v>
+        <v>4.2841722616122603E-2</v>
       </c>
       <c r="AK34" s="6">
-        <v>7.2348304912632E-2</v>
+        <v>8.3297970061168E-2</v>
       </c>
       <c r="AL34" s="6"/>
       <c r="AM34" s="6"/>
@@ -4624,22 +4624,22 @@
         <v>4.7592141649650088</v>
       </c>
       <c r="AF35" s="6">
-        <v>0.114246711834065</v>
+        <v>0.112093568135435</v>
       </c>
       <c r="AG35" s="6">
-        <v>8.6167489481481799E-2</v>
+        <v>0.105896306589069</v>
       </c>
       <c r="AH35" s="6">
-        <v>5.85732258220793E-2</v>
+        <v>7.1088492027079703E-2</v>
       </c>
       <c r="AI35" s="6">
-        <v>7.7293504893439197E-2</v>
+        <v>8.4411435986097502E-2</v>
       </c>
       <c r="AJ35" s="6">
-        <v>3.8385490017521E-2</v>
+        <v>4.3958015275540198E-2</v>
       </c>
       <c r="AK35" s="6">
-        <v>7.4008302360139E-2</v>
+        <v>8.4389446205877197E-2</v>
       </c>
       <c r="AL35" s="6"/>
       <c r="AM35" s="6"/>
@@ -4740,22 +4740,22 @@
         <v>4.5882055138394051</v>
       </c>
       <c r="AF36" s="6">
-        <v>0.111158166735234</v>
+        <v>0.110060000951846</v>
       </c>
       <c r="AG36" s="6">
-        <v>8.4568759396864202E-2</v>
+        <v>0.10454567846493899</v>
       </c>
       <c r="AH36" s="6">
-        <v>5.5969590609548099E-2</v>
+        <v>6.8388197104062201E-2</v>
       </c>
       <c r="AI36" s="6">
-        <v>7.9658523625768002E-2</v>
+        <v>8.63496579790968E-2</v>
       </c>
       <c r="AJ36" s="6">
-        <v>4.0087949644228703E-2</v>
+        <v>4.4915003129524698E-2</v>
       </c>
       <c r="AK36" s="6">
-        <v>7.3358831509157604E-2</v>
+        <v>8.3673062942625095E-2</v>
       </c>
       <c r="AL36" s="6"/>
       <c r="AM36" s="6"/>
@@ -4856,22 +4856,22 @@
         <v>4.6699945022016465</v>
       </c>
       <c r="AF37" s="6">
-        <v>0.10867123225396499</v>
+        <v>0.10836866315504499</v>
       </c>
       <c r="AG37" s="6">
-        <v>8.3743968018811399E-2</v>
+        <v>0.103711844591059</v>
       </c>
       <c r="AH37" s="6">
-        <v>5.90608297023726E-2</v>
+        <v>7.0029995147167595E-2</v>
       </c>
       <c r="AI37" s="6">
-        <v>8.6716269698535103E-2</v>
+        <v>9.0934835546624501E-2</v>
       </c>
       <c r="AJ37" s="6">
-        <v>4.1669475097285802E-2</v>
+        <v>4.5776939478255098E-2</v>
       </c>
       <c r="AK37" s="6">
-        <v>7.5511403069218094E-2</v>
+        <v>8.4886203763586507E-2</v>
       </c>
       <c r="AL37" s="6"/>
       <c r="AM37" s="6"/>
@@ -4972,22 +4972,22 @@
         <v>4.3316318270615994</v>
       </c>
       <c r="AF38" s="6">
-        <v>0.107414919797355</v>
+        <v>0.107453873226418</v>
       </c>
       <c r="AG38" s="6">
-        <v>8.5246369296912303E-2</v>
+        <v>0.10449340407638499</v>
       </c>
       <c r="AH38" s="6">
-        <v>6.0552834347044102E-2</v>
+        <v>7.08997584479127E-2</v>
       </c>
       <c r="AI38" s="6">
-        <v>9.0605136625496796E-2</v>
+        <v>9.3372770418452697E-2</v>
       </c>
       <c r="AJ38" s="6">
-        <v>4.2801549064696402E-2</v>
+        <v>4.6322092686742498E-2</v>
       </c>
       <c r="AK38" s="6">
-        <v>7.7194983300022904E-2</v>
+        <v>8.5814258577329397E-2</v>
       </c>
       <c r="AL38" s="6"/>
       <c r="AM38" s="6"/>
@@ -5088,22 +5088,22 @@
         <v>4.5012320215713331</v>
       </c>
       <c r="AF39" s="6">
-        <v>0.106948996117635</v>
+        <v>0.107043358649258</v>
       </c>
       <c r="AG39" s="6">
-        <v>8.8410624322883394E-2</v>
+        <v>0.106506290740602</v>
       </c>
       <c r="AH39" s="6">
-        <v>6.4190092862478093E-2</v>
+        <v>7.3585884208113003E-2</v>
       </c>
       <c r="AI39" s="6">
-        <v>9.2308707011116098E-2</v>
+        <v>9.4484554316621699E-2</v>
       </c>
       <c r="AJ39" s="6">
-        <v>4.3560636155575497E-2</v>
+        <v>4.6624817882560302E-2</v>
       </c>
       <c r="AK39" s="6">
-        <v>7.9406665862823994E-2</v>
+        <v>8.7240073026946405E-2</v>
       </c>
       <c r="AL39" s="6"/>
       <c r="AM39" s="6"/>
@@ -5204,22 +5204,22 @@
         <v>4.4252558200787107</v>
       </c>
       <c r="AF40" s="6">
-        <v>0.106988852581302</v>
+        <v>0.106979658731471</v>
       </c>
       <c r="AG40" s="6">
-        <v>9.2600674355226703E-2</v>
+        <v>0.109105349479625</v>
       </c>
       <c r="AH40" s="6">
-        <v>6.8391032463571394E-2</v>
+        <v>7.6731274110509298E-2</v>
       </c>
       <c r="AI40" s="6">
-        <v>9.27281288917607E-2</v>
+        <v>9.4985431400669604E-2</v>
       </c>
       <c r="AJ40" s="6">
-        <v>4.4045525236084002E-2</v>
+        <v>4.6760593559788802E-2</v>
       </c>
       <c r="AK40" s="6">
-        <v>8.1747932340667295E-2</v>
+        <v>8.8886289685753503E-2</v>
       </c>
       <c r="AL40" s="6"/>
       <c r="AM40" s="6"/>
@@ -5320,22 +5320,22 @@
         <v>5.5784965849474233</v>
       </c>
       <c r="AF41" s="6">
-        <v>0.10697859926969799</v>
+        <v>0.106843782967493</v>
       </c>
       <c r="AG41" s="6">
-        <v>9.6514949329494101E-2</v>
+        <v>0.11164943171354</v>
       </c>
       <c r="AH41" s="6">
-        <v>7.1112711231329798E-2</v>
+        <v>7.8818770162302307E-2</v>
       </c>
       <c r="AI41" s="6">
-        <v>9.2719077068530498E-2</v>
+        <v>9.5067531544464401E-2</v>
       </c>
       <c r="AJ41" s="6">
-        <v>4.4518144215082198E-2</v>
+        <v>4.6902649456939401E-2</v>
       </c>
       <c r="AK41" s="6">
-        <v>8.3524143154487404E-2</v>
+        <v>9.0148166425218501E-2</v>
       </c>
       <c r="AL41" s="6"/>
       <c r="AM41" s="6"/>
@@ -5436,22 +5436,22 @@
         <v>5.0356613119452831</v>
       </c>
       <c r="AF42" s="6">
-        <v>0.108165673530634</v>
+        <v>0.107287304480498</v>
       </c>
       <c r="AG42" s="6">
-        <v>0.10419066473164</v>
+        <v>0.117141076379729</v>
       </c>
       <c r="AH42" s="6">
-        <v>7.9389609810467304E-2</v>
+        <v>8.4790358682194103E-2</v>
       </c>
       <c r="AI42" s="6">
-        <v>0.11766941802528399</v>
+        <v>0.109173254113932</v>
       </c>
       <c r="AJ42" s="6">
-        <v>7.0019962547825804E-2</v>
+        <v>6.1712104043117597E-2</v>
       </c>
       <c r="AK42" s="6">
-        <v>9.7178311832098005E-2</v>
+        <v>9.8652962533303606E-2</v>
       </c>
       <c r="AL42" s="6"/>
       <c r="AM42" s="6"/>
@@ -5552,22 +5552,22 @@
         <v>4.5371001870508465</v>
       </c>
       <c r="AF43" s="6">
-        <v>0.10810647367923901</v>
+        <v>0.107159316809462</v>
       </c>
       <c r="AG43" s="6">
-        <v>0.107516679499051</v>
+        <v>0.119276015195649</v>
       </c>
       <c r="AH43" s="6">
-        <v>8.1821777234069901E-2</v>
+        <v>8.6548021675851794E-2</v>
       </c>
       <c r="AI43" s="6">
-        <v>0.11495382686191299</v>
+        <v>0.108086509056205</v>
       </c>
       <c r="AJ43" s="6">
-        <v>6.7989085710456601E-2</v>
+        <v>6.0677587835040701E-2</v>
       </c>
       <c r="AK43" s="6">
-        <v>9.7669191073357198E-2</v>
+        <v>9.9213233041704596E-2</v>
       </c>
       <c r="AL43" s="6"/>
       <c r="AM43" s="6"/>
@@ -5668,22 +5668,22 @@
         <v>3.7522854603023958</v>
       </c>
       <c r="AF44" s="6">
-        <v>0.104358228645823</v>
+        <v>0.10480909975392499</v>
       </c>
       <c r="AG44" s="6">
-        <v>0.10565572412692401</v>
+        <v>0.116050598326079</v>
       </c>
       <c r="AH44" s="6">
-        <v>8.1454820324493707E-2</v>
+        <v>8.7046094494732107E-2</v>
       </c>
       <c r="AI44" s="6">
-        <v>0.11159012623711199</v>
+        <v>0.106611165578351</v>
       </c>
       <c r="AJ44" s="6">
-        <v>6.60064495348376E-2</v>
+        <v>5.9647946598906702E-2</v>
       </c>
       <c r="AK44" s="6">
-        <v>9.5621921663055096E-2</v>
+        <v>9.7757335527832404E-2</v>
       </c>
       <c r="AL44" s="6"/>
       <c r="AM44" s="6"/>
@@ -5784,22 +5784,22 @@
         <v>2.2775599374066147</v>
       </c>
       <c r="AF45" s="6">
-        <v>0.10388622328132301</v>
+        <v>0.104199870841421</v>
       </c>
       <c r="AG45" s="6">
-        <v>0.10116974523824999</v>
+        <v>0.1136313229769</v>
       </c>
       <c r="AH45" s="6">
-        <v>8.1235565338396404E-2</v>
+        <v>8.7464673553047198E-2</v>
       </c>
       <c r="AI45" s="6">
-        <v>0.108749462033861</v>
+        <v>0.105318279701394</v>
       </c>
       <c r="AJ45" s="6">
-        <v>6.4271445552066195E-2</v>
+        <v>5.8718164344367503E-2</v>
       </c>
       <c r="AK45" s="6">
-        <v>9.3500476634526403E-2</v>
+        <v>9.6752627052488896E-2</v>
       </c>
       <c r="AL45" s="6"/>
       <c r="AM45" s="6"/>
@@ -5900,22 +5900,22 @@
         <v>3.818017823560993</v>
       </c>
       <c r="AF46" s="6">
-        <v>9.0864305014597094E-2</v>
+        <v>9.7116019133068804E-2</v>
       </c>
       <c r="AG46" s="6">
-        <v>9.70799803345158E-2</v>
+        <v>0.10796579861908399</v>
       </c>
       <c r="AH46" s="6">
-        <v>7.90987610156096E-2</v>
+        <v>8.6985991596281495E-2</v>
       </c>
       <c r="AI46" s="6">
-        <v>0.104410750659244</v>
+        <v>0.103158217915766</v>
       </c>
       <c r="AJ46" s="6">
-        <v>6.2381573564093601E-2</v>
+        <v>5.7696526023282499E-2</v>
       </c>
       <c r="AK46" s="6">
-        <v>8.9136424480481299E-2</v>
+        <v>9.3679809980490997E-2</v>
       </c>
       <c r="AL46" s="6"/>
       <c r="AM46" s="6"/>
@@ -6016,22 +6016,22 @@
         <v>2.6963875214681465</v>
       </c>
       <c r="AF47" s="6">
-        <v>9.19500212186595E-2</v>
+        <v>9.7589084757829694E-2</v>
       </c>
       <c r="AG47" s="6">
-        <v>0.100354363521738</v>
+        <v>0.110188091031879</v>
       </c>
       <c r="AH47" s="6">
-        <v>8.2023699067582806E-2</v>
+        <v>8.8978843973002097E-2</v>
       </c>
       <c r="AI47" s="6">
-        <v>0.106917010397955</v>
+        <v>0.104587649310598</v>
       </c>
       <c r="AJ47" s="6">
-        <v>6.2156735131551399E-2</v>
+        <v>5.7402829168835302E-2</v>
       </c>
       <c r="AK47" s="6">
-        <v>9.1394492165849398E-2</v>
+        <v>9.5090899139025201E-2</v>
       </c>
       <c r="AL47" s="6"/>
       <c r="AM47" s="6"/>
@@ -6132,22 +6132,22 @@
         <v>2.9961334919196503</v>
       </c>
       <c r="AF48" s="6">
-        <v>0.100298668193837</v>
+        <v>0.102611005000932</v>
       </c>
       <c r="AG48" s="6">
-        <v>0.114850783272946</v>
+        <v>0.119649167817657</v>
       </c>
       <c r="AH48" s="6">
-        <v>8.7862149696017605E-2</v>
+        <v>9.2839604621336794E-2</v>
       </c>
       <c r="AI48" s="6">
-        <v>0.111100258475834</v>
+        <v>0.10690876295094</v>
       </c>
       <c r="AJ48" s="6">
-        <v>6.20056205758963E-2</v>
+        <v>5.7245419887269E-2</v>
       </c>
       <c r="AK48" s="6">
-        <v>9.8492892163491594E-2</v>
+        <v>9.9567408076897804E-2</v>
       </c>
       <c r="AL48" s="6"/>
       <c r="AM48" s="6"/>
@@ -6248,22 +6248,22 @@
         <v>2.5035745600284542</v>
       </c>
       <c r="AF49" s="6">
-        <v>9.9768481842587894E-2</v>
+        <v>0.102179485453903</v>
       </c>
       <c r="AG49" s="6">
-        <v>0.113458894257727</v>
+        <v>0.119033210455339</v>
       </c>
       <c r="AH49" s="6">
-        <v>9.4554838874688601E-2</v>
+        <v>9.7086013398996293E-2</v>
       </c>
       <c r="AI49" s="6">
-        <v>0.115750879846734</v>
+        <v>0.10941838000109599</v>
       </c>
       <c r="AJ49" s="6">
-        <v>6.1952544567067003E-2</v>
+        <v>5.7140311724493402E-2</v>
       </c>
       <c r="AK49" s="6">
-        <v>0.100873103447849</v>
+        <v>0.10101157732961499</v>
       </c>
       <c r="AL49" s="6"/>
       <c r="AM49" s="6"/>
@@ -6364,22 +6364,22 @@
         <v>2.7779538257489023</v>
       </c>
       <c r="AF50" s="6">
-        <v>0.10294128961157401</v>
+        <v>0.10394881210861601</v>
       </c>
       <c r="AG50" s="6">
-        <v>0.141602239258557</v>
+        <v>0.13560575217941301</v>
       </c>
       <c r="AH50" s="6">
-        <v>0.10532887881111699</v>
+        <v>0.103512859766635</v>
       </c>
       <c r="AI50" s="6">
-        <v>0.123937916897956</v>
+        <v>0.113587355895045</v>
       </c>
       <c r="AJ50" s="6">
-        <v>6.2439038490868903E-2</v>
+        <v>5.7304323837801402E-2</v>
       </c>
       <c r="AK50" s="6">
-        <v>0.112887825090338</v>
+        <v>0.107924617600859</v>
       </c>
       <c r="AL50" s="6"/>
       <c r="AM50" s="6"/>
@@ -6480,22 +6480,22 @@
         <v>5.411164663720669</v>
       </c>
       <c r="AF51" s="6">
-        <v>0.10055288646693999</v>
+        <v>0.102504186942936</v>
       </c>
       <c r="AG51" s="6">
-        <v>0.126407971963994</v>
+        <v>0.12797515054512801</v>
       </c>
       <c r="AH51" s="6">
-        <v>0.10783485131621701</v>
+        <v>0.10514045222792701</v>
       </c>
       <c r="AI51" s="6">
-        <v>0.14088039644862399</v>
+        <v>0.121473794425574</v>
       </c>
       <c r="AJ51" s="6">
-        <v>6.3991646357904899E-2</v>
+        <v>5.7981427539131297E-2</v>
       </c>
       <c r="AK51" s="6">
-        <v>0.113677421902486</v>
+        <v>0.108239799177324</v>
       </c>
       <c r="AL51" s="6"/>
       <c r="AM51" s="6"/>
@@ -6596,22 +6596,22 @@
         <v>5.2813509537243064</v>
       </c>
       <c r="AF52" s="6">
-        <v>9.8378966966361003E-2</v>
+        <v>0.101131572397543</v>
       </c>
       <c r="AG52" s="6">
-        <v>0.114341280282154</v>
+        <v>0.121181970385159</v>
       </c>
       <c r="AH52" s="6">
-        <v>8.8473228243656304E-2</v>
+        <v>9.4681204421971796E-2</v>
       </c>
       <c r="AI52" s="6">
-        <v>7.3529336884428101E-2</v>
+        <v>8.8657348474770803E-2</v>
       </c>
       <c r="AJ52" s="6">
-        <v>2.0170324034996402E-2</v>
+        <v>3.1350484959917803E-2</v>
       </c>
       <c r="AK52" s="6">
-        <v>8.3383382947292306E-2</v>
+        <v>9.2132421475816406E-2</v>
       </c>
       <c r="AL52" s="6"/>
       <c r="AM52" s="6"/>
@@ -6712,22 +6712,22 @@
         <v>5.5307404812511507</v>
       </c>
       <c r="AF53" s="6">
-        <v>9.7300223349934503E-2</v>
+        <v>0.100375956617184</v>
       </c>
       <c r="AG53" s="6">
-        <v>0.109003921574365</v>
+        <v>0.117884823397641</v>
       </c>
       <c r="AH53" s="6">
-        <v>7.8675889361693896E-2</v>
+        <v>8.8540003010642299E-2</v>
       </c>
       <c r="AI53" s="6">
-        <v>6.8215641965613499E-2</v>
+        <v>8.2844939215447E-2</v>
       </c>
       <c r="AJ53" s="6">
-        <v>2.1867727549879399E-2</v>
+        <v>3.2531256463637401E-2</v>
       </c>
       <c r="AK53" s="6">
-        <v>7.8465878993318597E-2</v>
+        <v>8.8523091664214806E-2</v>
       </c>
       <c r="AL53" s="6"/>
       <c r="AM53" s="6"/>
@@ -6828,22 +6828,22 @@
         <v>6.8089865956245887</v>
       </c>
       <c r="AF54" s="6">
-        <v>9.6306681326656596E-2</v>
+        <v>9.9663808165729006E-2</v>
       </c>
       <c r="AG54" s="6">
-        <v>0.10446160411139099</v>
+        <v>0.114903887514435</v>
       </c>
       <c r="AH54" s="6">
-        <v>7.0185961255032195E-2</v>
+        <v>8.2290224910281207E-2</v>
       </c>
       <c r="AI54" s="6">
-        <v>7.0932965725687594E-2</v>
+        <v>8.5318802443126104E-2</v>
       </c>
       <c r="AJ54" s="6">
-        <v>2.3652250606396301E-2</v>
+        <v>3.3793479559130202E-2</v>
       </c>
       <c r="AK54" s="6">
-        <v>7.5702977691791198E-2</v>
+        <v>8.6760450041083001E-2</v>
       </c>
       <c r="AL54" s="6"/>
       <c r="AM54" s="6"/>
@@ -6944,22 +6944,22 @@
         <v>9.8184741985319235</v>
       </c>
       <c r="AF55" s="6">
-        <v>9.6452821336037997E-2</v>
+        <v>9.9586249084720704E-2</v>
       </c>
       <c r="AG55" s="6">
-        <v>0.104432820374773</v>
+        <v>0.11496702176134301</v>
       </c>
       <c r="AH55" s="6">
-        <v>7.0557237663908104E-2</v>
+        <v>8.2369188277287494E-2</v>
       </c>
       <c r="AI55" s="6">
-        <v>6.8399914013502497E-2</v>
+        <v>8.2493817346365905E-2</v>
       </c>
       <c r="AJ55" s="6">
-        <v>2.4728076222590399E-2</v>
+        <v>3.4314204640785197E-2</v>
       </c>
       <c r="AK55" s="6">
-        <v>7.5465755022282005E-2</v>
+        <v>8.62096509034362E-2</v>
       </c>
       <c r="AL55" s="6"/>
       <c r="AM55" s="6"/>
@@ -7060,22 +7060,22 @@
         <v>11.2713779135191</v>
       </c>
       <c r="AF56" s="6">
-        <v>9.6875023110998298E-2</v>
+        <v>9.9723832257704398E-2</v>
       </c>
       <c r="AG56" s="6">
-        <v>0.106014932983726</v>
+        <v>0.116009919359765</v>
       </c>
       <c r="AH56" s="6">
-        <v>7.2709458116194003E-2</v>
+        <v>8.3606209877864796E-2</v>
       </c>
       <c r="AI56" s="6">
-        <v>6.9104122529206793E-2</v>
+        <v>8.2505114788291006E-2</v>
       </c>
       <c r="AJ56" s="6">
-        <v>2.5353540229122101E-2</v>
+        <v>3.4201928865636097E-2</v>
       </c>
       <c r="AK56" s="6">
-        <v>7.6785197731573704E-2</v>
+        <v>8.6808595937349603E-2</v>
       </c>
       <c r="AL56" s="6"/>
       <c r="AM56" s="6"/>
@@ -7176,22 +7176,22 @@
         <v>9.6563000420584189</v>
       </c>
       <c r="AF57" s="6">
-        <v>9.8209637436548605E-2</v>
+        <v>0.100438715781695</v>
       </c>
       <c r="AG57" s="6">
-        <v>0.111875561213887</v>
+        <v>0.11981592679476399</v>
       </c>
       <c r="AH57" s="6">
-        <v>7.8283873310511801E-2</v>
+        <v>8.7252271880946197E-2</v>
       </c>
       <c r="AI57" s="6">
-        <v>7.9580508111846998E-2</v>
+        <v>9.0430124516079596E-2</v>
       </c>
       <c r="AJ57" s="6">
-        <v>3.1153651092612901E-2</v>
+        <v>3.9642406009635103E-2</v>
       </c>
       <c r="AK57" s="6">
-        <v>8.3066802350146102E-2</v>
+        <v>9.14200292171954E-2</v>
       </c>
       <c r="AL57" s="6"/>
       <c r="AM57" s="6"/>
@@ -7292,22 +7292,22 @@
         <v>7.7381955805552849</v>
       </c>
       <c r="AF58" s="6">
-        <v>0.10015299766875201</v>
+        <v>0.10151778070421601</v>
       </c>
       <c r="AG58" s="6">
-        <v>0.121049855148848</v>
+        <v>0.125605183047169</v>
       </c>
       <c r="AH58" s="6">
-        <v>9.0219265291223205E-2</v>
+        <v>9.5320901961121404E-2</v>
       </c>
       <c r="AI58" s="6">
-        <v>9.2674167951579095E-2</v>
+        <v>9.9224042871969703E-2</v>
       </c>
       <c r="AJ58" s="6">
-        <v>3.2209052007265003E-2</v>
+        <v>4.0033132136061599E-2</v>
       </c>
       <c r="AK58" s="6">
-        <v>9.1770278722997603E-2</v>
+        <v>9.71212640182465E-2</v>
       </c>
       <c r="AL58" s="6"/>
       <c r="AM58" s="6"/>
@@ -7408,22 +7408,22 @@
         <v>6.050577834166404</v>
       </c>
       <c r="AF59" s="6">
-        <v>8.5262988147522603E-2</v>
+        <v>9.4925878619860807E-2</v>
       </c>
       <c r="AG59" s="6">
-        <v>7.6776012624081805E-2</v>
+        <v>9.6714218065802396E-2</v>
       </c>
       <c r="AH59" s="6">
-        <v>7.7723094770720202E-2</v>
+        <v>8.7241673536421704E-2</v>
       </c>
       <c r="AI59" s="6">
-        <v>8.3135147232495904E-2</v>
+        <v>9.2643572408546399E-2</v>
       </c>
       <c r="AJ59" s="6">
-        <v>3.2671207777169899E-2</v>
+        <v>3.9947521754657801E-2</v>
       </c>
       <c r="AK59" s="6">
-        <v>7.3561642666140098E-2</v>
+        <v>8.5537272967671399E-2</v>
       </c>
       <c r="AL59" s="6"/>
       <c r="AM59" s="6"/>
@@ -7524,22 +7524,22 @@
         <v>5.9554942179740777</v>
       </c>
       <c r="AF60" s="6">
-        <v>5.9046319856598098E-2</v>
+        <v>7.6095981772360197E-2</v>
       </c>
       <c r="AG60" s="6">
-        <v>5.8146534139375303E-2</v>
+        <v>7.6340015357688307E-2</v>
       </c>
       <c r="AH60" s="6">
-        <v>7.0263973282821302E-2</v>
+        <v>7.8477278489292104E-2</v>
       </c>
       <c r="AI60" s="6">
-        <v>7.6017738452323499E-2</v>
+        <v>8.7216520884407497E-2</v>
       </c>
       <c r="AJ60" s="6">
-        <v>3.3099423689552598E-2</v>
+        <v>3.9868313054700399E-2</v>
       </c>
       <c r="AK60" s="6">
-        <v>6.2193454094948301E-2</v>
+        <v>7.4606305100212197E-2</v>
       </c>
       <c r="AL60" s="6"/>
       <c r="AM60" s="6"/>
@@ -7640,22 +7640,22 @@
         <v>6.4642742637365913</v>
       </c>
       <c r="AF61" s="6">
-        <v>6.2468565950754E-2</v>
+        <v>7.8863267685584895E-2</v>
       </c>
       <c r="AG61" s="6">
-        <v>5.9907013535676498E-2</v>
+        <v>7.7304467791622394E-2</v>
       </c>
       <c r="AH61" s="6">
-        <v>6.3662063876946104E-2</v>
+        <v>7.3931867228811898E-2</v>
       </c>
       <c r="AI61" s="6">
-        <v>7.2094326312022297E-2</v>
+        <v>8.3805652954805201E-2</v>
       </c>
       <c r="AJ61" s="6">
-        <v>3.3659140818617102E-2</v>
+        <v>3.9933970261517099E-2</v>
       </c>
       <c r="AK61" s="6">
-        <v>6.0592003779981703E-2</v>
+        <v>7.3255998328910998E-2</v>
       </c>
       <c r="AL61" s="6"/>
       <c r="AM61" s="6"/>
@@ -7756,22 +7756,22 @@
         <v>6.0324268579478257</v>
       </c>
       <c r="AF62" s="6">
-        <v>6.58438604364944E-2</v>
+        <v>8.0992189210760304E-2</v>
       </c>
       <c r="AG62" s="6">
-        <v>6.6902576625944496E-2</v>
+        <v>8.3007394370559207E-2</v>
       </c>
       <c r="AH62" s="6">
-        <v>7.2767325902149904E-2</v>
+        <v>8.0453475886994599E-2</v>
       </c>
       <c r="AI62" s="6">
-        <v>7.0707083428751594E-2</v>
+        <v>8.2175087728674406E-2</v>
       </c>
       <c r="AJ62" s="6">
-        <v>3.4276926884707799E-2</v>
+        <v>4.0079124133990202E-2</v>
       </c>
       <c r="AK62" s="6">
-        <v>6.4846549640168602E-2</v>
+        <v>7.6234331058996796E-2</v>
       </c>
       <c r="AL62" s="6"/>
       <c r="AM62" s="6"/>
@@ -7872,22 +7872,22 @@
         <v>4.7707118050080766</v>
       </c>
       <c r="AF63" s="6">
-        <v>6.9050225914965901E-2</v>
+        <v>8.2758894363294006E-2</v>
       </c>
       <c r="AG63" s="6">
-        <v>7.0128116386518002E-2</v>
+        <v>8.6221211396000405E-2</v>
       </c>
       <c r="AH63" s="6">
-        <v>7.0138443563615704E-2</v>
+        <v>7.8740492809042301E-2</v>
       </c>
       <c r="AI63" s="6">
-        <v>7.0490671548697301E-2</v>
+        <v>8.1558603481328804E-2</v>
       </c>
       <c r="AJ63" s="6">
-        <v>3.5112697262119297E-2</v>
+        <v>4.0426305220992997E-2</v>
       </c>
       <c r="AK63" s="6">
-        <v>6.5445529150293696E-2</v>
+        <v>7.6756568454100504E-2</v>
       </c>
       <c r="AL63" s="6"/>
       <c r="AM63" s="6"/>
@@ -7988,22 +7988,22 @@
         <v>6.2164693322383613</v>
       </c>
       <c r="AF64" s="6">
-        <v>6.5588518853245306E-2</v>
+        <v>7.9294415416814298E-2</v>
       </c>
       <c r="AG64" s="6">
-        <v>6.5292648202309206E-2</v>
+        <v>8.2397672729986701E-2</v>
       </c>
       <c r="AH64" s="6">
-        <v>7.1613697555930597E-2</v>
+        <v>7.8131593717818804E-2</v>
       </c>
       <c r="AI64" s="6">
-        <v>7.01207427527787E-2</v>
+        <v>8.0966823168268198E-2</v>
       </c>
       <c r="AJ64" s="6">
-        <v>3.5884231756576297E-2</v>
+        <v>4.0745415940220603E-2</v>
       </c>
       <c r="AK64" s="6">
-        <v>6.4209306006251896E-2</v>
+        <v>7.5114030259248205E-2</v>
       </c>
       <c r="AL64" s="6"/>
       <c r="AM64" s="6"/>
@@ -8104,22 +8104,22 @@
         <v>6.2127424014585486</v>
       </c>
       <c r="AF65" s="6">
-        <v>6.8537857013278206E-2</v>
+        <v>8.11887044661352E-2</v>
       </c>
       <c r="AG65" s="6">
-        <v>7.1723047370773493E-2</v>
+        <v>8.7248437659718001E-2</v>
       </c>
       <c r="AH65" s="6">
-        <v>8.3033640061377895E-2</v>
+        <v>8.4298234946012005E-2</v>
       </c>
       <c r="AI65" s="6">
-        <v>7.1784918232543501E-2</v>
+        <v>8.2725984834345498E-2</v>
       </c>
       <c r="AJ65" s="6">
-        <v>3.6555878254894897E-2</v>
+        <v>4.1008340280523699E-2</v>
       </c>
       <c r="AK65" s="6">
-        <v>6.9652516349543198E-2</v>
+        <v>7.8576608233416501E-2</v>
       </c>
       <c r="AL65" s="6"/>
       <c r="AM65" s="6"/>
@@ -8220,22 +8220,22 @@
         <v>6.6753941139458206</v>
       </c>
       <c r="AF66" s="6">
-        <v>7.1480212351785199E-2</v>
+        <v>8.3020432297771701E-2</v>
       </c>
       <c r="AG66" s="6">
-        <v>7.8333601270244704E-2</v>
+        <v>9.2211327684693006E-2</v>
       </c>
       <c r="AH66" s="6">
-        <v>9.2442082689617094E-2</v>
+        <v>9.0123641205917704E-2</v>
       </c>
       <c r="AI66" s="6">
-        <v>7.1463325098757899E-2</v>
+        <v>8.1956280328307096E-2</v>
       </c>
       <c r="AJ66" s="6">
-        <v>3.7163052413163797E-2</v>
+        <v>4.1242082376784603E-2</v>
       </c>
       <c r="AK66" s="6">
-        <v>7.4136844196954599E-2</v>
+        <v>8.1448751144336806E-2</v>
       </c>
       <c r="AL66" s="6"/>
       <c r="AM66" s="6"/>
@@ -8336,22 +8336,22 @@
         <v>6.0659258202697686</v>
       </c>
       <c r="AF67" s="6">
-        <v>7.4224712869624898E-2</v>
+        <v>8.4695386660154304E-2</v>
       </c>
       <c r="AG67" s="6">
-        <v>8.4665852752431603E-2</v>
+        <v>9.6749845491716002E-2</v>
       </c>
       <c r="AH67" s="6">
-        <v>0.103870638149039</v>
+        <v>9.7235663614045398E-2</v>
       </c>
       <c r="AI67" s="6">
-        <v>7.3192095395223297E-2</v>
+        <v>8.2470182836850106E-2</v>
       </c>
       <c r="AJ67" s="6">
-        <v>3.7785441178134198E-2</v>
+        <v>4.1515904258063799E-2</v>
       </c>
       <c r="AK67" s="6">
-        <v>7.9467403801088493E-2</v>
+        <v>8.4797241318593203E-2</v>
       </c>
       <c r="AL67" s="6"/>
       <c r="AM67" s="6"/>
@@ -8452,22 +8452,22 @@
         <v>6.5984407884510432</v>
       </c>
       <c r="AF68" s="6">
-        <v>7.6560140065654106E-2</v>
+        <v>8.6041453560064707E-2</v>
       </c>
       <c r="AG68" s="6">
-        <v>8.8634634750557204E-2</v>
+        <v>9.9845350242223393E-2</v>
       </c>
       <c r="AH68" s="6">
-        <v>0.10052507232010501</v>
+        <v>9.5772051098041197E-2</v>
       </c>
       <c r="AI68" s="6">
-        <v>7.4231950052241202E-2</v>
+        <v>8.3066130831378496E-2</v>
       </c>
       <c r="AJ68" s="6">
-        <v>3.8623024955385402E-2</v>
+        <v>4.19447467475755E-2</v>
       </c>
       <c r="AK68" s="6">
-        <v>8.0306222794441301E-2</v>
+        <v>8.5571603984319303E-2</v>
       </c>
       <c r="AL68" s="6"/>
       <c r="AM68" s="6"/>
@@ -8568,22 +8568,22 @@
         <v>5.7709830786818017</v>
       </c>
       <c r="AF69" s="6">
-        <v>7.8423201934100004E-2</v>
+        <v>8.7085834375695406E-2</v>
       </c>
       <c r="AG69" s="6">
-        <v>9.15899642185736E-2</v>
+        <v>0.101950466748445</v>
       </c>
       <c r="AH69" s="6">
-        <v>0.100597995487559</v>
+        <v>9.6431913573476497E-2</v>
       </c>
       <c r="AI69" s="6">
-        <v>7.6681052721305806E-2</v>
+        <v>8.4635688184685698E-2</v>
       </c>
       <c r="AJ69" s="6">
-        <v>3.9623435389081398E-2</v>
+        <v>4.2500088181447501E-2</v>
       </c>
       <c r="AK69" s="6">
-        <v>8.2020299151929696E-2</v>
+        <v>8.6841683309899803E-2</v>
       </c>
       <c r="AL69" s="6"/>
       <c r="AM69" s="6"/>
@@ -8684,22 +8684,22 @@
         <v>6.1921004856623441</v>
       </c>
       <c r="AF70" s="6">
-        <v>8.0037468527730193E-2</v>
+        <v>8.7980698260323106E-2</v>
       </c>
       <c r="AG70" s="6">
-        <v>9.0873229724152002E-2</v>
+        <v>0.10155511580184599</v>
       </c>
       <c r="AH70" s="6">
-        <v>9.9045920532848802E-2</v>
+        <v>9.6045565389183393E-2</v>
       </c>
       <c r="AI70" s="6">
-        <v>7.7646838871502102E-2</v>
+        <v>8.5225889433468205E-2</v>
       </c>
       <c r="AJ70" s="6">
-        <v>4.0364655643225902E-2</v>
+        <v>4.2886600118814899E-2</v>
       </c>
       <c r="AK70" s="6">
-        <v>8.1970973006200307E-2</v>
+        <v>8.6944691286286901E-2</v>
       </c>
       <c r="AL70" s="6"/>
       <c r="AM70" s="6"/>
@@ -8800,22 +8800,22 @@
         <v>6.8419991943043712</v>
       </c>
       <c r="AF71" s="6">
-        <v>8.2185167714632301E-2</v>
+        <v>8.9254396324067301E-2</v>
       </c>
       <c r="AG71" s="6">
-        <v>9.6172441708644099E-2</v>
+        <v>0.105361593797258</v>
       </c>
       <c r="AH71" s="6">
-        <v>0.10354776240253601</v>
+        <v>9.8731246509702802E-2</v>
       </c>
       <c r="AI71" s="6">
-        <v>7.7721702408539303E-2</v>
+        <v>8.5190723699878401E-2</v>
       </c>
       <c r="AJ71" s="6">
-        <v>4.0920418483859598E-2</v>
+        <v>4.3159636019392898E-2</v>
       </c>
       <c r="AK71" s="6">
-        <v>8.4809673388997905E-2</v>
+        <v>8.8790329269558793E-2</v>
       </c>
       <c r="AL71" s="6"/>
       <c r="AM71" s="6"/>
@@ -8916,22 +8916,22 @@
         <v>6.80453833061474</v>
       </c>
       <c r="AF72" s="6">
-        <v>8.3081875030159499E-2</v>
+        <v>8.96990623875734E-2</v>
       </c>
       <c r="AG72" s="6">
-        <v>9.5644889846420306E-2</v>
+        <v>0.105185306717848</v>
       </c>
       <c r="AH72" s="6">
-        <v>9.3398626124008705E-2</v>
+        <v>9.3598907547456298E-2</v>
       </c>
       <c r="AI72" s="6">
-        <v>7.9938059827294405E-2</v>
+        <v>8.7121618432897299E-2</v>
       </c>
       <c r="AJ72" s="6">
-        <v>4.2228843039238802E-2</v>
+        <v>4.3920231303471599E-2</v>
       </c>
       <c r="AK72" s="6">
-        <v>8.2851847613793606E-2</v>
+        <v>8.8013412873221397E-2</v>
       </c>
       <c r="AL72" s="6"/>
       <c r="AM72" s="6"/>
@@ -9032,22 +9032,22 @@
         <v>7.1162281247486803</v>
       </c>
       <c r="AF73" s="6">
-        <v>8.3852244821565197E-2</v>
+        <v>9.0080385364149904E-2</v>
       </c>
       <c r="AG73" s="6">
-        <v>9.5460692913654596E-2</v>
+        <v>0.105241627794086</v>
       </c>
       <c r="AH73" s="6">
-        <v>0.102785241007176</v>
+        <v>9.9013235962739199E-2</v>
       </c>
       <c r="AI73" s="6">
-        <v>8.5423382019742006E-2</v>
+        <v>9.0644589927426897E-2</v>
       </c>
       <c r="AJ73" s="6">
-        <v>4.3486262090260498E-2</v>
+        <v>4.4663945801796501E-2</v>
       </c>
       <c r="AK73" s="6">
-        <v>8.6806871889472906E-2</v>
+        <v>9.0380548501097793E-2</v>
       </c>
       <c r="AL73" s="6"/>
       <c r="AM73" s="6"/>
@@ -9148,22 +9148,22 @@
         <v>5.4275133110877505</v>
       </c>
       <c r="AF74" s="6">
-        <v>8.4386375432180499E-2</v>
+        <v>9.0315867696047797E-2</v>
       </c>
       <c r="AG74" s="6">
-        <v>9.3906374538434201E-2</v>
+        <v>0.10410270582268299</v>
       </c>
       <c r="AH74" s="6">
-        <v>9.8325499557933502E-2</v>
+        <v>9.6985389678754794E-2</v>
       </c>
       <c r="AI74" s="6">
-        <v>9.1977902015911994E-2</v>
+        <v>9.4738339788322204E-2</v>
       </c>
       <c r="AJ74" s="6">
-        <v>4.4832578521510999E-2</v>
+        <v>4.5460083628424103E-2</v>
       </c>
       <c r="AK74" s="6">
-        <v>8.6982391611477597E-2</v>
+        <v>9.0609150657976395E-2</v>
       </c>
       <c r="AL74" s="6"/>
       <c r="AM74" s="6"/>
@@ -9264,22 +9264,22 @@
         <v>8.6994845282365674</v>
       </c>
       <c r="AF75" s="6">
-        <v>9.8124898374347902E-2</v>
+        <v>9.8847235668932804E-2</v>
       </c>
       <c r="AG75" s="6">
-        <v>0.11094470794550999</v>
+        <v>0.115064156385549</v>
       </c>
       <c r="AH75" s="6">
-        <v>0.104872668240322</v>
+        <v>0.10207753708211501</v>
       </c>
       <c r="AI75" s="6">
-        <v>9.6984216000474896E-2</v>
+        <v>9.7592899907510994E-2</v>
       </c>
       <c r="AJ75" s="6">
-        <v>4.5904334556003297E-2</v>
+        <v>4.6083503024825501E-2</v>
       </c>
       <c r="AK75" s="6">
-        <v>9.5950552169375605E-2</v>
+        <v>9.6503623989006998E-2</v>
       </c>
       <c r="AL75" s="6"/>
       <c r="AM75" s="6"/>
@@ -9380,22 +9380,22 @@
         <v>7.3144456687566972</v>
       </c>
       <c r="AF76" s="6">
-        <v>9.8103604642983303E-2</v>
+        <v>9.8877778379797096E-2</v>
       </c>
       <c r="AG76" s="6">
-        <v>0.11082177878260401</v>
+        <v>0.11532277935945601</v>
       </c>
       <c r="AH76" s="6">
-        <v>0.10229990261562399</v>
+        <v>0.101265172932497</v>
       </c>
       <c r="AI76" s="6">
-        <v>8.8898398908652601E-2</v>
+        <v>9.2997894058828606E-2</v>
       </c>
       <c r="AJ76" s="6">
-        <v>4.4070796939145403E-2</v>
+        <v>4.5319209235904101E-2</v>
       </c>
       <c r="AK76" s="6">
-        <v>9.3179883180792594E-2</v>
+        <v>9.52388145596446E-2</v>
       </c>
       <c r="AL76" s="6"/>
       <c r="AM76" s="6"/>
@@ -9496,22 +9496,22 @@
         <v>8.2573379628323451</v>
       </c>
       <c r="AF77" s="6">
-        <v>9.8125003937868299E-2</v>
+        <v>9.8929572619698203E-2</v>
       </c>
       <c r="AG77" s="6">
-        <v>0.114604557680463</v>
+        <v>0.11787758466369599</v>
       </c>
       <c r="AH77" s="6">
-        <v>0.107904826237715</v>
+        <v>0.10480721085810001</v>
       </c>
       <c r="AI77" s="6">
-        <v>9.19243199400719E-2</v>
+        <v>9.4822207579183304E-2</v>
       </c>
       <c r="AJ77" s="6">
-        <v>4.4912531546828199E-2</v>
+        <v>4.5786342363457501E-2</v>
       </c>
       <c r="AK77" s="6">
-        <v>9.6383883706690293E-2</v>
+        <v>9.7286279691965405E-2</v>
       </c>
       <c r="AL77" s="6"/>
       <c r="AM77" s="6"/>
@@ -9612,22 +9612,22 @@
         <v>9.6678441455932074</v>
       </c>
       <c r="AF78" s="6">
-        <v>9.8417452113261902E-2</v>
+        <v>9.9134859551254798E-2</v>
       </c>
       <c r="AG78" s="6">
-        <v>0.11564636868533699</v>
+        <v>0.118834840897809</v>
       </c>
       <c r="AH78" s="6">
-        <v>0.106422769158592</v>
+        <v>0.104347454746678</v>
       </c>
       <c r="AI78" s="6">
-        <v>9.33286938442658E-2</v>
+        <v>9.5732028372278205E-2</v>
       </c>
       <c r="AJ78" s="6">
-        <v>4.5547243073732202E-2</v>
+        <v>4.6130823423493603E-2</v>
       </c>
       <c r="AK78" s="6">
-        <v>9.6712482870404695E-2</v>
+        <v>9.7682651121552194E-2</v>
       </c>
       <c r="AL78" s="6"/>
       <c r="AM78" s="6"/>
@@ -9728,22 +9728,22 @@
         <v>8.849735515448387</v>
       </c>
       <c r="AF79" s="6">
-        <v>9.8883270302594098E-2</v>
+        <v>9.9439008004649804E-2</v>
       </c>
       <c r="AG79" s="6">
-        <v>0.11758622479601399</v>
+        <v>0.120308029380037</v>
       </c>
       <c r="AH79" s="6">
-        <v>0.10738984643157699</v>
+        <v>0.105171240714361</v>
       </c>
       <c r="AI79" s="6">
-        <v>9.4820921676412706E-2</v>
+        <v>9.6681053826832702E-2</v>
       </c>
       <c r="AJ79" s="6">
-        <v>4.6047441342669498E-2</v>
+        <v>4.6399989445747303E-2</v>
       </c>
       <c r="AK79" s="6">
-        <v>9.79175689853444E-2</v>
+        <v>9.8554572379021405E-2</v>
       </c>
       <c r="AL79" s="6"/>
       <c r="AM79" s="6"/>
@@ -9844,22 +9844,22 @@
         <v>8.8077985717156082</v>
       </c>
       <c r="AF80" s="6">
-        <v>0.10081999345254999</v>
+        <v>0.10057939435796499</v>
       </c>
       <c r="AG80" s="6">
-        <v>0.117609487107856</v>
+        <v>0.12009031990982801</v>
       </c>
       <c r="AH80" s="6">
-        <v>9.1534868004015099E-2</v>
+        <v>9.6158190828242396E-2</v>
       </c>
       <c r="AI80" s="6">
-        <v>8.9166448014562194E-2</v>
+        <v>9.3557444204950005E-2</v>
       </c>
       <c r="AJ80" s="6">
-        <v>4.5608002293606599E-2</v>
+        <v>4.6113864402879297E-2</v>
       </c>
       <c r="AK80" s="6">
-        <v>9.2655186253603597E-2</v>
+        <v>9.5514206785739797E-2</v>
       </c>
       <c r="AL80" s="6"/>
       <c r="AM80" s="6"/>
@@ -9960,22 +9960,22 @@
         <v>9.6280034963541539</v>
       </c>
       <c r="AF81" s="6">
-        <v>0.10302168125995601</v>
+        <v>0.101862579366754</v>
       </c>
       <c r="AG81" s="6">
-        <v>0.12920206234710199</v>
+        <v>0.12705405576859199</v>
       </c>
       <c r="AH81" s="6">
-        <v>9.5182102478407901E-2</v>
+        <v>9.9045080246676798E-2</v>
       </c>
       <c r="AI81" s="6">
-        <v>8.14983448694096E-2</v>
+        <v>8.8798107997807199E-2</v>
       </c>
       <c r="AJ81" s="6">
-        <v>4.5026913458648898E-2</v>
+        <v>4.5736858928706402E-2</v>
       </c>
       <c r="AK81" s="6">
-        <v>9.4989258325475098E-2</v>
+        <v>9.7074550889389696E-2</v>
       </c>
       <c r="AL81" s="6"/>
       <c r="AM81" s="6"/>
@@ -10076,22 +10076,22 @@
         <v>8.7775342189468475</v>
       </c>
       <c r="AF82" s="6">
-        <v>0.104338543395277</v>
+        <v>0.102648513933222</v>
       </c>
       <c r="AG82" s="6">
-        <v>0.13703272507019701</v>
+        <v>0.13168879299590699</v>
       </c>
       <c r="AH82" s="6">
-        <v>0.10885545606531299</v>
+        <v>0.10743734111181499</v>
       </c>
       <c r="AI82" s="6">
-        <v>8.2092135940363506E-2</v>
+        <v>8.8987842520897004E-2</v>
       </c>
       <c r="AJ82" s="6">
-        <v>4.4922664864750397E-2</v>
+        <v>4.5643872153373399E-2</v>
       </c>
       <c r="AK82" s="6">
-        <v>0.100766976332366</v>
+        <v>0.100557915737801</v>
       </c>
       <c r="AL82" s="6"/>
       <c r="AM82" s="6"/>
@@ -10192,22 +10192,22 @@
         <v>7.488359046499049</v>
       </c>
       <c r="AF83" s="6">
-        <v>0.103322806425535</v>
+        <v>0.102172950522931</v>
       </c>
       <c r="AG83" s="6">
-        <v>0.12782204467804101</v>
+        <v>0.127337967551233</v>
       </c>
       <c r="AH83" s="6">
-        <v>0.105875130254447</v>
+        <v>0.105946382907067</v>
       </c>
       <c r="AI83" s="6">
-        <v>8.2555349033517494E-2</v>
+        <v>8.9236736243217402E-2</v>
       </c>
       <c r="AJ83" s="6">
-        <v>4.5265319453048201E-2</v>
+        <v>4.58194275790339E-2</v>
       </c>
       <c r="AK83" s="6">
-        <v>9.7744943420105104E-2</v>
+        <v>9.9112484775945295E-2</v>
       </c>
       <c r="AL83" s="6"/>
       <c r="AM83" s="6"/>
@@ -10308,22 +10308,22 @@
         <v>7.2995139134214071</v>
       </c>
       <c r="AF84" s="6">
-        <v>8.9935764570608201E-2</v>
+        <v>9.4632630633485496E-2</v>
       </c>
       <c r="AG84" s="6">
-        <v>0.10391127212165301</v>
+        <v>0.113896735636371</v>
       </c>
       <c r="AH84" s="6">
-        <v>9.7652289470705603E-2</v>
+        <v>0.101198264981083</v>
       </c>
       <c r="AI84" s="6">
-        <v>8.0432798338244599E-2</v>
+        <v>8.7853801170571802E-2</v>
       </c>
       <c r="AJ84" s="6">
-        <v>4.5166557441717603E-2</v>
+        <v>4.5730242883095802E-2</v>
       </c>
       <c r="AK84" s="6">
-        <v>8.7420773815487393E-2</v>
+        <v>9.3231782060163207E-2</v>
       </c>
       <c r="AL84" s="6"/>
       <c r="AM84" s="6"/>
@@ -10424,22 +10424,22 @@
         <v>7.0523039444982061</v>
       </c>
       <c r="AF85" s="6">
-        <v>9.11083290654853E-2</v>
+        <v>9.5362862701930007E-2</v>
       </c>
       <c r="AG85" s="6">
-        <v>9.7179874996301402E-2</v>
+        <v>0.10983107340940999</v>
       </c>
       <c r="AH85" s="6">
-        <v>9.2313486881872603E-2</v>
+        <v>9.7667471801258204E-2</v>
       </c>
       <c r="AI85" s="6">
-        <v>7.9547509657564394E-2</v>
+        <v>8.7233557680319596E-2</v>
       </c>
       <c r="AJ85" s="6">
-        <v>4.52422123295321E-2</v>
+        <v>4.5749284895375997E-2</v>
       </c>
       <c r="AK85" s="6">
-        <v>8.4306252223415201E-2</v>
+        <v>9.1251784301411301E-2</v>
       </c>
       <c r="AL85" s="6"/>
       <c r="AM85" s="6"/>
@@ -10540,22 +10540,22 @@
         <v>5.8123443623754767</v>
       </c>
       <c r="AF86" s="6">
-        <v>9.3600534151035697E-2</v>
+        <v>9.6832420531868704E-2</v>
       </c>
       <c r="AG86" s="6">
-        <v>9.4785331461107306E-2</v>
+        <v>0.108044558884394</v>
       </c>
       <c r="AH86" s="6">
-        <v>8.0201614203194105E-2</v>
+        <v>8.9255475517394003E-2</v>
       </c>
       <c r="AI86" s="6">
-        <v>7.5759949877864094E-2</v>
+        <v>8.4711980062414399E-2</v>
       </c>
       <c r="AJ86" s="6">
-        <v>4.4776582311054698E-2</v>
+        <v>4.5441174969572798E-2</v>
       </c>
       <c r="AK86" s="6">
-        <v>7.9880013745530498E-2</v>
+        <v>8.81682922197351E-2</v>
       </c>
       <c r="AL86" s="6"/>
       <c r="AM86" s="6"/>
@@ -10656,22 +10656,22 @@
         <v>5.3743758578301382</v>
       </c>
       <c r="AF87" s="6">
-        <v>9.1662481663782602E-2</v>
+        <v>9.58396211414837E-2</v>
       </c>
       <c r="AG87" s="6">
-        <v>6.0488129556216803E-2</v>
+        <v>8.7065325459292603E-2</v>
       </c>
       <c r="AH87" s="6">
-        <v>6.42480242532497E-2</v>
+        <v>7.9121286071637806E-2</v>
       </c>
       <c r="AI87" s="6">
-        <v>6.9921612999102906E-2</v>
+        <v>8.0527864315348696E-2</v>
       </c>
       <c r="AJ87" s="6">
-        <v>4.3716906418195103E-2</v>
+        <v>4.4760900255041598E-2</v>
       </c>
       <c r="AK87" s="6">
-        <v>6.5197437141053999E-2</v>
+        <v>7.8982656880527399E-2</v>
       </c>
       <c r="AL87" s="6"/>
       <c r="AM87" s="6"/>
@@ -10772,22 +10772,22 @@
         <v>6.3613838647389898</v>
       </c>
       <c r="AF88" s="6">
-        <v>9.5107461877745894E-2</v>
+        <v>9.8141457934701498E-2</v>
       </c>
       <c r="AG88" s="6">
-        <v>6.3568253073951697E-2</v>
+        <v>8.8778673466034602E-2</v>
       </c>
       <c r="AH88" s="6">
-        <v>5.5822972936641603E-2</v>
+        <v>6.9581223543345005E-2</v>
       </c>
       <c r="AI88" s="6">
-        <v>6.4585510711510905E-2</v>
+        <v>7.6226331538302994E-2</v>
       </c>
       <c r="AJ88" s="6">
-        <v>4.2746086518599402E-2</v>
+        <v>4.4112273201946398E-2</v>
       </c>
       <c r="AK88" s="6">
-        <v>6.2867888061270902E-2</v>
+        <v>7.6194133422060897E-2</v>
       </c>
       <c r="AL88" s="6"/>
       <c r="AM88" s="6"/>
@@ -10888,22 +10888,22 @@
         <v>5.5319298994474408</v>
       </c>
       <c r="AF89" s="6">
-        <v>9.90272137009829E-2</v>
+        <v>0.100507425852754</v>
       </c>
       <c r="AG89" s="6">
-        <v>7.4408168253503701E-2</v>
+        <v>9.8244355394532801E-2</v>
       </c>
       <c r="AH89" s="6">
-        <v>7.2018643609229702E-2</v>
+        <v>8.2845487520725805E-2</v>
       </c>
       <c r="AI89" s="6">
-        <v>6.7723727608526699E-2</v>
+        <v>7.8510153981254396E-2</v>
       </c>
       <c r="AJ89" s="6">
-        <v>4.1652703783417698E-2</v>
+        <v>4.3362364319840099E-2</v>
       </c>
       <c r="AK89" s="6">
-        <v>7.0881201286824999E-2</v>
+        <v>8.2706420227886601E-2</v>
       </c>
       <c r="AL89" s="6"/>
       <c r="AM89" s="6"/>
@@ -11004,22 +11004,22 @@
         <v>5.2191136537501848</v>
       </c>
       <c r="AF90" s="6">
-        <v>0.103333033028391</v>
+        <v>0.103948857747307</v>
       </c>
       <c r="AG90" s="6">
-        <v>8.2168697859106896E-2</v>
+        <v>0.102370891090593</v>
       </c>
       <c r="AH90" s="6">
-        <v>5.1645776467532198E-2</v>
+        <v>7.0672879655206106E-2</v>
       </c>
       <c r="AI90" s="6">
-        <v>6.1167410074762701E-2</v>
+        <v>7.3486151008486406E-2</v>
       </c>
       <c r="AJ90" s="6">
-        <v>4.0546583290156001E-2</v>
+        <v>4.25855591573637E-2</v>
       </c>
       <c r="AK90" s="6">
-        <v>6.6451661086842001E-2</v>
+        <v>7.9574396135269301E-2</v>
       </c>
       <c r="AL90" s="6"/>
       <c r="AM90" s="6"/>
@@ -11120,22 +11120,22 @@
         <v>3.0484792080605061</v>
       </c>
       <c r="AF91" s="6">
-        <v>0.10754620508165</v>
+        <v>0.10671716202326301</v>
       </c>
       <c r="AG91" s="6">
-        <v>9.5143114696243106E-2</v>
+        <v>0.110733606397678</v>
       </c>
       <c r="AH91" s="6">
-        <v>4.8016445553726798E-2</v>
+        <v>6.6891229143598394E-2</v>
       </c>
       <c r="AI91" s="6">
-        <v>5.6776996632181803E-2</v>
+        <v>6.9503209936777097E-2</v>
       </c>
       <c r="AJ91" s="6">
-        <v>3.9748636774405897E-2</v>
+        <v>4.19891108888251E-2</v>
       </c>
       <c r="AK91" s="6">
-        <v>6.79678246868161E-2</v>
+        <v>7.9940257432288803E-2</v>
       </c>
       <c r="AL91" s="6"/>
       <c r="AM91" s="6"/>
@@ -11236,22 +11236,22 @@
         <v>6.0338629875230865</v>
       </c>
       <c r="AF92" s="6">
-        <v>7.0028667951498993E-2</v>
+        <v>8.8141376698424603E-2</v>
       </c>
       <c r="AG92" s="6">
-        <v>7.4308176720658495E-2</v>
+        <v>8.0470079205420902E-2</v>
       </c>
       <c r="AH92" s="6">
-        <v>4.4542168485583303E-2</v>
+        <v>6.1827277332298203E-2</v>
       </c>
       <c r="AI92" s="6">
-        <v>5.4722949189534097E-2</v>
+        <v>6.7339401472623905E-2</v>
       </c>
       <c r="AJ92" s="6">
-        <v>3.9401875879817999E-2</v>
+        <v>4.1683350503686101E-2</v>
       </c>
       <c r="AK92" s="6">
-        <v>5.6874941189594401E-2</v>
+        <v>6.8473378757091197E-2</v>
       </c>
       <c r="AL92" s="6"/>
       <c r="AM92" s="6"/>
@@ -11352,22 +11352,22 @@
         <v>3.1878591219401287</v>
       </c>
       <c r="AF93" s="6">
-        <v>7.3311867940596701E-2</v>
+        <v>9.0135545034491005E-2</v>
       </c>
       <c r="AG93" s="6">
-        <v>8.3715309578136901E-2</v>
+        <v>8.69598334097893E-2</v>
       </c>
       <c r="AH93" s="6">
-        <v>5.2229552415251498E-2</v>
+        <v>6.8684790183952599E-2</v>
       </c>
       <c r="AI93" s="6">
-        <v>7.4790671905874698E-2</v>
+        <v>8.2226997758740303E-2</v>
       </c>
       <c r="AJ93" s="6">
-        <v>4.3565515813409103E-2</v>
+        <v>4.3821282121991802E-2</v>
       </c>
       <c r="AK93" s="6">
-        <v>6.7037490730242094E-2</v>
+        <v>7.5908034059999199E-2</v>
       </c>
       <c r="AL93" s="6"/>
       <c r="AM93" s="6"/>
@@ -11468,22 +11468,22 @@
         <v>4.0190825761813542</v>
       </c>
       <c r="AF94" s="6">
-        <v>6.9498853686997694E-2</v>
+        <v>8.6705178995204399E-2</v>
       </c>
       <c r="AG94" s="6">
-        <v>6.8327168841932295E-2</v>
+        <v>8.3113814676378406E-2</v>
       </c>
       <c r="AH94" s="6">
-        <v>4.9249503994851403E-2</v>
+        <v>6.6898045563601793E-2</v>
       </c>
       <c r="AI94" s="6">
-        <v>7.0297695316086095E-2</v>
+        <v>8.0493324986409903E-2</v>
       </c>
       <c r="AJ94" s="6">
-        <v>4.2724197077312599E-2</v>
+        <v>4.37210809599239E-2</v>
       </c>
       <c r="AK94" s="6">
-        <v>6.0718626333697803E-2</v>
+        <v>7.3666214667949995E-2</v>
       </c>
       <c r="AL94" s="6"/>
       <c r="AM94" s="6"/>
@@ -11584,22 +11584,22 @@
         <v>4.6556072566202644</v>
       </c>
       <c r="AF95" s="6">
-        <v>7.0130335400914096E-2</v>
+        <v>8.8323119594483093E-2</v>
       </c>
       <c r="AG95" s="6">
-        <v>6.9157721465965896E-2</v>
+        <v>8.6805726846080303E-2</v>
       </c>
       <c r="AH95" s="6">
-        <v>4.7319813859195502E-2</v>
+        <v>6.7193340715272803E-2</v>
       </c>
       <c r="AI95" s="6">
-        <v>6.7787828143964293E-2</v>
+        <v>8.0102565688840902E-2</v>
       </c>
       <c r="AJ95" s="6">
-        <v>4.2223730091810699E-2</v>
+        <v>4.3821546337725399E-2</v>
       </c>
       <c r="AK95" s="6">
-        <v>5.9812566044449497E-2</v>
+        <v>7.4736157142380494E-2</v>
       </c>
       <c r="AL95" s="6"/>
       <c r="AM95" s="6"/>
@@ -11700,22 +11700,22 @@
         <v>3.7376722023809705</v>
       </c>
       <c r="AF96" s="6">
-        <v>7.0424791965491895E-2</v>
+        <v>8.9553708660345704E-2</v>
       </c>
       <c r="AG96" s="6">
-        <v>6.9945825299063694E-2</v>
+        <v>9.0460077842986E-2</v>
       </c>
       <c r="AH96" s="6">
-        <v>4.8246147392736201E-2</v>
+        <v>7.0690700669952797E-2</v>
       </c>
       <c r="AI96" s="6">
-        <v>6.6750305190518E-2</v>
+        <v>8.0780426640943606E-2</v>
       </c>
       <c r="AJ96" s="6">
-        <v>4.19690830674554E-2</v>
+        <v>4.40661706976547E-2</v>
       </c>
       <c r="AK96" s="6">
-        <v>6.0004637705295502E-2</v>
+        <v>7.6892555978254395E-2</v>
       </c>
       <c r="AL96" s="6"/>
       <c r="AM96" s="6"/>
@@ -11816,22 +11816,22 @@
         <v>2.8366089322613419</v>
       </c>
       <c r="AF97" s="6">
-        <v>7.0780260296220004E-2</v>
+        <v>9.0622411713207604E-2</v>
       </c>
       <c r="AG97" s="6">
-        <v>6.87896861804011E-2</v>
+        <v>9.2554915735543405E-2</v>
       </c>
       <c r="AH97" s="6">
-        <v>4.7172014504573201E-2</v>
+        <v>7.1721157580524497E-2</v>
       </c>
       <c r="AI97" s="6">
-        <v>6.5693813213504301E-2</v>
+        <v>8.1384379454640998E-2</v>
       </c>
       <c r="AJ97" s="6">
-        <v>4.1748200597436898E-2</v>
+        <v>4.4314178104895401E-2</v>
       </c>
       <c r="AK97" s="6">
-        <v>5.9221339417400799E-2</v>
+        <v>7.8007432533915302E-2</v>
       </c>
       <c r="AL97" s="6"/>
       <c r="AM97" s="6"/>
@@ -11932,22 +11932,22 @@
         <v>5.4192606388028253</v>
       </c>
       <c r="AF98" s="6">
-        <v>7.08699901733022E-2</v>
+        <v>9.1610146134191495E-2</v>
       </c>
       <c r="AG98" s="6">
-        <v>6.6992128974012202E-2</v>
+        <v>9.3073039542104899E-2</v>
       </c>
       <c r="AH98" s="6">
-        <v>4.6103721974959197E-2</v>
+        <v>7.2611524433631003E-2</v>
       </c>
       <c r="AI98" s="6">
-        <v>6.4625375844601998E-2</v>
+        <v>8.1902876577503905E-2</v>
       </c>
       <c r="AJ98" s="6">
-        <v>4.15205112000075E-2</v>
+        <v>4.4538667298732099E-2</v>
       </c>
       <c r="AK98" s="6">
-        <v>5.8257592814059601E-2</v>
+        <v>7.86295113080515E-2</v>
       </c>
       <c r="AL98" s="6"/>
       <c r="AM98" s="6"/>
@@ -12048,22 +12048,22 @@
         <v>3.4538467046139942</v>
       </c>
       <c r="AF99" s="6">
-        <v>7.1113508556572294E-2</v>
+        <v>9.2547173267053598E-2</v>
       </c>
       <c r="AG99" s="6">
-        <v>6.7588691817704799E-2</v>
+        <v>9.66176033051694E-2</v>
       </c>
       <c r="AH99" s="6">
-        <v>4.6817936067358901E-2</v>
+        <v>7.5981031039899796E-2</v>
       </c>
       <c r="AI99" s="6">
-        <v>6.8358198615446994E-2</v>
+        <v>8.6644536622813198E-2</v>
       </c>
       <c r="AJ99" s="6">
-        <v>4.2755331570770098E-2</v>
+        <v>4.5773846965017698E-2</v>
       </c>
       <c r="AK99" s="6">
-        <v>5.96649873694386E-2</v>
+        <v>8.1852005066107805E-2</v>
       </c>
       <c r="AL99" s="6"/>
       <c r="AM99" s="6"/>
@@ -12164,22 +12164,22 @@
         <v>4.0870884533042329</v>
       </c>
       <c r="AF100" s="6">
-        <v>7.14236305769161E-2</v>
+        <v>9.3425788068286705E-2</v>
       </c>
       <c r="AG100" s="6">
-        <v>6.6792607698799897E-2</v>
+        <v>9.8585609449751005E-2</v>
       </c>
       <c r="AH100" s="6">
-        <v>4.5907976419538303E-2</v>
+        <v>7.6759368179163998E-2</v>
       </c>
       <c r="AI100" s="6">
-        <v>6.7370968156455893E-2</v>
+        <v>8.6909987356744697E-2</v>
       </c>
       <c r="AJ100" s="6">
-        <v>4.2549535399741899E-2</v>
+        <v>4.5920118138338198E-2</v>
       </c>
       <c r="AK100" s="6">
-        <v>5.9022566075068998E-2</v>
+        <v>8.2753279461731194E-2</v>
       </c>
       <c r="AL100" s="6"/>
       <c r="AM100" s="6"/>
@@ -12280,22 +12280,22 @@
         <v>2.8586727804182033</v>
       </c>
       <c r="AF101" s="6">
-        <v>7.14521802861776E-2</v>
+        <v>9.4098275168590401E-2</v>
       </c>
       <c r="AG101" s="6">
-        <v>6.6860866928663706E-2</v>
+        <v>0.10112031794090599</v>
       </c>
       <c r="AH101" s="6">
-        <v>4.59092190218802E-2</v>
+        <v>7.88784897145203E-2</v>
       </c>
       <c r="AI101" s="6">
-        <v>6.7256375653345302E-2</v>
+        <v>8.7964595566035503E-2</v>
       </c>
       <c r="AJ101" s="6">
-        <v>4.2525341211356198E-2</v>
+        <v>4.6183844895223501E-2</v>
       </c>
       <c r="AK101" s="6">
-        <v>5.9012007938840698E-2</v>
+        <v>8.4299713813013794E-2</v>
       </c>
       <c r="AL101" s="6"/>
       <c r="AM101" s="6"/>
@@ -12396,22 +12396,22 @@
         <v>4.2956031456759192</v>
       </c>
       <c r="AF102" s="6">
-        <v>7.15148488414898E-2</v>
+        <v>9.4757868590386596E-2</v>
       </c>
       <c r="AG102" s="6">
-        <v>6.6564066346781997E-2</v>
+        <v>0.10306833436761099</v>
       </c>
       <c r="AH102" s="6">
-        <v>4.5682667296230398E-2</v>
+        <v>8.0509400873956305E-2</v>
       </c>
       <c r="AI102" s="6">
-        <v>6.7008508883463394E-2</v>
+        <v>8.8824535537784299E-2</v>
       </c>
       <c r="AJ102" s="6">
-        <v>4.2472881270412502E-2</v>
+        <v>4.6410112717334903E-2</v>
       </c>
       <c r="AK102" s="6">
-        <v>5.8827447980708797E-2</v>
+        <v>8.5513786373521694E-2</v>
       </c>
       <c r="AL102" s="6"/>
       <c r="AM102" s="6"/>
@@ -12512,22 +12512,22 @@
         <v>2.7332359184002897</v>
       </c>
       <c r="AF103" s="6">
-        <v>7.15471379155658E-2</v>
+        <v>9.5354269981983097E-2</v>
       </c>
       <c r="AG103" s="6">
-        <v>6.6640528783641198E-2</v>
+        <v>0.10540283750195099</v>
       </c>
       <c r="AH103" s="6">
-        <v>4.58040418579818E-2</v>
+        <v>8.2660499904805201E-2</v>
       </c>
       <c r="AI103" s="6">
-        <v>6.7245133566832302E-2</v>
+        <v>9.0125711636182507E-2</v>
       </c>
       <c r="AJ103" s="6">
-        <v>4.2450692063256697E-2</v>
+        <v>4.6644045634969399E-2</v>
       </c>
       <c r="AK103" s="6">
-        <v>5.8934304206244299E-2</v>
+        <v>8.7051547454181699E-2</v>
       </c>
       <c r="AL103" s="6"/>
       <c r="AM103" s="6"/>
@@ -12628,22 +12628,22 @@
         <v>2.7377874355572374</v>
       </c>
       <c r="AF104" s="6">
-        <v>7.1660836802048794E-2</v>
+        <v>9.5993562409841401E-2</v>
       </c>
       <c r="AG104" s="6">
-        <v>6.5807463538865296E-2</v>
+        <v>0.106286869936026</v>
       </c>
       <c r="AH104" s="6">
-        <v>4.5253713470661303E-2</v>
+        <v>8.3477119907974795E-2</v>
       </c>
       <c r="AI104" s="6">
-        <v>6.6636800447773495E-2</v>
+        <v>9.0473611101030305E-2</v>
       </c>
       <c r="AJ104" s="6">
-        <v>4.2322036035532702E-2</v>
+        <v>4.6783225804740203E-2</v>
       </c>
       <c r="AK104" s="6">
-        <v>5.8454236279262203E-2</v>
+        <v>8.7659265036643105E-2</v>
       </c>
       <c r="AL104" s="6"/>
       <c r="AM104" s="6"/>
@@ -12744,22 +12744,22 @@
         <v>3.2439968311216205</v>
       </c>
       <c r="AF105" s="6">
-        <v>7.1786517854542098E-2</v>
+        <v>9.6584557557951603E-2</v>
       </c>
       <c r="AG105" s="6">
-        <v>6.5922367407791102E-2</v>
+        <v>0.10861777215257799</v>
       </c>
       <c r="AH105" s="6">
-        <v>4.4907206191830903E-2</v>
+        <v>8.4581139900718694E-2</v>
       </c>
       <c r="AI105" s="6">
-        <v>6.6203070809171899E-2</v>
+        <v>9.0969910764079301E-2</v>
       </c>
       <c r="AJ105" s="6">
-        <v>4.2229404903699599E-2</v>
+        <v>4.69391826643498E-2</v>
       </c>
       <c r="AK105" s="6">
-        <v>5.8288634020700503E-2</v>
+        <v>8.8728456277148995E-2</v>
       </c>
       <c r="AL105" s="6"/>
       <c r="AM105" s="6"/>
@@ -12860,22 +12860,22 @@
         <v>2.5252849464417082</v>
       </c>
       <c r="AF106" s="6">
-        <v>7.19885283141313E-2</v>
+        <v>9.7222850072065201E-2</v>
       </c>
       <c r="AG106" s="6">
-        <v>6.6388432437756398E-2</v>
+        <v>0.111409257588049</v>
       </c>
       <c r="AH106" s="6">
-        <v>4.4938722274666297E-2</v>
+        <v>8.6370167286834706E-2</v>
       </c>
       <c r="AI106" s="6">
-        <v>6.5433459968238697E-2</v>
+        <v>9.1058687910222993E-2</v>
       </c>
       <c r="AJ106" s="6">
-        <v>4.2063505663733201E-2</v>
+        <v>4.7028312303472902E-2</v>
       </c>
       <c r="AK106" s="6">
-        <v>5.8226248018683598E-2</v>
+        <v>8.9981801923681798E-2</v>
       </c>
       <c r="AL106" s="6"/>
       <c r="AM106" s="6"/>
@@ -12976,22 +12976,22 @@
         <v>3.8647886914272789</v>
       </c>
       <c r="AF107" s="6">
-        <v>7.2247446315293604E-2</v>
+        <v>9.7842794436428807E-2</v>
       </c>
       <c r="AG107" s="6">
-        <v>6.6561925025917706E-2</v>
+        <v>0.11372645876003799</v>
       </c>
       <c r="AH107" s="6">
-        <v>4.4236294294938E-2</v>
+        <v>8.6493231819344901E-2</v>
       </c>
       <c r="AI107" s="6">
-        <v>6.4602188524105403E-2</v>
+        <v>9.10507248093715E-2</v>
       </c>
       <c r="AJ107" s="6">
-        <v>4.1882099196979203E-2</v>
+        <v>4.7097950815527603E-2</v>
       </c>
       <c r="AK107" s="6">
-        <v>5.7889175451300401E-2</v>
+        <v>9.0669465626815701E-2</v>
       </c>
       <c r="AL107" s="6"/>
       <c r="AM107" s="6"/>
@@ -13092,22 +13092,22 @@
         <v>3.5671314143314703</v>
       </c>
       <c r="AF108" s="6">
-        <v>7.2381586749370203E-2</v>
+        <v>9.8337569901634295E-2</v>
       </c>
       <c r="AG108" s="6">
-        <v>6.6871660832459698E-2</v>
+        <v>0.11599129057596499</v>
       </c>
       <c r="AH108" s="6">
-        <v>4.4680848828038203E-2</v>
+        <v>8.9056938630120097E-2</v>
       </c>
       <c r="AI108" s="6">
-        <v>6.58110153430327E-2</v>
+        <v>9.3475641786639502E-2</v>
       </c>
       <c r="AJ108" s="6">
-        <v>4.1833449240317497E-2</v>
+        <v>4.7288857689695103E-2</v>
       </c>
       <c r="AK108" s="6">
-        <v>5.8374462151095603E-2</v>
+        <v>9.2537524157435505E-2</v>
       </c>
       <c r="AL108" s="6"/>
       <c r="AM108" s="6"/>
@@ -13208,22 +13208,22 @@
         <v>4.0448186525978258</v>
       </c>
       <c r="AF109" s="6">
-        <v>7.2487714744110296E-2</v>
+        <v>9.8773603523747103E-2</v>
       </c>
       <c r="AG109" s="6">
-        <v>6.7114895621145795E-2</v>
+        <v>0.11801142028601599</v>
       </c>
       <c r="AH109" s="6">
-        <v>4.45985890027739E-2</v>
+        <v>9.0365607876437506E-2</v>
       </c>
       <c r="AI109" s="6">
-        <v>6.5418731995360496E-2</v>
+        <v>9.3794658461155506E-2</v>
       </c>
       <c r="AJ109" s="6">
-        <v>4.1749595487264597E-2</v>
+        <v>4.7415191464896603E-2</v>
       </c>
       <c r="AK109" s="6">
-        <v>5.8317491079717801E-2</v>
+        <v>9.3511685916019799E-2</v>
       </c>
       <c r="AL109" s="6"/>
       <c r="AM109" s="6"/>
@@ -13324,22 +13324,22 @@
         <v>3.8412195539606842</v>
       </c>
       <c r="AF110" s="6">
-        <v>7.2285276445469004E-2</v>
+        <v>9.8883274649578703E-2</v>
       </c>
       <c r="AG110" s="6">
-        <v>6.6644619163820307E-2</v>
+        <v>0.11843273653810001</v>
       </c>
       <c r="AH110" s="6">
-        <v>4.4016471738675803E-2</v>
+        <v>9.0512201752289898E-2</v>
       </c>
       <c r="AI110" s="6">
-        <v>6.5978423463510197E-2</v>
+        <v>9.5162654323248899E-2</v>
       </c>
       <c r="AJ110" s="6">
-        <v>4.1909512947840101E-2</v>
+        <v>4.7727295235969899E-2</v>
       </c>
       <c r="AK110" s="6">
-        <v>5.8177841981398103E-2</v>
+        <v>9.4036302855612902E-2</v>
       </c>
       <c r="AL110" s="6"/>
       <c r="AM110" s="6"/>
@@ -13440,22 +13440,22 @@
         <v>4.8187959313533923</v>
       </c>
       <c r="AF111" s="6">
-        <v>7.2161800207029905E-2</v>
+        <v>9.9062678677093105E-2</v>
       </c>
       <c r="AG111" s="6">
-        <v>6.6377898614258302E-2</v>
+        <v>0.119242879740668</v>
       </c>
       <c r="AH111" s="6">
-        <v>4.41837344162418E-2</v>
+        <v>9.2461062615128001E-2</v>
       </c>
       <c r="AI111" s="6">
-        <v>6.6436615802188501E-2</v>
+        <v>9.6383433797004495E-2</v>
       </c>
       <c r="AJ111" s="6">
-        <v>4.2007093730311203E-2</v>
+        <v>4.7969514699482997E-2</v>
       </c>
       <c r="AK111" s="6">
-        <v>5.8267700200909503E-2</v>
+        <v>9.5073041786528201E-2</v>
       </c>
       <c r="AL111" s="6"/>
       <c r="AM111" s="6"/>
@@ -13556,22 +13556,22 @@
         <v>4.5807185628746083</v>
       </c>
       <c r="AF112" s="6">
-        <v>7.1857102491707694E-2</v>
+        <v>9.9049142006893603E-2</v>
       </c>
       <c r="AG112" s="6">
-        <v>6.5679624701302897E-2</v>
+        <v>0.11905217390751199</v>
       </c>
       <c r="AH112" s="6">
-        <v>4.3202819048343603E-2</v>
+        <v>9.1480014770034604E-2</v>
       </c>
       <c r="AI112" s="6">
-        <v>6.3376879921556703E-2</v>
+        <v>9.32529026459194E-2</v>
       </c>
       <c r="AJ112" s="6">
-        <v>4.2068950757456598E-2</v>
+        <v>4.8147961597143997E-2</v>
       </c>
       <c r="AK112" s="6">
-        <v>5.7094099577791602E-2</v>
+        <v>9.4059812589570205E-2</v>
       </c>
       <c r="AL112" s="6"/>
       <c r="AM112" s="6"/>
@@ -13672,22 +13672,22 @@
         <v>4.4441879453643196</v>
       </c>
       <c r="AF113" s="6">
-        <v>7.1604390195057405E-2</v>
+        <v>9.9085676551713103E-2</v>
       </c>
       <c r="AG113" s="6">
-        <v>6.5108849501741201E-2</v>
+        <v>0.119127290195489</v>
       </c>
       <c r="AH113" s="6">
-        <v>4.3237685449931902E-2</v>
+        <v>9.3143294352637102E-2</v>
       </c>
       <c r="AI113" s="6">
-        <v>6.4273263149599802E-2</v>
+        <v>9.5163700153238495E-2</v>
       </c>
       <c r="AJ113" s="6">
-        <v>4.2274025143698199E-2</v>
+        <v>4.8450581109468503E-2</v>
       </c>
       <c r="AK113" s="6">
-        <v>5.7180165447128999E-2</v>
+        <v>9.4999593188713399E-2</v>
       </c>
       <c r="AL113" s="6"/>
       <c r="AM113" s="6"/>
@@ -13788,22 +13788,22 @@
         <v>4.341842394944706</v>
       </c>
       <c r="AF114" s="6">
-        <v>7.1157566064949496E-2</v>
+        <v>9.8926928159012995E-2</v>
       </c>
       <c r="AG114" s="6">
-        <v>6.4148365581159703E-2</v>
+        <v>0.118296945585075</v>
       </c>
       <c r="AH114" s="6">
-        <v>4.3750513928725497E-2</v>
+        <v>9.6196498964181101E-2</v>
       </c>
       <c r="AI114" s="6">
-        <v>6.5912786287581807E-2</v>
+        <v>9.7907059255055107E-2</v>
       </c>
       <c r="AJ114" s="6">
-        <v>4.2642390222655799E-2</v>
+        <v>4.8866560537872299E-2</v>
       </c>
       <c r="AK114" s="6">
-        <v>5.7464804724988001E-2</v>
+        <v>9.6252029360128805E-2</v>
       </c>
       <c r="AL114" s="6"/>
       <c r="AM114" s="6"/>
@@ -13904,22 +13904,22 @@
         <v>3.6225124394089647</v>
       </c>
       <c r="AF115" s="6">
-        <v>7.0682965599445702E-2</v>
+        <v>9.8687349433953894E-2</v>
       </c>
       <c r="AG115" s="6">
-        <v>6.2868174010379904E-2</v>
+        <v>0.117254733385873</v>
       </c>
       <c r="AH115" s="6">
-        <v>4.4809931872466902E-2</v>
+        <v>0.100507405713417</v>
       </c>
       <c r="AI115" s="6">
-        <v>6.8007425264372895E-2</v>
+        <v>0.101063895312703</v>
       </c>
       <c r="AJ115" s="6">
-        <v>4.3099589589263E-2</v>
+        <v>4.93266499918932E-2</v>
       </c>
       <c r="AK115" s="6">
-        <v>5.7913478058950398E-2</v>
+        <v>9.78525289523203E-2</v>
       </c>
       <c r="AL115" s="6"/>
       <c r="AM115" s="6"/>
@@ -14020,22 +14020,22 @@
         <v>2.9656736082419144</v>
       </c>
       <c r="AF116" s="6">
-        <v>7.0203167847638095E-2</v>
+        <v>9.8533590189840703E-2</v>
       </c>
       <c r="AG116" s="6">
-        <v>6.5042023334535307E-2</v>
+        <v>0.123681894427512</v>
       </c>
       <c r="AH116" s="6">
-        <v>4.6831274079210797E-2</v>
+        <v>0.10694650862965301</v>
       </c>
       <c r="AI116" s="6">
-        <v>7.0299940876649397E-2</v>
+        <v>0.10426395934237601</v>
       </c>
       <c r="AJ116" s="6">
-        <v>4.3582703145622202E-2</v>
+        <v>4.9775210697789798E-2</v>
       </c>
       <c r="AK116" s="6">
-        <v>5.9538423215829001E-2</v>
+        <v>0.10189899463763499</v>
       </c>
       <c r="AL116" s="6"/>
       <c r="AM116" s="6"/>
@@ -14136,22 +14136,22 @@
         <v>3.6452533962400224</v>
       </c>
       <c r="AF117" s="6">
-        <v>7.0010231702995404E-2</v>
+        <v>9.8561048105690496E-2</v>
       </c>
       <c r="AG117" s="6">
-        <v>6.8438629941499796E-2</v>
+        <v>0.13250029937354599</v>
       </c>
       <c r="AH117" s="6">
-        <v>4.8981473028056402E-2</v>
+        <v>0.114310858661429</v>
       </c>
       <c r="AI117" s="6">
-        <v>7.2797196156367497E-2</v>
+        <v>0.107090475418733</v>
       </c>
       <c r="AJ117" s="6">
-        <v>4.4088638362873897E-2</v>
+        <v>5.0208663737224497E-2</v>
       </c>
       <c r="AK117" s="6">
-        <v>6.1514292772414401E-2</v>
+        <v>0.106718239560852</v>
       </c>
       <c r="AL117" s="6"/>
       <c r="AM117" s="6"/>
@@ -14252,22 +14252,22 @@
         <v>4.5798541332082721</v>
       </c>
       <c r="AF118" s="6">
-        <v>6.9631317893120395E-2</v>
+        <v>9.8478680699296897E-2</v>
       </c>
       <c r="AG118" s="6">
-        <v>6.7442391708771504E-2</v>
+        <v>0.13047202421683299</v>
       </c>
       <c r="AH118" s="6">
-        <v>4.8913397465909697E-2</v>
+        <v>0.11393460020464601</v>
       </c>
       <c r="AI118" s="6">
-        <v>7.4683393223251807E-2</v>
+        <v>0.109566510297195</v>
       </c>
       <c r="AJ118" s="6">
-        <v>4.4456636835313798E-2</v>
+        <v>5.0497732031358399E-2</v>
       </c>
       <c r="AK118" s="6">
-        <v>6.1706461867091299E-2</v>
+        <v>0.10668898878818001</v>
       </c>
       <c r="AL118" s="6"/>
       <c r="AM118" s="6"/>
@@ -14368,22 +14368,22 @@
         <v>4.4437593142720999</v>
       </c>
       <c r="AF119" s="6">
-        <v>6.9136623887030402E-2</v>
+        <v>9.8275362508515998E-2</v>
       </c>
       <c r="AG119" s="6">
-        <v>6.6165745559264105E-2</v>
+        <v>0.12794681265448701</v>
       </c>
       <c r="AH119" s="6">
-        <v>4.7030960832208701E-2</v>
+        <v>0.109849364867627</v>
       </c>
       <c r="AI119" s="6">
-        <v>6.62577863741938E-2</v>
+        <v>9.8063865608424894E-2</v>
       </c>
       <c r="AJ119" s="6">
-        <v>4.3865143638623101E-2</v>
+        <v>4.9707776548546898E-2</v>
       </c>
       <c r="AK119" s="6">
-        <v>5.8790405907993601E-2</v>
+        <v>0.102317536838912</v>
       </c>
       <c r="AL119" s="6"/>
       <c r="AM119" s="6"/>
@@ -14484,22 +14484,22 @@
         <v>4.0219303860613564</v>
       </c>
       <c r="AF120" s="6">
-        <v>6.8746168885088901E-2</v>
+        <v>9.8194311871552906E-2</v>
       </c>
       <c r="AG120" s="6">
-        <v>6.5185965454634495E-2</v>
+        <v>0.12618640035515399</v>
       </c>
       <c r="AH120" s="6">
-        <v>4.6955098160936799E-2</v>
+        <v>0.11039427253222101</v>
       </c>
       <c r="AI120" s="6">
-        <v>6.7924370660927894E-2</v>
+        <v>0.100798575684019</v>
       </c>
       <c r="AJ120" s="6">
-        <v>4.4242189199466E-2</v>
+        <v>5.00351797083399E-2</v>
       </c>
       <c r="AK120" s="6">
-        <v>5.8938831262669598E-2</v>
+        <v>0.10267020121498401</v>
       </c>
       <c r="AL120" s="6"/>
       <c r="AM120" s="6"/>
@@ -14600,22 +14600,22 @@
         <v>3.344574200966477</v>
       </c>
       <c r="AF121" s="6">
-        <v>6.8525439486905898E-2</v>
+        <v>9.8315239221592396E-2</v>
       </c>
       <c r="AG121" s="6">
-        <v>6.4806369633125305E-2</v>
+        <v>0.12603396501963199</v>
       </c>
       <c r="AH121" s="6">
-        <v>4.7563607345892302E-2</v>
+        <v>0.112701387283195</v>
       </c>
       <c r="AI121" s="6">
-        <v>6.8850656149657005E-2</v>
+        <v>0.102253649803042</v>
       </c>
       <c r="AJ121" s="6">
-        <v>4.4447357554976599E-2</v>
+        <v>5.0204206565951703E-2</v>
       </c>
       <c r="AK121" s="6">
-        <v>5.9232621855662297E-2</v>
+        <v>0.103600653935242</v>
       </c>
       <c r="AL121" s="6"/>
       <c r="AM121" s="6"/>
@@ -14716,22 +14716,22 @@
         <v>3.5348306185678524</v>
       </c>
       <c r="AF122" s="6">
-        <v>6.8829616394816301E-2</v>
+        <v>9.8927079794635595E-2</v>
       </c>
       <c r="AG122" s="6">
-        <v>6.3754920109960603E-2</v>
+        <v>0.12531953979223301</v>
       </c>
       <c r="AH122" s="6">
-        <v>4.6485921583544497E-2</v>
+        <v>0.10919899685981301</v>
       </c>
       <c r="AI122" s="6">
-        <v>6.7681245680444105E-2</v>
+        <v>0.101086002235883</v>
       </c>
       <c r="AJ122" s="6">
-        <v>4.4189573982882001E-2</v>
+        <v>4.9997088169186597E-2</v>
       </c>
       <c r="AK122" s="6">
-        <v>5.8437046242822401E-2</v>
+        <v>0.102293846146748</v>
       </c>
       <c r="AL122" s="6"/>
       <c r="AM122" s="6"/>
@@ -14832,22 +14832,22 @@
         <v>3.07157282318542</v>
       </c>
       <c r="AF123" s="6">
-        <v>6.9416893819939596E-2</v>
+        <v>9.9862952239414396E-2</v>
       </c>
       <c r="AG123" s="6">
-        <v>6.5147963032858802E-2</v>
+        <v>0.13005353562702501</v>
       </c>
       <c r="AH123" s="6">
-        <v>4.6065101036126002E-2</v>
+        <v>0.109304686934985</v>
       </c>
       <c r="AI123" s="6">
-        <v>6.5153626095125303E-2</v>
+        <v>9.78371542150204E-2</v>
       </c>
       <c r="AJ123" s="6">
-        <v>4.3617159087815799E-2</v>
+        <v>4.9553405540664397E-2</v>
       </c>
       <c r="AK123" s="6">
-        <v>5.8044760581472898E-2</v>
+        <v>0.10282911510044999</v>
       </c>
       <c r="AL123" s="6"/>
       <c r="AM123" s="6"/>
@@ -14948,22 +14948,22 @@
         <v>3.5854223537917562</v>
       </c>
       <c r="AF124" s="6">
-        <v>7.0040367839026896E-2</v>
+        <v>0.10070595624614399</v>
       </c>
       <c r="AG124" s="6">
-        <v>6.5849444633995405E-2</v>
+        <v>0.13388127759295099</v>
       </c>
       <c r="AH124" s="6">
-        <v>4.4287874606282203E-2</v>
+        <v>0.104827414390517</v>
       </c>
       <c r="AI124" s="6">
-        <v>6.2964772549693904E-2</v>
+        <v>9.5501685069572698E-2</v>
       </c>
       <c r="AJ124" s="6">
-        <v>4.3102093308990501E-2</v>
+        <v>4.9183107814065499E-2</v>
       </c>
       <c r="AK124" s="6">
-        <v>5.7218785179426197E-2</v>
+        <v>0.10211697047035</v>
       </c>
       <c r="AL124" s="6"/>
       <c r="AM124" s="6"/>
@@ -15064,22 +15064,22 @@
         <v>3.1347841205434435</v>
       </c>
       <c r="AF125" s="6">
-        <v>7.0646246002228894E-2</v>
+        <v>0.10154809235352801</v>
       </c>
       <c r="AG125" s="6">
-        <v>6.7316796571535803E-2</v>
+        <v>0.13835481296105501</v>
       </c>
       <c r="AH125" s="6">
-        <v>4.6473697077507502E-2</v>
+        <v>0.113405349050879</v>
       </c>
       <c r="AI125" s="6">
-        <v>6.1966992591589998E-2</v>
+        <v>9.4859561564528794E-2</v>
       </c>
       <c r="AJ125" s="6">
-        <v>4.2568331105917401E-2</v>
+        <v>4.8813751270877503E-2</v>
       </c>
       <c r="AK125" s="6">
-        <v>5.7914005480805601E-2</v>
+        <v>0.105391055669579</v>
       </c>
       <c r="AL125" s="6"/>
       <c r="AM125" s="6"/>
@@ -15180,22 +15180,22 @@
         <v>3.0498152476294393</v>
       </c>
       <c r="AF126" s="6">
-        <v>7.1503638259840296E-2</v>
+        <v>0.10244559880084</v>
       </c>
       <c r="AG126" s="6">
-        <v>6.7596082428516099E-2</v>
+        <v>0.141350027010547</v>
       </c>
       <c r="AH126" s="6">
-        <v>4.4036042482997098E-2</v>
+        <v>0.105209803643383</v>
       </c>
       <c r="AI126" s="6">
-        <v>5.9542207220808503E-2</v>
+        <v>9.2413132911057502E-2</v>
       </c>
       <c r="AJ126" s="6">
-        <v>4.1974840660593003E-2</v>
+        <v>4.84231317911707E-2</v>
       </c>
       <c r="AK126" s="6">
-        <v>5.6777240795112503E-2</v>
+        <v>0.103469528952669</v>
       </c>
       <c r="AL126" s="6"/>
       <c r="AM126" s="6"/>
@@ -15296,22 +15296,22 @@
         <v>2.8130785086869281</v>
       </c>
       <c r="AF127" s="6">
-        <v>7.2072846511043995E-2</v>
+        <v>0.10310803433601599</v>
       </c>
       <c r="AG127" s="6">
-        <v>6.8793741535405295E-2</v>
+        <v>0.145132335530401</v>
       </c>
       <c r="AH127" s="6">
-        <v>4.30802378944301E-2</v>
+        <v>0.103836789362226</v>
       </c>
       <c r="AI127" s="6">
-        <v>5.7830066645551501E-2</v>
+        <v>9.0669715261726097E-2</v>
       </c>
       <c r="AJ127" s="6">
-        <v>4.1537625671694597E-2</v>
+        <v>4.8178800123797903E-2</v>
       </c>
       <c r="AK127" s="6">
-        <v>5.63933233341226E-2</v>
+        <v>0.103677913922595</v>
       </c>
       <c r="AL127" s="6"/>
       <c r="AM127" s="6"/>
@@ -15412,22 +15412,22 @@
         <v>2.3625618204203391</v>
       </c>
       <c r="AF128" s="6">
-        <v>7.2534618231312201E-2</v>
+        <v>0.10358282880019</v>
       </c>
       <c r="AG128" s="6">
-        <v>6.9502129445957406E-2</v>
+        <v>0.14703540922011599</v>
       </c>
       <c r="AH128" s="6">
-        <v>4.2107101985585003E-2</v>
+        <v>0.10071188868393301</v>
       </c>
       <c r="AI128" s="6">
-        <v>5.6607851454337998E-2</v>
+        <v>8.9940452060552803E-2</v>
       </c>
       <c r="AJ128" s="6">
-        <v>4.1216385472957501E-2</v>
+        <v>4.8043643286706801E-2</v>
       </c>
       <c r="AK128" s="6">
-        <v>5.6011295606557099E-2</v>
+        <v>0.10316820071378099</v>
       </c>
       <c r="AL128" s="6"/>
       <c r="AM128" s="6"/>
@@ -15528,22 +15528,22 @@
         <v>2.9204035567993003</v>
       </c>
       <c r="AF129" s="6">
-        <v>7.2974197020370002E-2</v>
+        <v>0.103913683374264</v>
       </c>
       <c r="AG129" s="6">
-        <v>6.8831507200647304E-2</v>
+        <v>0.14543156107518301</v>
       </c>
       <c r="AH129" s="6">
-        <v>4.1154365162310497E-2</v>
+        <v>9.8005700475030003E-2</v>
       </c>
       <c r="AI129" s="6">
-        <v>5.5724093157860297E-2</v>
+        <v>8.9802491894653794E-2</v>
       </c>
       <c r="AJ129" s="6">
-        <v>4.0978991080284903E-2</v>
+        <v>4.7984824220919098E-2</v>
       </c>
       <c r="AK129" s="6">
-        <v>5.5419731117004198E-2</v>
+        <v>0.102048352551237</v>
       </c>
       <c r="AL129" s="6"/>
       <c r="AM129" s="6"/>
@@ -15644,22 +15644,22 @@
         <v>2.7487730323958459</v>
       </c>
       <c r="AF130" s="6">
-        <v>7.3177428628668495E-2</v>
+        <v>0.104088794972828</v>
       </c>
       <c r="AG130" s="6">
-        <v>6.9313165067119695E-2</v>
+        <v>0.14647305362073201</v>
       </c>
       <c r="AH130" s="6">
-        <v>4.1723224899969699E-2</v>
+        <v>0.100938100172971</v>
       </c>
       <c r="AI130" s="6">
-        <v>5.5483246751956199E-2</v>
+        <v>9.0249643618001002E-2</v>
       </c>
       <c r="AJ130" s="6">
-        <v>4.0833166037710297E-2</v>
+        <v>4.8005180815208999E-2</v>
       </c>
       <c r="AK130" s="6">
-        <v>5.5633118190055598E-2</v>
+        <v>0.103226362262283</v>
       </c>
       <c r="AL130" s="6"/>
       <c r="AM130" s="6"/>
@@ -15760,22 +15760,22 @@
         <v>3.0247997236873658</v>
       </c>
       <c r="AF131" s="6">
-        <v>7.3576995591836405E-2</v>
+        <v>0.10444135210076801</v>
       </c>
       <c r="AG131" s="6">
-        <v>7.0051462067578799E-2</v>
+        <v>0.14838552462517299</v>
       </c>
       <c r="AH131" s="6">
-        <v>4.1047211839007301E-2</v>
+        <v>9.9354462117242304E-2</v>
       </c>
       <c r="AI131" s="6">
-        <v>5.4505398604712901E-2</v>
+        <v>8.9699320833563204E-2</v>
       </c>
       <c r="AJ131" s="6">
-        <v>4.0565749229641998E-2</v>
+        <v>4.79184223100508E-2</v>
       </c>
       <c r="AK131" s="6">
-        <v>5.5393961984497399E-2</v>
+        <v>0.103162215973988</v>
       </c>
       <c r="AL131" s="6"/>
       <c r="AM131" s="6"/>
@@ -15876,22 +15876,22 @@
         <v>2.2300999718893877</v>
       </c>
       <c r="AF132" s="6">
-        <v>7.3997922238973002E-2</v>
+        <v>0.104813133278905</v>
       </c>
       <c r="AG132" s="6">
-        <v>7.1066099729443305E-2</v>
+        <v>0.150811961003321</v>
       </c>
       <c r="AH132" s="6">
-        <v>4.2002930026721903E-2</v>
+        <v>0.10430498536916</v>
       </c>
       <c r="AI132" s="6">
-        <v>5.3682643940343298E-2</v>
+        <v>8.9603560334207702E-2</v>
       </c>
       <c r="AJ132" s="6">
-        <v>4.0277254072356702E-2</v>
+        <v>4.7813801035243401E-2</v>
       </c>
       <c r="AK132" s="6">
-        <v>5.5701314249723501E-2</v>
+        <v>0.105105908036305</v>
       </c>
       <c r="AL132" s="6"/>
       <c r="AM132" s="6"/>
@@ -15992,22 +15992,22 @@
         <v>2.0520308764275796</v>
       </c>
       <c r="AF133" s="6">
-        <v>7.4154094338055504E-2</v>
+        <v>0.104735127817858</v>
       </c>
       <c r="AG133" s="6">
-        <v>6.79888053717429E-2</v>
+        <v>0.139866048749481</v>
       </c>
       <c r="AH133" s="6">
-        <v>4.0608091612166199E-2</v>
+        <v>9.9968028707321896E-2</v>
       </c>
       <c r="AI133" s="6">
-        <v>5.2500642062183002E-2</v>
+        <v>8.8925558234820901E-2</v>
       </c>
       <c r="AJ133" s="6">
-        <v>3.9944027353498203E-2</v>
+        <v>4.7676463092910598E-2</v>
       </c>
       <c r="AK133" s="6">
-        <v>5.4338052718115398E-2</v>
+        <v>0.101122771590601</v>
       </c>
       <c r="AL133" s="6"/>
       <c r="AM133" s="6"/>
@@ -16108,22 +16108,22 @@
         <v>1.8110351478739517</v>
       </c>
       <c r="AF134" s="6">
-        <v>7.4487525169690094E-2</v>
+        <v>0.104925497382776</v>
       </c>
       <c r="AG134" s="6">
-        <v>6.8042636255433803E-2</v>
+        <v>0.141081601399907</v>
       </c>
       <c r="AH134" s="6">
-        <v>3.9910632092611698E-2</v>
+        <v>9.8534693017819003E-2</v>
       </c>
       <c r="AI134" s="6">
-        <v>5.18717667351795E-2</v>
+        <v>8.8988338049312596E-2</v>
       </c>
       <c r="AJ134" s="6">
-        <v>3.9762765314355603E-2</v>
+        <v>4.7680262493807801E-2</v>
       </c>
       <c r="AK134" s="6">
-        <v>5.40295693641029E-2</v>
+        <v>0.101065670241171</v>
       </c>
       <c r="AL134" s="6"/>
       <c r="AM134" s="6"/>
@@ -16224,22 +16224,22 @@
         <v>2.6825128643984897</v>
       </c>
       <c r="AF135" s="6">
-        <v>7.4720288722285505E-2</v>
+        <v>0.10500964945147399</v>
       </c>
       <c r="AG135" s="6">
-        <v>6.8019007973315601E-2</v>
+        <v>0.14099144621607401</v>
       </c>
       <c r="AH135" s="6">
-        <v>3.94406663900502E-2</v>
+        <v>9.7610405576466205E-2</v>
       </c>
       <c r="AI135" s="6">
-        <v>5.1453548781142701E-2</v>
+        <v>8.9411549167740106E-2</v>
       </c>
       <c r="AJ135" s="6">
-        <v>3.9640726458374902E-2</v>
+        <v>4.77357829780303E-2</v>
       </c>
       <c r="AK135" s="6">
-        <v>5.3810846536800801E-2</v>
+        <v>0.100903032340699</v>
       </c>
       <c r="AL135" s="6"/>
       <c r="AM135" s="6"/>
@@ -16340,22 +16340,22 @@
         <v>2.2270029244918277</v>
       </c>
       <c r="AF136" s="6">
-        <v>7.4687031983763405E-2</v>
+        <v>0.104852598681929</v>
       </c>
       <c r="AG136" s="6">
-        <v>6.7946067793847001E-2</v>
+        <v>0.14070969017283699</v>
       </c>
       <c r="AH136" s="6">
-        <v>3.9364414959043102E-2</v>
+        <v>9.8420250178667706E-2</v>
       </c>
       <c r="AI136" s="6">
-        <v>5.12487707708656E-2</v>
+        <v>9.0062928244813406E-2</v>
       </c>
       <c r="AJ136" s="6">
-        <v>3.9642871380934003E-2</v>
+        <v>4.7897826252133499E-2</v>
       </c>
       <c r="AK136" s="6">
-        <v>5.3720065494934903E-2</v>
+        <v>0.101202192897725</v>
       </c>
       <c r="AL136" s="6"/>
       <c r="AM136" s="6"/>
@@ -16456,22 +16456,22 @@
         <v>2.027165358505556</v>
       </c>
       <c r="AF137" s="6">
-        <v>7.47037508860523E-2</v>
+        <v>0.104754952593492</v>
       </c>
       <c r="AG137" s="6">
-        <v>6.7907807863167594E-2</v>
+        <v>0.14055721923709799</v>
       </c>
       <c r="AH137" s="6">
-        <v>3.9331251904514801E-2</v>
+        <v>9.9277755771488799E-2</v>
       </c>
       <c r="AI137" s="6">
-        <v>5.1220087400087502E-2</v>
+        <v>9.1000524542930297E-2</v>
       </c>
       <c r="AJ137" s="6">
-        <v>3.9634386964774102E-2</v>
+        <v>4.80424349766422E-2</v>
       </c>
       <c r="AK137" s="6">
-        <v>5.3696928923547903E-2</v>
+        <v>0.101613132736316</v>
       </c>
       <c r="AL137" s="6"/>
       <c r="AM137" s="6"/>
@@ -16572,22 +16572,22 @@
         <v>2.0908024736979058</v>
       </c>
       <c r="AF138" s="6">
-        <v>7.4552230912411699E-2</v>
+        <v>0.104510449906521</v>
       </c>
       <c r="AG138" s="6">
-        <v>6.7770704776776894E-2</v>
+        <v>0.13999304468705601</v>
       </c>
       <c r="AH138" s="6">
-        <v>3.9618264478678403E-2</v>
+        <v>0.10140981055647701</v>
       </c>
       <c r="AI138" s="6">
-        <v>5.1508837826986599E-2</v>
+        <v>9.2411919198905096E-2</v>
       </c>
       <c r="AJ138" s="6">
-        <v>3.9719682316393903E-2</v>
+        <v>4.8265409762780001E-2</v>
       </c>
       <c r="AK138" s="6">
-        <v>5.3805740110235797E-2</v>
+        <v>0.10236732815128</v>
       </c>
       <c r="AL138" s="6"/>
       <c r="AM138" s="6"/>
@@ -16688,22 +16688,22 @@
         <v>2.3679027430318911</v>
       </c>
       <c r="AF139" s="6">
-        <v>7.4548340924662407E-2</v>
+        <v>0.104419397722222</v>
       </c>
       <c r="AG139" s="6">
-        <v>6.7763174787124403E-2</v>
+        <v>0.139968571612334</v>
       </c>
       <c r="AH139" s="6">
-        <v>3.9623046876947898E-2</v>
+        <v>0.102239345589026</v>
       </c>
       <c r="AI139" s="6">
-        <v>5.1517073053439597E-2</v>
+        <v>9.3269070234468496E-2</v>
       </c>
       <c r="AJ139" s="6">
-        <v>3.9722104131468101E-2</v>
+        <v>4.8395710652815602E-2</v>
       </c>
       <c r="AK139" s="6">
-        <v>5.3807177881990798E-2</v>
+        <v>0.102781476684187</v>
       </c>
       <c r="AL139" s="6"/>
       <c r="AM139" s="6"/>
@@ -16804,22 +16804,22 @@
         <v>1.9023562292566965</v>
       </c>
       <c r="AF140" s="6">
-        <v>7.4696165374586995E-2</v>
+        <v>0.104492059989408</v>
       </c>
       <c r="AG140" s="6">
-        <v>6.8087583480754402E-2</v>
+        <v>0.14090916197304801</v>
       </c>
       <c r="AH140" s="6">
-        <v>3.9639519829081801E-2</v>
+        <v>0.10373096618126899</v>
       </c>
       <c r="AI140" s="6">
-        <v>5.1197574290160801E-2</v>
+        <v>9.34002459776241E-2</v>
       </c>
       <c r="AJ140" s="6">
-        <v>3.9627968583321599E-2</v>
+        <v>4.8425373259626099E-2</v>
       </c>
       <c r="AK140" s="6">
-        <v>5.3813397531940997E-2</v>
+        <v>0.103455636451261</v>
       </c>
       <c r="AL140" s="6"/>
       <c r="AM140" s="6"/>
@@ -16920,22 +16920,22 @@
         <v>2.0005076522497944</v>
       </c>
       <c r="AF141" s="6">
-        <v>7.4832628830934E-2</v>
+        <v>0.10451719303477899</v>
       </c>
       <c r="AG141" s="6">
-        <v>6.7954896740556603E-2</v>
+        <v>0.140629831047246</v>
       </c>
       <c r="AH141" s="6">
-        <v>3.9372358568709798E-2</v>
+        <v>0.10322974193711799</v>
       </c>
       <c r="AI141" s="6">
-        <v>5.0969479340191901E-2</v>
+        <v>9.3796064763463097E-2</v>
       </c>
       <c r="AJ141" s="6">
-        <v>3.9560399968150799E-2</v>
+        <v>4.8477983521818299E-2</v>
       </c>
       <c r="AK141" s="6">
-        <v>5.3666251991800903E-2</v>
+        <v>0.103350345514547</v>
       </c>
       <c r="AL141" s="6"/>
       <c r="AM141" s="6"/>
@@ -17036,22 +17036,22 @@
         <v>1.5696029305924952</v>
       </c>
       <c r="AF142" s="6">
-        <v>7.4964299525706504E-2</v>
+        <v>0.104564796389648</v>
       </c>
       <c r="AG142" s="6">
-        <v>6.8236341910422604E-2</v>
+        <v>0.141400663015459</v>
       </c>
       <c r="AH142" s="6">
-        <v>3.9290202006434898E-2</v>
+        <v>0.10354919693124701</v>
       </c>
       <c r="AI142" s="6">
-        <v>5.06942951866583E-2</v>
+        <v>9.3963048086620704E-2</v>
       </c>
       <c r="AJ142" s="6">
-        <v>3.94784444768378E-2</v>
+        <v>4.8512659605288097E-2</v>
       </c>
       <c r="AK142" s="6">
-        <v>5.3645922555980101E-2</v>
+        <v>0.103671075773396</v>
       </c>
       <c r="AL142" s="6"/>
       <c r="AM142" s="6"/>
@@ -17152,22 +17152,22 @@
         <v>1.8974321429318763</v>
       </c>
       <c r="AF143" s="6">
-        <v>7.5131527137435899E-2</v>
+        <v>0.10461189441903999</v>
       </c>
       <c r="AG143" s="6">
-        <v>6.7854773675233501E-2</v>
+        <v>0.140899242347823</v>
       </c>
       <c r="AH143" s="6">
-        <v>3.8964249292077202E-2</v>
+        <v>0.102777006078263</v>
       </c>
       <c r="AI143" s="6">
-        <v>5.0416838674510203E-2</v>
+        <v>9.4228388109155806E-2</v>
       </c>
       <c r="AJ143" s="6">
-        <v>3.93953589655862E-2</v>
+        <v>4.8543373828911801E-2</v>
       </c>
       <c r="AK143" s="6">
-        <v>5.3418868368831599E-2</v>
+        <v>0.103409115466445</v>
       </c>
       <c r="AL143" s="6"/>
       <c r="AM143" s="6"/>
@@ -17268,22 +17268,22 @@
         <v>1.820507471401811</v>
       </c>
       <c r="AF144" s="6">
-        <v>7.4957103153310098E-2</v>
+        <v>0.10433871971316599</v>
       </c>
       <c r="AG144" s="6">
-        <v>6.7479146641796495E-2</v>
+        <v>0.13973429018786401</v>
       </c>
       <c r="AH144" s="6">
-        <v>3.8857286924119598E-2</v>
+        <v>0.10273121004038401</v>
       </c>
       <c r="AI144" s="6">
-        <v>5.07741297675572E-2</v>
+        <v>9.5760518399189101E-2</v>
       </c>
       <c r="AJ144" s="6">
-        <v>3.95029434455587E-2</v>
+        <v>4.87580445826966E-2</v>
       </c>
       <c r="AK144" s="6">
-        <v>5.3383949414289797E-2</v>
+        <v>0.103444482335949</v>
       </c>
       <c r="AL144" s="6"/>
       <c r="AM144" s="6"/>
@@ -17384,22 +17384,22 @@
         <v>2.2706152643269917</v>
       </c>
       <c r="AF145" s="6">
-        <v>7.47601398349554E-2</v>
+        <v>0.104065265043189</v>
       </c>
       <c r="AG145" s="6">
-        <v>6.7091596588757602E-2</v>
+        <v>0.138699137152408</v>
       </c>
       <c r="AH145" s="6">
-        <v>3.9061615469191902E-2</v>
+        <v>0.104703596066684</v>
       </c>
       <c r="AI145" s="6">
-        <v>5.1179815423790798E-2</v>
+        <v>9.7234847488104695E-2</v>
       </c>
       <c r="AJ145" s="6">
-        <v>3.9623871347717603E-2</v>
+        <v>4.8972000669482998E-2</v>
       </c>
       <c r="AK145" s="6">
-        <v>5.34422312843926E-2</v>
+        <v>0.104046685987846</v>
       </c>
       <c r="AL145" s="6"/>
       <c r="AM145" s="6"/>
@@ -17500,22 +17500,22 @@
         <v>1.5683318643308297</v>
       </c>
       <c r="AF146" s="6">
-        <v>7.4512813038531994E-2</v>
+        <v>0.103756119415051</v>
       </c>
       <c r="AG146" s="6">
-        <v>6.6564340987366799E-2</v>
+        <v>0.13726869160791699</v>
       </c>
       <c r="AH146" s="6">
-        <v>3.8452033734891103E-2</v>
+        <v>0.102329793705248</v>
       </c>
       <c r="AI146" s="6">
-        <v>5.1175153136913197E-2</v>
+        <v>9.7783563543039506E-2</v>
       </c>
       <c r="AJ146" s="6">
-        <v>3.9780560704646202E-2</v>
+        <v>4.9208418810094801E-2</v>
       </c>
       <c r="AK146" s="6">
-        <v>5.3144381202278899E-2</v>
+        <v>0.10316613660968101</v>
       </c>
       <c r="AL146" s="6"/>
       <c r="AM146" s="6"/>
@@ -17616,22 +17616,22 @@
         <v>2.0815893879536418</v>
       </c>
       <c r="AF147" s="6">
-        <v>7.52692015941933E-2</v>
+        <v>0.104659583105145</v>
       </c>
       <c r="AG147" s="6">
-        <v>6.7602848279984501E-2</v>
+        <v>0.141176327538799</v>
       </c>
       <c r="AH147" s="6">
-        <v>3.8792634584467002E-2</v>
+        <v>0.104302332056787</v>
       </c>
       <c r="AI147" s="6">
-        <v>5.1496981425697301E-2</v>
+        <v>9.8865113388278497E-2</v>
       </c>
       <c r="AJ147" s="6">
-        <v>3.9876607106518601E-2</v>
+        <v>4.9368057234990499E-2</v>
       </c>
       <c r="AK147" s="6">
-        <v>5.3660872801854803E-2</v>
+        <v>0.105026040612984</v>
       </c>
       <c r="AL147" s="6"/>
       <c r="AM147" s="6"/>
@@ -17732,22 +17732,22 @@
         <v>0.93282150971987221</v>
       </c>
       <c r="AF148" s="6">
-        <v>7.4860993667559397E-2</v>
+        <v>0.104144109660426</v>
       </c>
       <c r="AG148" s="6">
-        <v>6.6734992051951894E-2</v>
+        <v>0.13855048259388</v>
       </c>
       <c r="AH148" s="6">
-        <v>3.7844509742888201E-2</v>
+        <v>0.10016112635452</v>
       </c>
       <c r="AI148" s="6">
-        <v>5.18039974474825E-2</v>
+        <v>9.9586339983679203E-2</v>
       </c>
       <c r="AJ148" s="6">
-        <v>4.0135621971011497E-2</v>
+        <v>4.9679937805093999E-2</v>
       </c>
       <c r="AK148" s="6">
-        <v>5.3260837230450303E-2</v>
+        <v>0.103383639249589</v>
       </c>
       <c r="AL148" s="6"/>
       <c r="AM148" s="6"/>
@@ -17848,22 +17848,22 @@
         <v>1.2638241161472052</v>
       </c>
       <c r="AF149" s="6">
-        <v>8.3594247433249502E-2</v>
+        <v>0.11309475548534299</v>
       </c>
       <c r="AG149" s="6">
-        <v>7.0248863549322998E-2</v>
+        <v>0.151559894537245</v>
       </c>
       <c r="AH149" s="6">
-        <v>3.8953585425367102E-2</v>
+        <v>0.105094582327591</v>
       </c>
       <c r="AI149" s="6">
-        <v>5.2902037283802897E-2</v>
+        <v>0.10190454377896201</v>
       </c>
       <c r="AJ149" s="6">
-        <v>4.0460937504705898E-2</v>
+        <v>5.0036068493322601E-2</v>
       </c>
       <c r="AK149" s="6">
-        <v>5.5821466762587597E-2</v>
+        <v>0.109607194560487</v>
       </c>
       <c r="AL149" s="6"/>
       <c r="AM149" s="6"/>
@@ -17964,22 +17964,22 @@
         <v>1.1768382139329958</v>
       </c>
       <c r="AF150" s="6">
-        <v>8.3070872067634693E-2</v>
+        <v>0.111842114241808</v>
       </c>
       <c r="AG150" s="6">
-        <v>6.9314266324984594E-2</v>
+        <v>0.14923910384959499</v>
       </c>
       <c r="AH150" s="6">
-        <v>3.9875152809428001E-2</v>
+        <v>0.110669323677261</v>
       </c>
       <c r="AI150" s="6">
-        <v>5.3927652539908999E-2</v>
+        <v>0.10403779319716901</v>
       </c>
       <c r="AJ150" s="6">
-        <v>4.0757970710334601E-2</v>
+        <v>5.0338367710147602E-2</v>
       </c>
       <c r="AK150" s="6">
-        <v>5.6054540580416798E-2</v>
+        <v>0.110923667830546</v>
       </c>
       <c r="AL150" s="6"/>
       <c r="AM150" s="6"/>
@@ -18080,22 +18080,22 @@
         <v>1.2230453941256769</v>
       </c>
       <c r="AF151" s="6">
-        <v>8.2569534384228496E-2</v>
+        <v>0.110702867031773</v>
       </c>
       <c r="AG151" s="6">
-        <v>6.8346738644338906E-2</v>
+        <v>0.14610478297704199</v>
       </c>
       <c r="AH151" s="6">
-        <v>4.0771435393889097E-2</v>
+        <v>0.11490913773188099</v>
       </c>
       <c r="AI151" s="6">
-        <v>5.4981016159053799E-2</v>
+        <v>0.106301217810042</v>
       </c>
       <c r="AJ151" s="6">
-        <v>4.1056658270416199E-2</v>
+        <v>5.0619791309464299E-2</v>
       </c>
       <c r="AK151" s="6">
-        <v>5.62801045706793E-2</v>
+        <v>0.111695162850482</v>
       </c>
       <c r="AL151" s="6"/>
       <c r="AM151" s="6"/>
@@ -18196,22 +18196,22 @@
         <v>1.4172889011298651</v>
       </c>
       <c r="AF152" s="6">
-        <v>8.2141608342865893E-2</v>
+        <v>0.10970618790683601</v>
       </c>
       <c r="AG152" s="6">
-        <v>6.7286319771068304E-2</v>
+        <v>0.14297011106225799</v>
       </c>
       <c r="AH152" s="6">
-        <v>4.1184013092309603E-2</v>
+        <v>0.116354250710909</v>
       </c>
       <c r="AI152" s="6">
-        <v>5.5976862889879297E-2</v>
+        <v>0.108540398425477</v>
       </c>
       <c r="AJ152" s="6">
-        <v>4.13332385993148E-2</v>
+        <v>5.0858488203259902E-2</v>
       </c>
       <c r="AK152" s="6">
-        <v>5.6345556773382502E-2</v>
+        <v>0.111708745472912</v>
       </c>
       <c r="AL152" s="6"/>
       <c r="AM152" s="6"/>
@@ -18312,22 +18312,22 @@
         <v>1.2734727038456128</v>
       </c>
       <c r="AF153" s="6">
-        <v>8.16433723792101E-2</v>
+        <v>0.108707574888497</v>
       </c>
       <c r="AG153" s="6">
-        <v>6.6035987498691703E-2</v>
+        <v>0.139591299524843</v>
       </c>
       <c r="AH153" s="6">
-        <v>4.1292981365445298E-2</v>
+        <v>0.11595184615482999</v>
       </c>
       <c r="AI153" s="6">
-        <v>5.7205217999149502E-2</v>
+        <v>0.111290879878888</v>
       </c>
       <c r="AJ153" s="6">
-        <v>4.1667694590389097E-2</v>
+        <v>5.1136389926716097E-2</v>
       </c>
       <c r="AK153" s="6">
-        <v>5.6337090929403102E-2</v>
+        <v>0.11127730312008299</v>
       </c>
       <c r="AL153" s="6"/>
       <c r="AM153" s="6"/>
@@ -18428,22 +18428,22 @@
         <v>1.0016539814294845</v>
       </c>
       <c r="AF154" s="6">
-        <v>8.0926088378840993E-2</v>
+        <v>0.107577644010903</v>
       </c>
       <c r="AG154" s="6">
-        <v>6.4602427756343103E-2</v>
+        <v>0.136129707062982</v>
       </c>
       <c r="AH154" s="6">
-        <v>4.2680952162233297E-2</v>
+        <v>0.122023825088932</v>
       </c>
       <c r="AI154" s="6">
-        <v>5.9021707911249499E-2</v>
+        <v>0.11472178293966701</v>
       </c>
       <c r="AJ154" s="6">
-        <v>4.2150229303370097E-2</v>
+        <v>5.15386736680013E-2</v>
       </c>
       <c r="AK154" s="6">
-        <v>5.6748377246639101E-2</v>
+        <v>0.11269920166007601</v>
       </c>
       <c r="AL154" s="6"/>
       <c r="AM154" s="6"/>
@@ -18544,22 +18544,22 @@
         <v>1.3861300951614197</v>
       </c>
       <c r="AF155" s="6">
-        <v>8.0196438780252802E-2</v>
+        <v>0.106596903760796</v>
       </c>
       <c r="AG155" s="6">
-        <v>6.4978076620511804E-2</v>
+        <v>0.137686345698631</v>
       </c>
       <c r="AH155" s="6">
-        <v>4.4725178584179098E-2</v>
+        <v>0.13063763633938599</v>
       </c>
       <c r="AI155" s="6">
-        <v>6.0823288976893798E-2</v>
+        <v>0.11752202000300201</v>
       </c>
       <c r="AJ155" s="6">
-        <v>4.2612839820066098E-2</v>
+        <v>5.1888738810674101E-2</v>
       </c>
       <c r="AK155" s="6">
-        <v>5.7781865218037499E-2</v>
+        <v>0.115881957614328</v>
       </c>
       <c r="AL155" s="6"/>
       <c r="AM155" s="6"/>
@@ -18660,22 +18660,22 @@
         <v>1.4700067976651354</v>
       </c>
       <c r="AF156" s="6">
-        <v>7.9659552742512005E-2</v>
+        <v>0.10578385310384</v>
       </c>
       <c r="AG156" s="6">
-        <v>6.3631182464689295E-2</v>
+        <v>0.13445593413975801</v>
       </c>
       <c r="AH156" s="6">
-        <v>4.3376838734000299E-2</v>
+        <v>0.122337223427609</v>
       </c>
       <c r="AI156" s="6">
-        <v>6.20534555981389E-2</v>
+        <v>0.119291396828255</v>
       </c>
       <c r="AJ156" s="6">
-        <v>4.3025386101613099E-2</v>
+        <v>5.2161914212206999E-2</v>
       </c>
       <c r="AK156" s="6">
-        <v>5.7371770771123903E-2</v>
+        <v>0.113214843072956</v>
       </c>
       <c r="AL156" s="6"/>
       <c r="AM156" s="6"/>
@@ -18776,22 +18776,22 @@
         <v>1.8772174071937542</v>
       </c>
       <c r="AF157" s="6">
-        <v>7.9039871891235194E-2</v>
+        <v>0.104941463632701</v>
       </c>
       <c r="AG157" s="6">
-        <v>6.2124418559616902E-2</v>
+        <v>0.13108674433436299</v>
       </c>
       <c r="AH157" s="6">
-        <v>4.3801058752607799E-2</v>
+        <v>0.123266404354664</v>
       </c>
       <c r="AI157" s="6">
-        <v>6.4077549652269403E-2</v>
+        <v>0.122960229916678</v>
       </c>
       <c r="AJ157" s="6">
-        <v>4.3520869937333402E-2</v>
+        <v>5.24911949283937E-2</v>
       </c>
       <c r="AK157" s="6">
-        <v>5.7569059239158803E-2</v>
+        <v>0.113351313634663</v>
       </c>
       <c r="AL157" s="6"/>
       <c r="AM157" s="6"/>
@@ -18892,22 +18892,22 @@
         <v>2.0906440296744933</v>
       </c>
       <c r="AF158" s="6">
-        <v>7.8239119777405802E-2</v>
+        <v>0.103962744248514</v>
       </c>
       <c r="AG158" s="6">
-        <v>6.0218246568917902E-2</v>
+        <v>0.12698141384659001</v>
       </c>
       <c r="AH158" s="6">
-        <v>4.1337845713973601E-2</v>
+        <v>0.11153046812911201</v>
       </c>
       <c r="AI158" s="6">
-        <v>6.4056732121283502E-2</v>
+        <v>0.111276658011249</v>
       </c>
       <c r="AJ158" s="6">
-        <v>4.4196456247368898E-2</v>
+        <v>5.2809129633973398E-2</v>
       </c>
       <c r="AK158" s="6">
-        <v>5.6427968394051203E-2</v>
+        <v>0.106610724245101</v>
       </c>
       <c r="AL158" s="6"/>
       <c r="AM158" s="6"/>
@@ -19008,22 +19008,22 @@
         <v>1.3930722664508011</v>
       </c>
       <c r="AF159" s="6">
-        <v>7.7686692560289303E-2</v>
+        <v>0.10331949849437699</v>
       </c>
       <c r="AG159" s="6">
-        <v>5.8952582472588298E-2</v>
+        <v>0.12514439055587301</v>
       </c>
       <c r="AH159" s="6">
-        <v>4.1613079762436798E-2</v>
+        <v>0.116116598329582</v>
       </c>
       <c r="AI159" s="6">
-        <v>6.6053891359719202E-2</v>
+        <v>0.114410485901749</v>
       </c>
       <c r="AJ159" s="6">
-        <v>4.4685958991247998E-2</v>
+        <v>5.3062142983976497E-2</v>
       </c>
       <c r="AK159" s="6">
-        <v>5.6644656679419703E-2</v>
+        <v>0.108009940448913</v>
       </c>
       <c r="AL159" s="6"/>
       <c r="AM159" s="6"/>
@@ -19124,22 +19124,22 @@
         <v>1.9251312156534084</v>
       </c>
       <c r="AF160" s="6">
-        <v>7.7718785430859694E-2</v>
+        <v>0.103002309394189</v>
       </c>
       <c r="AG160" s="6">
-        <v>6.4819995429547403E-2</v>
+        <v>0.13866763243072699</v>
       </c>
       <c r="AH160" s="6">
-        <v>4.3440379482435197E-2</v>
+        <v>0.12724729143635199</v>
       </c>
       <c r="AI160" s="6">
-        <v>6.9206409443318601E-2</v>
+        <v>0.118504667047287</v>
       </c>
       <c r="AJ160" s="6">
-        <v>4.5430877395103299E-2</v>
+        <v>5.3518011417627499E-2</v>
       </c>
       <c r="AK160" s="6">
-        <v>5.94722368196689E-2</v>
+        <v>0.115229342528541</v>
       </c>
       <c r="AL160" s="6"/>
       <c r="AM160" s="6"/>
@@ -19240,22 +19240,22 @@
         <v>1.9760215457679919</v>
       </c>
       <c r="AF161" s="6">
-        <v>7.7196677850704595E-2</v>
+        <v>0.102458641705906</v>
       </c>
       <c r="AG161" s="6">
-        <v>6.3449643922624893E-2</v>
+        <v>0.13532041289444399</v>
       </c>
       <c r="AH161" s="6">
-        <v>4.17855581930986E-2</v>
+        <v>0.116682194337544</v>
       </c>
       <c r="AI161" s="6">
-        <v>6.5791949206014402E-2</v>
+        <v>0.115644839670437</v>
       </c>
       <c r="AJ161" s="6">
-        <v>4.5870546664132802E-2</v>
+        <v>5.3693487363496099E-2</v>
       </c>
       <c r="AK161" s="6">
-        <v>5.7885912361254198E-2</v>
+        <v>0.110927575313022</v>
       </c>
       <c r="AL161" s="6"/>
       <c r="AM161" s="6"/>
@@ -19356,22 +19356,22 @@
         <v>2.5920852647836057</v>
       </c>
       <c r="AF162" s="6">
-        <v>7.6778051454679905E-2</v>
+        <v>0.102076536206018</v>
       </c>
       <c r="AG162" s="6">
-        <v>6.2541009972980802E-2</v>
+        <v>0.133166005140709</v>
       </c>
       <c r="AH162" s="6">
-        <v>4.2661271200388103E-2</v>
+        <v>0.118809374636341</v>
       </c>
       <c r="AI162" s="6">
-        <v>6.7361681136493004E-2</v>
+        <v>0.117926859247535</v>
       </c>
       <c r="AJ162" s="6">
-        <v>4.6264326224471401E-2</v>
+        <v>5.3781321650543001E-2</v>
       </c>
       <c r="AK162" s="6">
-        <v>5.8258192281632197E-2</v>
+        <v>0.111422666456353</v>
       </c>
       <c r="AL162" s="6"/>
       <c r="AM162" s="6"/>
@@ -19472,22 +19472,22 @@
         <v>1.50943244568289</v>
       </c>
       <c r="AF163" s="6">
-        <v>7.6764279393630799E-2</v>
+        <v>0.102143739659731</v>
       </c>
       <c r="AG163" s="6">
-        <v>6.2505962688491096E-2</v>
+        <v>0.133539243239647</v>
       </c>
       <c r="AH163" s="6">
-        <v>4.2628829885152701E-2</v>
+        <v>0.118351992506743</v>
       </c>
       <c r="AI163" s="6">
-        <v>6.7148485832776203E-2</v>
+        <v>0.116612249589163</v>
       </c>
       <c r="AJ163" s="6">
-        <v>4.6231267707882398E-2</v>
+        <v>5.3446286045831799E-2</v>
       </c>
       <c r="AK163" s="6">
-        <v>5.8184658436934801E-2</v>
+        <v>0.111068047775486</v>
       </c>
       <c r="AL163" s="6"/>
       <c r="AM163" s="6"/>
@@ -19588,22 +19588,22 @@
         <v>1.031059022288261</v>
       </c>
       <c r="AF164" s="6">
-        <v>7.6187712434719002E-2</v>
+        <v>0.10161958156062099</v>
       </c>
       <c r="AG164" s="6">
-        <v>6.1987082656166703E-2</v>
+        <v>0.13274281420091799</v>
       </c>
       <c r="AH164" s="6">
-        <v>4.2553193396304402E-2</v>
+        <v>0.11745463770212</v>
       </c>
       <c r="AI164" s="6">
-        <v>6.69546321789007E-2</v>
+        <v>0.115498870121792</v>
       </c>
       <c r="AJ164" s="6">
-        <v>4.6183254967675398E-2</v>
+        <v>5.3168575214657898E-2</v>
       </c>
       <c r="AK164" s="6">
-        <v>5.7912903154717803E-2</v>
+        <v>0.110281635212178</v>
       </c>
       <c r="AL164" s="6"/>
       <c r="AM164" s="6"/>
@@ -19704,22 +19704,22 @@
         <v>1.9256671894165578</v>
       </c>
       <c r="AF165" s="6">
-        <v>7.6142228781076293E-2</v>
+        <v>0.101780461484669</v>
       </c>
       <c r="AG165" s="6">
-        <v>5.8933127524333502E-2</v>
+        <v>0.12593013849771501</v>
       </c>
       <c r="AH165" s="6">
-        <v>4.1533198403408501E-2</v>
+        <v>0.111574956262571</v>
       </c>
       <c r="AI165" s="6">
-        <v>6.5314889329097903E-2</v>
+        <v>0.112340491066747</v>
       </c>
       <c r="AJ165" s="6">
-        <v>4.5772949143208397E-2</v>
+        <v>5.2606164464058199E-2</v>
       </c>
       <c r="AK165" s="6">
-        <v>5.6415121480443399E-2</v>
+        <v>0.106296238440832</v>
       </c>
       <c r="AL165" s="6"/>
       <c r="AM165" s="6"/>
@@ -19820,22 +19820,22 @@
         <v>1.2261250335935614</v>
       </c>
       <c r="AF166" s="6">
-        <v>7.6678316405655103E-2</v>
+        <v>0.102469178361729</v>
       </c>
       <c r="AG166" s="6">
-        <v>6.019797563992E-2</v>
+        <v>0.130065674409855</v>
       </c>
       <c r="AH166" s="6">
-        <v>4.2759688391741997E-2</v>
+        <v>0.117302293425518</v>
       </c>
       <c r="AI166" s="6">
-        <v>7.3867613496681403E-2</v>
+        <v>0.12550656316304601</v>
       </c>
       <c r="AJ166" s="6">
-        <v>4.7065726745027701E-2</v>
+        <v>5.4059928039486498E-2</v>
       </c>
       <c r="AK166" s="6">
-        <v>5.92908620533414E-2</v>
+        <v>0.112139906854013</v>
       </c>
       <c r="AL166" s="6"/>
       <c r="AM166" s="6"/>
@@ -19936,22 +19936,22 @@
         <v>2.1948426317724312</v>
       </c>
       <c r="AF167" s="6">
-        <v>7.6965328032323005E-2</v>
+        <v>0.103027687938856</v>
       </c>
       <c r="AG167" s="6">
-        <v>5.7567177252140597E-2</v>
+        <v>0.126636051736255</v>
       </c>
       <c r="AH167" s="6">
-        <v>4.13444533249624E-2</v>
+        <v>0.11061998648919499</v>
       </c>
       <c r="AI167" s="6">
-        <v>7.1541421077934403E-2</v>
+        <v>0.120195234998621</v>
       </c>
       <c r="AJ167" s="6">
-        <v>4.6551507798420197E-2</v>
+        <v>5.33465763108774E-2</v>
       </c>
       <c r="AK167" s="6">
-        <v>5.7661680767691501E-2</v>
+        <v>0.108353960233622</v>
       </c>
       <c r="AL167" s="6"/>
       <c r="AM167" s="6"/>
@@ -20052,22 +20052,22 @@
         <v>2.1280528703382373</v>
       </c>
       <c r="AF168" s="6">
-        <v>7.7454186256407598E-2</v>
+        <v>0.10358270728048501</v>
       </c>
       <c r="AG168" s="6">
-        <v>5.8656956487531602E-2</v>
+        <v>0.13042708972688599</v>
       </c>
       <c r="AH168" s="6">
-        <v>4.23646923859681E-2</v>
+        <v>0.115880271501383</v>
       </c>
       <c r="AI168" s="6">
-        <v>8.1094234139449994E-2</v>
+        <v>0.13254594073551099</v>
       </c>
       <c r="AJ168" s="6">
-        <v>4.8920937922221998E-2</v>
+        <v>5.4275694860445201E-2</v>
       </c>
       <c r="AK168" s="6">
-        <v>6.0785835650152401E-2</v>
+        <v>0.113683954589613</v>
       </c>
       <c r="AL168" s="6"/>
       <c r="AM168" s="6"/>
@@ -20168,22 +20168,22 @@
         <v>1.4192658654465617</v>
       </c>
       <c r="AF169" s="6">
-        <v>7.8013173480443607E-2</v>
+        <v>0.10417315131218401</v>
       </c>
       <c r="AG169" s="6">
-        <v>5.9887172830917802E-2</v>
+        <v>0.13450647721775699</v>
       </c>
       <c r="AH169" s="6">
-        <v>4.1498402276737199E-2</v>
+        <v>0.11412704832196099</v>
       </c>
       <c r="AI169" s="6">
-        <v>7.7984625845099104E-2</v>
+        <v>0.125773854738504</v>
       </c>
       <c r="AJ169" s="6">
-        <v>4.8286155963881097E-2</v>
+        <v>5.3482727511855802E-2</v>
       </c>
       <c r="AK169" s="6">
-        <v>6.0138650297856901E-2</v>
+        <v>0.112636893026411</v>
       </c>
       <c r="AL169" s="6"/>
       <c r="AM169" s="6"/>
@@ -20284,22 +20284,22 @@
         <v>1.2322096829791462</v>
       </c>
       <c r="AF170" s="6">
-        <v>7.8713677937626902E-2</v>
+        <v>0.104849611611618</v>
       </c>
       <c r="AG170" s="6">
-        <v>5.7633764134223497E-2</v>
+        <v>0.12877648920780299</v>
       </c>
       <c r="AH170" s="6">
-        <v>3.9331940338806597E-2</v>
+        <v>0.105431233714496</v>
       </c>
       <c r="AI170" s="6">
-        <v>7.4367917273614095E-2</v>
+        <v>0.118903671595103</v>
       </c>
       <c r="AJ170" s="6">
-        <v>4.7513866246445699E-2</v>
+        <v>5.2644989251930799E-2</v>
       </c>
       <c r="AK170" s="6">
-        <v>5.8121830666505302E-2</v>
+        <v>0.10740782240774099</v>
       </c>
       <c r="AL170" s="6"/>
       <c r="AM170" s="6"/>
@@ -20400,22 +20400,22 @@
         <v>1.5133294061204339</v>
       </c>
       <c r="AF171" s="6">
-        <v>7.9481003396307898E-2</v>
+        <v>0.10554700535662601</v>
       </c>
       <c r="AG171" s="6">
-        <v>5.8866996579854503E-2</v>
+        <v>0.13329226390416901</v>
       </c>
       <c r="AH171" s="6">
-        <v>3.7650995003778602E-2</v>
+        <v>0.10062287048118</v>
       </c>
       <c r="AI171" s="6">
-        <v>7.0993864715378399E-2</v>
+        <v>0.113004663623076</v>
       </c>
       <c r="AJ171" s="6">
-        <v>4.67539139708716E-2</v>
+        <v>5.1878501200049401E-2</v>
       </c>
       <c r="AK171" s="6">
-        <v>5.71969866280405E-2</v>
+        <v>0.105893030820367</v>
       </c>
       <c r="AL171" s="6"/>
       <c r="AM171" s="6"/>
@@ -20516,22 +20516,22 @@
         <v>1.8266957194658318</v>
       </c>
       <c r="AF172" s="6">
-        <v>8.01428008092155E-2</v>
+        <v>0.10610397525387801</v>
       </c>
       <c r="AG172" s="6">
-        <v>6.0295463309626401E-2</v>
+        <v>0.13774068363540101</v>
       </c>
       <c r="AH172" s="6">
-        <v>3.7543486063486599E-2</v>
+        <v>0.101419489826098</v>
       </c>
       <c r="AI172" s="6">
-        <v>6.8304457724111395E-2</v>
+        <v>0.10856392130584</v>
       </c>
       <c r="AJ172" s="6">
-        <v>4.6118007262963702E-2</v>
+        <v>5.1262571048062901E-2</v>
       </c>
       <c r="AK172" s="6">
-        <v>5.6905698594763299E-2</v>
+        <v>0.106112338588777</v>
       </c>
       <c r="AL172" s="6"/>
       <c r="AM172" s="6"/>
@@ -20632,22 +20632,22 @@
         <v>1.7881526975653372</v>
       </c>
       <c r="AF173" s="6">
-        <v>8.0454203533189605E-2</v>
+        <v>0.106239991617348</v>
       </c>
       <c r="AG173" s="6">
-        <v>6.0980015179271402E-2</v>
+        <v>0.139834271201984</v>
       </c>
       <c r="AH173" s="6">
-        <v>3.8262160930226302E-2</v>
+        <v>0.10513334685656001</v>
       </c>
       <c r="AI173" s="6">
-        <v>7.0482611978192999E-2</v>
+        <v>0.111664804872945</v>
       </c>
       <c r="AJ173" s="6">
-        <v>4.5883037969168997E-2</v>
+        <v>5.10120129690457E-2</v>
       </c>
       <c r="AK173" s="6">
-        <v>5.7779070923571797E-2</v>
+        <v>0.108268069756813</v>
       </c>
       <c r="AL173" s="6"/>
       <c r="AM173" s="6"/>
@@ -20748,22 +20748,22 @@
         <v>2.1947699042637936</v>
       </c>
       <c r="AF174" s="6">
-        <v>8.0579410925430806E-2</v>
+        <v>0.106161920404967</v>
       </c>
       <c r="AG174" s="6">
-        <v>6.1221760377788897E-2</v>
+        <v>0.14049319433729501</v>
       </c>
       <c r="AH174" s="6">
-        <v>3.8055135892091703E-2</v>
+        <v>0.104795266870979</v>
       </c>
       <c r="AI174" s="6">
-        <v>6.9997483068301405E-2</v>
+        <v>0.110512411986197</v>
       </c>
       <c r="AJ174" s="6">
-        <v>4.5772078120310901E-2</v>
+        <v>5.0864818330795099E-2</v>
       </c>
       <c r="AK174" s="6">
-        <v>5.7672755972154301E-2</v>
+        <v>0.10803825431616899</v>
       </c>
       <c r="AL174" s="6"/>
       <c r="AM174" s="6"/>
@@ -20864,22 +20864,22 @@
         <v>2.2791609796911416</v>
       </c>
       <c r="AF175" s="6">
-        <v>8.07218894481741E-2</v>
+        <v>0.106110321699998</v>
       </c>
       <c r="AG175" s="6">
-        <v>6.1539532890125197E-2</v>
+        <v>0.141363390573958</v>
       </c>
       <c r="AH175" s="6">
-        <v>3.8399584462286598E-2</v>
+        <v>0.10679898925741201</v>
       </c>
       <c r="AI175" s="6">
-        <v>7.0344186498531705E-2</v>
+        <v>0.110242074679541</v>
       </c>
       <c r="AJ175" s="6">
-        <v>4.56444157657813E-2</v>
+        <v>5.0715086360549201E-2</v>
       </c>
       <c r="AK175" s="6">
-        <v>5.7925551620030998E-2</v>
+        <v>0.10866144801520999</v>
       </c>
       <c r="AL175" s="6"/>
       <c r="AM175" s="6"/>
@@ -20980,22 +20980,22 @@
         <v>1.4294968863346469</v>
       </c>
       <c r="AF176" s="6">
-        <v>8.0814646871261303E-2</v>
+        <v>0.10600881459082601</v>
       </c>
       <c r="AG176" s="6">
-        <v>6.1747571910271103E-2</v>
+        <v>0.14186041952523901</v>
       </c>
       <c r="AH176" s="6">
-        <v>3.8373101300629299E-2</v>
+        <v>0.107205025496784</v>
       </c>
       <c r="AI176" s="6">
-        <v>6.99806523334046E-2</v>
+        <v>0.109377374924482</v>
       </c>
       <c r="AJ176" s="6">
-        <v>4.55618371126763E-2</v>
+        <v>5.0611108147633602E-2</v>
       </c>
       <c r="AK176" s="6">
-        <v>5.7887525520204201E-2</v>
+        <v>0.108650569072976</v>
       </c>
       <c r="AL176" s="6"/>
       <c r="AM176" s="6"/>
@@ -21096,22 +21096,22 @@
         <v>2.1627028623058209</v>
       </c>
       <c r="AF177" s="6">
-        <v>8.0812052508151405E-2</v>
+        <v>0.105831030036275</v>
       </c>
       <c r="AG177" s="6">
-        <v>6.1836751335269703E-2</v>
+        <v>0.14204606223564201</v>
       </c>
       <c r="AH177" s="6">
-        <v>3.8400608902145299E-2</v>
+        <v>0.107769763316932</v>
       </c>
       <c r="AI177" s="6">
-        <v>7.0035882937100002E-2</v>
+        <v>0.10916657691918701</v>
       </c>
       <c r="AJ177" s="6">
-        <v>4.5574424564569303E-2</v>
+        <v>5.0588084169235298E-2</v>
       </c>
       <c r="AK177" s="6">
-        <v>5.7931836159258801E-2</v>
+        <v>0.108760693571599</v>
       </c>
       <c r="AL177" s="6"/>
       <c r="AM177" s="6"/>
@@ -21212,22 +21212,22 @@
         <v>2.8366527901891203</v>
       </c>
       <c r="AF178" s="6">
-        <v>8.0668024892420101E-2</v>
+        <v>0.105498022319631</v>
       </c>
       <c r="AG178" s="6">
-        <v>6.1512803736921598E-2</v>
+        <v>0.14097485136537999</v>
       </c>
       <c r="AH178" s="6">
-        <v>3.8131412372316702E-2</v>
+        <v>0.106909703615017</v>
       </c>
       <c r="AI178" s="6">
-        <v>6.8091420491566398E-2</v>
+        <v>0.106201924440019</v>
       </c>
       <c r="AJ178" s="6">
-        <v>4.5428385113202803E-2</v>
+        <v>5.0363937363823101E-2</v>
       </c>
       <c r="AK178" s="6">
-        <v>5.7292718810659102E-2</v>
+        <v>0.107523794136692</v>
       </c>
       <c r="AL178" s="6"/>
       <c r="AM178" s="6"/>
@@ -21328,22 +21328,22 @@
         <v>1.9765206556776604</v>
       </c>
       <c r="AF179" s="6">
-        <v>8.03600401472708E-2</v>
+        <v>0.105015949890887</v>
       </c>
       <c r="AG179" s="6">
-        <v>6.0825811140622299E-2</v>
+        <v>0.13895019627942501</v>
       </c>
       <c r="AH179" s="6">
-        <v>3.7475771121948102E-2</v>
+        <v>0.10502026951594901</v>
       </c>
       <c r="AI179" s="6">
-        <v>6.5078064660100798E-2</v>
+        <v>0.10136965681575499</v>
       </c>
       <c r="AJ179" s="6">
-        <v>4.5501876021279801E-2</v>
+        <v>5.0320147419351799E-2</v>
       </c>
       <c r="AK179" s="6">
-        <v>5.6218126299547803E-2</v>
+        <v>0.10541166570417899</v>
       </c>
       <c r="AL179" s="6"/>
       <c r="AM179" s="6"/>
@@ -21444,22 +21444,22 @@
         <v>1.5554177048553441</v>
       </c>
       <c r="AF180" s="6">
-        <v>8.1162502359593505E-2</v>
+        <v>0.106120776824028</v>
       </c>
       <c r="AG180" s="6">
-        <v>6.3309355185796695E-2</v>
+        <v>0.145749534144473</v>
       </c>
       <c r="AH180" s="6">
-        <v>3.7741219463816797E-2</v>
+        <v>0.10786835857456099</v>
       </c>
       <c r="AI180" s="6">
-        <v>6.5976747110672307E-2</v>
+        <v>0.102717753068715</v>
       </c>
       <c r="AJ180" s="6">
-        <v>4.57313929253459E-2</v>
+        <v>5.0482828632075302E-2</v>
       </c>
       <c r="AK180" s="6">
-        <v>5.72549184592984E-2</v>
+        <v>0.108293191020902</v>
       </c>
       <c r="AL180" s="6"/>
       <c r="AM180" s="6"/>
@@ -21560,22 +21560,22 @@
         <v>2.6648568901471492</v>
       </c>
       <c r="AF181" s="6">
-        <v>8.0780784499424302E-2</v>
+        <v>0.105578810589933</v>
       </c>
       <c r="AG181" s="6">
-        <v>6.3489337422530406E-2</v>
+        <v>0.147550921770527</v>
       </c>
       <c r="AH181" s="6">
-        <v>3.8574150760377901E-2</v>
+        <v>0.11225143750225999</v>
       </c>
       <c r="AI181" s="6">
-        <v>6.7112816571034503E-2</v>
+        <v>0.104261198195963</v>
       </c>
       <c r="AJ181" s="6">
-        <v>4.6017127813934099E-2</v>
+        <v>5.0675914568426003E-2</v>
       </c>
       <c r="AK181" s="6">
-        <v>5.77832612720071E-2</v>
+        <v>0.110212690836378</v>
       </c>
       <c r="AL181" s="6"/>
       <c r="AM181" s="6"/>
@@ -21676,22 +21676,22 @@
         <v>2.3096726271411683</v>
       </c>
       <c r="AF182" s="6">
-        <v>8.0472480166973101E-2</v>
+        <v>0.105090219800305</v>
       </c>
       <c r="AG182" s="6">
-        <v>6.2767639032851097E-2</v>
+        <v>0.14490152421003899</v>
       </c>
       <c r="AH182" s="6">
-        <v>3.80858308139801E-2</v>
+        <v>0.110292898485623</v>
       </c>
       <c r="AI182" s="6">
-        <v>6.27858902533278E-2</v>
+        <v>9.8397461980715903E-2</v>
       </c>
       <c r="AJ182" s="6">
-        <v>4.1679319103731398E-2</v>
+        <v>4.7411623102624499E-2</v>
       </c>
       <c r="AK182" s="6">
-        <v>5.5834974202172698E-2</v>
+        <v>0.107220918323553</v>
       </c>
       <c r="AL182" s="6"/>
       <c r="AM182" s="6"/>
@@ -21792,22 +21792,22 @@
         <v>3.1738291117644479</v>
       </c>
       <c r="AF183" s="6">
-        <v>7.9880723731316106E-2</v>
+        <v>0.104358188429117</v>
       </c>
       <c r="AG183" s="6">
-        <v>6.1644988445636803E-2</v>
+        <v>0.141356531992609</v>
       </c>
       <c r="AH183" s="6">
-        <v>3.9114361190376597E-2</v>
+        <v>0.115392733476419</v>
       </c>
       <c r="AI183" s="6">
-        <v>6.4619863317197199E-2</v>
+        <v>0.101451973859983</v>
       </c>
       <c r="AJ183" s="6">
-        <v>4.2101901949670499E-2</v>
+        <v>4.7936493984922203E-2</v>
       </c>
       <c r="AK183" s="6">
-        <v>5.6238456627314103E-2</v>
+        <v>0.10836996872579201</v>
       </c>
       <c r="AL183" s="6"/>
       <c r="AM183" s="6"/>
@@ -21908,22 +21908,22 @@
         <v>2.1488358405154173</v>
       </c>
       <c r="AF184" s="6">
-        <v>7.9426914186538106E-2</v>
+        <v>0.103802679359248</v>
       </c>
       <c r="AG184" s="6">
-        <v>6.0610203094502497E-2</v>
+        <v>0.138309562124519</v>
       </c>
       <c r="AH184" s="6">
-        <v>3.8293627913307697E-2</v>
+        <v>0.111568590524645</v>
       </c>
       <c r="AI184" s="6">
-        <v>5.8989094737606801E-2</v>
+        <v>9.3763616706930494E-2</v>
       </c>
       <c r="AJ184" s="6">
-        <v>4.1256113810779101E-2</v>
+        <v>4.7347254969049603E-2</v>
       </c>
       <c r="AK184" s="6">
-        <v>5.4274821825654601E-2</v>
+        <v>0.104741898013635</v>
       </c>
       <c r="AL184" s="6"/>
       <c r="AM184" s="6"/>
@@ -22024,22 +22024,22 @@
         <v>1.7192872763967415</v>
       </c>
       <c r="AF185" s="6">
-        <v>8.0397968212396295E-2</v>
+        <v>0.10453327888564</v>
       </c>
       <c r="AG185" s="6">
-        <v>6.3675037940098295E-2</v>
+        <v>0.14634192647353</v>
       </c>
       <c r="AH185" s="6">
-        <v>3.8637014275529603E-2</v>
+        <v>0.11474830804684</v>
       </c>
       <c r="AI185" s="6">
-        <v>5.9905455891433798E-2</v>
+        <v>9.5768602777015599E-2</v>
       </c>
       <c r="AJ185" s="6">
-        <v>4.1486606053399697E-2</v>
+        <v>4.7724469695091302E-2</v>
       </c>
       <c r="AK185" s="6">
-        <v>5.5505823987260297E-2</v>
+        <v>0.10814268576059601</v>
       </c>
       <c r="AL185" s="6"/>
       <c r="AM185" s="6"/>
@@ -22140,22 +22140,22 @@
         <v>2.7486993518014202</v>
       </c>
       <c r="AF186" s="6">
-        <v>7.9875471642579798E-2</v>
+        <v>0.103977980391737</v>
       </c>
       <c r="AG186" s="6">
-        <v>6.3942796884327704E-2</v>
+        <v>0.14695273515073201</v>
       </c>
       <c r="AH186" s="6">
-        <v>3.9835979147736303E-2</v>
+        <v>0.120491250865675</v>
       </c>
       <c r="AI186" s="6">
-        <v>6.1209037135041701E-2</v>
+        <v>9.8182235837423804E-2</v>
       </c>
       <c r="AJ186" s="6">
-        <v>4.1808553709429597E-2</v>
+        <v>4.81526394383801E-2</v>
       </c>
       <c r="AK186" s="6">
-        <v>5.61807068972629E-2</v>
+        <v>0.110324566358216</v>
       </c>
       <c r="AL186" s="6"/>
       <c r="AM186" s="6"/>
@@ -22256,22 +22256,22 @@
         <v>1.6613507142512418</v>
       </c>
       <c r="AF187" s="6">
-        <v>7.9509723460219395E-2</v>
+        <v>0.103544289570751</v>
       </c>
       <c r="AG187" s="6">
-        <v>6.3056539628857197E-2</v>
+        <v>0.143923623370211</v>
       </c>
       <c r="AH187" s="6">
-        <v>3.9151467106350299E-2</v>
+        <v>0.11646361962665799</v>
       </c>
       <c r="AI187" s="6">
-        <v>5.70881486498147E-2</v>
+        <v>9.2864294385810495E-2</v>
       </c>
       <c r="AJ187" s="6">
-        <v>4.11598645927959E-2</v>
+        <v>4.7867478514824403E-2</v>
       </c>
       <c r="AK187" s="6">
-        <v>5.4672694272080297E-2</v>
+        <v>0.10722589058149599</v>
       </c>
       <c r="AL187" s="6"/>
       <c r="AM187" s="6"/>
@@ -22372,22 +22372,22 @@
         <v>1.9594839504094352</v>
       </c>
       <c r="AF188" s="6">
-        <v>8.0382025205115504E-2</v>
+        <v>0.1045023661895</v>
       </c>
       <c r="AG188" s="6">
-        <v>6.6951214202603596E-2</v>
+        <v>0.15434571965753999</v>
       </c>
       <c r="AH188" s="6">
-        <v>3.9684186415749202E-2</v>
+        <v>0.120323771165067</v>
       </c>
       <c r="AI188" s="6">
-        <v>5.81687096738163E-2</v>
+        <v>9.5241950451970495E-2</v>
       </c>
       <c r="AJ188" s="6">
-        <v>4.1444456415077997E-2</v>
+        <v>4.8260120715205697E-2</v>
       </c>
       <c r="AK188" s="6">
-        <v>5.61957083575449E-2</v>
+        <v>0.11149808575556901</v>
       </c>
       <c r="AL188" s="6"/>
       <c r="AM188" s="6"/>
@@ -22488,22 +22488,22 @@
         <v>2.7561479170152836</v>
       </c>
       <c r="AF189" s="6">
-        <v>7.9951181711287594E-2</v>
+        <v>0.10396467371712</v>
       </c>
       <c r="AG189" s="6">
-        <v>6.5844167733616593E-2</v>
+        <v>0.149930129860253</v>
       </c>
       <c r="AH189" s="6">
-        <v>3.9778673312583702E-2</v>
+        <v>0.12052829931965101</v>
       </c>
       <c r="AI189" s="6">
-        <v>5.93514928615924E-2</v>
+        <v>9.7885163142824805E-2</v>
       </c>
       <c r="AJ189" s="6">
-        <v>4.1749689903638101E-2</v>
+        <v>4.8644477623594903E-2</v>
       </c>
       <c r="AK189" s="6">
-        <v>5.6211398793055603E-2</v>
+        <v>0.11106244537498899</v>
       </c>
       <c r="AL189" s="6"/>
       <c r="AM189" s="6"/>
@@ -22604,22 +22604,22 @@
         <v>2.1124407643469567</v>
       </c>
       <c r="AF190" s="6">
-        <v>7.9482648323929303E-2</v>
+        <v>0.10342593839464299</v>
       </c>
       <c r="AG190" s="6">
-        <v>6.4660011387799796E-2</v>
+        <v>0.145884771393437</v>
       </c>
       <c r="AH190" s="6">
-        <v>3.8875913712250403E-2</v>
+        <v>0.11554901943585601</v>
       </c>
       <c r="AI190" s="6">
-        <v>5.4632205494705398E-2</v>
+        <v>9.1102541054804906E-2</v>
       </c>
       <c r="AJ190" s="6">
-        <v>4.1188019465345498E-2</v>
+        <v>4.8206438593470902E-2</v>
       </c>
       <c r="AK190" s="6">
-        <v>5.44222359954806E-2</v>
+        <v>0.10709457869344501</v>
       </c>
       <c r="AL190" s="6"/>
       <c r="AM190" s="6"/>
@@ -22720,22 +22720,22 @@
         <v>1.6767802651994401</v>
       </c>
       <c r="AF191" s="6">
-        <v>7.9314865141238297E-2</v>
+        <v>0.103267755029561</v>
       </c>
       <c r="AG191" s="6">
-        <v>6.4759801265603101E-2</v>
+        <v>0.145815000325551</v>
       </c>
       <c r="AH191" s="6">
-        <v>3.9254676742733002E-2</v>
+        <v>0.11723038553470699</v>
       </c>
       <c r="AI191" s="6">
-        <v>5.4981448030965503E-2</v>
+        <v>9.2553218241661697E-2</v>
       </c>
       <c r="AJ191" s="6">
-        <v>4.12874718399939E-2</v>
+        <v>4.8422956286286699E-2</v>
       </c>
       <c r="AK191" s="6">
-        <v>5.4624160172522598E-2</v>
+        <v>0.10785588301535</v>
       </c>
       <c r="AL191" s="6"/>
       <c r="AM191" s="6"/>
@@ -22836,22 +22836,22 @@
         <v>2.0365320511899654</v>
       </c>
       <c r="AF192" s="6">
-        <v>7.9106123977313494E-2</v>
+        <v>0.103077671513314</v>
       </c>
       <c r="AG192" s="6">
-        <v>6.4648878641357002E-2</v>
+        <v>0.14516438836945</v>
       </c>
       <c r="AH192" s="6">
-        <v>3.9738011935221598E-2</v>
+        <v>0.11933821076534</v>
       </c>
       <c r="AI192" s="6">
-        <v>5.5440583738160201E-2</v>
+        <v>9.4100018351454401E-2</v>
       </c>
       <c r="AJ192" s="6">
-        <v>4.1417196483943E-2</v>
+        <v>4.8651358900965898E-2</v>
       </c>
       <c r="AK192" s="6">
-        <v>5.4825628321552002E-2</v>
+        <v>0.108602906054551</v>
       </c>
       <c r="AL192" s="6"/>
       <c r="AM192" s="6"/>
@@ -22952,22 +22952,22 @@
         <v>-0.31520406547045354</v>
       </c>
       <c r="AF193" s="6">
-        <v>7.9258985572028595E-2</v>
+        <v>0.10325067643048599</v>
       </c>
       <c r="AG193" s="6">
-        <v>6.5034437513101104E-2</v>
+        <v>0.145945223072205</v>
       </c>
       <c r="AH193" s="6">
-        <v>3.9726891224465398E-2</v>
+        <v>0.118873235568692</v>
       </c>
       <c r="AI193" s="6">
-        <v>5.5048942109866099E-2</v>
+        <v>9.4147953549233498E-2</v>
       </c>
       <c r="AJ193" s="6">
-        <v>4.1307027522040803E-2</v>
+        <v>4.8658723942571397E-2</v>
       </c>
       <c r="AK193" s="6">
-        <v>5.4829874019229501E-2</v>
+        <v>0.108710103041627</v>
       </c>
       <c r="AL193" s="6"/>
       <c r="AM193" s="6"/>
@@ -23068,22 +23068,22 @@
         <v>-4.5480300396860684E-3</v>
       </c>
       <c r="AF194" s="6">
-        <v>5.3232745170238203E-2</v>
+        <v>7.64304726639915E-2</v>
       </c>
       <c r="AG194" s="6">
-        <v>5.4850309317544803E-2</v>
+        <v>0.119118568550038</v>
       </c>
       <c r="AH194" s="6">
-        <v>3.8476070555040598E-2</v>
+        <v>0.108621227857869</v>
       </c>
       <c r="AI194" s="6">
-        <v>5.2480429106448498E-2</v>
+        <v>9.0769742163595804E-2</v>
       </c>
       <c r="AJ194" s="6">
-        <v>4.0569897008095802E-2</v>
+        <v>4.8120258252298598E-2</v>
       </c>
       <c r="AK194" s="6">
-        <v>4.8085545818749201E-2</v>
+        <v>9.5025816623338102E-2</v>
       </c>
       <c r="AL194" s="6"/>
       <c r="AM194" s="6"/>
@@ -23184,22 +23184,22 @@
         <v>1.5629895948606531</v>
       </c>
       <c r="AF195" s="6">
-        <v>5.38004710635685E-2</v>
+        <v>7.8949899432089202E-2</v>
       </c>
       <c r="AG195" s="6">
-        <v>5.1130237063916201E-2</v>
+        <v>0.11962315964841699</v>
       </c>
       <c r="AH195" s="6">
-        <v>3.5079520486250501E-2</v>
+        <v>9.3738578867923902E-2</v>
       </c>
       <c r="AI195" s="6">
-        <v>4.9052489548743902E-2</v>
+        <v>8.6001307462379106E-2</v>
       </c>
       <c r="AJ195" s="6">
-        <v>3.9529406033879E-2</v>
+        <v>4.7332863414777E-2</v>
       </c>
       <c r="AK195" s="6">
-        <v>4.5376943768579502E-2</v>
+        <v>9.0411862680629798E-2</v>
       </c>
       <c r="AL195" s="6"/>
       <c r="AM195" s="6"/>
@@ -23300,22 +23300,22 @@
         <v>1.4169872215187951</v>
       </c>
       <c r="AF196" s="6">
-        <v>5.4693312226561902E-2</v>
+        <v>8.1509239479097606E-2</v>
       </c>
       <c r="AG196" s="6">
-        <v>5.3359265311932302E-2</v>
+        <v>0.129203695840934</v>
       </c>
       <c r="AH196" s="6">
-        <v>3.7620495506761199E-2</v>
+        <v>0.10367404942620601</v>
       </c>
       <c r="AI196" s="6">
-        <v>6.5407091823257393E-2</v>
+        <v>0.115789687389187</v>
       </c>
       <c r="AJ196" s="6">
-        <v>4.9900212592181699E-2</v>
+        <v>5.4178203446836902E-2</v>
       </c>
       <c r="AK196" s="6">
-        <v>5.1950453658565099E-2</v>
+        <v>0.10346209461184</v>
       </c>
       <c r="AL196" s="6"/>
       <c r="AM196" s="6"/>
@@ -23416,22 +23416,22 @@
         <v>2.4841632440153916</v>
       </c>
       <c r="AF197" s="6">
-        <v>5.5610293120210999E-2</v>
+        <v>8.4008180881055397E-2</v>
       </c>
       <c r="AG197" s="6">
-        <v>5.5794257065301001E-2</v>
+        <v>0.13947336729231699</v>
       </c>
       <c r="AH197" s="6">
-        <v>3.7386479049407298E-2</v>
+        <v>0.120774516391744</v>
       </c>
       <c r="AI197" s="6">
-        <v>5.9607950599926803E-2</v>
+        <v>0.10925734590464101</v>
       </c>
       <c r="AJ197" s="6">
-        <v>4.8115718133208099E-2</v>
+        <v>5.2528545836638803E-2</v>
       </c>
       <c r="AK197" s="6">
-        <v>5.0962413212584802E-2</v>
+        <v>0.108969652940896</v>
       </c>
       <c r="AL197" s="6"/>
       <c r="AM197" s="6"/>
@@ -23532,22 +23532,22 @@
         <v>1.366001726903221</v>
       </c>
       <c r="AF198" s="6">
-        <v>5.6203521872628802E-2</v>
+        <v>8.6268598540529706E-2</v>
       </c>
       <c r="AG198" s="6">
-        <v>5.8732657052723798E-2</v>
+        <v>0.14889267318496699</v>
       </c>
       <c r="AH198" s="6">
-        <v>3.9822876615236397E-2</v>
+        <v>0.133823342465654</v>
       </c>
       <c r="AI198" s="6">
-        <v>8.0566826549739096E-2</v>
+        <v>0.145074324826477</v>
       </c>
       <c r="AJ198" s="6">
-        <v>6.7820069961475701E-2</v>
+        <v>5.5301382949273399E-2</v>
       </c>
       <c r="AK198" s="6">
-        <v>5.9996004387839301E-2</v>
+        <v>0.1233655812236</v>
       </c>
       <c r="AL198" s="6"/>
       <c r="AM198" s="6"/>
@@ -23648,22 +23648,22 @@
         <v>1.0760756542293137</v>
       </c>
       <c r="AF199" s="6">
-        <v>5.6790557723670497E-2</v>
+        <v>8.8422675234230794E-2</v>
       </c>
       <c r="AG199" s="6">
-        <v>5.8344615522165598E-2</v>
+        <v>0.15115606301548201</v>
       </c>
       <c r="AH199" s="6">
-        <v>3.63710083211254E-2</v>
+        <v>0.112002170931869</v>
       </c>
       <c r="AI199" s="6">
-        <v>7.3221841379294897E-2</v>
+        <v>0.12917356762460599</v>
       </c>
       <c r="AJ199" s="6">
-        <v>6.5096661652772794E-2</v>
+        <v>5.3706810433077803E-2</v>
       </c>
       <c r="AK199" s="6">
-        <v>5.6800309947623799E-2</v>
+        <v>0.11476847804394801</v>
       </c>
       <c r="AL199" s="6"/>
       <c r="AM199" s="6"/>
@@ -23764,22 +23764,22 @@
         <v>0.6148751967291588</v>
       </c>
       <c r="AF200" s="6">
-        <v>5.7297115406286299E-2</v>
+        <v>9.0334480897383607E-2</v>
       </c>
       <c r="AG200" s="6">
-        <v>6.01191540293666E-2</v>
+        <v>0.156218244878638</v>
       </c>
       <c r="AH200" s="6">
-        <v>3.4065870115521299E-2</v>
+        <v>0.100574259717851</v>
       </c>
       <c r="AI200" s="6">
-        <v>6.7517797975688396E-2</v>
+        <v>0.11865599395588999</v>
       </c>
       <c r="AJ200" s="6">
-        <v>6.3347447710846605E-2</v>
+        <v>5.2493760027116303E-2</v>
       </c>
       <c r="AK200" s="6">
-        <v>5.4986518178371503E-2</v>
+        <v>0.110635101353453</v>
       </c>
       <c r="AL200" s="6"/>
       <c r="AM200" s="6"/>
@@ -23880,22 +23880,22 @@
         <v>1.2624289991201465</v>
       </c>
       <c r="AF201" s="6">
-        <v>5.7752187124328197E-2</v>
+        <v>9.2055884132332705E-2</v>
       </c>
       <c r="AG201" s="6">
-        <v>5.9877924420808498E-2</v>
+        <v>0.149806441963071</v>
       </c>
       <c r="AH201" s="6">
-        <v>3.2020630692987599E-2</v>
+        <v>9.1411307344941004E-2</v>
       </c>
       <c r="AI201" s="6">
-        <v>6.3217914141998899E-2</v>
+        <v>0.111135149706433</v>
       </c>
       <c r="AJ201" s="6">
-        <v>6.1905521285774E-2</v>
+        <v>5.15336307923085E-2</v>
       </c>
       <c r="AK201" s="6">
-        <v>5.3099260358339603E-2</v>
+        <v>0.105101074818143</v>
       </c>
       <c r="AL201" s="6"/>
       <c r="AM201" s="6"/>
@@ -23996,22 +23996,22 @@
         <v>1.7521907302608497</v>
       </c>
       <c r="AF202" s="6">
-        <v>5.81883819356507E-2</v>
+        <v>9.3645985509698895E-2</v>
       </c>
       <c r="AG202" s="6">
-        <v>6.2113542888540201E-2</v>
+        <v>0.156180044131255</v>
       </c>
       <c r="AH202" s="6">
-        <v>3.3433445071491701E-2</v>
+        <v>9.8483841449753903E-2</v>
       </c>
       <c r="AI202" s="6">
-        <v>6.0278907331997603E-2</v>
+        <v>0.10601409443734799</v>
       </c>
       <c r="AJ202" s="6">
-        <v>6.0615219826731397E-2</v>
+        <v>5.0720621495196697E-2</v>
       </c>
       <c r="AK202" s="6">
-        <v>5.3277892583636001E-2</v>
+        <v>0.10733426970894901</v>
       </c>
       <c r="AL202" s="6"/>
       <c r="AM202" s="6"/>
@@ -24112,22 +24112,22 @@
         <v>2.3321882907563207</v>
       </c>
       <c r="AF203" s="6">
-        <v>5.8725569108799898E-2</v>
+        <v>9.5353104806050207E-2</v>
       </c>
       <c r="AG203" s="6">
-        <v>6.5027926625079002E-2</v>
+        <v>0.164302433715242</v>
       </c>
       <c r="AH203" s="6">
-        <v>3.5823797124660099E-2</v>
+        <v>0.110811828954211</v>
       </c>
       <c r="AI203" s="6">
-        <v>6.71309636227269E-2</v>
+        <v>0.11595764781006</v>
       </c>
       <c r="AJ203" s="6">
-        <v>5.8487523647263701E-2</v>
+        <v>4.9923889273876601E-2</v>
       </c>
       <c r="AK203" s="6">
-        <v>5.6351519524640903E-2</v>
+        <v>0.114852579233455</v>
       </c>
       <c r="AL203" s="6"/>
       <c r="AM203" s="6"/>
@@ -24228,22 +24228,22 @@
         <v>1.8219006186775744</v>
       </c>
       <c r="AF204" s="6">
-        <v>5.92305754244681E-2</v>
+        <v>9.6903240410701794E-2</v>
       </c>
       <c r="AG204" s="6">
-        <v>6.7957737059502796E-2</v>
+        <v>0.17190486668553301</v>
       </c>
       <c r="AH204" s="6">
-        <v>3.8380108632785001E-2</v>
+        <v>0.12372346801567</v>
       </c>
       <c r="AI204" s="6">
-        <v>7.4612335425907894E-2</v>
+        <v>0.13069299255745501</v>
       </c>
       <c r="AJ204" s="6">
-        <v>5.72418390592506E-2</v>
+        <v>4.9451272237456302E-2</v>
       </c>
       <c r="AK204" s="6">
-        <v>5.9498380148471801E-2</v>
+        <v>0.12349641243418701</v>
       </c>
       <c r="AL204" s="6"/>
       <c r="AM204" s="6"/>
@@ -24344,22 +24344,22 @@
         <v>1.4231006705795579</v>
       </c>
       <c r="AF205" s="6">
-        <v>5.9933324690917597E-2</v>
+        <v>9.8524789473531396E-2</v>
       </c>
       <c r="AG205" s="6">
-        <v>7.0129658416130905E-2</v>
+        <v>0.17915405933031001</v>
       </c>
       <c r="AH205" s="6">
-        <v>3.5705907026653001E-2</v>
+        <v>0.110817843535698</v>
       </c>
       <c r="AI205" s="6">
-        <v>6.9142848283282599E-2</v>
+        <v>0.119590991775212</v>
       </c>
       <c r="AJ205" s="6">
-        <v>5.5529737508754999E-2</v>
+        <v>4.86452332658713E-2</v>
       </c>
       <c r="AK205" s="6">
-        <v>5.7844981497025903E-2</v>
+        <v>0.119370004673975</v>
       </c>
       <c r="AL205" s="6"/>
       <c r="AM205" s="6"/>
@@ -24460,22 +24460,22 @@
         <v>2.5165602770652384</v>
       </c>
       <c r="AF206" s="6">
-        <v>6.0515409806233399E-2</v>
+        <v>9.9845660558206498E-2</v>
       </c>
       <c r="AG206" s="6">
-        <v>7.1580338084159104E-2</v>
+        <v>0.18408496731843901</v>
       </c>
       <c r="AH206" s="6">
-        <v>3.3670462337762302E-2</v>
+        <v>0.102365952092518</v>
       </c>
       <c r="AI206" s="6">
-        <v>6.53211043349258E-2</v>
+        <v>0.112260977087954</v>
       </c>
       <c r="AJ206" s="6">
-        <v>5.42443392889514E-2</v>
+        <v>4.80935024980612E-2</v>
       </c>
       <c r="AK206" s="6">
-        <v>5.6601519576049399E-2</v>
+        <v>0.11666824627216001</v>
       </c>
       <c r="AL206" s="6"/>
       <c r="AM206" s="6"/>
@@ -24576,22 +24576,22 @@
         <v>1.6507461498299847</v>
       </c>
       <c r="AF207" s="6">
-        <v>6.0936664732783502E-2</v>
+        <v>0.100961337141265</v>
       </c>
       <c r="AG207" s="6">
-        <v>7.4287366915681205E-2</v>
+        <v>0.18946736750474899</v>
       </c>
       <c r="AH207" s="6">
-        <v>3.5064008166466099E-2</v>
+        <v>0.111365882310121</v>
       </c>
       <c r="AI207" s="6">
-        <v>7.7048847326461195E-2</v>
+        <v>0.12587551267720801</v>
       </c>
       <c r="AJ207" s="6">
-        <v>5.52748317059105E-2</v>
+        <v>4.8187386602674097E-2</v>
       </c>
       <c r="AK207" s="6">
-        <v>6.0554159392390103E-2</v>
+        <v>0.123587383902293</v>
       </c>
       <c r="AL207" s="6"/>
       <c r="AM207" s="6"/>
@@ -24692,22 +24692,22 @@
         <v>1.1540622643664733</v>
       </c>
       <c r="AF208" s="6">
-        <v>6.1449938723841899E-2</v>
+        <v>0.102015369425039</v>
       </c>
       <c r="AG208" s="6">
-        <v>7.2440491822673495E-2</v>
+        <v>0.182575618313077</v>
       </c>
       <c r="AH208" s="6">
-        <v>3.32102919750175E-2</v>
+        <v>0.101454257743325</v>
       </c>
       <c r="AI208" s="6">
-        <v>7.3088424393102494E-2</v>
+        <v>0.11848230676751501</v>
       </c>
       <c r="AJ208" s="6">
-        <v>5.4165658992624703E-2</v>
+        <v>4.7766933149784099E-2</v>
       </c>
       <c r="AK208" s="6">
-        <v>5.8561764655205503E-2</v>
+        <v>0.11778295101344601</v>
       </c>
       <c r="AL208" s="6"/>
       <c r="AM208" s="6"/>
@@ -24808,22 +24808,22 @@
         <v>1.7648328335621244</v>
       </c>
       <c r="AF209" s="6">
-        <v>6.19300481853578E-2</v>
+        <v>0.103111626367432</v>
       </c>
       <c r="AG209" s="6">
-        <v>7.2173866127648201E-2</v>
+        <v>0.17634028496812301</v>
       </c>
       <c r="AH209" s="6">
-        <v>3.1447225580492399E-2</v>
+        <v>9.2765281084887699E-2</v>
       </c>
       <c r="AI209" s="6">
-        <v>6.9119837594836905E-2</v>
+        <v>0.11173285570979501</v>
       </c>
       <c r="AJ209" s="6">
-        <v>5.29898697081395E-2</v>
+        <v>4.73295783174962E-2</v>
       </c>
       <c r="AK209" s="6">
-        <v>5.6930934035639702E-2</v>
+        <v>0.11257802265935</v>
       </c>
       <c r="AL209" s="6"/>
       <c r="AM209" s="6"/>
@@ -24924,22 +24924,22 @@
         <v>1.5595450080951423</v>
       </c>
       <c r="AF210" s="6">
-        <v>6.2473073993781901E-2</v>
+        <v>0.104262876304133</v>
       </c>
       <c r="AG210" s="6">
-        <v>7.5563882419085099E-2</v>
+        <v>0.18365831646026501</v>
       </c>
       <c r="AH210" s="6">
-        <v>3.3454505709544599E-2</v>
+        <v>0.10277163632535601</v>
       </c>
       <c r="AI210" s="6">
-        <v>6.7759877227744902E-2</v>
+        <v>0.10903437405142</v>
       </c>
       <c r="AJ210" s="6">
-        <v>5.17477800331652E-2</v>
+        <v>4.6872434328914699E-2</v>
       </c>
       <c r="AK210" s="6">
-        <v>5.7972691795506501E-2</v>
+        <v>0.11637727128302899</v>
       </c>
       <c r="AL210" s="6"/>
       <c r="AM210" s="6"/>
@@ -25040,22 +25040,22 @@
         <v>1.1270571978375443</v>
       </c>
       <c r="AF211" s="6">
-        <v>6.3030634889838497E-2</v>
+        <v>0.105160881621917</v>
       </c>
       <c r="AG211" s="6">
-        <v>7.8160340013291002E-2</v>
+        <v>0.18887622862557299</v>
       </c>
       <c r="AH211" s="6">
-        <v>3.2486395133944197E-2</v>
+        <v>9.9393704534268004E-2</v>
       </c>
       <c r="AI211" s="6">
-        <v>6.4589801950295095E-2</v>
+        <v>0.104154796950606</v>
       </c>
       <c r="AJ211" s="6">
-        <v>5.0769478123852699E-2</v>
+        <v>4.6570383954446598E-2</v>
       </c>
       <c r="AK211" s="6">
-        <v>5.7495689880734599E-2</v>
+        <v>0.115602332988752</v>
       </c>
       <c r="AL211" s="6"/>
       <c r="AM211" s="6"/>
@@ -25156,22 +25156,22 @@
         <v>1.570304901288111</v>
       </c>
       <c r="AF212" s="6">
-        <v>6.36432627356215E-2</v>
+        <v>0.106088890153871</v>
       </c>
       <c r="AG212" s="6">
-        <v>7.9278207950968696E-2</v>
+        <v>0.189871709385911</v>
       </c>
       <c r="AH212" s="6">
-        <v>3.0760810494973E-2</v>
+        <v>9.1894023527111304E-2</v>
       </c>
       <c r="AI212" s="6">
-        <v>6.14992227299496E-2</v>
+        <v>9.9692182648804903E-2</v>
       </c>
       <c r="AJ212" s="6">
-        <v>4.9768877932817097E-2</v>
+        <v>4.62632257062809E-2</v>
       </c>
       <c r="AK212" s="6">
-        <v>5.6469159417016003E-2</v>
+        <v>0.112857119628422</v>
       </c>
       <c r="AL212" s="6"/>
       <c r="AM212" s="6"/>
@@ -25272,22 +25272,22 @@
         <v>1.7202449082450499</v>
       </c>
       <c r="AF213" s="6">
-        <v>6.4083855590803304E-2</v>
+        <v>0.106813900570182</v>
       </c>
       <c r="AG213" s="6">
-        <v>8.2336958553449704E-2</v>
+        <v>0.19459631993203699</v>
       </c>
       <c r="AH213" s="6">
-        <v>3.1325617870631199E-2</v>
+        <v>9.7285899415356203E-2</v>
       </c>
       <c r="AI213" s="6">
-        <v>5.9126185939491899E-2</v>
+        <v>9.6793538076291902E-2</v>
       </c>
       <c r="AJ213" s="6">
-        <v>4.8951084466305701E-2</v>
+        <v>4.60641905359103E-2</v>
       </c>
       <c r="AK213" s="6">
-        <v>5.6730350893416798E-2</v>
+        <v>0.114766935354973</v>
       </c>
       <c r="AL213" s="6"/>
       <c r="AM213" s="6"/>
@@ -25388,22 +25388,22 @@
         <v>1.2618727644106542</v>
       </c>
       <c r="AF214" s="6">
-        <v>6.4534936753316993E-2</v>
+        <v>0.107337900456438</v>
       </c>
       <c r="AG214" s="6">
-        <v>8.4788127059540294E-2</v>
+        <v>0.19770208050785601</v>
       </c>
       <c r="AH214" s="6">
-        <v>3.1876517229236401E-2</v>
+        <v>0.100169891821595</v>
       </c>
       <c r="AI214" s="6">
-        <v>5.73398461199967E-2</v>
+        <v>9.3713377061061795E-2</v>
       </c>
       <c r="AJ214" s="6">
-        <v>4.8301815929564E-2</v>
+        <v>4.5963802758234099E-2</v>
       </c>
       <c r="AK214" s="6">
-        <v>5.70031614940417E-2</v>
+        <v>0.11574964716132199</v>
       </c>
       <c r="AL214" s="6"/>
       <c r="AM214" s="6"/>
@@ -25504,22 +25504,22 @@
         <v>1.7423798552176351</v>
       </c>
       <c r="AF215" s="6">
-        <v>6.5190661425212099E-2</v>
+        <v>0.108167288057875</v>
       </c>
       <c r="AG215" s="6">
-        <v>8.7176254840878903E-2</v>
+        <v>0.202159662781913</v>
       </c>
       <c r="AH215" s="6">
-        <v>3.03339061468361E-2</v>
+        <v>9.41444366331987E-2</v>
       </c>
       <c r="AI215" s="6">
-        <v>5.4866401966418198E-2</v>
+        <v>9.0779282504550696E-2</v>
       </c>
       <c r="AJ215" s="6">
-        <v>4.7409495965668902E-2</v>
+        <v>4.5721723430819303E-2</v>
       </c>
       <c r="AK215" s="6">
-        <v>5.6470342683543798E-2</v>
+        <v>0.114424351200418</v>
       </c>
       <c r="AL215" s="6"/>
       <c r="AM215" s="6"/>
@@ -25620,22 +25620,22 @@
         <v>1.4999625873922895</v>
       </c>
       <c r="AF216" s="6">
-        <v>6.5664464792294694E-2</v>
+        <v>0.108621751171498</v>
       </c>
       <c r="AG216" s="6">
-        <v>8.9913667524238697E-2</v>
+        <v>0.20512631645813301</v>
       </c>
       <c r="AH216" s="6">
-        <v>3.1423392420216398E-2</v>
+        <v>0.102858396623718</v>
       </c>
       <c r="AI216" s="6">
-        <v>5.5232827562307497E-2</v>
+        <v>9.2806573632466194E-2</v>
       </c>
       <c r="AJ216" s="6">
-        <v>4.6805739457222099E-2</v>
+        <v>4.5652709628189903E-2</v>
       </c>
       <c r="AK216" s="6">
-        <v>5.7481562719132198E-2</v>
+        <v>0.118159694352357</v>
       </c>
       <c r="AL216" s="6"/>
       <c r="AM216" s="6"/>
@@ -25736,22 +25736,22 @@
         <v>1.082822661978966</v>
       </c>
       <c r="AF217" s="6">
-        <v>6.5965070760341596E-2</v>
+        <v>0.108744244642747</v>
       </c>
       <c r="AG217" s="6">
-        <v>9.1402957961566098E-2</v>
+        <v>0.203986303650003</v>
       </c>
       <c r="AH217" s="6">
-        <v>3.08570319620683E-2</v>
+        <v>0.100310479532356</v>
       </c>
       <c r="AI217" s="6">
-        <v>5.42125057365936E-2</v>
+        <v>9.2012219635539502E-2</v>
       </c>
       <c r="AJ217" s="6">
-        <v>4.6437553745306399E-2</v>
+        <v>4.5725411061304497E-2</v>
       </c>
       <c r="AK217" s="6">
-        <v>5.7396261717589402E-2</v>
+        <v>0.117015653757685</v>
       </c>
       <c r="AL217" s="6"/>
       <c r="AM217" s="6"/>
@@ -25852,22 +25852,22 @@
         <v>0.66766647422866754</v>
       </c>
       <c r="AF218" s="6">
-        <v>6.6264918826050498E-2</v>
+        <v>0.108700768854105</v>
       </c>
       <c r="AG218" s="6">
-        <v>9.0096304625338297E-2</v>
+        <v>0.188472656369573</v>
       </c>
       <c r="AH218" s="6">
-        <v>3.0111016721747801E-2</v>
+        <v>9.6553146256221703E-2</v>
       </c>
       <c r="AI218" s="6">
-        <v>5.32391991358247E-2</v>
+        <v>9.1595179995945394E-2</v>
       </c>
       <c r="AJ218" s="6">
-        <v>4.6079795832500603E-2</v>
+        <v>4.57952076479098E-2</v>
       </c>
       <c r="AK218" s="6">
-        <v>5.6644915619309698E-2</v>
+        <v>0.112335504903969</v>
       </c>
       <c r="AL218" s="6"/>
       <c r="AM218" s="6"/>
@@ -25968,22 +25968,22 @@
         <v>1.7786890783948905</v>
       </c>
       <c r="AF219" s="6">
-        <v>6.6465685159976903E-2</v>
+        <v>0.108638234219209</v>
       </c>
       <c r="AG219" s="6">
-        <v>8.9886882312240596E-2</v>
+        <v>0.18465371041630099</v>
       </c>
       <c r="AH219" s="6">
-        <v>2.96370112686862E-2</v>
+        <v>9.4699914662808901E-2</v>
       </c>
       <c r="AI219" s="6">
-        <v>5.2615346604980899E-2</v>
+        <v>9.1637740215801206E-2</v>
       </c>
       <c r="AJ219" s="6">
-        <v>4.5846609834639201E-2</v>
+        <v>4.5935098151412598E-2</v>
       </c>
       <c r="AK219" s="6">
-        <v>5.6304882809689899E-2</v>
+        <v>0.11094443166953</v>
       </c>
       <c r="AL219" s="6"/>
       <c r="AM219" s="6"/>
@@ -26084,22 +26084,22 @@
         <v>1.2848963631856947</v>
       </c>
       <c r="AF220" s="6">
-        <v>6.6638182733719395E-2</v>
+        <v>0.10853152325014399</v>
       </c>
       <c r="AG220" s="6">
-        <v>9.0890206726431305E-2</v>
+        <v>0.183503465818387</v>
       </c>
       <c r="AH220" s="6">
-        <v>2.9882544720663502E-2</v>
+        <v>9.7057920469292694E-2</v>
       </c>
       <c r="AI220" s="6">
-        <v>5.4728811431340903E-2</v>
+        <v>9.6251109514944894E-2</v>
       </c>
       <c r="AJ220" s="6">
-        <v>4.6288213193448703E-2</v>
+        <v>4.6819739951833E-2</v>
       </c>
       <c r="AK220" s="6">
-        <v>5.7184078254065199E-2</v>
+        <v>0.112449278913132</v>
       </c>
       <c r="AL220" s="6"/>
       <c r="AM220" s="6"/>
@@ -26200,22 +26200,22 @@
         <v>0.99590919540268885</v>
       </c>
       <c r="AF221" s="6">
-        <v>6.6840035418285607E-2</v>
+        <v>0.10847604525980301</v>
       </c>
       <c r="AG221" s="6">
-        <v>9.1679276586314001E-2</v>
+        <v>0.18083538522030901</v>
       </c>
       <c r="AH221" s="6">
-        <v>2.94777533642239E-2</v>
+        <v>9.5250954444801694E-2</v>
       </c>
       <c r="AI221" s="6">
-        <v>5.4076724540839699E-2</v>
+        <v>9.5918172545541594E-2</v>
       </c>
       <c r="AJ221" s="6">
-        <v>4.60532833101761E-2</v>
+        <v>4.6886723111152898E-2</v>
       </c>
       <c r="AK221" s="6">
-        <v>5.7080237657006302E-2</v>
+        <v>0.11126379333478099</v>
       </c>
       <c r="AL221" s="6"/>
       <c r="AM221" s="6"/>
@@ -26316,22 +26316,22 @@
         <v>1.6720951998170364</v>
       </c>
       <c r="AF222" s="6">
-        <v>6.7129269834370703E-2</v>
+        <v>0.108557470686082</v>
       </c>
       <c r="AG222" s="6">
-        <v>9.2528761149105104E-2</v>
+        <v>0.17983089530669</v>
       </c>
       <c r="AH222" s="6">
-        <v>2.8871781150136899E-2</v>
+        <v>9.3292507622618495E-2</v>
       </c>
       <c r="AI222" s="6">
-        <v>5.31747354262746E-2</v>
+        <v>9.4919082401003496E-2</v>
       </c>
       <c r="AJ222" s="6">
-        <v>4.5723882161484798E-2</v>
+        <v>4.6883214368024298E-2</v>
       </c>
       <c r="AK222" s="6">
-        <v>5.68683231887393E-2</v>
+        <v>0.11029101059122</v>
       </c>
       <c r="AL222" s="6"/>
       <c r="AM222" s="6"/>
@@ -26432,22 +26432,22 @@
         <v>2.1878870669183925</v>
       </c>
       <c r="AF223" s="6">
-        <v>6.7404157525546904E-2</v>
+        <v>0.108606202612489</v>
       </c>
       <c r="AG223" s="6">
-        <v>9.4176988190806998E-2</v>
+        <v>0.18024836962643101</v>
       </c>
       <c r="AH223" s="6">
-        <v>2.9390431411902899E-2</v>
+        <v>9.7464101981978093E-2</v>
       </c>
       <c r="AI223" s="6">
-        <v>5.4636589800639797E-2</v>
+        <v>9.8847497113117494E-2</v>
       </c>
       <c r="AJ223" s="6">
-        <v>4.5463898298715999E-2</v>
+        <v>4.6960840975373598E-2</v>
       </c>
       <c r="AK223" s="6">
-        <v>5.7740531627573297E-2</v>
+        <v>0.112439181465449</v>
       </c>
       <c r="AL223" s="6"/>
       <c r="AM223" s="6"/>
@@ -26548,22 +26548,22 @@
         <v>1.7317363171024169</v>
       </c>
       <c r="AF224" s="6">
-        <v>6.7733246648086498E-2</v>
+        <v>0.108729783677273</v>
       </c>
       <c r="AG224" s="6">
-        <v>9.6198999359559098E-2</v>
+        <v>0.18131600364745301</v>
       </c>
       <c r="AH224" s="6">
-        <v>3.0050531678552199E-2</v>
+        <v>0.102294740316254</v>
       </c>
       <c r="AI224" s="6">
-        <v>5.5216713067338198E-2</v>
+        <v>0.10227661710803</v>
       </c>
       <c r="AJ224" s="6">
-        <v>4.5105892742305302E-2</v>
+        <v>4.6946104513897302E-2</v>
       </c>
       <c r="AK224" s="6">
-        <v>5.8523824271441503E-2</v>
+        <v>0.114778911621328</v>
       </c>
       <c r="AL224" s="6"/>
       <c r="AM224" s="6"/>
@@ -26664,22 +26664,22 @@
         <v>1.3757026939757111</v>
       </c>
       <c r="AF225" s="6">
-        <v>6.8011700341814793E-2</v>
+        <v>0.108762151684714</v>
       </c>
       <c r="AG225" s="6">
-        <v>9.66681978168972E-2</v>
+        <v>0.178109726576893</v>
       </c>
       <c r="AH225" s="6">
-        <v>2.9429672592488701E-2</v>
+        <v>9.8798531957090804E-2</v>
       </c>
       <c r="AI225" s="6">
-        <v>5.4346301847207103E-2</v>
+        <v>0.10112492163046501</v>
       </c>
       <c r="AJ225" s="6">
-        <v>4.48103846303088E-2</v>
+        <v>4.6950866474331103E-2</v>
       </c>
       <c r="AK225" s="6">
-        <v>5.8232764549755199E-2</v>
+        <v>0.112861899273132</v>
       </c>
       <c r="AL225" s="6"/>
       <c r="AM225" s="6"/>
@@ -26780,22 +26780,22 @@
         <v>1.8524055397911354</v>
       </c>
       <c r="AF226" s="6">
-        <v>6.8278177314374605E-2</v>
+        <v>0.108769169225053</v>
       </c>
       <c r="AG226" s="6">
-        <v>9.6897456828114306E-2</v>
+        <v>0.17471547567318499</v>
       </c>
       <c r="AH226" s="6">
-        <v>2.8854532820553998E-2</v>
+        <v>9.6494703663268996E-2</v>
       </c>
       <c r="AI226" s="6">
-        <v>5.3546642035370302E-2</v>
+        <v>9.9832870099977003E-2</v>
       </c>
       <c r="AJ226" s="6">
-        <v>4.4534440009522003E-2</v>
+        <v>4.6966547705174999E-2</v>
       </c>
       <c r="AK226" s="6">
-        <v>5.7919413963172801E-2</v>
+        <v>0.11117787086297801</v>
       </c>
       <c r="AL226" s="6"/>
       <c r="AM226" s="6"/>
@@ -26896,22 +26896,22 @@
         <v>1.3352790660718483</v>
       </c>
       <c r="AF227" s="6">
-        <v>6.8550190366921906E-2</v>
+        <v>0.108779060071042</v>
       </c>
       <c r="AG227" s="6">
-        <v>9.8604356569976001E-2</v>
+        <v>0.17522899005213499</v>
       </c>
       <c r="AH227" s="6">
-        <v>2.93617283184235E-2</v>
+        <v>0.100577462577652</v>
       </c>
       <c r="AI227" s="6">
-        <v>5.3492910273798697E-2</v>
+        <v>0.10040311203786501</v>
       </c>
       <c r="AJ227" s="6">
-        <v>4.42591601569177E-2</v>
+        <v>4.6979189480862403E-2</v>
       </c>
       <c r="AK227" s="6">
-        <v>5.84395294152531E-2</v>
+        <v>0.112509243027111</v>
       </c>
       <c r="AL227" s="6"/>
       <c r="AM227" s="6"/>
@@ -27012,22 +27012,22 @@
         <v>1.2070075560622229</v>
       </c>
       <c r="AF228" s="6">
-        <v>6.8711134198766302E-2</v>
+        <v>0.10855373451339401</v>
       </c>
       <c r="AG228" s="6">
-        <v>9.4971587961633602E-2</v>
+        <v>0.16523461619719201</v>
       </c>
       <c r="AH228" s="6">
-        <v>2.8863455845970699E-2</v>
+        <v>9.7974589281577998E-2</v>
       </c>
       <c r="AI228" s="6">
-        <v>5.27587490317665E-2</v>
+        <v>9.9555401574445396E-2</v>
       </c>
       <c r="AJ228" s="6">
-        <v>4.4004738211082098E-2</v>
+        <v>4.7003750182784798E-2</v>
       </c>
       <c r="AK228" s="6">
-        <v>5.7302011387661597E-2</v>
+        <v>0.10929149220659801</v>
       </c>
       <c r="AL228" s="6"/>
       <c r="AM228" s="6"/>
@@ -27128,22 +27128,22 @@
         <v>1.7752058794531678</v>
       </c>
       <c r="AF229" s="6">
-        <v>6.8886443465299693E-2</v>
+        <v>0.108430314052449</v>
       </c>
       <c r="AG229" s="6">
-        <v>9.5985681986903798E-2</v>
+        <v>0.165151583845255</v>
       </c>
       <c r="AH229" s="6">
-        <v>2.8711030724037301E-2</v>
+        <v>9.8295161061214706E-2</v>
       </c>
       <c r="AI229" s="6">
-        <v>5.2269072874653599E-2</v>
+        <v>9.8947691921965897E-2</v>
       </c>
       <c r="AJ229" s="6">
-        <v>4.3832832855186202E-2</v>
+        <v>4.7086142972853802E-2</v>
       </c>
       <c r="AK229" s="6">
-        <v>5.7365535317233901E-2</v>
+        <v>0.109206909456126</v>
       </c>
       <c r="AL229" s="6"/>
       <c r="AM229" s="6"/>
@@ -27244,22 +27244,22 @@
         <v>2.5374757999355069</v>
       </c>
       <c r="AF230" s="6">
-        <v>6.8886986746573606E-2</v>
+        <v>0.108063610055684</v>
       </c>
       <c r="AG230" s="6">
-        <v>9.5988964911136301E-2</v>
+        <v>0.163266101986101</v>
       </c>
       <c r="AH230" s="6">
-        <v>2.8712008710158901E-2</v>
+        <v>9.9301377030844601E-2</v>
       </c>
       <c r="AI230" s="6">
-        <v>5.22701743062274E-2</v>
+        <v>9.9380356117227203E-2</v>
       </c>
       <c r="AJ230" s="6">
-        <v>4.3832309535365203E-2</v>
+        <v>4.7291679032298001E-2</v>
       </c>
       <c r="AK230" s="6">
-        <v>5.7366825994464299E-2</v>
+        <v>0.10911275846492099</v>
       </c>
       <c r="AL230" s="6"/>
       <c r="AM230" s="6"/>
@@ -27360,22 +27360,22 @@
         <v>2.1416492550333288</v>
       </c>
       <c r="AF231" s="6">
-        <v>6.8800818015439497E-2</v>
+        <v>0.107600610769413</v>
       </c>
       <c r="AG231" s="6">
-        <v>9.5469361953215107E-2</v>
+        <v>0.160647699632332</v>
       </c>
       <c r="AH231" s="6">
-        <v>2.8577098855519002E-2</v>
+        <v>9.9343014255118101E-2</v>
       </c>
       <c r="AI231" s="6">
-        <v>5.1591384181281903E-2</v>
+        <v>9.8473654188815193E-2</v>
       </c>
       <c r="AJ231" s="6">
-        <v>4.3843562324325999E-2</v>
+        <v>4.7492705034352899E-2</v>
       </c>
       <c r="AK231" s="6">
-        <v>5.7039965955331902E-2</v>
+        <v>0.108289872761059</v>
       </c>
       <c r="AL231" s="6"/>
       <c r="AM231" s="6"/>
@@ -27476,22 +27476,22 @@
         <v>1.2729760319036387</v>
       </c>
       <c r="AF232" s="6">
-        <v>6.8709925199645097E-2</v>
+        <v>0.10717368753456</v>
       </c>
       <c r="AG232" s="6">
-        <v>9.5251869757475002E-2</v>
+        <v>0.16039146137920099</v>
       </c>
       <c r="AH232" s="6">
-        <v>2.8755643530996099E-2</v>
+        <v>0.101546312250669</v>
       </c>
       <c r="AI232" s="6">
-        <v>5.1835902782309602E-2</v>
+        <v>9.9347944433776106E-2</v>
       </c>
       <c r="AJ232" s="6">
-        <v>4.3931773507847001E-2</v>
+        <v>4.7739858056654497E-2</v>
       </c>
       <c r="AK232" s="6">
-        <v>5.7103317521006398E-2</v>
+        <v>0.109020800856253</v>
       </c>
       <c r="AL232" s="6"/>
       <c r="AM232" s="6"/>
@@ -27592,22 +27592,22 @@
         <v>1.8635476233541226</v>
       </c>
       <c r="AF233" s="6">
-        <v>6.9724782080642894E-2</v>
+        <v>0.107943640187524</v>
       </c>
       <c r="AG233" s="6">
-        <v>9.8377910666931995E-2</v>
+        <v>0.16380806703064099</v>
       </c>
       <c r="AH233" s="6">
-        <v>2.8864748359567701E-2</v>
+        <v>0.103630358885103</v>
       </c>
       <c r="AI233" s="6">
-        <v>5.21663788704127E-2</v>
+        <v>0.100321034141319</v>
       </c>
       <c r="AJ233" s="6">
-        <v>4.4050356091639202E-2</v>
+        <v>4.7994570683851899E-2</v>
       </c>
       <c r="AK233" s="6">
-        <v>5.8058812790219801E-2</v>
+        <v>0.110760594729036</v>
       </c>
       <c r="AL233" s="6"/>
       <c r="AM233" s="6"/>
@@ -27708,22 +27708,22 @@
         <v>1.6011751205105895</v>
       </c>
       <c r="AF234" s="6">
-        <v>6.9709668590793902E-2</v>
+        <v>0.10759069728800499</v>
       </c>
       <c r="AG234" s="6">
-        <v>9.8284816557374796E-2</v>
+        <v>0.16187292370526701</v>
       </c>
       <c r="AH234" s="6">
-        <v>2.88380316070776E-2</v>
+        <v>0.104123244405208</v>
       </c>
       <c r="AI234" s="6">
-        <v>5.2129195901907399E-2</v>
+        <v>0.100482778526451</v>
       </c>
       <c r="AJ234" s="6">
-        <v>4.4064522616899998E-2</v>
+        <v>4.8148162259308097E-2</v>
       </c>
       <c r="AK234" s="6">
-        <v>5.8021085998920502E-2</v>
+        <v>0.11045571606259801</v>
       </c>
       <c r="AL234" s="6"/>
       <c r="AM234" s="6"/>
@@ -27824,22 +27824,22 @@
         <v>1.6863567581214767</v>
       </c>
       <c r="AF235" s="6">
-        <v>6.9667032335025497E-2</v>
+        <v>0.107225889731875</v>
       </c>
       <c r="AG235" s="6">
-        <v>9.8063727317867097E-2</v>
+        <v>0.15992637618122299</v>
       </c>
       <c r="AH235" s="6">
-        <v>2.8898977359022901E-2</v>
+        <v>0.10521613730929601</v>
       </c>
       <c r="AI235" s="6">
-        <v>5.2242561864717998E-2</v>
+        <v>0.101040297836267</v>
       </c>
       <c r="AJ235" s="6">
-        <v>4.4105077857185301E-2</v>
+        <v>4.8315701814233197E-2</v>
       </c>
       <c r="AK235" s="6">
-        <v>5.8017313428081703E-2</v>
+        <v>0.110399665189098</v>
       </c>
       <c r="AL235" s="6"/>
       <c r="AM235" s="6"/>
@@ -27940,22 +27940,22 @@
         <v>1.4827607624205541</v>
       </c>
       <c r="AF236" s="6">
-        <v>6.95358565339151E-2</v>
+        <v>0.106767843243743</v>
       </c>
       <c r="AG236" s="6">
-        <v>9.7262065990726093E-2</v>
+        <v>0.15718671404908799</v>
       </c>
       <c r="AH236" s="6">
-        <v>2.8924830113953401E-2</v>
+        <v>0.105649416343298</v>
       </c>
       <c r="AI236" s="6">
-        <v>5.2594537662902202E-2</v>
+        <v>0.102252469022085</v>
       </c>
       <c r="AJ236" s="6">
-        <v>4.42305476419129E-2</v>
+        <v>4.8538850413922703E-2</v>
       </c>
       <c r="AK236" s="6">
-        <v>5.7930046252190497E-2</v>
+        <v>0.11010287491012299</v>
       </c>
       <c r="AL236" s="6"/>
       <c r="AM236" s="6"/>
@@ -28056,22 +28056,22 @@
         <v>1.4030377167227215</v>
       </c>
       <c r="AF237" s="6">
-        <v>6.9219915842342702E-2</v>
+        <v>0.106094914138796</v>
       </c>
       <c r="AG237" s="6">
-        <v>9.5448117164520105E-2</v>
+        <v>0.15342486490902599</v>
       </c>
       <c r="AH237" s="6">
-        <v>2.9233507891162601E-2</v>
+        <v>0.10911562348364801</v>
       </c>
       <c r="AI237" s="6">
-        <v>5.3463676248334799E-2</v>
+        <v>0.10435234668014</v>
       </c>
       <c r="AJ237" s="6">
-        <v>4.4537563733951603E-2</v>
+        <v>4.8890556021020097E-2</v>
       </c>
       <c r="AK237" s="6">
-        <v>5.7825433990953003E-2</v>
+        <v>0.110584597752566</v>
       </c>
       <c r="AL237" s="6"/>
       <c r="AM237" s="6"/>
@@ -28172,22 +28172,22 @@
         <v>1.7985251251584344</v>
       </c>
       <c r="AF238" s="6">
-        <v>6.8858900794436795E-2</v>
+        <v>0.105411439031145</v>
       </c>
       <c r="AG238" s="6">
-        <v>9.3424139029056497E-2</v>
+        <v>0.149687872047752</v>
       </c>
       <c r="AH238" s="6">
-        <v>2.9600548924718698E-2</v>
+        <v>0.11305967326177099</v>
       </c>
       <c r="AI238" s="6">
-        <v>5.4504960127357102E-2</v>
+        <v>0.106688369477745</v>
       </c>
       <c r="AJ238" s="6">
-        <v>4.4899258573514303E-2</v>
+        <v>4.9261569970108103E-2</v>
       </c>
       <c r="AK238" s="6">
-        <v>5.7731362635918597E-2</v>
+        <v>0.111238497338238</v>
       </c>
       <c r="AL238" s="6"/>
       <c r="AM238" s="6"/>
@@ -28288,22 +28288,22 @@
         <v>-0.75265924520984129</v>
       </c>
       <c r="AF239" s="6">
-        <v>6.9016760190093701E-2</v>
+        <v>0.105471754504169</v>
       </c>
       <c r="AG239" s="6">
-        <v>9.4343550089825007E-2</v>
+        <v>0.1504043822235</v>
       </c>
       <c r="AH239" s="6">
-        <v>2.98779941787581E-2</v>
+        <v>0.115661628187543</v>
       </c>
       <c r="AI239" s="6">
-        <v>5.4222271306921602E-2</v>
+        <v>0.106026989102066</v>
       </c>
       <c r="AJ239" s="6">
-        <v>4.4737232955425497E-2</v>
+        <v>4.91941740936764E-2</v>
       </c>
       <c r="AK239" s="6">
-        <v>5.7953660373401099E-2</v>
+        <v>0.11197421841702</v>
       </c>
       <c r="AL239" s="6"/>
       <c r="AM239" s="6"/>
@@ -28404,22 +28404,22 @@
         <v>2.9641544564512401</v>
       </c>
       <c r="AF240" s="6">
-        <v>2.54201864590657E-2</v>
+        <v>4.3323228461134899E-2</v>
       </c>
       <c r="AG240" s="6">
-        <v>4.9209604500326999E-2</v>
+        <v>8.2634937857699597E-2</v>
       </c>
       <c r="AH240" s="6">
-        <v>2.7507322368911701E-2</v>
+        <v>8.8024371025721304E-2</v>
       </c>
       <c r="AI240" s="6">
-        <v>4.7335073455576998E-2</v>
+        <v>9.2692123728196504E-2</v>
       </c>
       <c r="AJ240" s="6">
-        <v>4.2274321125553301E-2</v>
+        <v>4.7299488500184797E-2</v>
       </c>
       <c r="AK240" s="6">
-        <v>3.9112570033621903E-2</v>
+        <v>7.6675823302368398E-2</v>
       </c>
       <c r="AL240" s="6"/>
       <c r="AM240" s="6"/>
@@ -28520,22 +28520,22 @@
         <v>1.793242944103568</v>
       </c>
       <c r="AF241" s="6">
-        <v>2.5499483119903001E-2</v>
+        <v>4.6115845995379198E-2</v>
       </c>
       <c r="AG241" s="6">
-        <v>5.0148010505945299E-2</v>
+        <v>8.7291830763055703E-2</v>
       </c>
       <c r="AH241" s="6">
-        <v>2.84395031204621E-2</v>
+        <v>9.4128362518056299E-2</v>
       </c>
       <c r="AI241" s="6">
-        <v>5.4891723320398697E-2</v>
+        <v>0.106036747619479</v>
       </c>
       <c r="AJ241" s="6">
-        <v>6.1167316282926598E-2</v>
+        <v>6.1690446544020297E-2</v>
       </c>
       <c r="AK241" s="6">
-        <v>4.3672870924369701E-2</v>
+        <v>8.4976050788264701E-2</v>
       </c>
       <c r="AL241" s="6"/>
       <c r="AM241" s="6"/>
@@ -28636,22 +28636,22 @@
         <v>3.4011855199125307</v>
       </c>
       <c r="AF242" s="6">
-        <v>2.55555424086641E-2</v>
+        <v>4.8845956223843301E-2</v>
       </c>
       <c r="AG242" s="6">
-        <v>5.0829054567335899E-2</v>
+        <v>9.1503356206325603E-2</v>
       </c>
       <c r="AH242" s="6">
-        <v>2.8362510561837199E-2</v>
+        <v>9.8455880180805297E-2</v>
       </c>
       <c r="AI242" s="6">
-        <v>5.3774833207992E-2</v>
+        <v>0.103542712867151</v>
       </c>
       <c r="AJ242" s="6">
-        <v>6.02358182683451E-2</v>
+        <v>6.0277835773850597E-2</v>
       </c>
       <c r="AK242" s="6">
-        <v>4.3439462169849001E-2</v>
+        <v>8.6641496424046699E-2</v>
       </c>
       <c r="AL242" s="6"/>
       <c r="AM242" s="6"/>
@@ -28752,22 +28752,22 @@
         <v>5.6462756680954129</v>
       </c>
       <c r="AF243" s="6">
-        <v>2.5578859881992599E-2</v>
+        <v>5.1470391530728202E-2</v>
       </c>
       <c r="AG243" s="6">
-        <v>5.1116451787233702E-2</v>
+        <v>9.4799149518532702E-2</v>
       </c>
       <c r="AH243" s="6">
-        <v>2.86433220099198E-2</v>
+        <v>0.101009015654123</v>
       </c>
       <c r="AI243" s="6">
-        <v>5.5250181570233502E-2</v>
+        <v>0.108133165516063</v>
       </c>
       <c r="AJ243" s="6">
-        <v>7.1487131561959003E-2</v>
+        <v>6.5596392482302895E-2</v>
       </c>
       <c r="AK243" s="6">
-        <v>4.53560597355879E-2</v>
+        <v>9.0276685462775605E-2</v>
       </c>
       <c r="AL243" s="6"/>
       <c r="AM243" s="6"/>
@@ -28868,22 +28868,22 @@
         <v>4.7188637431982983</v>
       </c>
       <c r="AF244" s="6">
-        <v>2.55583863568727E-2</v>
+        <v>5.3936880499844297E-2</v>
       </c>
       <c r="AG244" s="6">
-        <v>5.0863105438856498E-2</v>
+        <v>9.6866700407973405E-2</v>
       </c>
       <c r="AH244" s="6">
-        <v>2.85430693221147E-2</v>
+        <v>0.100399681988697</v>
       </c>
       <c r="AI244" s="6">
-        <v>5.3068326742762698E-2</v>
+        <v>0.103809283971892</v>
       </c>
       <c r="AJ244" s="6">
-        <v>6.0236734015233197E-2</v>
+        <v>5.8663459351756E-2</v>
       </c>
       <c r="AK244" s="6">
-        <v>4.3349003670419398E-2</v>
+        <v>8.8910855758704901E-2</v>
       </c>
       <c r="AL244" s="6"/>
       <c r="AM244" s="6"/>
@@ -28984,22 +28984,22 @@
         <v>5.1696142914430254</v>
       </c>
       <c r="AF245" s="6">
-        <v>2.5527149123120599E-2</v>
+        <v>5.6310500500468402E-2</v>
       </c>
       <c r="AG245" s="6">
-        <v>5.0479700836902598E-2</v>
+        <v>9.8526103093137293E-2</v>
       </c>
       <c r="AH245" s="6">
-        <v>2.8170469988059901E-2</v>
+        <v>9.89697903360445E-2</v>
       </c>
       <c r="AI245" s="6">
-        <v>5.1197010563140598E-2</v>
+        <v>9.8650609692160898E-2</v>
       </c>
       <c r="AJ245" s="6">
-        <v>5.8793565228657099E-2</v>
+        <v>5.7548498136789798E-2</v>
       </c>
       <c r="AK245" s="6">
-        <v>4.2543926462414797E-2</v>
+        <v>8.7844434083819006E-2</v>
       </c>
       <c r="AL245" s="6"/>
       <c r="AM245" s="6"/>
@@ -29100,22 +29100,22 @@
         <v>5.9511291308389502</v>
       </c>
       <c r="AF246" s="6">
-        <v>2.54535276675984E-2</v>
+        <v>5.84835225516789E-2</v>
       </c>
       <c r="AG246" s="6">
-        <v>4.9590387173164198E-2</v>
+        <v>9.88577015467524E-2</v>
       </c>
       <c r="AH246" s="6">
-        <v>2.7327323002620502E-2</v>
+        <v>9.4998459995158602E-2</v>
       </c>
       <c r="AI246" s="6">
-        <v>4.7253259758596497E-2</v>
+        <v>8.9787126726770403E-2</v>
       </c>
       <c r="AJ246" s="6">
-        <v>5.7117149572426203E-2</v>
+        <v>5.6983349162772402E-2</v>
       </c>
       <c r="AK246" s="6">
-        <v>4.0933860416079097E-2</v>
+        <v>8.5103703672684106E-2</v>
       </c>
       <c r="AL246" s="6"/>
       <c r="AM246" s="6"/>
@@ -29216,22 +29216,22 @@
         <v>4.7476483472724595</v>
       </c>
       <c r="AF247" s="6">
-        <v>2.54111390126769E-2</v>
+        <v>6.0677462595118997E-2</v>
       </c>
       <c r="AG247" s="6">
-        <v>4.9090336562081498E-2</v>
+        <v>0.10001061471595001</v>
       </c>
       <c r="AH247" s="6">
-        <v>2.7054890802053502E-2</v>
+        <v>9.4096089335198196E-2</v>
       </c>
       <c r="AI247" s="6">
-        <v>4.4308456393120102E-2</v>
+        <v>8.4958312103919506E-2</v>
       </c>
       <c r="AJ247" s="6">
-        <v>5.5910738594578603E-2</v>
+        <v>5.5913105925562298E-2</v>
       </c>
       <c r="AK247" s="6">
-        <v>3.9856407418805098E-2</v>
+        <v>8.4193803475832593E-2</v>
       </c>
       <c r="AL247" s="6"/>
       <c r="AM247" s="6"/>
@@ -29332,22 +29332,22 @@
         <v>5.0137613215522236</v>
       </c>
       <c r="AF248" s="6">
-        <v>2.5385054319140499E-2</v>
+        <v>6.2848459090122197E-2</v>
       </c>
       <c r="AG248" s="6">
-        <v>4.8789674207339602E-2</v>
+        <v>0.102467229785453</v>
       </c>
       <c r="AH248" s="6">
-        <v>2.71313913533857E-2</v>
+        <v>9.7355464618240906E-2</v>
       </c>
       <c r="AI248" s="6">
-        <v>4.4738345750143897E-2</v>
+        <v>8.7093941536360603E-2</v>
       </c>
       <c r="AJ248" s="6">
-        <v>5.6224746964172699E-2</v>
+        <v>5.56876017121044E-2</v>
       </c>
       <c r="AK248" s="6">
-        <v>3.9952179194439399E-2</v>
+        <v>8.6395924456535697E-2</v>
       </c>
       <c r="AL248" s="6"/>
       <c r="AM248" s="6"/>
@@ -29448,22 +29448,22 @@
         <v>4.6052563158959003</v>
       </c>
       <c r="AF249" s="6">
-        <v>2.5355494911066999E-2</v>
+        <v>6.4924235871472696E-2</v>
       </c>
       <c r="AG249" s="6">
-        <v>4.8448247472283601E-2</v>
+        <v>0.103751606122927</v>
       </c>
       <c r="AH249" s="6">
-        <v>2.6799246512715501E-2</v>
+        <v>9.5596760332738895E-2</v>
       </c>
       <c r="AI249" s="6">
-        <v>4.49722600628817E-2</v>
+        <v>8.8603294022788603E-2</v>
       </c>
       <c r="AJ249" s="6">
-        <v>5.66251728397833E-2</v>
+        <v>5.5511311692476098E-2</v>
       </c>
       <c r="AK249" s="6">
-        <v>3.9886908463743799E-2</v>
+        <v>8.6869503510982299E-2</v>
       </c>
       <c r="AL249" s="6"/>
       <c r="AM249" s="6"/>
@@ -29564,22 +29564,22 @@
         <v>4.6105104403611818</v>
       </c>
       <c r="AF250" s="6">
-        <v>2.53241937547358E-2</v>
+        <v>6.6908641172503405E-2</v>
       </c>
       <c r="AG250" s="6">
-        <v>4.8096769652240301E-2</v>
+        <v>0.104888318849513</v>
       </c>
       <c r="AH250" s="6">
-        <v>2.69115216155884E-2</v>
+        <v>9.8137380513041494E-2</v>
       </c>
       <c r="AI250" s="6">
-        <v>4.5507674502981502E-2</v>
+        <v>9.0859347641228994E-2</v>
       </c>
       <c r="AJ250" s="6">
-        <v>5.7016088901633503E-2</v>
+        <v>5.5357583211121601E-2</v>
       </c>
       <c r="AK250" s="6">
-        <v>4.0015777986974997E-2</v>
+        <v>8.8574185150011905E-2</v>
       </c>
       <c r="AL250" s="6"/>
       <c r="AM250" s="6"/>
@@ -29680,22 +29680,22 @@
         <v>3.8911294306007704</v>
       </c>
       <c r="AF251" s="6">
-        <v>2.5290581712130299E-2</v>
+        <v>6.8797494728115305E-2</v>
       </c>
       <c r="AG251" s="6">
-        <v>4.7716329586117899E-2</v>
+        <v>0.105737982305945</v>
       </c>
       <c r="AH251" s="6">
-        <v>2.67153529253739E-2</v>
+        <v>9.9028326996905502E-2</v>
       </c>
       <c r="AI251" s="6">
-        <v>4.6071794394016902E-2</v>
+        <v>9.3163885696015206E-2</v>
       </c>
       <c r="AJ251" s="6">
-        <v>5.7449593113837301E-2</v>
+        <v>5.5234411866709798E-2</v>
       </c>
       <c r="AK251" s="6">
-        <v>4.0065315774535801E-2</v>
+        <v>8.9779711948985305E-2</v>
       </c>
       <c r="AL251" s="6"/>
       <c r="AM251" s="6"/>
@@ -29796,22 +29796,22 @@
         <v>2.34023919135673</v>
       </c>
       <c r="AF252" s="6">
-        <v>2.5293921182218598E-2</v>
+        <v>7.0750662878875895E-2</v>
       </c>
       <c r="AG252" s="6">
-        <v>4.8788194832780303E-2</v>
+        <v>0.111187855078763</v>
       </c>
       <c r="AH252" s="6">
-        <v>2.7029907472297499E-2</v>
+        <v>0.102651148772212</v>
       </c>
       <c r="AI252" s="6">
-        <v>4.6651314488568303E-2</v>
+        <v>9.5204649867097396E-2</v>
       </c>
       <c r="AJ252" s="6">
-        <v>5.7867365573206299E-2</v>
+        <v>5.5110466172897603E-2</v>
       </c>
       <c r="AK252" s="6">
-        <v>4.0586513420291001E-2</v>
+        <v>9.2764386897902798E-2</v>
       </c>
       <c r="AL252" s="6"/>
       <c r="AM252" s="6"/>
@@ -29912,22 +29912,22 @@
         <v>2.1140630187133524</v>
       </c>
       <c r="AF253" s="6">
-        <v>2.5853856120273098E-2</v>
+        <v>7.6739991370623206E-2</v>
       </c>
       <c r="AG253" s="6">
-        <v>5.11040919319624E-2</v>
+        <v>0.120871475240774</v>
       </c>
       <c r="AH253" s="6">
-        <v>2.74260809519619E-2</v>
+        <v>0.10716648549476999</v>
       </c>
       <c r="AI253" s="6">
-        <v>4.7567816601319202E-2</v>
+        <v>9.7872784666604498E-2</v>
       </c>
       <c r="AJ253" s="6">
-        <v>5.8520980283702402E-2</v>
+        <v>5.5128630723156803E-2</v>
       </c>
       <c r="AK253" s="6">
-        <v>4.1601620163261098E-2</v>
+        <v>9.7724775332169098E-2</v>
       </c>
       <c r="AL253" s="6"/>
       <c r="AM253" s="6"/>
@@ -30028,22 +30028,22 @@
         <v>3.9186505670670613</v>
       </c>
       <c r="AF254" s="6">
-        <v>2.5832490487237899E-2</v>
+        <v>7.8695422769037196E-2</v>
       </c>
       <c r="AG254" s="6">
-        <v>5.2957183790270701E-2</v>
+        <v>0.131329146915664</v>
       </c>
       <c r="AH254" s="6">
-        <v>2.8043411161911901E-2</v>
+        <v>0.11279619058729901</v>
       </c>
       <c r="AI254" s="6">
-        <v>4.8643341129100098E-2</v>
+        <v>0.100726889276701</v>
       </c>
       <c r="AJ254" s="6">
-        <v>5.9277015687379898E-2</v>
+        <v>5.5196068265600202E-2</v>
       </c>
       <c r="AK254" s="6">
-        <v>4.2538234403763003E-2</v>
+        <v>0.10264851633769401</v>
       </c>
       <c r="AL254" s="6"/>
       <c r="AM254" s="6"/>
@@ -30144,22 +30144,22 @@
         <v>2.8421418063750536</v>
       </c>
       <c r="AF255" s="6">
-        <v>2.5790499482962598E-2</v>
+        <v>7.9949503970223199E-2</v>
       </c>
       <c r="AG255" s="6">
-        <v>5.2419071275241001E-2</v>
+        <v>0.12981385328149</v>
       </c>
       <c r="AH255" s="6">
-        <v>2.78127591644203E-2</v>
+        <v>0.11009729625004</v>
       </c>
       <c r="AI255" s="6">
-        <v>4.5447382340486703E-2</v>
+        <v>9.3879135409318804E-2</v>
       </c>
       <c r="AJ255" s="6">
-        <v>5.4787738010700797E-2</v>
+        <v>5.2364172859205901E-2</v>
       </c>
       <c r="AK255" s="6">
-        <v>4.1015864010330201E-2</v>
+        <v>9.9798832261187201E-2</v>
       </c>
       <c r="AL255" s="6"/>
       <c r="AM255" s="6"/>
@@ -30260,22 +30260,22 @@
         <v>2.3244359851286589</v>
       </c>
       <c r="AF256" s="6">
-        <v>2.57401302613205E-2</v>
+        <v>8.10814021315623E-2</v>
       </c>
       <c r="AG256" s="6">
-        <v>5.1783561340580098E-2</v>
+        <v>0.12786642287236699</v>
       </c>
       <c r="AH256" s="6">
-        <v>2.78277791114614E-2</v>
+        <v>0.11141639071262199</v>
       </c>
       <c r="AI256" s="6">
-        <v>4.6280621458745098E-2</v>
+        <v>9.6730768446071203E-2</v>
       </c>
       <c r="AJ256" s="6">
-        <v>5.5348506361838301E-2</v>
+        <v>5.2535417829899102E-2</v>
       </c>
       <c r="AK256" s="6">
-        <v>4.1148215361506098E-2</v>
+        <v>0.100502412426117</v>
       </c>
       <c r="AL256" s="6"/>
       <c r="AM256" s="6"/>
@@ -30376,22 +30376,22 @@
         <v>2.6810800379859501</v>
       </c>
       <c r="AF257" s="6">
-        <v>2.5687998560796999E-2</v>
+        <v>8.2145364649880703E-2</v>
       </c>
       <c r="AG257" s="6">
-        <v>5.2854767485284199E-2</v>
+        <v>0.13342992731988301</v>
       </c>
       <c r="AH257" s="6">
-        <v>2.84900635098085E-2</v>
+        <v>0.1177941266261</v>
       </c>
       <c r="AI257" s="6">
-        <v>4.7262616733478598E-2</v>
+        <v>9.9552193201759495E-2</v>
       </c>
       <c r="AJ257" s="6">
-        <v>5.6001596333434503E-2</v>
+        <v>5.2744747628181703E-2</v>
       </c>
       <c r="AK257" s="6">
-        <v>4.1883934883935603E-2</v>
+        <v>0.104322150403446</v>
       </c>
       <c r="AL257" s="6"/>
       <c r="AM257" s="6"/>
@@ -30492,22 +30492,22 @@
         <v>3.2225548435167894</v>
       </c>
       <c r="AF258" s="6">
-        <v>2.56373623737206E-2</v>
+        <v>8.3140445862120896E-2</v>
       </c>
       <c r="AG258" s="6">
-        <v>5.2200785947190603E-2</v>
+        <v>0.13121002147574901</v>
       </c>
       <c r="AH258" s="6">
-        <v>2.7875687034181799E-2</v>
+        <v>0.111644835853937</v>
       </c>
       <c r="AI258" s="6">
-        <v>4.7557951371967902E-2</v>
+        <v>0.10119005823017101</v>
       </c>
       <c r="AJ258" s="6">
-        <v>5.6690328860415001E-2</v>
+        <v>5.2908607207946802E-2</v>
       </c>
       <c r="AK258" s="6">
-        <v>4.1717602709549099E-2</v>
+        <v>0.102713470560488</v>
       </c>
       <c r="AL258" s="6"/>
       <c r="AM258" s="6"/>
@@ -30599,22 +30599,22 @@
         <v>2.5666877007683553</v>
       </c>
       <c r="AF259" s="6">
-        <v>2.5616151926523899E-2</v>
+        <v>8.4262341251246806E-2</v>
       </c>
       <c r="AG259" s="6">
-        <v>5.19311451300438E-2</v>
+        <v>0.13070973271580999</v>
       </c>
       <c r="AH259" s="6">
-        <v>2.7616725444222098E-2</v>
+        <v>0.109108017618969</v>
       </c>
       <c r="AI259" s="6">
-        <v>4.7124345389838597E-2</v>
+        <v>0.100801987266273</v>
       </c>
       <c r="AJ259" s="6">
-        <v>5.6980647862228499E-2</v>
+        <v>5.2858166340310299E-2</v>
       </c>
       <c r="AK259" s="6">
-        <v>4.1508361020976901E-2</v>
+        <v>0.101981543753686</v>
       </c>
       <c r="AL259" s="6"/>
       <c r="AM259" s="6"/>
@@ -30706,22 +30706,22 @@
         <v>2.8356142624129901</v>
       </c>
       <c r="AF260" s="6">
-        <v>2.55813773408997E-2</v>
+        <v>8.5227189214983207E-2</v>
       </c>
       <c r="AG260" s="6">
-        <v>5.2322217661906097E-2</v>
+        <v>0.13145246185128301</v>
       </c>
       <c r="AH260" s="6">
-        <v>2.8025384021670499E-2</v>
+        <v>0.113338834934684</v>
       </c>
       <c r="AI260" s="6">
-        <v>4.7755283475517898E-2</v>
+        <v>0.102552674141834</v>
       </c>
       <c r="AJ260" s="6">
-        <v>5.7410889511879601E-2</v>
+        <v>5.29062052368659E-2</v>
       </c>
       <c r="AK260" s="6">
-        <v>4.19118556836491E-2</v>
+        <v>0.10380875532878001</v>
       </c>
       <c r="AL260" s="6"/>
       <c r="AM260" s="6"/>
@@ -30813,22 +30813,22 @@
         <v>2.6222861571262999</v>
       </c>
       <c r="AF261" s="6">
-        <v>2.5527182408082501E-2</v>
+        <v>8.6003282910575102E-2</v>
       </c>
       <c r="AG261" s="6">
-        <v>5.1629947061353397E-2</v>
+        <v>0.129148480370432</v>
       </c>
       <c r="AH261" s="6">
-        <v>2.7552941024093301E-2</v>
+        <v>0.10975815589537501</v>
       </c>
       <c r="AI261" s="6">
-        <v>4.8599570300350503E-2</v>
+        <v>0.10522892891027701</v>
       </c>
       <c r="AJ261" s="6">
-        <v>5.8120022304744903E-2</v>
+        <v>5.3086100191529803E-2</v>
       </c>
       <c r="AK261" s="6">
-        <v>4.1915533682810299E-2</v>
+        <v>0.103022956567039</v>
       </c>
       <c r="AL261" s="6"/>
       <c r="AM261" s="6"/>
@@ -30920,22 +30920,22 @@
         <v>4.32677217130255</v>
       </c>
       <c r="AF262" s="6">
-        <v>2.54894280439199E-2</v>
+        <v>8.6840901806339799E-2</v>
       </c>
       <c r="AG262" s="6">
-        <v>5.11748035030141E-2</v>
+        <v>0.12821135459413299</v>
       </c>
       <c r="AH262" s="6">
-        <v>2.7747574898928401E-2</v>
+        <v>0.112725841763213</v>
       </c>
       <c r="AI262" s="6">
-        <v>4.9327854130246103E-2</v>
+        <v>0.107137234505155</v>
       </c>
       <c r="AJ262" s="6">
-        <v>5.8609600272521101E-2</v>
+        <v>5.3144036123707099E-2</v>
       </c>
       <c r="AK262" s="6">
-        <v>4.2103447647493998E-2</v>
+        <v>0.104127083878422</v>
       </c>
       <c r="AL262" s="6"/>
       <c r="AM262" s="6"/>
@@ -31027,22 +31027,22 @@
         <v>3.5082118242694804</v>
       </c>
       <c r="AF263" s="6">
-        <v>2.5453496359285399E-2</v>
+        <v>8.7637696225598097E-2</v>
       </c>
       <c r="AG263" s="6">
-        <v>5.0728762031546103E-2</v>
+        <v>0.12718112679320001</v>
       </c>
       <c r="AH263" s="6">
-        <v>2.7541178938433199E-2</v>
+        <v>0.11057443947703099</v>
       </c>
       <c r="AI263" s="6">
-        <v>4.6456053452338497E-2</v>
+        <v>9.9880864677710998E-2</v>
       </c>
       <c r="AJ263" s="6">
-        <v>5.5716895518355201E-2</v>
+        <v>5.0855800982847803E-2</v>
       </c>
       <c r="AK263" s="6">
-        <v>4.0880016995191698E-2</v>
+        <v>0.101479060591586</v>
       </c>
       <c r="AL263" s="6"/>
       <c r="AM263" s="6"/>

--- a/estimates_PS2026.xlsx
+++ b/estimates_PS2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\GitHub\tibor-pal.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE17497E-8B44-4E4A-BE09-56144D211C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BE620A-4862-4C56-97E2-158E6C96F04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{898E4DB8-E74C-49BD-9493-76D0D230C2FB}"/>
   </bookViews>

--- a/estimates_PS2026.xlsx
+++ b/estimates_PS2026.xlsx
@@ -8,15 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\GitHub\tibor-pal.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BE620A-4862-4C56-97E2-158E6C96F04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A47ED78-8BF3-47EB-9E86-70F2BE6A5D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{898E4DB8-E74C-49BD-9493-76D0D230C2FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
-    <sheet name="hlw" sheetId="4" r:id="rId3"/>
-    <sheet name="info_READ IT" sheetId="3" r:id="rId4"/>
+    <sheet name="hlw" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Date</t>
   </si>
@@ -66,12 +64,6 @@
   </si>
   <si>
     <t>infVol</t>
-  </si>
-  <si>
-    <t>simulated median</t>
-  </si>
-  <si>
-    <t>(add CI later)</t>
   </si>
   <si>
     <t>q95</t>
@@ -599,16 +591,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>3</v>
@@ -620,34 +612,34 @@
         <v>4</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="O1" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="R1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>7</v>
@@ -656,49 +648,49 @@
         <v>8</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="X1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="Y1" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="Z1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="AA1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE1" s="8" t="s">
+      <c r="AG1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="8" t="s">
+      <c r="AH1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AG1" s="8" t="s">
+      <c r="AI1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="AH1" s="8" t="s">
+      <c r="AJ1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="AI1" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="AJ1" s="8" t="s">
-        <v>21</v>
-      </c>
       <c r="AK1" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
@@ -796,22 +788,22 @@
         <v>0.68202628184472758</v>
       </c>
       <c r="AF2" s="6">
-        <v>0.105076808074302</v>
+        <v>0.10473432128837799</v>
       </c>
       <c r="AG2" s="6">
-        <v>0.158248776402827</v>
+        <v>0.15923720090131799</v>
       </c>
       <c r="AH2" s="6">
-        <v>0.12338968605319101</v>
+        <v>0.12325197992105601</v>
       </c>
       <c r="AI2" s="6">
-        <v>9.8498378117968299E-2</v>
+        <v>9.8114522534915205E-2</v>
       </c>
       <c r="AJ2" s="6">
-        <v>4.9224327290621699E-2</v>
+        <v>4.7779629488922101E-2</v>
       </c>
       <c r="AK2" s="6">
-        <v>0.114200790307074</v>
+        <v>0.11406454103429001</v>
       </c>
       <c r="AL2" s="6"/>
       <c r="AM2" s="6"/>
@@ -912,22 +904,22 @@
         <v>1.3108781333286856</v>
       </c>
       <c r="AF3" s="6">
-        <v>0.10631038726976701</v>
+        <v>0.10594788628273499</v>
       </c>
       <c r="AG3" s="6">
-        <v>0.16738473978888099</v>
+        <v>0.168293643550564</v>
       </c>
       <c r="AH3" s="6">
-        <v>0.11618855859225601</v>
+        <v>0.11681361189752</v>
       </c>
       <c r="AI3" s="6">
-        <v>9.3134528332838598E-2</v>
+        <v>9.2836355103888699E-2</v>
       </c>
       <c r="AJ3" s="6">
-        <v>4.85080910015767E-2</v>
+        <v>4.7088063750173298E-2</v>
       </c>
       <c r="AK3" s="6">
-        <v>0.113342504305152</v>
+        <v>0.113408157727016</v>
       </c>
       <c r="AL3" s="6"/>
       <c r="AM3" s="6"/>
@@ -1028,22 +1020,22 @@
         <v>1.7356833581507303</v>
       </c>
       <c r="AF4" s="6">
-        <v>0.107211555399974</v>
+        <v>0.10678968275968</v>
       </c>
       <c r="AG4" s="6">
-        <v>0.174246224495479</v>
+        <v>0.17459641989642899</v>
       </c>
       <c r="AH4" s="6">
-        <v>0.13063200417924101</v>
+        <v>0.131837256759995</v>
       </c>
       <c r="AI4" s="6">
-        <v>9.7289535576220998E-2</v>
+        <v>9.6585120315993797E-2</v>
       </c>
       <c r="AJ4" s="6">
-        <v>4.7994434928294298E-2</v>
+        <v>4.6610421529349501E-2</v>
       </c>
       <c r="AK4" s="6">
-        <v>0.119781518780938</v>
+        <v>0.11976189275850301</v>
       </c>
       <c r="AL4" s="6"/>
       <c r="AM4" s="6"/>
@@ -1144,22 +1136,22 @@
         <v>0.95553907752421452</v>
       </c>
       <c r="AF5" s="6">
-        <v>0.107692691174126</v>
+        <v>0.10718235510315199</v>
       </c>
       <c r="AG5" s="6">
-        <v>0.178013929446657</v>
+        <v>0.177537919514514</v>
       </c>
       <c r="AH5" s="6">
-        <v>0.14108671291720901</v>
+        <v>0.142110304241652</v>
       </c>
       <c r="AI5" s="6">
-        <v>9.7987383609731193E-2</v>
+        <v>9.7568829277957694E-2</v>
       </c>
       <c r="AJ5" s="6">
-        <v>4.7715887285492302E-2</v>
+        <v>4.6382198578681498E-2</v>
       </c>
       <c r="AK5" s="6">
-        <v>0.123557233939373</v>
+        <v>0.123346122166621</v>
       </c>
       <c r="AL5" s="6"/>
       <c r="AM5" s="6"/>
@@ -1260,22 +1252,22 @@
         <v>1.4782286312740922</v>
       </c>
       <c r="AF6" s="6">
-        <v>0.10694221673716101</v>
+        <v>0.106921956185989</v>
       </c>
       <c r="AG6" s="6">
-        <v>0.16526210560972601</v>
+        <v>0.16584878706235501</v>
       </c>
       <c r="AH6" s="6">
-        <v>0.13423632938104901</v>
+        <v>0.13370543776689101</v>
       </c>
       <c r="AI6" s="6">
-        <v>9.7111741841987204E-2</v>
+        <v>9.6881277332041105E-2</v>
       </c>
       <c r="AJ6" s="6">
-        <v>4.7698110345238097E-2</v>
+        <v>4.6418977617296998E-2</v>
       </c>
       <c r="AK6" s="6">
-        <v>0.118412522633945</v>
+        <v>0.11818559852314101</v>
       </c>
       <c r="AL6" s="6"/>
       <c r="AM6" s="6"/>
@@ -1376,22 +1368,22 @@
         <v>1.5381172948124799</v>
       </c>
       <c r="AF7" s="6">
-        <v>0.10671659128658401</v>
+        <v>0.10656065094913</v>
       </c>
       <c r="AG7" s="6">
-        <v>0.16362522638209601</v>
+        <v>0.16352731964397199</v>
       </c>
       <c r="AH7" s="6">
-        <v>0.13324142313095</v>
+        <v>0.132168762086081</v>
       </c>
       <c r="AI7" s="6">
-        <v>9.7709939744775598E-2</v>
+        <v>9.7650680027747405E-2</v>
       </c>
       <c r="AJ7" s="6">
-        <v>4.78441538736172E-2</v>
+        <v>4.6615584565586003E-2</v>
       </c>
       <c r="AK7" s="6">
-        <v>0.11789046860003601</v>
+        <v>0.11738604068768201</v>
       </c>
       <c r="AL7" s="6"/>
       <c r="AM7" s="6"/>
@@ -1492,22 +1484,22 @@
         <v>1.3125323859656035</v>
       </c>
       <c r="AF8" s="6">
-        <v>0.106540890767089</v>
+        <v>0.10627002695283599</v>
       </c>
       <c r="AG8" s="6">
-        <v>0.16241883936754101</v>
+        <v>0.16176418004342699</v>
       </c>
       <c r="AH8" s="6">
-        <v>0.13195428332386799</v>
+        <v>0.13037088522618501</v>
       </c>
       <c r="AI8" s="6">
-        <v>9.7933508493593904E-2</v>
+        <v>9.8048207265503007E-2</v>
       </c>
       <c r="AJ8" s="6">
-        <v>4.7964340272376497E-2</v>
+        <v>4.6777367743986699E-2</v>
       </c>
       <c r="AK8" s="6">
-        <v>0.117313602006532</v>
+        <v>0.116571924892059</v>
       </c>
       <c r="AL8" s="6"/>
       <c r="AM8" s="6"/>
@@ -1608,22 +1600,22 @@
         <v>0.74808933823362622</v>
       </c>
       <c r="AF9" s="6">
-        <v>0.106300750865667</v>
+        <v>0.10592956070145899</v>
       </c>
       <c r="AG9" s="6">
-        <v>0.16067414889784101</v>
+        <v>0.15955169473162001</v>
       </c>
       <c r="AH9" s="6">
-        <v>0.13064334788208601</v>
+        <v>0.12870017936398501</v>
       </c>
       <c r="AI9" s="6">
-        <v>9.8466039188470106E-2</v>
+        <v>9.8740609635759299E-2</v>
       </c>
       <c r="AJ9" s="6">
-        <v>4.8117228455105299E-2</v>
+        <v>4.6965209026240802E-2</v>
       </c>
       <c r="AK9" s="6">
-        <v>0.11666596045717501</v>
+        <v>0.115743694987279</v>
       </c>
       <c r="AL9" s="6"/>
       <c r="AM9" s="6"/>
@@ -1724,22 +1716,22 @@
         <v>1.321993518747</v>
       </c>
       <c r="AF10" s="6">
-        <v>0.106096579345689</v>
+        <v>0.105642647705451</v>
       </c>
       <c r="AG10" s="6">
-        <v>0.153413503948544</v>
+        <v>0.15191369724915099</v>
       </c>
       <c r="AH10" s="6">
-        <v>0.12598663342187499</v>
+        <v>0.12374813857071</v>
       </c>
       <c r="AI10" s="6">
-        <v>9.7870817200975402E-2</v>
+        <v>9.8260869777238496E-2</v>
       </c>
       <c r="AJ10" s="6">
-        <v>4.8109638430665E-2</v>
+        <v>4.6982823454277997E-2</v>
       </c>
       <c r="AK10" s="6">
-        <v>0.113532006673795</v>
+        <v>0.112455954908287</v>
       </c>
       <c r="AL10" s="6"/>
       <c r="AM10" s="6"/>
@@ -1840,22 +1832,22 @@
         <v>1.5112808287716106</v>
       </c>
       <c r="AF11" s="6">
-        <v>0.106153230519673</v>
+        <v>0.105634492484251</v>
       </c>
       <c r="AG11" s="6">
-        <v>0.1542089770566</v>
+        <v>0.15259312474687101</v>
       </c>
       <c r="AH11" s="6">
-        <v>0.12823474750867001</v>
+        <v>0.12584727876045901</v>
       </c>
       <c r="AI11" s="6">
-        <v>0.101048656359659</v>
+        <v>0.101646868631179</v>
       </c>
       <c r="AJ11" s="6">
-        <v>4.8192256681084497E-2</v>
+        <v>4.7091737208412199E-2</v>
       </c>
       <c r="AK11" s="6">
-        <v>0.11505334009052599</v>
+        <v>0.113948210746878</v>
       </c>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6"/>
@@ -1956,22 +1948,22 @@
         <v>1.537735749143998</v>
       </c>
       <c r="AF12" s="6">
-        <v>0.106188460013406</v>
+        <v>0.10560915716224401</v>
       </c>
       <c r="AG12" s="6">
-        <v>0.15490061141536601</v>
+        <v>0.15314803465332599</v>
       </c>
       <c r="AH12" s="6">
-        <v>0.12943259353627601</v>
+        <v>0.126881780287115</v>
       </c>
       <c r="AI12" s="6">
-        <v>0.100430357638902</v>
+        <v>0.10102828180657</v>
       </c>
       <c r="AJ12" s="6">
-        <v>4.8191187101512697E-2</v>
+        <v>4.7109105477598397E-2</v>
       </c>
       <c r="AK12" s="6">
-        <v>0.115393238124986</v>
+        <v>0.114210916367675</v>
       </c>
       <c r="AL12" s="6"/>
       <c r="AM12" s="6"/>
@@ -2072,22 +2064,22 @@
         <v>1.9238899590684255</v>
       </c>
       <c r="AF13" s="6">
-        <v>0.105799609965169</v>
+        <v>0.10515798077447</v>
       </c>
       <c r="AG13" s="6">
-        <v>0.15244477102096399</v>
+        <v>0.150568887868027</v>
       </c>
       <c r="AH13" s="6">
-        <v>0.12733476790522899</v>
+        <v>0.124747451078907</v>
       </c>
       <c r="AI13" s="6">
-        <v>0.10155866541886099</v>
+        <v>0.102242012861864</v>
       </c>
       <c r="AJ13" s="6">
-        <v>4.8425795308995899E-2</v>
+        <v>4.7364593870661303E-2</v>
       </c>
       <c r="AK13" s="6">
-        <v>0.114491531972875</v>
+        <v>0.113277119931794</v>
       </c>
       <c r="AL13" s="6"/>
       <c r="AM13" s="6"/>
@@ -2188,22 +2180,22 @@
         <v>1.6917730954455479</v>
       </c>
       <c r="AF14" s="6">
-        <v>0.10560178255915401</v>
+        <v>0.10491738077444</v>
       </c>
       <c r="AG14" s="6">
-        <v>0.15140679980670799</v>
+        <v>0.14948067512813101</v>
       </c>
       <c r="AH14" s="6">
-        <v>0.12606572365886701</v>
+        <v>0.123362510014409</v>
       </c>
       <c r="AI14" s="6">
-        <v>0.101853078780743</v>
+        <v>0.10254835803312801</v>
       </c>
       <c r="AJ14" s="6">
-        <v>4.8554564272175998E-2</v>
+        <v>4.75041320652888E-2</v>
       </c>
       <c r="AK14" s="6">
-        <v>0.113968357916492</v>
+        <v>0.11270689446495399</v>
       </c>
       <c r="AL14" s="6"/>
       <c r="AM14" s="6"/>
@@ -2304,22 +2296,22 @@
         <v>1.1847619757674011</v>
       </c>
       <c r="AF15" s="6">
-        <v>0.10503163809586701</v>
+        <v>0.104309005308513</v>
       </c>
       <c r="AG15" s="6">
-        <v>0.14764648142619999</v>
+        <v>0.14573774957253999</v>
       </c>
       <c r="AH15" s="6">
-        <v>0.12641418955504299</v>
+        <v>0.123156252183784</v>
       </c>
       <c r="AI15" s="6">
-        <v>0.104020387005752</v>
+        <v>0.104796971371469</v>
       </c>
       <c r="AJ15" s="6">
-        <v>4.88969368953995E-2</v>
+        <v>4.7857753791346699E-2</v>
       </c>
       <c r="AK15" s="6">
-        <v>0.113599106040513</v>
+        <v>0.112208658761244</v>
       </c>
       <c r="AL15" s="6"/>
       <c r="AM15" s="6"/>
@@ -2420,22 +2412,22 @@
         <v>1.1100106231305418</v>
       </c>
       <c r="AF16" s="6">
-        <v>0.105329272396224</v>
+        <v>0.10483222120396</v>
       </c>
       <c r="AG16" s="6">
-        <v>0.15671519716773599</v>
+        <v>0.15531493085832501</v>
       </c>
       <c r="AH16" s="6">
-        <v>0.13024892270086599</v>
+        <v>0.12679996683340999</v>
       </c>
       <c r="AI16" s="6">
-        <v>0.105927600245299</v>
+        <v>0.106662491317431</v>
       </c>
       <c r="AJ16" s="6">
-        <v>4.9221753598774599E-2</v>
+        <v>4.8183750456038198E-2</v>
       </c>
       <c r="AK16" s="6">
-        <v>0.117331362131496</v>
+        <v>0.116034915390176</v>
       </c>
       <c r="AL16" s="6"/>
       <c r="AM16" s="6"/>
@@ -2536,22 +2528,22 @@
         <v>1.0200758723504677</v>
       </c>
       <c r="AF17" s="6">
-        <v>0.104596591822177</v>
+        <v>0.104045511771298</v>
       </c>
       <c r="AG17" s="6">
-        <v>0.15096395846713201</v>
+        <v>0.14941660106343699</v>
       </c>
       <c r="AH17" s="6">
-        <v>0.12846643719125</v>
+        <v>0.124653772599537</v>
       </c>
       <c r="AI17" s="6">
-        <v>0.108928126394609</v>
+        <v>0.109681858587147</v>
       </c>
       <c r="AJ17" s="6">
-        <v>4.9635378031372003E-2</v>
+        <v>4.8592094056045199E-2</v>
       </c>
       <c r="AK17" s="6">
-        <v>0.116096675671313</v>
+        <v>0.114654411916967</v>
       </c>
       <c r="AL17" s="6"/>
       <c r="AM17" s="6"/>
@@ -2652,22 +2644,22 @@
         <v>1.5055836632347663</v>
       </c>
       <c r="AF18" s="6">
-        <v>0.104213155271101</v>
+        <v>0.103639173574701</v>
       </c>
       <c r="AG18" s="6">
-        <v>0.14918887954281901</v>
+        <v>0.14726590357953701</v>
       </c>
       <c r="AH18" s="6">
-        <v>0.13136525100024099</v>
+        <v>0.12718370109194299</v>
       </c>
       <c r="AI18" s="6">
-        <v>0.110112269633034</v>
+        <v>0.11070438029464599</v>
       </c>
       <c r="AJ18" s="6">
-        <v>4.9851032836263097E-2</v>
+        <v>4.8787474299876302E-2</v>
       </c>
       <c r="AK18" s="6">
-        <v>0.116659230177608</v>
+        <v>0.114994267708226</v>
       </c>
       <c r="AL18" s="6"/>
       <c r="AM18" s="6"/>
@@ -2768,22 +2760,22 @@
         <v>1.2411879791372371</v>
       </c>
       <c r="AF19" s="6">
-        <v>0.10337723565909</v>
+        <v>0.102785902017008</v>
       </c>
       <c r="AG19" s="6">
-        <v>0.14338190774585699</v>
+        <v>0.14151339136765301</v>
       </c>
       <c r="AH19" s="6">
-        <v>0.119866859176296</v>
+        <v>0.115696882954301</v>
       </c>
       <c r="AI19" s="6">
-        <v>9.9848739272189402E-2</v>
+        <v>0.100789279201731</v>
       </c>
       <c r="AJ19" s="6">
-        <v>5.0045786930137601E-2</v>
+        <v>4.9041034405827098E-2</v>
       </c>
       <c r="AK19" s="6">
-        <v>0.109855568826041</v>
+        <v>0.10829469420679801</v>
       </c>
       <c r="AL19" s="6"/>
       <c r="AM19" s="6"/>
@@ -2884,22 +2876,22 @@
         <v>1.2373485207907819</v>
       </c>
       <c r="AF20" s="6">
-        <v>0.10311197066779799</v>
+        <v>0.10253382330857599</v>
       </c>
       <c r="AG20" s="6">
-        <v>0.15833887329808899</v>
+        <v>0.15652205191482599</v>
       </c>
       <c r="AH20" s="6">
-        <v>0.12993720754555199</v>
+        <v>0.125890412673553</v>
       </c>
       <c r="AI20" s="6">
-        <v>0.10383268773316599</v>
+        <v>0.10484664778132501</v>
       </c>
       <c r="AJ20" s="6">
-        <v>5.0582087697999399E-2</v>
+        <v>4.9551569571160303E-2</v>
       </c>
       <c r="AK20" s="6">
-        <v>0.11706436325724399</v>
+        <v>0.11557145948415</v>
       </c>
       <c r="AL20" s="6"/>
       <c r="AM20" s="6"/>
@@ -3000,22 +2992,22 @@
         <v>1.3270635306140477</v>
       </c>
       <c r="AF21" s="6">
-        <v>0.101867660317355</v>
+        <v>0.101294651373019</v>
       </c>
       <c r="AG21" s="6">
-        <v>0.14727878433931499</v>
+        <v>0.14541854258694001</v>
       </c>
       <c r="AH21" s="6">
-        <v>0.118427007739872</v>
+        <v>0.11342916729670301</v>
       </c>
       <c r="AI21" s="6">
-        <v>0.109897369035535</v>
+        <v>0.110906935530715</v>
       </c>
       <c r="AJ21" s="6">
-        <v>5.1371894374191603E-2</v>
+        <v>5.0309361476957498E-2</v>
       </c>
       <c r="AK21" s="6">
-        <v>0.112643495034424</v>
+        <v>0.110818038615312</v>
       </c>
       <c r="AL21" s="6"/>
       <c r="AM21" s="6"/>
@@ -3116,22 +3108,22 @@
         <v>1.9978857770267311</v>
       </c>
       <c r="AF22" s="6">
-        <v>0.100318051899775</v>
+        <v>9.9776705863453705E-2</v>
       </c>
       <c r="AG22" s="6">
-        <v>0.14314757946252499</v>
+        <v>0.14248295982335599</v>
       </c>
       <c r="AH22" s="6">
-        <v>0.14258339685263299</v>
+        <v>0.13800499497398999</v>
       </c>
       <c r="AI22" s="6">
-        <v>0.11823500094554799</v>
+        <v>0.118879326419583</v>
       </c>
       <c r="AJ22" s="6">
-        <v>5.2464328546471997E-2</v>
+        <v>5.1358976803991499E-2</v>
       </c>
       <c r="AK22" s="6">
-        <v>0.119729293646317</v>
+        <v>0.118300712584665</v>
       </c>
       <c r="AL22" s="6"/>
       <c r="AM22" s="6"/>
@@ -3232,22 +3224,22 @@
         <v>3.2436993539228354</v>
       </c>
       <c r="AF23" s="6">
-        <v>9.8468172059748796E-2</v>
+        <v>9.7985537961387995E-2</v>
       </c>
       <c r="AG23" s="6">
-        <v>0.13009347208322999</v>
+        <v>0.129122962751996</v>
       </c>
       <c r="AH23" s="6">
-        <v>0.113832083128544</v>
+        <v>0.111070748245075</v>
       </c>
       <c r="AI23" s="6">
-        <v>7.5084486622640598E-2</v>
+        <v>7.4417599189262801E-2</v>
       </c>
       <c r="AJ23" s="6">
-        <v>4.33652757001717E-2</v>
+        <v>3.94915876425595E-2</v>
       </c>
       <c r="AK23" s="6">
-        <v>9.7594366538378399E-2</v>
+        <v>9.5944877646523999E-2</v>
       </c>
       <c r="AL23" s="6"/>
       <c r="AM23" s="6"/>
@@ -3348,22 +3340,22 @@
         <v>3.2862730925906192</v>
       </c>
       <c r="AF24" s="6">
-        <v>9.7088913044482694E-2</v>
+        <v>9.6713686821103803E-2</v>
       </c>
       <c r="AG24" s="6">
-        <v>0.120920110249694</v>
+        <v>0.120307200219506</v>
       </c>
       <c r="AH24" s="6">
-        <v>9.8362748160522095E-2</v>
+        <v>9.6146680128710693E-2</v>
       </c>
       <c r="AI24" s="6">
-        <v>5.9836483775925403E-2</v>
+        <v>6.0013191725517799E-2</v>
       </c>
       <c r="AJ24" s="6">
-        <v>3.4893221195057E-2</v>
+        <v>3.4325451417232901E-2</v>
       </c>
       <c r="AK24" s="6">
-        <v>8.6434232176735903E-2</v>
+        <v>8.5667298776135201E-2</v>
       </c>
       <c r="AL24" s="6"/>
       <c r="AM24" s="6"/>
@@ -3464,22 +3456,22 @@
         <v>3.4410611294228843</v>
       </c>
       <c r="AF25" s="6">
-        <v>9.5943850840720907E-2</v>
+        <v>9.5700597620392194E-2</v>
       </c>
       <c r="AG25" s="6">
-        <v>0.11296255291779</v>
+        <v>0.11293457489533899</v>
       </c>
       <c r="AH25" s="6">
-        <v>0.10162853059139799</v>
+        <v>9.9744842037268702E-2</v>
       </c>
       <c r="AI25" s="6">
-        <v>6.5605892062962204E-2</v>
+        <v>6.6854583717194702E-2</v>
       </c>
       <c r="AJ25" s="6">
-        <v>3.62866592529714E-2</v>
+        <v>3.6031449592838501E-2</v>
       </c>
       <c r="AK25" s="6">
-        <v>8.6693450826414095E-2</v>
+        <v>8.6475509596988201E-2</v>
       </c>
       <c r="AL25" s="6"/>
       <c r="AM25" s="6"/>
@@ -3580,22 +3572,22 @@
         <v>2.1949687837057752</v>
       </c>
       <c r="AF26" s="6">
-        <v>9.5011247688139594E-2</v>
+        <v>9.4915415002774298E-2</v>
       </c>
       <c r="AG26" s="6">
-        <v>0.107807322214874</v>
+        <v>0.108358340273312</v>
       </c>
       <c r="AH26" s="6">
-        <v>8.7640493844146197E-2</v>
+        <v>8.6111487052169006E-2</v>
       </c>
       <c r="AI26" s="6">
-        <v>6.7110156752779301E-2</v>
+        <v>6.9242476891714505E-2</v>
       </c>
       <c r="AJ26" s="6">
-        <v>3.7741145667066801E-2</v>
+        <v>3.7752024374777197E-2</v>
       </c>
       <c r="AK26" s="6">
-        <v>8.2370767341815601E-2</v>
+        <v>8.2605723134526896E-2</v>
       </c>
       <c r="AL26" s="6"/>
       <c r="AM26" s="6"/>
@@ -3696,22 +3688,22 @@
         <v>2.6689756779388674</v>
       </c>
       <c r="AF27" s="6">
-        <v>0.144486338470737</v>
+        <v>0.14632149896140501</v>
       </c>
       <c r="AG27" s="6">
-        <v>0.13879945144566799</v>
+        <v>0.14125873432922001</v>
       </c>
       <c r="AH27" s="6">
-        <v>9.7593339224943801E-2</v>
+        <v>9.7099360635677201E-2</v>
       </c>
       <c r="AI27" s="6">
-        <v>7.2611192564029703E-2</v>
+        <v>7.5695796515751701E-2</v>
       </c>
       <c r="AJ27" s="6">
-        <v>3.9054603381092602E-2</v>
+        <v>3.9301677305628502E-2</v>
       </c>
       <c r="AK27" s="6">
-        <v>0.100139444906046</v>
+        <v>0.101568414042938</v>
       </c>
       <c r="AL27" s="6"/>
       <c r="AM27" s="6"/>
@@ -3812,22 +3804,22 @@
         <v>3.6150873681068063</v>
       </c>
       <c r="AF28" s="6">
-        <v>0.13859406828901699</v>
+        <v>0.13873535194390799</v>
       </c>
       <c r="AG28" s="6">
-        <v>0.13218380880846001</v>
+        <v>0.13422611534447201</v>
       </c>
       <c r="AH28" s="6">
-        <v>9.0968977580913296E-2</v>
+        <v>9.0595316234597906E-2</v>
       </c>
       <c r="AI28" s="6">
-        <v>7.7262975897774103E-2</v>
+        <v>8.1245013772599295E-2</v>
       </c>
       <c r="AJ28" s="6">
-        <v>4.0209524366080197E-2</v>
+        <v>4.0639221063724501E-2</v>
       </c>
       <c r="AK28" s="6">
-        <v>9.7233083773239401E-2</v>
+        <v>9.8549340492002202E-2</v>
       </c>
       <c r="AL28" s="6"/>
       <c r="AM28" s="6"/>
@@ -3928,22 +3920,22 @@
         <v>4.0154692025668126</v>
       </c>
       <c r="AF29" s="6">
-        <v>0.133543184181417</v>
+        <v>0.132475495412165</v>
       </c>
       <c r="AG29" s="6">
-        <v>0.12707180931304199</v>
+        <v>0.128958467479246</v>
       </c>
       <c r="AH29" s="6">
-        <v>8.6434454781022296E-2</v>
+        <v>8.6791365067288698E-2</v>
       </c>
       <c r="AI29" s="6">
-        <v>6.7229034716918504E-2</v>
+        <v>7.00574699887348E-2</v>
       </c>
       <c r="AJ29" s="6">
-        <v>3.70645658545724E-2</v>
+        <v>3.7245617840931902E-2</v>
       </c>
       <c r="AK29" s="6">
-        <v>9.1418690336137406E-2</v>
+        <v>9.2471700195953105E-2</v>
       </c>
       <c r="AL29" s="6"/>
       <c r="AM29" s="6"/>
@@ -4044,22 +4036,22 @@
         <v>4.5340719456142153</v>
       </c>
       <c r="AF30" s="6">
-        <v>0.12932955904946999</v>
+        <v>0.12741175404167099</v>
       </c>
       <c r="AG30" s="6">
-        <v>0.123292592548188</v>
+        <v>0.125207767676526</v>
       </c>
       <c r="AH30" s="6">
-        <v>8.0525921687074994E-2</v>
+        <v>8.1261306224082702E-2</v>
       </c>
       <c r="AI30" s="6">
-        <v>6.9281965115656E-2</v>
+        <v>7.3460519322029197E-2</v>
       </c>
       <c r="AJ30" s="6">
-        <v>3.8222086583701298E-2</v>
+        <v>3.8620373466399099E-2</v>
       </c>
       <c r="AK30" s="6">
-        <v>8.8975795848219297E-2</v>
+        <v>9.0328634796314297E-2</v>
       </c>
       <c r="AL30" s="6"/>
       <c r="AM30" s="6"/>
@@ -4160,22 +4152,22 @@
         <v>4.6265784409410315</v>
       </c>
       <c r="AF31" s="6">
-        <v>0.125029081518827</v>
+        <v>0.12252385415450701</v>
       </c>
       <c r="AG31" s="6">
-        <v>0.118683162258759</v>
+        <v>0.120661472785459</v>
       </c>
       <c r="AH31" s="6">
-        <v>7.4646631527392204E-2</v>
+        <v>7.5961927679048996E-2</v>
       </c>
       <c r="AI31" s="6">
-        <v>6.5276228685030802E-2</v>
+        <v>6.8361564769378699E-2</v>
       </c>
       <c r="AJ31" s="6">
-        <v>3.93030323489491E-2</v>
+        <v>3.9805999731150697E-2</v>
       </c>
       <c r="AK31" s="6">
-        <v>8.4946253107674993E-2</v>
+        <v>8.6174365618523499E-2</v>
       </c>
       <c r="AL31" s="6"/>
       <c r="AM31" s="6"/>
@@ -4276,22 +4268,22 @@
         <v>4.4461527613668395</v>
       </c>
       <c r="AF32" s="6">
-        <v>0.120906542435416</v>
+        <v>0.118039780837639</v>
       </c>
       <c r="AG32" s="6">
-        <v>0.113980992007488</v>
+        <v>0.11609296885616099</v>
       </c>
       <c r="AH32" s="6">
-        <v>7.0181009943087805E-2</v>
+        <v>7.1706710085998701E-2</v>
       </c>
       <c r="AI32" s="6">
-        <v>7.0396247203902806E-2</v>
+        <v>7.45972757108853E-2</v>
       </c>
       <c r="AJ32" s="6">
-        <v>4.05765588993003E-2</v>
+        <v>4.1255424689232399E-2</v>
       </c>
       <c r="AK32" s="6">
-        <v>8.3348010349002397E-2</v>
+        <v>8.4931305260363896E-2</v>
       </c>
       <c r="AL32" s="6"/>
       <c r="AM32" s="6"/>
@@ -4392,22 +4384,22 @@
         <v>4.6284826785427668</v>
       </c>
       <c r="AF33" s="6">
-        <v>0.11744825688504</v>
+        <v>0.114389794524277</v>
       </c>
       <c r="AG33" s="6">
-        <v>0.110507605214843</v>
+        <v>0.112875051950081</v>
       </c>
       <c r="AH33" s="6">
-        <v>7.2163971408063701E-2</v>
+        <v>7.4987772483127296E-2</v>
       </c>
       <c r="AI33" s="6">
-        <v>7.5852465860949E-2</v>
+        <v>8.1080041357890806E-2</v>
       </c>
       <c r="AJ33" s="6">
-        <v>4.1779619475585401E-2</v>
+        <v>4.2593681089638701E-2</v>
       </c>
       <c r="AK33" s="6">
-        <v>8.4105651493777994E-2</v>
+        <v>8.6323614936313006E-2</v>
       </c>
       <c r="AL33" s="6"/>
       <c r="AM33" s="6"/>
@@ -4508,22 +4500,22 @@
         <v>4.3469602313372491</v>
       </c>
       <c r="AF34" s="6">
-        <v>0.114747908730971</v>
+        <v>0.11161529602889</v>
       </c>
       <c r="AG34" s="6">
-        <v>0.108341990085246</v>
+        <v>0.11105406327367499</v>
       </c>
       <c r="AH34" s="6">
-        <v>6.9140767252738697E-2</v>
+        <v>7.20693192874578E-2</v>
       </c>
       <c r="AI34" s="6">
-        <v>7.8798280869200904E-2</v>
+        <v>8.4540850508860205E-2</v>
       </c>
       <c r="AJ34" s="6">
-        <v>4.2841722616122603E-2</v>
+        <v>4.3742488814161602E-2</v>
       </c>
       <c r="AK34" s="6">
-        <v>8.3297970061168E-2</v>
+        <v>8.5740326004077702E-2</v>
       </c>
       <c r="AL34" s="6"/>
       <c r="AM34" s="6"/>
@@ -4624,22 +4616,22 @@
         <v>4.7592141649650088</v>
       </c>
       <c r="AF35" s="6">
-        <v>0.112093568135435</v>
+        <v>0.108979242560066</v>
       </c>
       <c r="AG35" s="6">
-        <v>0.105896306589069</v>
+        <v>0.108913157507377</v>
       </c>
       <c r="AH35" s="6">
-        <v>7.1088492027079703E-2</v>
+        <v>7.4792864497028294E-2</v>
       </c>
       <c r="AI35" s="6">
-        <v>8.4411435986097502E-2</v>
+        <v>9.1035310526797503E-2</v>
       </c>
       <c r="AJ35" s="6">
-        <v>4.3958015275540198E-2</v>
+        <v>4.4924048978182897E-2</v>
       </c>
       <c r="AK35" s="6">
-        <v>8.4389446205877197E-2</v>
+        <v>8.7320928831170402E-2</v>
       </c>
       <c r="AL35" s="6"/>
       <c r="AM35" s="6"/>
@@ -4740,22 +4732,22 @@
         <v>4.5882055138394051</v>
       </c>
       <c r="AF36" s="6">
-        <v>0.110060000951846</v>
+        <v>0.10702438487474999</v>
       </c>
       <c r="AG36" s="6">
-        <v>0.10454567846493899</v>
+        <v>0.10794309529196799</v>
       </c>
       <c r="AH36" s="6">
-        <v>6.8388197104062201E-2</v>
+        <v>7.2063023473204105E-2</v>
       </c>
       <c r="AI36" s="6">
-        <v>8.63496579790968E-2</v>
+        <v>9.3048444477172199E-2</v>
       </c>
       <c r="AJ36" s="6">
-        <v>4.4915003129524698E-2</v>
+        <v>4.5898643329255299E-2</v>
       </c>
       <c r="AK36" s="6">
-        <v>8.3673062942625095E-2</v>
+        <v>8.6748121320782495E-2</v>
       </c>
       <c r="AL36" s="6"/>
       <c r="AM36" s="6"/>
@@ -4856,22 +4848,22 @@
         <v>4.6699945022016465</v>
       </c>
       <c r="AF37" s="6">
-        <v>0.10836866315504499</v>
+        <v>0.10575742606847501</v>
       </c>
       <c r="AG37" s="6">
-        <v>0.103711844591059</v>
+        <v>0.10657206862799901</v>
       </c>
       <c r="AH37" s="6">
-        <v>7.0029995147167595E-2</v>
+        <v>7.4692753457014399E-2</v>
       </c>
       <c r="AI37" s="6">
-        <v>9.0934835546624501E-2</v>
+        <v>9.8140138883724803E-2</v>
       </c>
       <c r="AJ37" s="6">
-        <v>4.5776939478255098E-2</v>
+        <v>4.6743487796615503E-2</v>
       </c>
       <c r="AK37" s="6">
-        <v>8.4886203763586507E-2</v>
+        <v>8.8271120306097406E-2</v>
       </c>
       <c r="AL37" s="6"/>
       <c r="AM37" s="6"/>
@@ -4972,22 +4964,22 @@
         <v>4.3316318270615994</v>
       </c>
       <c r="AF38" s="6">
-        <v>0.107453873226418</v>
+        <v>0.1050801081163</v>
       </c>
       <c r="AG38" s="6">
-        <v>0.10449340407638499</v>
+        <v>0.107538451310696</v>
       </c>
       <c r="AH38" s="6">
-        <v>7.08997584479127E-2</v>
+        <v>7.6001519367505099E-2</v>
       </c>
       <c r="AI38" s="6">
-        <v>9.3372770418452697E-2</v>
+        <v>0.100563356913128</v>
       </c>
       <c r="AJ38" s="6">
-        <v>4.6322092686742498E-2</v>
+        <v>4.7215091577920601E-2</v>
       </c>
       <c r="AK38" s="6">
-        <v>8.5814258577329397E-2</v>
+        <v>8.94431814616274E-2</v>
       </c>
       <c r="AL38" s="6"/>
       <c r="AM38" s="6"/>
@@ -5088,22 +5080,22 @@
         <v>4.5012320215713331</v>
       </c>
       <c r="AF39" s="6">
-        <v>0.107043358649258</v>
+        <v>0.104795691065783</v>
       </c>
       <c r="AG39" s="6">
-        <v>0.106506290740602</v>
+        <v>0.110110648178467</v>
       </c>
       <c r="AH39" s="6">
-        <v>7.3585884208113003E-2</v>
+        <v>7.9393828947850395E-2</v>
       </c>
       <c r="AI39" s="6">
-        <v>9.4484554316621699E-2</v>
+        <v>0.101372310762955</v>
       </c>
       <c r="AJ39" s="6">
-        <v>4.6624817882560302E-2</v>
+        <v>4.7409888674188098E-2</v>
       </c>
       <c r="AK39" s="6">
-        <v>8.7240073026946405E-2</v>
+        <v>9.1227503391616102E-2</v>
       </c>
       <c r="AL39" s="6"/>
       <c r="AM39" s="6"/>
@@ -5204,22 +5196,22 @@
         <v>4.4252558200787107</v>
       </c>
       <c r="AF40" s="6">
-        <v>0.106979658731471</v>
+        <v>0.104759550728734</v>
       </c>
       <c r="AG40" s="6">
-        <v>0.109105349479625</v>
+        <v>0.113575615851816</v>
       </c>
       <c r="AH40" s="6">
-        <v>7.6731274110509298E-2</v>
+        <v>8.3274561671145497E-2</v>
       </c>
       <c r="AI40" s="6">
-        <v>9.4985431400669604E-2</v>
+        <v>0.10147605345235799</v>
       </c>
       <c r="AJ40" s="6">
-        <v>4.6760593559788802E-2</v>
+        <v>4.7422650408184198E-2</v>
       </c>
       <c r="AK40" s="6">
-        <v>8.8886289685753503E-2</v>
+        <v>9.3179400631037995E-2</v>
       </c>
       <c r="AL40" s="6"/>
       <c r="AM40" s="6"/>
@@ -5320,22 +5312,22 @@
         <v>5.5784965849474233</v>
       </c>
       <c r="AF41" s="6">
-        <v>0.106843782967493</v>
+        <v>0.104729496897344</v>
       </c>
       <c r="AG41" s="6">
-        <v>0.11164943171354</v>
+        <v>0.116628123986028</v>
       </c>
       <c r="AH41" s="6">
-        <v>7.8818770162302307E-2</v>
+        <v>8.5742750547126795E-2</v>
       </c>
       <c r="AI41" s="6">
-        <v>9.5067531544464401E-2</v>
+        <v>0.101118892814499</v>
       </c>
       <c r="AJ41" s="6">
-        <v>4.6902649456939401E-2</v>
+        <v>4.7451442545112202E-2</v>
       </c>
       <c r="AK41" s="6">
-        <v>9.0148166425218501E-2</v>
+        <v>9.4482719785815406E-2</v>
       </c>
       <c r="AL41" s="6"/>
       <c r="AM41" s="6"/>
@@ -5436,22 +5428,22 @@
         <v>5.0356613119452831</v>
       </c>
       <c r="AF42" s="6">
-        <v>0.107287304480498</v>
+        <v>0.10538538089204801</v>
       </c>
       <c r="AG42" s="6">
-        <v>0.117141076379729</v>
+        <v>0.12256290333421101</v>
       </c>
       <c r="AH42" s="6">
-        <v>8.4790358682194103E-2</v>
+        <v>9.2731491343360894E-2</v>
       </c>
       <c r="AI42" s="6">
-        <v>0.109173254113932</v>
+        <v>0.116872134429844</v>
       </c>
       <c r="AJ42" s="6">
-        <v>6.1712104043117597E-2</v>
+        <v>6.36018750694895E-2</v>
       </c>
       <c r="AK42" s="6">
-        <v>9.8652962533303606E-2</v>
+        <v>0.10386850629119999</v>
       </c>
       <c r="AL42" s="6"/>
       <c r="AM42" s="6"/>
@@ -5552,22 +5544,22 @@
         <v>4.5371001870508465</v>
       </c>
       <c r="AF43" s="6">
-        <v>0.107159316809462</v>
+        <v>0.105299279818151</v>
       </c>
       <c r="AG43" s="6">
-        <v>0.119276015195649</v>
+        <v>0.124995978871361</v>
       </c>
       <c r="AH43" s="6">
-        <v>8.6548021675851794E-2</v>
+        <v>9.4599110008455001E-2</v>
       </c>
       <c r="AI43" s="6">
-        <v>0.108086509056205</v>
+        <v>0.11472213379443599</v>
       </c>
       <c r="AJ43" s="6">
-        <v>6.0677587835040701E-2</v>
+        <v>6.1803344816523297E-2</v>
       </c>
       <c r="AK43" s="6">
-        <v>9.9213233041704596E-2</v>
+        <v>0.104169388682366</v>
       </c>
       <c r="AL43" s="6"/>
       <c r="AM43" s="6"/>
@@ -5668,22 +5660,22 @@
         <v>3.7522854603023958</v>
       </c>
       <c r="AF44" s="6">
-        <v>0.10480909975392499</v>
+        <v>0.10298473805629001</v>
       </c>
       <c r="AG44" s="6">
-        <v>0.116050598326079</v>
+        <v>0.121442080902327</v>
       </c>
       <c r="AH44" s="6">
-        <v>8.7046094494732107E-2</v>
+        <v>9.4853952125849197E-2</v>
       </c>
       <c r="AI44" s="6">
-        <v>0.106611165578351</v>
+        <v>0.112282789604915</v>
       </c>
       <c r="AJ44" s="6">
-        <v>5.9647946598906702E-2</v>
+        <v>6.0135160265923401E-2</v>
       </c>
       <c r="AK44" s="6">
-        <v>9.7757335527832404E-2</v>
+        <v>0.10225239783890799</v>
       </c>
       <c r="AL44" s="6"/>
       <c r="AM44" s="6"/>
@@ -5784,22 +5776,22 @@
         <v>2.2775599374066147</v>
       </c>
       <c r="AF45" s="6">
-        <v>0.104199870841421</v>
+        <v>0.102463285040307</v>
       </c>
       <c r="AG45" s="6">
-        <v>0.1136313229769</v>
+        <v>0.118868218831453</v>
       </c>
       <c r="AH45" s="6">
-        <v>8.7464673553047198E-2</v>
+        <v>9.5043981598911004E-2</v>
       </c>
       <c r="AI45" s="6">
-        <v>0.105318279701394</v>
+        <v>0.11020549995477399</v>
       </c>
       <c r="AJ45" s="6">
-        <v>5.8718164344367503E-2</v>
+        <v>5.8684393108517099E-2</v>
       </c>
       <c r="AK45" s="6">
-        <v>9.6752627052488896E-2</v>
+        <v>0.100901266808097</v>
       </c>
       <c r="AL45" s="6"/>
       <c r="AM45" s="6"/>
@@ -5900,22 +5892,22 @@
         <v>3.818017823560993</v>
       </c>
       <c r="AF46" s="6">
-        <v>9.7116019133068804E-2</v>
+        <v>9.5495400935278099E-2</v>
       </c>
       <c r="AG46" s="6">
-        <v>0.10796579861908399</v>
+        <v>0.112798703149118</v>
       </c>
       <c r="AH46" s="6">
-        <v>8.6985991596281495E-2</v>
+        <v>9.4139049618653506E-2</v>
       </c>
       <c r="AI46" s="6">
-        <v>0.103158217915766</v>
+        <v>0.10729432120507899</v>
       </c>
       <c r="AJ46" s="6">
-        <v>5.7696526023282499E-2</v>
+        <v>5.7227421400096498E-2</v>
       </c>
       <c r="AK46" s="6">
-        <v>9.3679809980490997E-2</v>
+        <v>9.73869458421735E-2</v>
       </c>
       <c r="AL46" s="6"/>
       <c r="AM46" s="6"/>
@@ -6016,22 +6008,22 @@
         <v>2.6963875214681465</v>
       </c>
       <c r="AF47" s="6">
-        <v>9.7589084757829694E-2</v>
+        <v>9.6247761508608698E-2</v>
       </c>
       <c r="AG47" s="6">
-        <v>0.110188091031879</v>
+        <v>0.115554245016379</v>
       </c>
       <c r="AH47" s="6">
-        <v>8.8978843973002097E-2</v>
+        <v>9.6316614973407794E-2</v>
       </c>
       <c r="AI47" s="6">
-        <v>0.104587649310598</v>
+        <v>0.108466615188774</v>
       </c>
       <c r="AJ47" s="6">
-        <v>5.7402829168835302E-2</v>
+        <v>5.6617629183225202E-2</v>
       </c>
       <c r="AK47" s="6">
-        <v>9.5090899139025201E-2</v>
+        <v>9.8899719068436004E-2</v>
       </c>
       <c r="AL47" s="6"/>
       <c r="AM47" s="6"/>
@@ -6132,22 +6124,22 @@
         <v>2.9961334919196503</v>
       </c>
       <c r="AF48" s="6">
-        <v>0.102611005000932</v>
+        <v>0.101557354786264</v>
       </c>
       <c r="AG48" s="6">
-        <v>0.119649167817657</v>
+        <v>0.12626431447896799</v>
       </c>
       <c r="AH48" s="6">
-        <v>9.2839604621336794E-2</v>
+        <v>0.10073463718297</v>
       </c>
       <c r="AI48" s="6">
-        <v>0.10690876295094</v>
+        <v>0.110607463959949</v>
       </c>
       <c r="AJ48" s="6">
-        <v>5.7245419887269E-2</v>
+        <v>5.6188297484683403E-2</v>
       </c>
       <c r="AK48" s="6">
-        <v>9.9567408076897804E-2</v>
+        <v>0.103770008691476</v>
       </c>
       <c r="AL48" s="6"/>
       <c r="AM48" s="6"/>
@@ -6248,22 +6240,22 @@
         <v>2.5035745600284542</v>
       </c>
       <c r="AF49" s="6">
-        <v>0.102179485453903</v>
+        <v>0.101201083672944</v>
       </c>
       <c r="AG49" s="6">
-        <v>0.119033210455339</v>
+        <v>0.12545964574243501</v>
       </c>
       <c r="AH49" s="6">
-        <v>9.7086013398996293E-2</v>
+        <v>0.105452680908406</v>
       </c>
       <c r="AI49" s="6">
-        <v>0.10941838000109599</v>
+        <v>0.112901183297302</v>
       </c>
       <c r="AJ49" s="6">
-        <v>5.7140311724493402E-2</v>
+        <v>5.5843732335579703E-2</v>
       </c>
       <c r="AK49" s="6">
-        <v>0.10101157732961499</v>
+        <v>0.105201013291849</v>
       </c>
       <c r="AL49" s="6"/>
       <c r="AM49" s="6"/>
@@ -6364,22 +6356,22 @@
         <v>2.7779538257489023</v>
       </c>
       <c r="AF50" s="6">
-        <v>0.10394881210861601</v>
+        <v>0.103131229436296</v>
       </c>
       <c r="AG50" s="6">
-        <v>0.13560575217941301</v>
+        <v>0.14399793518047099</v>
       </c>
       <c r="AH50" s="6">
-        <v>0.103512859766635</v>
+        <v>0.112768075579251</v>
       </c>
       <c r="AI50" s="6">
-        <v>0.113587355895045</v>
+        <v>0.116932414652197</v>
       </c>
       <c r="AJ50" s="6">
-        <v>5.7304323837801402E-2</v>
+        <v>5.5798776031248401E-2</v>
       </c>
       <c r="AK50" s="6">
-        <v>0.107924617600859</v>
+        <v>0.112745861614836</v>
       </c>
       <c r="AL50" s="6"/>
       <c r="AM50" s="6"/>
@@ -6480,22 +6472,22 @@
         <v>5.411164663720669</v>
       </c>
       <c r="AF51" s="6">
-        <v>0.102504186942936</v>
+        <v>0.10167730955423</v>
       </c>
       <c r="AG51" s="6">
-        <v>0.12797515054512801</v>
+        <v>0.13469227470935899</v>
       </c>
       <c r="AH51" s="6">
-        <v>0.10514045222792701</v>
+        <v>0.113962556505965</v>
       </c>
       <c r="AI51" s="6">
-        <v>0.121473794425574</v>
+        <v>0.124851127707645</v>
       </c>
       <c r="AJ51" s="6">
-        <v>5.7981427539131297E-2</v>
+        <v>5.6285102223725798E-2</v>
       </c>
       <c r="AK51" s="6">
-        <v>0.108239799177324</v>
+        <v>0.11252903189855901</v>
       </c>
       <c r="AL51" s="6"/>
       <c r="AM51" s="6"/>
@@ -6596,22 +6588,22 @@
         <v>5.2813509537243064</v>
       </c>
       <c r="AF52" s="6">
-        <v>0.101131572397543</v>
+        <v>0.10033753413980701</v>
       </c>
       <c r="AG52" s="6">
-        <v>0.121181970385159</v>
+        <v>0.12677993283913</v>
       </c>
       <c r="AH52" s="6">
-        <v>9.4681204421971796E-2</v>
+        <v>0.100697033934272</v>
       </c>
       <c r="AI52" s="6">
-        <v>8.8657348474770803E-2</v>
+        <v>8.9511837278956397E-2</v>
       </c>
       <c r="AJ52" s="6">
-        <v>3.1350484959917803E-2</v>
+        <v>2.9816176542147299E-2</v>
       </c>
       <c r="AK52" s="6">
-        <v>9.2132421475816406E-2</v>
+        <v>9.4964198480292E-2</v>
       </c>
       <c r="AL52" s="6"/>
       <c r="AM52" s="6"/>
@@ -6712,22 +6704,22 @@
         <v>5.5307404812511507</v>
       </c>
       <c r="AF53" s="6">
-        <v>0.100375956617184</v>
+        <v>9.96605307802957E-2</v>
       </c>
       <c r="AG53" s="6">
-        <v>0.117884823397641</v>
+        <v>0.12308617131937501</v>
       </c>
       <c r="AH53" s="6">
-        <v>8.8540003010642299E-2</v>
+        <v>9.3307672219618998E-2</v>
       </c>
       <c r="AI53" s="6">
-        <v>8.2844939215447E-2</v>
+        <v>8.3765835467290495E-2</v>
       </c>
       <c r="AJ53" s="6">
-        <v>3.2531256463637401E-2</v>
+        <v>3.1395102746975302E-2</v>
       </c>
       <c r="AK53" s="6">
-        <v>8.8523091664214806E-2</v>
+        <v>9.1021014393685803E-2</v>
       </c>
       <c r="AL53" s="6"/>
       <c r="AM53" s="6"/>
@@ -6828,22 +6820,22 @@
         <v>6.8089865956245887</v>
       </c>
       <c r="AF54" s="6">
-        <v>9.9663808165729006E-2</v>
+        <v>9.9038323005309001E-2</v>
       </c>
       <c r="AG54" s="6">
-        <v>0.114903887514435</v>
+        <v>0.11985232795770701</v>
       </c>
       <c r="AH54" s="6">
-        <v>8.2290224910281207E-2</v>
+        <v>8.6580461429958205E-2</v>
       </c>
       <c r="AI54" s="6">
-        <v>8.5318802443126104E-2</v>
+        <v>8.69774042592181E-2</v>
       </c>
       <c r="AJ54" s="6">
-        <v>3.3793479559130202E-2</v>
+        <v>3.3025654973085398E-2</v>
       </c>
       <c r="AK54" s="6">
-        <v>8.6760450041083001E-2</v>
+        <v>8.92338802576014E-2</v>
       </c>
       <c r="AL54" s="6"/>
       <c r="AM54" s="6"/>
@@ -6944,22 +6936,22 @@
         <v>9.8184741985319235</v>
       </c>
       <c r="AF55" s="6">
-        <v>9.9586249084720704E-2</v>
+        <v>9.9074670605313303E-2</v>
       </c>
       <c r="AG55" s="6">
-        <v>0.11496702176134301</v>
+        <v>0.120072331839099</v>
       </c>
       <c r="AH55" s="6">
-        <v>8.2369188277287494E-2</v>
+        <v>8.6864430707529097E-2</v>
       </c>
       <c r="AI55" s="6">
-        <v>8.2493817346365905E-2</v>
+        <v>8.42249382848103E-2</v>
       </c>
       <c r="AJ55" s="6">
-        <v>3.4314204640785197E-2</v>
+        <v>3.3732903391483597E-2</v>
       </c>
       <c r="AK55" s="6">
-        <v>8.62096509034362E-2</v>
+        <v>8.8905625225759399E-2</v>
       </c>
       <c r="AL55" s="6"/>
       <c r="AM55" s="6"/>
@@ -7060,22 +7052,22 @@
         <v>11.2713779135191</v>
       </c>
       <c r="AF56" s="6">
-        <v>9.9723832257704398E-2</v>
+        <v>9.9322673492932501E-2</v>
       </c>
       <c r="AG56" s="6">
-        <v>0.116009919359765</v>
+        <v>0.12136012953346401</v>
       </c>
       <c r="AH56" s="6">
-        <v>8.3606209877864796E-2</v>
+        <v>8.8639833553189107E-2</v>
       </c>
       <c r="AI56" s="6">
-        <v>8.2505114788291006E-2</v>
+        <v>8.4456393366020593E-2</v>
       </c>
       <c r="AJ56" s="6">
-        <v>3.4201928865636097E-2</v>
+        <v>3.3890720680858299E-2</v>
       </c>
       <c r="AK56" s="6">
-        <v>8.6808595937349603E-2</v>
+        <v>8.9816240511552306E-2</v>
       </c>
       <c r="AL56" s="6"/>
       <c r="AM56" s="6"/>
@@ -7176,22 +7168,22 @@
         <v>9.6563000420584189</v>
       </c>
       <c r="AF57" s="6">
-        <v>0.100438715781695</v>
+        <v>0.10015153767384</v>
       </c>
       <c r="AG57" s="6">
-        <v>0.11981592679476399</v>
+        <v>0.125685836201507</v>
       </c>
       <c r="AH57" s="6">
-        <v>8.7252271880946197E-2</v>
+        <v>9.3130396410556898E-2</v>
       </c>
       <c r="AI57" s="6">
-        <v>9.0430124516079596E-2</v>
+        <v>9.3135233331074499E-2</v>
       </c>
       <c r="AJ57" s="6">
-        <v>3.9642406009635103E-2</v>
+        <v>3.9860704972755297E-2</v>
       </c>
       <c r="AK57" s="6">
-        <v>9.14200292171954E-2</v>
+        <v>9.4961650706096898E-2</v>
       </c>
       <c r="AL57" s="6"/>
       <c r="AM57" s="6"/>
@@ -7292,22 +7284,22 @@
         <v>7.7381955805552849</v>
       </c>
       <c r="AF58" s="6">
-        <v>0.10151778070421601</v>
+        <v>0.101329508624612</v>
       </c>
       <c r="AG58" s="6">
-        <v>0.125605183047169</v>
+        <v>0.132123470814451</v>
       </c>
       <c r="AH58" s="6">
-        <v>9.5320901961121404E-2</v>
+        <v>0.10249995080280901</v>
       </c>
       <c r="AI58" s="6">
-        <v>9.9224042871969703E-2</v>
+        <v>0.102760233466409</v>
       </c>
       <c r="AJ58" s="6">
-        <v>4.0033132136061599E-2</v>
+        <v>4.03621122039255E-2</v>
       </c>
       <c r="AK58" s="6">
-        <v>9.71212640182465E-2</v>
+        <v>0.10136146193881</v>
       </c>
       <c r="AL58" s="6"/>
       <c r="AM58" s="6"/>
@@ -7408,22 +7400,22 @@
         <v>6.050577834166404</v>
       </c>
       <c r="AF59" s="6">
-        <v>9.4925878619860807E-2</v>
+        <v>9.2042102866222095E-2</v>
       </c>
       <c r="AG59" s="6">
-        <v>9.6714218065802396E-2</v>
+        <v>9.9981410963138104E-2</v>
       </c>
       <c r="AH59" s="6">
-        <v>8.7241673536421704E-2</v>
+        <v>9.24986995341429E-2</v>
       </c>
       <c r="AI59" s="6">
-        <v>9.2643572408546399E-2</v>
+        <v>9.5344397428102301E-2</v>
       </c>
       <c r="AJ59" s="6">
-        <v>3.9947521754657801E-2</v>
+        <v>4.0325573513762897E-2</v>
       </c>
       <c r="AK59" s="6">
-        <v>8.5537272967671399E-2</v>
+        <v>8.8004517061475704E-2</v>
       </c>
       <c r="AL59" s="6"/>
       <c r="AM59" s="6"/>
@@ -7524,22 +7516,22 @@
         <v>5.9554942179740777</v>
       </c>
       <c r="AF60" s="6">
-        <v>7.6095981772360197E-2</v>
+        <v>7.2831401330337303E-2</v>
       </c>
       <c r="AG60" s="6">
-        <v>7.6340015357688307E-2</v>
+        <v>8.2187740503484596E-2</v>
       </c>
       <c r="AH60" s="6">
-        <v>7.8477278489292104E-2</v>
+        <v>8.5303708180393803E-2</v>
       </c>
       <c r="AI60" s="6">
-        <v>8.7216520884407497E-2</v>
+        <v>8.9480961153959399E-2</v>
       </c>
       <c r="AJ60" s="6">
-        <v>3.9868313054700399E-2</v>
+        <v>4.0293247514875501E-2</v>
       </c>
       <c r="AK60" s="6">
-        <v>7.4606305100212197E-2</v>
+        <v>7.7991076687486602E-2</v>
       </c>
       <c r="AL60" s="6"/>
       <c r="AM60" s="6"/>
@@ -7640,22 +7632,22 @@
         <v>6.4642742637365913</v>
       </c>
       <c r="AF61" s="6">
-        <v>7.8863267685584895E-2</v>
+        <v>7.6006823215084104E-2</v>
       </c>
       <c r="AG61" s="6">
-        <v>7.7304467791622394E-2</v>
+        <v>8.7033774089596005E-2</v>
       </c>
       <c r="AH61" s="6">
-        <v>7.3931867228811898E-2</v>
+        <v>7.7462643293857297E-2</v>
       </c>
       <c r="AI61" s="6">
-        <v>8.3805652954805201E-2</v>
+        <v>8.6006011724947803E-2</v>
       </c>
       <c r="AJ61" s="6">
-        <v>3.9933970261517099E-2</v>
+        <v>4.0415791023996797E-2</v>
       </c>
       <c r="AK61" s="6">
-        <v>7.3255998328910998E-2</v>
+        <v>7.6845579505558495E-2</v>
       </c>
       <c r="AL61" s="6"/>
       <c r="AM61" s="6"/>
@@ -7756,22 +7748,22 @@
         <v>6.0324268579478257</v>
       </c>
       <c r="AF62" s="6">
-        <v>8.0992189210760304E-2</v>
+        <v>7.8909095934689394E-2</v>
       </c>
       <c r="AG62" s="6">
-        <v>8.3007394370559207E-2</v>
+        <v>9.4303217992278796E-2</v>
       </c>
       <c r="AH62" s="6">
-        <v>8.0453475886994599E-2</v>
+        <v>8.5326150649371504E-2</v>
       </c>
       <c r="AI62" s="6">
-        <v>8.2175087728674406E-2</v>
+        <v>8.4493238013269398E-2</v>
       </c>
       <c r="AJ62" s="6">
-        <v>4.0079124133990202E-2</v>
+        <v>4.0617165189108399E-2</v>
       </c>
       <c r="AK62" s="6">
-        <v>7.6234331058996796E-2</v>
+        <v>8.0664089543502002E-2</v>
       </c>
       <c r="AL62" s="6"/>
       <c r="AM62" s="6"/>
@@ -7872,22 +7864,22 @@
         <v>4.7707118050080766</v>
       </c>
       <c r="AF63" s="6">
-        <v>8.2758894363294006E-2</v>
+        <v>8.1356852312589198E-2</v>
       </c>
       <c r="AG63" s="6">
-        <v>8.6221211396000405E-2</v>
+        <v>9.8473522001717106E-2</v>
       </c>
       <c r="AH63" s="6">
-        <v>7.8740492809042301E-2</v>
+        <v>8.3008145527199401E-2</v>
       </c>
       <c r="AI63" s="6">
-        <v>8.1558603481328804E-2</v>
+        <v>8.4335148807271804E-2</v>
       </c>
       <c r="AJ63" s="6">
-        <v>4.0426305220992997E-2</v>
+        <v>4.1030944589941103E-2</v>
       </c>
       <c r="AK63" s="6">
-        <v>7.6756568454100504E-2</v>
+        <v>8.1446068040609304E-2</v>
       </c>
       <c r="AL63" s="6"/>
       <c r="AM63" s="6"/>
@@ -7988,22 +7980,22 @@
         <v>6.2164693322383613</v>
       </c>
       <c r="AF64" s="6">
-        <v>7.9294415416814298E-2</v>
+        <v>7.8391217268108299E-2</v>
       </c>
       <c r="AG64" s="6">
-        <v>8.2397672729986701E-2</v>
+        <v>9.3316473261499097E-2</v>
       </c>
       <c r="AH64" s="6">
-        <v>7.8131593717818804E-2</v>
+        <v>8.2475133374793397E-2</v>
       </c>
       <c r="AI64" s="6">
-        <v>8.0966823168268198E-2</v>
+        <v>8.3899615352939494E-2</v>
       </c>
       <c r="AJ64" s="6">
-        <v>4.0745415940220603E-2</v>
+        <v>4.1399939562684999E-2</v>
       </c>
       <c r="AK64" s="6">
-        <v>7.5114030259248205E-2</v>
+        <v>7.9607911709023996E-2</v>
       </c>
       <c r="AL64" s="6"/>
       <c r="AM64" s="6"/>
@@ -8104,22 +8096,22 @@
         <v>6.2127424014585486</v>
       </c>
       <c r="AF65" s="6">
-        <v>8.11887044661352E-2</v>
+        <v>8.0927003728299696E-2</v>
       </c>
       <c r="AG65" s="6">
-        <v>8.7248437659718001E-2</v>
+        <v>9.9406075712471204E-2</v>
       </c>
       <c r="AH65" s="6">
-        <v>8.4298234946012005E-2</v>
+        <v>8.9851693995428805E-2</v>
       </c>
       <c r="AI65" s="6">
-        <v>8.2725984834345498E-2</v>
+        <v>8.6055577625754401E-2</v>
       </c>
       <c r="AJ65" s="6">
-        <v>4.1008340280523699E-2</v>
+        <v>4.1695655339494597E-2</v>
       </c>
       <c r="AK65" s="6">
-        <v>7.8576608233416501E-2</v>
+        <v>8.3897071348503605E-2</v>
       </c>
       <c r="AL65" s="6"/>
       <c r="AM65" s="6"/>
@@ -8220,22 +8212,22 @@
         <v>6.6753941139458206</v>
       </c>
       <c r="AF66" s="6">
-        <v>8.3020432297771701E-2</v>
+        <v>8.3322137269434299E-2</v>
       </c>
       <c r="AG66" s="6">
-        <v>9.2211327684693006E-2</v>
+        <v>0.10551142622496799</v>
       </c>
       <c r="AH66" s="6">
-        <v>9.0123641205917704E-2</v>
+        <v>9.67595283608709E-2</v>
       </c>
       <c r="AI66" s="6">
-        <v>8.1956280328307096E-2</v>
+        <v>8.5332667377959096E-2</v>
       </c>
       <c r="AJ66" s="6">
-        <v>4.1242082376784603E-2</v>
+        <v>4.1950697659608599E-2</v>
       </c>
       <c r="AK66" s="6">
-        <v>8.1448751144336806E-2</v>
+        <v>8.7415040554201504E-2</v>
       </c>
       <c r="AL66" s="6"/>
       <c r="AM66" s="6"/>
@@ -8336,22 +8328,22 @@
         <v>6.0659258202697686</v>
       </c>
       <c r="AF67" s="6">
-        <v>8.4695386660154304E-2</v>
+        <v>8.5478818600180001E-2</v>
       </c>
       <c r="AG67" s="6">
-        <v>9.6749845491716002E-2</v>
+        <v>0.110968717823174</v>
       </c>
       <c r="AH67" s="6">
-        <v>9.7235663614045398E-2</v>
+        <v>0.105000418490312</v>
       </c>
       <c r="AI67" s="6">
-        <v>8.2470182836850106E-2</v>
+        <v>8.6323206624098106E-2</v>
       </c>
       <c r="AJ67" s="6">
-        <v>4.1515904258063799E-2</v>
+        <v>4.2241185962564799E-2</v>
       </c>
       <c r="AK67" s="6">
-        <v>8.4797241318593203E-2</v>
+        <v>9.1439144614609502E-2</v>
       </c>
       <c r="AL67" s="6"/>
       <c r="AM67" s="6"/>
@@ -8452,22 +8444,22 @@
         <v>6.5984407884510432</v>
       </c>
       <c r="AF68" s="6">
-        <v>8.6041453560064707E-2</v>
+        <v>8.7214874139418003E-2</v>
       </c>
       <c r="AG68" s="6">
-        <v>9.9845350242223393E-2</v>
+        <v>0.11397584739538499</v>
       </c>
       <c r="AH68" s="6">
-        <v>9.5772051098041197E-2</v>
+        <v>0.10335372197557501</v>
       </c>
       <c r="AI68" s="6">
-        <v>8.3066130831378496E-2</v>
+        <v>8.7068264558493605E-2</v>
       </c>
       <c r="AJ68" s="6">
-        <v>4.19447467475755E-2</v>
+        <v>4.2697264471858398E-2</v>
       </c>
       <c r="AK68" s="6">
-        <v>8.5571603984319303E-2</v>
+        <v>9.2233278634091101E-2</v>
       </c>
       <c r="AL68" s="6"/>
       <c r="AM68" s="6"/>
@@ -8568,22 +8560,22 @@
         <v>5.7709830786818017</v>
       </c>
       <c r="AF69" s="6">
-        <v>8.7085834375695406E-2</v>
+        <v>8.8566655453493098E-2</v>
       </c>
       <c r="AG69" s="6">
-        <v>0.101950466748445</v>
+        <v>0.116013671893204</v>
       </c>
       <c r="AH69" s="6">
-        <v>9.6431913573476497E-2</v>
+        <v>0.103723634221516</v>
       </c>
       <c r="AI69" s="6">
-        <v>8.4635688184685698E-2</v>
+        <v>8.8876655317283795E-2</v>
       </c>
       <c r="AJ69" s="6">
-        <v>4.2500088181447501E-2</v>
+        <v>4.3281491686910298E-2</v>
       </c>
       <c r="AK69" s="6">
-        <v>8.6841683309899803E-2</v>
+        <v>9.35059075510844E-2</v>
       </c>
       <c r="AL69" s="6"/>
       <c r="AM69" s="6"/>
@@ -8684,22 +8676,22 @@
         <v>6.1921004856623441</v>
       </c>
       <c r="AF70" s="6">
-        <v>8.7980698260323106E-2</v>
+        <v>8.96951277010022E-2</v>
       </c>
       <c r="AG70" s="6">
-        <v>0.10155511580184599</v>
+        <v>0.11480028773437401</v>
       </c>
       <c r="AH70" s="6">
-        <v>9.6045565389183393E-2</v>
+        <v>0.102811360652101</v>
       </c>
       <c r="AI70" s="6">
-        <v>8.5225889433468205E-2</v>
+        <v>8.9543367366822904E-2</v>
       </c>
       <c r="AJ70" s="6">
-        <v>4.2886600118814899E-2</v>
+        <v>4.36645486733407E-2</v>
       </c>
       <c r="AK70" s="6">
-        <v>8.6944691286286901E-2</v>
+        <v>9.3320731557989006E-2</v>
       </c>
       <c r="AL70" s="6"/>
       <c r="AM70" s="6"/>
@@ -8800,22 +8792,22 @@
         <v>6.8419991943043712</v>
       </c>
       <c r="AF71" s="6">
-        <v>8.9254396324067301E-2</v>
+        <v>9.1214357170673305E-2</v>
       </c>
       <c r="AG71" s="6">
-        <v>0.105361593797258</v>
+        <v>0.119025442400696</v>
       </c>
       <c r="AH71" s="6">
-        <v>9.8731246509702802E-2</v>
+        <v>0.10583553408082</v>
       </c>
       <c r="AI71" s="6">
-        <v>8.5190723699878401E-2</v>
+        <v>8.9451683716801497E-2</v>
       </c>
       <c r="AJ71" s="6">
-        <v>4.3159636019392898E-2</v>
+        <v>4.3913952587910497E-2</v>
       </c>
       <c r="AK71" s="6">
-        <v>8.8790329269558793E-2</v>
+        <v>9.5367609832966493E-2</v>
       </c>
       <c r="AL71" s="6"/>
       <c r="AM71" s="6"/>
@@ -8916,22 +8908,22 @@
         <v>6.80453833061474</v>
       </c>
       <c r="AF72" s="6">
-        <v>8.96990623875734E-2</v>
+        <v>9.1777136504443094E-2</v>
       </c>
       <c r="AG72" s="6">
-        <v>0.105185306717848</v>
+        <v>0.118063731508931</v>
       </c>
       <c r="AH72" s="6">
-        <v>9.3598907547456298E-2</v>
+        <v>9.9498900846121896E-2</v>
       </c>
       <c r="AI72" s="6">
-        <v>8.7121618432897299E-2</v>
+        <v>9.1556343642822904E-2</v>
       </c>
       <c r="AJ72" s="6">
-        <v>4.3920231303471599E-2</v>
+        <v>4.4699669371130901E-2</v>
       </c>
       <c r="AK72" s="6">
-        <v>8.8013412873221397E-2</v>
+        <v>9.4129536960568694E-2</v>
       </c>
       <c r="AL72" s="6"/>
       <c r="AM72" s="6"/>
@@ -9032,22 +9024,22 @@
         <v>7.1162281247486803</v>
       </c>
       <c r="AF73" s="6">
-        <v>9.0080385364149904E-2</v>
+        <v>9.2250625085702503E-2</v>
       </c>
       <c r="AG73" s="6">
-        <v>0.105241627794086</v>
+        <v>0.11784518303939701</v>
       </c>
       <c r="AH73" s="6">
-        <v>9.9013235962739199E-2</v>
+        <v>0.106295305745313</v>
       </c>
       <c r="AI73" s="6">
-        <v>9.0644589927426897E-2</v>
+        <v>9.5390177393658002E-2</v>
       </c>
       <c r="AJ73" s="6">
-        <v>4.4663945801796501E-2</v>
+        <v>4.54466284630815E-2</v>
       </c>
       <c r="AK73" s="6">
-        <v>9.0380548501097793E-2</v>
+        <v>9.6881623697113298E-2</v>
       </c>
       <c r="AL73" s="6"/>
       <c r="AM73" s="6"/>
@@ -9148,22 +9140,22 @@
         <v>5.4275133110877505</v>
       </c>
       <c r="AF74" s="6">
-        <v>9.0315867696047797E-2</v>
+        <v>9.2547422489839604E-2</v>
       </c>
       <c r="AG74" s="6">
-        <v>0.10410270582268299</v>
+        <v>0.115907714308274</v>
       </c>
       <c r="AH74" s="6">
-        <v>9.6985389678754794E-2</v>
+        <v>0.102630162216981</v>
       </c>
       <c r="AI74" s="6">
-        <v>9.4738339788322204E-2</v>
+        <v>9.9822209695047806E-2</v>
       </c>
       <c r="AJ74" s="6">
-        <v>4.5460083628424103E-2</v>
+        <v>4.6234305221523997E-2</v>
       </c>
       <c r="AK74" s="6">
-        <v>9.0609150657976395E-2</v>
+        <v>9.6557613528444997E-2</v>
       </c>
       <c r="AL74" s="6"/>
       <c r="AM74" s="6"/>
@@ -9264,22 +9256,22 @@
         <v>8.6994845282365674</v>
       </c>
       <c r="AF75" s="6">
-        <v>9.8847235668932804E-2</v>
+        <v>0.101909773584912</v>
       </c>
       <c r="AG75" s="6">
-        <v>0.115064156385549</v>
+        <v>0.12907905256534899</v>
       </c>
       <c r="AH75" s="6">
-        <v>0.10207753708211501</v>
+        <v>0.10843203271556801</v>
       </c>
       <c r="AI75" s="6">
-        <v>9.7592899907510994E-2</v>
+        <v>0.10270514492966901</v>
       </c>
       <c r="AJ75" s="6">
-        <v>4.6083503024825501E-2</v>
+        <v>4.6813813602452001E-2</v>
       </c>
       <c r="AK75" s="6">
-        <v>9.6503623989006998E-2</v>
+        <v>0.10328707953984299</v>
       </c>
       <c r="AL75" s="6"/>
       <c r="AM75" s="6"/>
@@ -9380,22 +9372,22 @@
         <v>7.3144456687566972</v>
       </c>
       <c r="AF76" s="6">
-        <v>9.8877778379797096E-2</v>
+        <v>0.101705632917742</v>
       </c>
       <c r="AG76" s="6">
-        <v>0.11532277935945601</v>
+        <v>0.12852864218228499</v>
       </c>
       <c r="AH76" s="6">
-        <v>0.101265172932497</v>
+        <v>0.10704540580324801</v>
       </c>
       <c r="AI76" s="6">
-        <v>9.2997894058828606E-2</v>
+        <v>9.7229377508274706E-2</v>
       </c>
       <c r="AJ76" s="6">
-        <v>4.5319209235904101E-2</v>
+        <v>4.5853927115456598E-2</v>
       </c>
       <c r="AK76" s="6">
-        <v>9.52388145596446E-2</v>
+        <v>0.10142128981644701</v>
       </c>
       <c r="AL76" s="6"/>
       <c r="AM76" s="6"/>
@@ -9496,22 +9488,22 @@
         <v>8.2573379628323451</v>
       </c>
       <c r="AF77" s="6">
-        <v>9.8929572619698203E-2</v>
+        <v>0.101550952929431</v>
       </c>
       <c r="AG77" s="6">
-        <v>0.11787758466369599</v>
+        <v>0.13122842975684801</v>
       </c>
       <c r="AH77" s="6">
-        <v>0.10480721085810001</v>
+        <v>0.11087410629258</v>
       </c>
       <c r="AI77" s="6">
-        <v>9.4822207579183304E-2</v>
+        <v>9.9075042709366304E-2</v>
       </c>
       <c r="AJ77" s="6">
-        <v>4.5786342363457501E-2</v>
+        <v>4.6284045030603002E-2</v>
       </c>
       <c r="AK77" s="6">
-        <v>9.7286279691965405E-2</v>
+        <v>0.10354991970644099</v>
       </c>
       <c r="AL77" s="6"/>
       <c r="AM77" s="6"/>
@@ -9612,22 +9604,22 @@
         <v>9.6678441455932074</v>
       </c>
       <c r="AF78" s="6">
-        <v>9.9134859551254798E-2</v>
+        <v>0.10158239237899599</v>
       </c>
       <c r="AG78" s="6">
-        <v>0.118834840897809</v>
+        <v>0.131578521248884</v>
       </c>
       <c r="AH78" s="6">
-        <v>0.104347454746678</v>
+        <v>0.109939935912369</v>
       </c>
       <c r="AI78" s="6">
-        <v>9.5732028372278205E-2</v>
+        <v>9.9871665846616206E-2</v>
       </c>
       <c r="AJ78" s="6">
-        <v>4.6130823423493603E-2</v>
+        <v>4.6572823639686102E-2</v>
       </c>
       <c r="AK78" s="6">
-        <v>9.7682651121552194E-2</v>
+        <v>0.103610562667854</v>
       </c>
       <c r="AL78" s="6"/>
       <c r="AM78" s="6"/>
@@ -9728,22 +9720,22 @@
         <v>8.849735515448387</v>
       </c>
       <c r="AF79" s="6">
-        <v>9.9439008004649804E-2</v>
+        <v>0.101734660051523</v>
       </c>
       <c r="AG79" s="6">
-        <v>0.120308029380037</v>
+        <v>0.13260837944022899</v>
       </c>
       <c r="AH79" s="6">
-        <v>0.105171240714361</v>
+        <v>0.11052905277196499</v>
       </c>
       <c r="AI79" s="6">
-        <v>9.6681053826832702E-2</v>
+        <v>0.10070496875236599</v>
       </c>
       <c r="AJ79" s="6">
-        <v>4.6399989445747303E-2</v>
+        <v>4.6776844384850101E-2</v>
       </c>
       <c r="AK79" s="6">
-        <v>9.8554572379021405E-2</v>
+        <v>0.104252887815638</v>
       </c>
       <c r="AL79" s="6"/>
       <c r="AM79" s="6"/>
@@ -9844,22 +9836,22 @@
         <v>8.8077985717156082</v>
       </c>
       <c r="AF80" s="6">
-        <v>0.10057939435796499</v>
+        <v>0.102808357076906</v>
       </c>
       <c r="AG80" s="6">
-        <v>0.12009031990982801</v>
+        <v>0.131562676343742</v>
       </c>
       <c r="AH80" s="6">
-        <v>9.6158190828242396E-2</v>
+        <v>9.9792345212202399E-2</v>
       </c>
       <c r="AI80" s="6">
-        <v>9.3557444204950005E-2</v>
+        <v>9.7091869616976301E-2</v>
       </c>
       <c r="AJ80" s="6">
-        <v>4.6113864402879297E-2</v>
+        <v>4.6379176006877403E-2</v>
       </c>
       <c r="AK80" s="6">
-        <v>9.5514206785739797E-2</v>
+        <v>0.100397872371635</v>
       </c>
       <c r="AL80" s="6"/>
       <c r="AM80" s="6"/>
@@ -9960,22 +9952,22 @@
         <v>9.6280034963541539</v>
       </c>
       <c r="AF81" s="6">
-        <v>0.101862579366754</v>
+        <v>0.10401502857723099</v>
       </c>
       <c r="AG81" s="6">
-        <v>0.12705405576859199</v>
+        <v>0.139312875742612</v>
       </c>
       <c r="AH81" s="6">
-        <v>9.9045080246676798E-2</v>
+        <v>0.10322658683849401</v>
       </c>
       <c r="AI81" s="6">
-        <v>8.8798107997807199E-2</v>
+        <v>9.17176894835319E-2</v>
       </c>
       <c r="AJ81" s="6">
-        <v>4.5736858928706402E-2</v>
+        <v>4.5903099571834402E-2</v>
       </c>
       <c r="AK81" s="6">
-        <v>9.7074550889389696E-2</v>
+        <v>0.102136191535937</v>
       </c>
       <c r="AL81" s="6"/>
       <c r="AM81" s="6"/>
@@ -10076,22 +10068,22 @@
         <v>8.7775342189468475</v>
       </c>
       <c r="AF82" s="6">
-        <v>0.102648513933222</v>
+        <v>0.104656183373232</v>
       </c>
       <c r="AG82" s="6">
-        <v>0.13168879299590699</v>
+        <v>0.14404782237317099</v>
       </c>
       <c r="AH82" s="6">
-        <v>0.10743734111181499</v>
+        <v>0.11254098233275101</v>
       </c>
       <c r="AI82" s="6">
-        <v>8.8987842520897004E-2</v>
+        <v>9.2004671109019498E-2</v>
       </c>
       <c r="AJ82" s="6">
-        <v>4.5643872153373399E-2</v>
+        <v>4.57528544289377E-2</v>
       </c>
       <c r="AK82" s="6">
-        <v>0.100557915737801</v>
+        <v>0.105889393825096</v>
       </c>
       <c r="AL82" s="6"/>
       <c r="AM82" s="6"/>
@@ -10192,22 +10184,22 @@
         <v>7.488359046499049</v>
       </c>
       <c r="AF83" s="6">
-        <v>0.102172950522931</v>
+        <v>0.103908947117544</v>
       </c>
       <c r="AG83" s="6">
-        <v>0.127337967551233</v>
+        <v>0.13789449417878699</v>
       </c>
       <c r="AH83" s="6">
-        <v>0.105946382907067</v>
+        <v>0.110458063240864</v>
       </c>
       <c r="AI83" s="6">
-        <v>8.9236736243217402E-2</v>
+        <v>9.2330517220155298E-2</v>
       </c>
       <c r="AJ83" s="6">
-        <v>4.58194275790339E-2</v>
+        <v>4.5898843960805999E-2</v>
       </c>
       <c r="AK83" s="6">
-        <v>9.9112484775945295E-2</v>
+        <v>0.103832953466265</v>
       </c>
       <c r="AL83" s="6"/>
       <c r="AM83" s="6"/>
@@ -10308,22 +10300,22 @@
         <v>7.2995139134214071</v>
       </c>
       <c r="AF84" s="6">
-        <v>9.4632630633485496E-2</v>
+        <v>9.5665670898164995E-2</v>
       </c>
       <c r="AG84" s="6">
-        <v>0.113896735636371</v>
+        <v>0.12153026579786499</v>
       </c>
       <c r="AH84" s="6">
-        <v>0.101198264981083</v>
+        <v>0.104774523047457</v>
       </c>
       <c r="AI84" s="6">
-        <v>8.7853801170571802E-2</v>
+        <v>9.0882738466589896E-2</v>
       </c>
       <c r="AJ84" s="6">
-        <v>4.5730242883095802E-2</v>
+        <v>4.5760398312217697E-2</v>
       </c>
       <c r="AK84" s="6">
-        <v>9.3231782060163207E-2</v>
+        <v>9.6884739208214998E-2</v>
       </c>
       <c r="AL84" s="6"/>
       <c r="AM84" s="6"/>
@@ -10424,22 +10416,22 @@
         <v>7.0523039444982061</v>
       </c>
       <c r="AF85" s="6">
-        <v>9.5362862701930007E-2</v>
+        <v>9.6499984856394702E-2</v>
       </c>
       <c r="AG85" s="6">
-        <v>0.10983107340940999</v>
+        <v>0.116709557817473</v>
       </c>
       <c r="AH85" s="6">
-        <v>9.7667471801258204E-2</v>
+        <v>0.100728818020211</v>
       </c>
       <c r="AI85" s="6">
-        <v>8.7233557680319596E-2</v>
+        <v>9.0296011568061899E-2</v>
       </c>
       <c r="AJ85" s="6">
-        <v>4.5749284895375997E-2</v>
+        <v>4.5744595288091099E-2</v>
       </c>
       <c r="AK85" s="6">
-        <v>9.1251784301411301E-2</v>
+        <v>9.4603262036510399E-2</v>
       </c>
       <c r="AL85" s="6"/>
       <c r="AM85" s="6"/>
@@ -10540,22 +10532,22 @@
         <v>5.8123443623754767</v>
       </c>
       <c r="AF86" s="6">
-        <v>9.6832420531868704E-2</v>
+        <v>9.8108522894003694E-2</v>
       </c>
       <c r="AG86" s="6">
-        <v>0.108044558884394</v>
+        <v>0.115535931860519</v>
       </c>
       <c r="AH86" s="6">
-        <v>8.9255475517394003E-2</v>
+        <v>9.1391924313218798E-2</v>
       </c>
       <c r="AI86" s="6">
-        <v>8.4711980062414399E-2</v>
+        <v>8.7676123044094001E-2</v>
       </c>
       <c r="AJ86" s="6">
-        <v>4.5441174969572798E-2</v>
+        <v>4.5382800836201102E-2</v>
       </c>
       <c r="AK86" s="6">
-        <v>8.81682922197351E-2</v>
+        <v>9.1403199108972696E-2</v>
       </c>
       <c r="AL86" s="6"/>
       <c r="AM86" s="6"/>
@@ -10656,22 +10648,22 @@
         <v>5.3743758578301382</v>
       </c>
       <c r="AF87" s="6">
-        <v>9.58396211414837E-2</v>
+        <v>9.6015048296350505E-2</v>
       </c>
       <c r="AG87" s="6">
-        <v>8.7065325459292603E-2</v>
+        <v>9.0218774483261294E-2</v>
       </c>
       <c r="AH87" s="6">
-        <v>7.9121286071637806E-2</v>
+        <v>8.0890370794823502E-2</v>
       </c>
       <c r="AI87" s="6">
-        <v>8.0527864315348696E-2</v>
+        <v>8.3368895143201199E-2</v>
       </c>
       <c r="AJ87" s="6">
-        <v>4.4760900255041598E-2</v>
+        <v>4.4637943446089498E-2</v>
       </c>
       <c r="AK87" s="6">
-        <v>7.8982656880527399E-2</v>
+        <v>8.0918902719678706E-2</v>
       </c>
       <c r="AL87" s="6"/>
       <c r="AM87" s="6"/>
@@ -10772,22 +10764,22 @@
         <v>6.3613838647389898</v>
       </c>
       <c r="AF88" s="6">
-        <v>9.8141457934701498E-2</v>
+        <v>9.8680885671086793E-2</v>
       </c>
       <c r="AG88" s="6">
-        <v>8.8778673466034602E-2</v>
+        <v>9.2165038852506195E-2</v>
       </c>
       <c r="AH88" s="6">
-        <v>6.9581223543345005E-2</v>
+        <v>7.1666288956512197E-2</v>
       </c>
       <c r="AI88" s="6">
-        <v>7.6226331538302994E-2</v>
+        <v>7.8913987311349298E-2</v>
       </c>
       <c r="AJ88" s="6">
-        <v>4.4112273201946398E-2</v>
+        <v>4.3951502130424203E-2</v>
       </c>
       <c r="AK88" s="6">
-        <v>7.6194133422060897E-2</v>
+        <v>7.8273271005953299E-2</v>
       </c>
       <c r="AL88" s="6"/>
       <c r="AM88" s="6"/>
@@ -10888,22 +10880,22 @@
         <v>5.5319298994474408</v>
       </c>
       <c r="AF89" s="6">
-        <v>0.100507425852754</v>
+        <v>0.10119030214901401</v>
       </c>
       <c r="AG89" s="6">
-        <v>9.8244355394532801E-2</v>
+        <v>0.103383916624938</v>
       </c>
       <c r="AH89" s="6">
-        <v>8.2845487520725805E-2</v>
+        <v>8.7063473403517694E-2</v>
       </c>
       <c r="AI89" s="6">
-        <v>7.8510153981254396E-2</v>
+        <v>8.3915623324866004E-2</v>
       </c>
       <c r="AJ89" s="6">
-        <v>4.3362364319840099E-2</v>
+        <v>4.3177728942675103E-2</v>
       </c>
       <c r="AK89" s="6">
-        <v>8.2706420227886601E-2</v>
+        <v>8.6406278338685402E-2</v>
       </c>
       <c r="AL89" s="6"/>
       <c r="AM89" s="6"/>
@@ -11004,22 +10996,22 @@
         <v>5.2191136537501848</v>
       </c>
       <c r="AF90" s="6">
-        <v>0.103948857747307</v>
+        <v>0.103419803459811</v>
       </c>
       <c r="AG90" s="6">
-        <v>0.102370891090593</v>
+        <v>0.11276228919056699</v>
       </c>
       <c r="AH90" s="6">
-        <v>7.0672879655206106E-2</v>
+        <v>7.3343235006368093E-2</v>
       </c>
       <c r="AI90" s="6">
-        <v>7.3486151008486406E-2</v>
+        <v>7.8157879173870501E-2</v>
       </c>
       <c r="AJ90" s="6">
-        <v>4.25855591573637E-2</v>
+        <v>4.23845901226391E-2</v>
       </c>
       <c r="AK90" s="6">
-        <v>7.9574396135269301E-2</v>
+        <v>8.4008178835616606E-2</v>
       </c>
       <c r="AL90" s="6"/>
       <c r="AM90" s="6"/>
@@ -11120,22 +11112,22 @@
         <v>3.0484792080605061</v>
       </c>
       <c r="AF91" s="6">
-        <v>0.10671716202326301</v>
+        <v>0.105386971572107</v>
       </c>
       <c r="AG91" s="6">
-        <v>0.110733606397678</v>
+        <v>0.12612721841807001</v>
       </c>
       <c r="AH91" s="6">
-        <v>6.6891229143598394E-2</v>
+        <v>6.9650842376374394E-2</v>
       </c>
       <c r="AI91" s="6">
-        <v>6.9503209936777097E-2</v>
+        <v>7.3735158324367805E-2</v>
       </c>
       <c r="AJ91" s="6">
-        <v>4.19891108888251E-2</v>
+        <v>4.1805363659403003E-2</v>
       </c>
       <c r="AK91" s="6">
-        <v>7.9940257432288803E-2</v>
+        <v>8.5404484498063399E-2</v>
       </c>
       <c r="AL91" s="6"/>
       <c r="AM91" s="6"/>
@@ -11236,22 +11228,22 @@
         <v>6.0338629875230865</v>
       </c>
       <c r="AF92" s="6">
-        <v>8.8141376698424603E-2</v>
+        <v>8.4350627217765706E-2</v>
       </c>
       <c r="AG92" s="6">
-        <v>8.0470079205420902E-2</v>
+        <v>9.2711938333286906E-2</v>
       </c>
       <c r="AH92" s="6">
-        <v>6.1827277332298203E-2</v>
+        <v>6.7374846272412803E-2</v>
       </c>
       <c r="AI92" s="6">
-        <v>6.7339401472623905E-2</v>
+        <v>7.1503693356573694E-2</v>
       </c>
       <c r="AJ92" s="6">
-        <v>4.1683350503686101E-2</v>
+        <v>4.1547232536320103E-2</v>
       </c>
       <c r="AK92" s="6">
-        <v>6.8473378757091197E-2</v>
+        <v>7.3503399489820903E-2</v>
       </c>
       <c r="AL92" s="6"/>
       <c r="AM92" s="6"/>
@@ -11352,22 +11344,22 @@
         <v>3.1878591219401287</v>
       </c>
       <c r="AF93" s="6">
-        <v>9.0135545034491005E-2</v>
+        <v>8.6987460755879098E-2</v>
       </c>
       <c r="AG93" s="6">
-        <v>8.69598334097893E-2</v>
+        <v>0.10098510275679</v>
       </c>
       <c r="AH93" s="6">
-        <v>6.8684790183952599E-2</v>
+        <v>7.62114652015978E-2</v>
       </c>
       <c r="AI93" s="6">
-        <v>8.2226997758740303E-2</v>
+        <v>8.8936131903707902E-2</v>
       </c>
       <c r="AJ93" s="6">
-        <v>4.3821282121991802E-2</v>
+        <v>4.3939383303898398E-2</v>
       </c>
       <c r="AK93" s="6">
-        <v>7.5908034059999199E-2</v>
+        <v>8.2589322879504198E-2</v>
       </c>
       <c r="AL93" s="6"/>
       <c r="AM93" s="6"/>
@@ -11468,22 +11460,22 @@
         <v>4.0190825761813542</v>
       </c>
       <c r="AF94" s="6">
-        <v>8.6705178995204399E-2</v>
+        <v>8.5203135776036498E-2</v>
       </c>
       <c r="AG94" s="6">
-        <v>8.3113814676378406E-2</v>
+        <v>9.0608172250331201E-2</v>
       </c>
       <c r="AH94" s="6">
-        <v>6.6898045563601793E-2</v>
+        <v>7.5235184696442498E-2</v>
       </c>
       <c r="AI94" s="6">
-        <v>8.0493324986409903E-2</v>
+        <v>8.6635962910618494E-2</v>
       </c>
       <c r="AJ94" s="6">
-        <v>4.37210809599239E-2</v>
+        <v>4.3825189808045402E-2</v>
       </c>
       <c r="AK94" s="6">
-        <v>7.3666214667949995E-2</v>
+        <v>7.8991844662718802E-2</v>
       </c>
       <c r="AL94" s="6"/>
       <c r="AM94" s="6"/>
@@ -11584,22 +11576,22 @@
         <v>4.6556072566202644</v>
       </c>
       <c r="AF95" s="6">
-        <v>8.8323119594483093E-2</v>
+        <v>8.7214035344863702E-2</v>
       </c>
       <c r="AG95" s="6">
-        <v>8.6805726846080303E-2</v>
+        <v>9.5931845286619397E-2</v>
       </c>
       <c r="AH95" s="6">
-        <v>6.7193340715272803E-2</v>
+        <v>7.54591784605015E-2</v>
       </c>
       <c r="AI95" s="6">
-        <v>8.0102565688840902E-2</v>
+        <v>8.6019812419964897E-2</v>
       </c>
       <c r="AJ95" s="6">
-        <v>4.3821546337725399E-2</v>
+        <v>4.39324575856797E-2</v>
       </c>
       <c r="AK95" s="6">
-        <v>7.4736157142380494E-2</v>
+        <v>8.0496955669111497E-2</v>
       </c>
       <c r="AL95" s="6"/>
       <c r="AM95" s="6"/>
@@ -11700,22 +11692,22 @@
         <v>3.7376722023809705</v>
       </c>
       <c r="AF96" s="6">
-        <v>8.9553708660345704E-2</v>
+        <v>8.8864138520193398E-2</v>
       </c>
       <c r="AG96" s="6">
-        <v>9.0460077842986E-2</v>
+        <v>0.100643428221903</v>
       </c>
       <c r="AH96" s="6">
-        <v>7.0690700669952797E-2</v>
+        <v>7.9853736468106604E-2</v>
       </c>
       <c r="AI96" s="6">
-        <v>8.0780426640943606E-2</v>
+        <v>8.6747039741679993E-2</v>
       </c>
       <c r="AJ96" s="6">
-        <v>4.40661706976547E-2</v>
+        <v>4.4192807711212E-2</v>
       </c>
       <c r="AK96" s="6">
-        <v>7.6892555978254395E-2</v>
+        <v>8.3189956230366194E-2</v>
       </c>
       <c r="AL96" s="6"/>
       <c r="AM96" s="6"/>
@@ -11816,22 +11808,22 @@
         <v>2.8366089322613419</v>
       </c>
       <c r="AF97" s="6">
-        <v>9.0622411713207604E-2</v>
+        <v>9.0354924452885094E-2</v>
       </c>
       <c r="AG97" s="6">
-        <v>9.2554915735543405E-2</v>
+        <v>0.103001520242977</v>
       </c>
       <c r="AH97" s="6">
-        <v>7.1721157580524497E-2</v>
+        <v>8.0826726073709707E-2</v>
       </c>
       <c r="AI97" s="6">
-        <v>8.1384379454640998E-2</v>
+        <v>8.7315315484396194E-2</v>
       </c>
       <c r="AJ97" s="6">
-        <v>4.4314178104895401E-2</v>
+        <v>4.4449923487816602E-2</v>
       </c>
       <c r="AK97" s="6">
-        <v>7.8007432533915302E-2</v>
+        <v>8.4378167519262096E-2</v>
       </c>
       <c r="AL97" s="6"/>
       <c r="AM97" s="6"/>
@@ -11932,22 +11924,22 @@
         <v>5.4192606388028253</v>
       </c>
       <c r="AF98" s="6">
-        <v>9.1610146134191495E-2</v>
+        <v>9.1632327561401494E-2</v>
       </c>
       <c r="AG98" s="6">
-        <v>9.3073039542104899E-2</v>
+        <v>0.103518013999503</v>
       </c>
       <c r="AH98" s="6">
-        <v>7.2611524433631003E-2</v>
+        <v>8.1726257009716502E-2</v>
       </c>
       <c r="AI98" s="6">
-        <v>8.1902876577503905E-2</v>
+        <v>8.7776871978264503E-2</v>
       </c>
       <c r="AJ98" s="6">
-        <v>4.4538667298732099E-2</v>
+        <v>4.4675244875383401E-2</v>
       </c>
       <c r="AK98" s="6">
-        <v>7.86295113080515E-2</v>
+        <v>8.5036141536804805E-2</v>
       </c>
       <c r="AL98" s="6"/>
       <c r="AM98" s="6"/>
@@ -12048,22 +12040,22 @@
         <v>3.4538467046139942</v>
       </c>
       <c r="AF99" s="6">
-        <v>9.2547173267053598E-2</v>
+        <v>9.2884678913127197E-2</v>
       </c>
       <c r="AG99" s="6">
-        <v>9.66176033051694E-2</v>
+        <v>0.107662357835925</v>
       </c>
       <c r="AH99" s="6">
-        <v>7.5981031039899796E-2</v>
+        <v>8.5746501811502798E-2</v>
       </c>
       <c r="AI99" s="6">
-        <v>8.6644536622813198E-2</v>
+        <v>9.3144016033971294E-2</v>
       </c>
       <c r="AJ99" s="6">
-        <v>4.5773846965017698E-2</v>
+        <v>4.59909328967327E-2</v>
       </c>
       <c r="AK99" s="6">
-        <v>8.1852005066107805E-2</v>
+        <v>8.8690875773961605E-2</v>
       </c>
       <c r="AL99" s="6"/>
       <c r="AM99" s="6"/>
@@ -12164,22 +12156,22 @@
         <v>4.0870884533042329</v>
       </c>
       <c r="AF100" s="6">
-        <v>9.3425788068286705E-2</v>
+        <v>9.4027839051777903E-2</v>
       </c>
       <c r="AG100" s="6">
-        <v>9.8585609449751005E-2</v>
+        <v>0.10969722120863599</v>
       </c>
       <c r="AH100" s="6">
-        <v>7.6759368179163998E-2</v>
+        <v>8.6268071921333803E-2</v>
       </c>
       <c r="AI100" s="6">
-        <v>8.6909987356744697E-2</v>
+        <v>9.3157120024942697E-2</v>
       </c>
       <c r="AJ100" s="6">
-        <v>4.5920118138338198E-2</v>
+        <v>4.6090554761788603E-2</v>
       </c>
       <c r="AK100" s="6">
-        <v>8.2753279461731194E-2</v>
+        <v>8.9486930316895599E-2</v>
       </c>
       <c r="AL100" s="6"/>
       <c r="AM100" s="6"/>
@@ -12280,22 +12272,22 @@
         <v>2.8586727804182033</v>
       </c>
       <c r="AF101" s="6">
-        <v>9.4098275168590401E-2</v>
+        <v>9.4879580861784302E-2</v>
       </c>
       <c r="AG101" s="6">
-        <v>0.10112031794090599</v>
+        <v>0.112524032510279</v>
       </c>
       <c r="AH101" s="6">
-        <v>7.88784897145203E-2</v>
+        <v>8.8601531515975399E-2</v>
       </c>
       <c r="AI101" s="6">
-        <v>8.7964595566035503E-2</v>
+        <v>9.41151747807185E-2</v>
       </c>
       <c r="AJ101" s="6">
-        <v>4.6183844895223501E-2</v>
+        <v>4.6318471118192303E-2</v>
       </c>
       <c r="AK101" s="6">
-        <v>8.4299713813013794E-2</v>
+        <v>9.1137722002785304E-2</v>
       </c>
       <c r="AL101" s="6"/>
       <c r="AM101" s="6"/>
@@ -12396,22 +12388,22 @@
         <v>4.2956031456759192</v>
       </c>
       <c r="AF102" s="6">
-        <v>9.4757868590386596E-2</v>
+        <v>9.56821304565042E-2</v>
       </c>
       <c r="AG102" s="6">
-        <v>0.10306833436761099</v>
+        <v>0.11455582006358001</v>
       </c>
       <c r="AH102" s="6">
-        <v>8.0509400873956305E-2</v>
+        <v>9.0260823677933297E-2</v>
       </c>
       <c r="AI102" s="6">
-        <v>8.8824535537784299E-2</v>
+        <v>9.4834040253209406E-2</v>
       </c>
       <c r="AJ102" s="6">
-        <v>4.6410112717334903E-2</v>
+        <v>4.6503132322895303E-2</v>
       </c>
       <c r="AK102" s="6">
-        <v>8.5513786373521694E-2</v>
+        <v>9.2353521276949999E-2</v>
       </c>
       <c r="AL102" s="6"/>
       <c r="AM102" s="6"/>
@@ -12512,22 +12504,22 @@
         <v>2.7332359184002897</v>
       </c>
       <c r="AF103" s="6">
-        <v>9.5354269981983097E-2</v>
+        <v>9.6390191939365502E-2</v>
       </c>
       <c r="AG103" s="6">
-        <v>0.10540283750195099</v>
+        <v>0.11704086881789701</v>
       </c>
       <c r="AH103" s="6">
-        <v>8.2660499904805201E-2</v>
+        <v>9.2562709721398503E-2</v>
       </c>
       <c r="AI103" s="6">
-        <v>9.0125711636182507E-2</v>
+        <v>9.6063444469924805E-2</v>
       </c>
       <c r="AJ103" s="6">
-        <v>4.6644045634969399E-2</v>
+        <v>4.6694861278524701E-2</v>
       </c>
       <c r="AK103" s="6">
-        <v>8.7051547454181699E-2</v>
+        <v>9.3950645554312706E-2</v>
       </c>
       <c r="AL103" s="6"/>
       <c r="AM103" s="6"/>
@@ -12628,22 +12620,22 @@
         <v>2.7377874355572374</v>
       </c>
       <c r="AF104" s="6">
-        <v>9.5993562409841401E-2</v>
+        <v>9.7118726894227306E-2</v>
       </c>
       <c r="AG104" s="6">
-        <v>0.106286869936026</v>
+        <v>0.11764679863748</v>
       </c>
       <c r="AH104" s="6">
-        <v>8.3477119907974795E-2</v>
+        <v>9.3104128701717498E-2</v>
       </c>
       <c r="AI104" s="6">
-        <v>9.0473611101030305E-2</v>
+        <v>9.6166833262344598E-2</v>
       </c>
       <c r="AJ104" s="6">
-        <v>4.6783225804740203E-2</v>
+        <v>4.6782986371185199E-2</v>
       </c>
       <c r="AK104" s="6">
-        <v>8.7659265036643105E-2</v>
+        <v>9.4366207129626595E-2</v>
       </c>
       <c r="AL104" s="6"/>
       <c r="AM104" s="6"/>
@@ -12744,22 +12736,22 @@
         <v>3.2439968311216205</v>
       </c>
       <c r="AF105" s="6">
-        <v>9.6584557557951603E-2</v>
+        <v>9.7775254564861899E-2</v>
       </c>
       <c r="AG105" s="6">
-        <v>0.10861777215257799</v>
+        <v>0.120076537709461</v>
       </c>
       <c r="AH105" s="6">
-        <v>8.4581139900718694E-2</v>
+        <v>9.40298549333074E-2</v>
       </c>
       <c r="AI105" s="6">
-        <v>9.0969910764079301E-2</v>
+        <v>9.6459248890299207E-2</v>
       </c>
       <c r="AJ105" s="6">
-        <v>4.69391826643498E-2</v>
+        <v>4.6890796146386603E-2</v>
       </c>
       <c r="AK105" s="6">
-        <v>8.8728456277148995E-2</v>
+        <v>9.5362917142942302E-2</v>
       </c>
       <c r="AL105" s="6"/>
       <c r="AM105" s="6"/>
@@ -12860,22 +12852,22 @@
         <v>2.5252849464417082</v>
       </c>
       <c r="AF106" s="6">
-        <v>9.7222850072065201E-2</v>
+        <v>9.8463260477450396E-2</v>
       </c>
       <c r="AG106" s="6">
-        <v>0.111409257588049</v>
+        <v>0.123028942636739</v>
       </c>
       <c r="AH106" s="6">
-        <v>8.6370167286834706E-2</v>
+        <v>9.58319507924284E-2</v>
       </c>
       <c r="AI106" s="6">
-        <v>9.1058687910222993E-2</v>
+        <v>9.6295804273602903E-2</v>
       </c>
       <c r="AJ106" s="6">
-        <v>4.7028312303472902E-2</v>
+        <v>4.6928098790671301E-2</v>
       </c>
       <c r="AK106" s="6">
-        <v>8.9981801923681798E-2</v>
+        <v>9.6590842956504899E-2</v>
       </c>
       <c r="AL106" s="6"/>
       <c r="AM106" s="6"/>
@@ -12976,22 +12968,22 @@
         <v>3.8647886914272789</v>
       </c>
       <c r="AF107" s="6">
-        <v>9.7842794436428807E-2</v>
+        <v>9.9112616679664894E-2</v>
       </c>
       <c r="AG107" s="6">
-        <v>0.11372645876003799</v>
+        <v>0.12532269869594601</v>
       </c>
       <c r="AH107" s="6">
-        <v>8.6493231819344901E-2</v>
+        <v>9.5495913624767906E-2</v>
       </c>
       <c r="AI107" s="6">
-        <v>9.10507248093715E-2</v>
+        <v>9.6047602838141094E-2</v>
       </c>
       <c r="AJ107" s="6">
-        <v>4.7097950815527603E-2</v>
+        <v>4.6947671444139603E-2</v>
       </c>
       <c r="AK107" s="6">
-        <v>9.0669465626815701E-2</v>
+        <v>9.7093223898705699E-2</v>
       </c>
       <c r="AL107" s="6"/>
       <c r="AM107" s="6"/>
@@ -13092,22 +13084,22 @@
         <v>3.5671314143314703</v>
       </c>
       <c r="AF108" s="6">
-        <v>9.8337569901634295E-2</v>
+        <v>9.9610781680776E-2</v>
       </c>
       <c r="AG108" s="6">
-        <v>0.11599129057596499</v>
+        <v>0.12751783650030499</v>
       </c>
       <c r="AH108" s="6">
-        <v>8.9056938630120097E-2</v>
+        <v>9.8259546088357005E-2</v>
       </c>
       <c r="AI108" s="6">
-        <v>9.3475641786639502E-2</v>
+        <v>9.8584858832604996E-2</v>
       </c>
       <c r="AJ108" s="6">
-        <v>4.7288857689695103E-2</v>
+        <v>4.7101795597794101E-2</v>
       </c>
       <c r="AK108" s="6">
-        <v>9.2537524157435505E-2</v>
+        <v>9.9010138972255496E-2</v>
       </c>
       <c r="AL108" s="6"/>
       <c r="AM108" s="6"/>
@@ -13208,22 +13200,22 @@
         <v>4.0448186525978258</v>
       </c>
       <c r="AF109" s="6">
-        <v>9.8773603523747103E-2</v>
+        <v>0.10003420151546601</v>
       </c>
       <c r="AG109" s="6">
-        <v>0.11801142028601599</v>
+        <v>0.129375277907989</v>
       </c>
       <c r="AH109" s="6">
-        <v>9.0365607876437506E-2</v>
+        <v>9.9397544681592204E-2</v>
       </c>
       <c r="AI109" s="6">
-        <v>9.3794658461155506E-2</v>
+        <v>9.8672480240162397E-2</v>
       </c>
       <c r="AJ109" s="6">
-        <v>4.7415191464896603E-2</v>
+        <v>4.7183960041551197E-2</v>
       </c>
       <c r="AK109" s="6">
-        <v>9.3511685916019799E-2</v>
+        <v>9.9852452319767596E-2</v>
       </c>
       <c r="AL109" s="6"/>
       <c r="AM109" s="6"/>
@@ -13324,22 +13316,22 @@
         <v>3.8412195539606842</v>
       </c>
       <c r="AF110" s="6">
-        <v>9.8883274649578703E-2</v>
+        <v>0.100099045501423</v>
       </c>
       <c r="AG110" s="6">
-        <v>0.11843273653810001</v>
+        <v>0.12926705747529799</v>
       </c>
       <c r="AH110" s="6">
-        <v>9.0512201752289898E-2</v>
+        <v>9.8813468587504005E-2</v>
       </c>
       <c r="AI110" s="6">
-        <v>9.5162654323248899E-2</v>
+        <v>0.100101753476281</v>
       </c>
       <c r="AJ110" s="6">
-        <v>4.7727295235969899E-2</v>
+        <v>4.7464192199821002E-2</v>
       </c>
       <c r="AK110" s="6">
-        <v>9.4036302855612902E-2</v>
+        <v>0.100051239887069</v>
       </c>
       <c r="AL110" s="6"/>
       <c r="AM110" s="6"/>
@@ -13440,22 +13432,22 @@
         <v>4.8187959313533923</v>
       </c>
       <c r="AF111" s="6">
-        <v>9.9062678677093105E-2</v>
+        <v>0.10024048361810101</v>
       </c>
       <c r="AG111" s="6">
-        <v>0.119242879740668</v>
+        <v>0.129690616992618</v>
       </c>
       <c r="AH111" s="6">
-        <v>9.2461062615128001E-2</v>
+        <v>0.100855434746771</v>
       </c>
       <c r="AI111" s="6">
-        <v>9.6383433797004495E-2</v>
+        <v>0.101185268062272</v>
       </c>
       <c r="AJ111" s="6">
-        <v>4.7969514699482997E-2</v>
+        <v>4.7665678981816798E-2</v>
       </c>
       <c r="AK111" s="6">
-        <v>9.5073041786528201E-2</v>
+        <v>0.100971514428169</v>
       </c>
       <c r="AL111" s="6"/>
       <c r="AM111" s="6"/>
@@ -13556,22 +13548,22 @@
         <v>4.5807185628746083</v>
       </c>
       <c r="AF112" s="6">
-        <v>9.9049142006893603E-2</v>
+        <v>0.10017549555262401</v>
       </c>
       <c r="AG112" s="6">
-        <v>0.11905217390751199</v>
+        <v>0.128927504984402</v>
       </c>
       <c r="AH112" s="6">
-        <v>9.1480014770034604E-2</v>
+        <v>9.9216357368006394E-2</v>
       </c>
       <c r="AI112" s="6">
-        <v>9.32529026459194E-2</v>
+        <v>9.7380235616515307E-2</v>
       </c>
       <c r="AJ112" s="6">
-        <v>4.8147961597143997E-2</v>
+        <v>4.77923118773632E-2</v>
       </c>
       <c r="AK112" s="6">
-        <v>9.4059812589570205E-2</v>
+        <v>9.9526700800173895E-2</v>
       </c>
       <c r="AL112" s="6"/>
       <c r="AM112" s="6"/>
@@ -13672,22 +13664,22 @@
         <v>4.4441879453643196</v>
       </c>
       <c r="AF113" s="6">
-        <v>9.9085676551713103E-2</v>
+        <v>0.100169606335631</v>
       </c>
       <c r="AG113" s="6">
-        <v>0.119127290195489</v>
+        <v>0.12854547353458301</v>
       </c>
       <c r="AH113" s="6">
-        <v>9.3143294352637102E-2</v>
+        <v>0.100363285356303</v>
       </c>
       <c r="AI113" s="6">
-        <v>9.5163700153238495E-2</v>
+        <v>9.9609276123047694E-2</v>
       </c>
       <c r="AJ113" s="6">
-        <v>4.8450581109468503E-2</v>
+        <v>4.80550588610077E-2</v>
       </c>
       <c r="AK113" s="6">
-        <v>9.4999593188713399E-2</v>
+        <v>0.100263218711539</v>
       </c>
       <c r="AL113" s="6"/>
       <c r="AM113" s="6"/>
@@ -13788,22 +13780,22 @@
         <v>4.341842394944706</v>
       </c>
       <c r="AF114" s="6">
-        <v>9.8926928159012995E-2</v>
+        <v>9.9959387457325605E-2</v>
       </c>
       <c r="AG114" s="6">
-        <v>0.118296945585075</v>
+        <v>0.12715027435043</v>
       </c>
       <c r="AH114" s="6">
-        <v>9.6196498964181101E-2</v>
+        <v>0.103079038691203</v>
       </c>
       <c r="AI114" s="6">
-        <v>9.7907059255055107E-2</v>
+        <v>0.10275444517238901</v>
       </c>
       <c r="AJ114" s="6">
-        <v>4.8866560537872299E-2</v>
+        <v>4.8433261290529502E-2</v>
       </c>
       <c r="AK114" s="6">
-        <v>9.6252029360128805E-2</v>
+        <v>0.101365952526893</v>
       </c>
       <c r="AL114" s="6"/>
       <c r="AM114" s="6"/>
@@ -13904,22 +13896,22 @@
         <v>3.6225124394089647</v>
       </c>
       <c r="AF115" s="6">
-        <v>9.8687349433953894E-2</v>
+        <v>9.9672622688462401E-2</v>
       </c>
       <c r="AG115" s="6">
-        <v>0.117254733385873</v>
+        <v>0.12569322765757801</v>
       </c>
       <c r="AH115" s="6">
-        <v>0.100507405713417</v>
+        <v>0.107951799438203</v>
       </c>
       <c r="AI115" s="6">
-        <v>0.101063895312703</v>
+        <v>0.106053771420798</v>
       </c>
       <c r="AJ115" s="6">
-        <v>4.93266499918932E-2</v>
+        <v>4.8850903225962597E-2</v>
       </c>
       <c r="AK115" s="6">
-        <v>9.78525289523203E-2</v>
+        <v>0.10306004047752899</v>
       </c>
       <c r="AL115" s="6"/>
       <c r="AM115" s="6"/>
@@ -14020,22 +14012,22 @@
         <v>2.9656736082419144</v>
       </c>
       <c r="AF116" s="6">
-        <v>9.8533590189840703E-2</v>
+        <v>9.9491516661203303E-2</v>
       </c>
       <c r="AG116" s="6">
-        <v>0.123681894427512</v>
+        <v>0.13297963810966801</v>
       </c>
       <c r="AH116" s="6">
-        <v>0.10694650862965301</v>
+        <v>0.11594965502008001</v>
       </c>
       <c r="AI116" s="6">
-        <v>0.10426395934237601</v>
+        <v>0.10875874888760401</v>
       </c>
       <c r="AJ116" s="6">
-        <v>4.9775210697789798E-2</v>
+        <v>4.9247866658530898E-2</v>
       </c>
       <c r="AK116" s="6">
-        <v>0.10189899463763499</v>
+        <v>0.107613475260639</v>
       </c>
       <c r="AL116" s="6"/>
       <c r="AM116" s="6"/>
@@ -14136,22 +14128,22 @@
         <v>3.6452533962400224</v>
       </c>
       <c r="AF117" s="6">
-        <v>9.8561048105690496E-2</v>
+        <v>9.9515898841610703E-2</v>
       </c>
       <c r="AG117" s="6">
-        <v>0.13250029937354599</v>
+        <v>0.14291828684881899</v>
       </c>
       <c r="AH117" s="6">
-        <v>0.114310858661429</v>
+        <v>0.12380823501131</v>
       </c>
       <c r="AI117" s="6">
-        <v>0.107090475418733</v>
+        <v>0.11151229594024201</v>
       </c>
       <c r="AJ117" s="6">
-        <v>5.0208663737224497E-2</v>
+        <v>4.9620364673141203E-2</v>
       </c>
       <c r="AK117" s="6">
-        <v>0.106718239560852</v>
+        <v>0.112791422170875</v>
       </c>
       <c r="AL117" s="6"/>
       <c r="AM117" s="6"/>
@@ -14252,22 +14244,22 @@
         <v>4.5798541332082721</v>
       </c>
       <c r="AF118" s="6">
-        <v>9.8478680699296897E-2</v>
+        <v>9.9412165279760795E-2</v>
       </c>
       <c r="AG118" s="6">
-        <v>0.13047202421683299</v>
+        <v>0.13969786195936201</v>
       </c>
       <c r="AH118" s="6">
-        <v>0.11393460020464601</v>
+        <v>0.12275811721916199</v>
       </c>
       <c r="AI118" s="6">
-        <v>0.109566510297195</v>
+        <v>0.113610448318304</v>
       </c>
       <c r="AJ118" s="6">
-        <v>5.0497732031358399E-2</v>
+        <v>4.9835973738966401E-2</v>
       </c>
       <c r="AK118" s="6">
-        <v>0.10668898878818001</v>
+        <v>0.11220096665187999</v>
       </c>
       <c r="AL118" s="6"/>
       <c r="AM118" s="6"/>
@@ -14368,22 +14360,22 @@
         <v>4.4437593142720999</v>
       </c>
       <c r="AF119" s="6">
-        <v>9.8275362508515998E-2</v>
+        <v>9.9184927576551701E-2</v>
       </c>
       <c r="AG119" s="6">
-        <v>0.12794681265448701</v>
+        <v>0.136177449337892</v>
       </c>
       <c r="AH119" s="6">
-        <v>0.109849364867627</v>
+        <v>0.11660827740615599</v>
       </c>
       <c r="AI119" s="6">
-        <v>9.8063865608424894E-2</v>
+        <v>0.100802084202137</v>
       </c>
       <c r="AJ119" s="6">
-        <v>4.9707776548546898E-2</v>
+        <v>4.89179729874053E-2</v>
       </c>
       <c r="AK119" s="6">
-        <v>0.102317536838912</v>
+        <v>0.106732077870297</v>
       </c>
       <c r="AL119" s="6"/>
       <c r="AM119" s="6"/>
@@ -14484,22 +14476,22 @@
         <v>4.0219303860613564</v>
       </c>
       <c r="AF120" s="6">
-        <v>9.8194311871552906E-2</v>
+        <v>9.9094976668089793E-2</v>
       </c>
       <c r="AG120" s="6">
-        <v>0.12618640035515399</v>
+        <v>0.133669386737334</v>
       </c>
       <c r="AH120" s="6">
-        <v>0.11039427253222101</v>
+        <v>0.116809736487143</v>
       </c>
       <c r="AI120" s="6">
-        <v>0.100798575684019</v>
+        <v>0.10357947221003</v>
       </c>
       <c r="AJ120" s="6">
-        <v>5.00351797083399E-2</v>
+        <v>4.92031417902314E-2</v>
       </c>
       <c r="AK120" s="6">
-        <v>0.10267020121498401</v>
+        <v>0.10681552138682</v>
       </c>
       <c r="AL120" s="6"/>
       <c r="AM120" s="6"/>
@@ -14600,22 +14592,22 @@
         <v>3.344574200966477</v>
       </c>
       <c r="AF121" s="6">
-        <v>9.8315239221592396E-2</v>
+        <v>9.9221932309262198E-2</v>
       </c>
       <c r="AG121" s="6">
-        <v>0.12603396501963199</v>
+        <v>0.13315366372429999</v>
       </c>
       <c r="AH121" s="6">
-        <v>0.112701387283195</v>
+        <v>0.118911126104023</v>
       </c>
       <c r="AI121" s="6">
-        <v>0.102253649803042</v>
+        <v>0.10494385748568801</v>
       </c>
       <c r="AJ121" s="6">
-        <v>5.0204206565951703E-2</v>
+        <v>4.9320468407847998E-2</v>
       </c>
       <c r="AK121" s="6">
-        <v>0.103600653935242</v>
+        <v>0.107573935462511</v>
       </c>
       <c r="AL121" s="6"/>
       <c r="AM121" s="6"/>
@@ -14716,22 +14708,22 @@
         <v>3.5348306185678524</v>
       </c>
       <c r="AF122" s="6">
-        <v>9.8927079794635595E-2</v>
+        <v>9.9864582837070601E-2</v>
       </c>
       <c r="AG122" s="6">
-        <v>0.12531953979223301</v>
+        <v>0.13201288599373501</v>
       </c>
       <c r="AH122" s="6">
-        <v>0.10919899685981301</v>
+        <v>0.114376064979279</v>
       </c>
       <c r="AI122" s="6">
-        <v>0.101086002235883</v>
+        <v>0.10346952249347</v>
       </c>
       <c r="AJ122" s="6">
-        <v>4.9997088169186597E-2</v>
+        <v>4.9051865417713898E-2</v>
       </c>
       <c r="AK122" s="6">
-        <v>0.102293846146748</v>
+        <v>0.105822583620223</v>
       </c>
       <c r="AL122" s="6"/>
       <c r="AM122" s="6"/>
@@ -14832,22 +14824,22 @@
         <v>3.07157282318542</v>
       </c>
       <c r="AF123" s="6">
-        <v>9.9862952239414396E-2</v>
+        <v>0.100832572531574</v>
       </c>
       <c r="AG123" s="6">
-        <v>0.13005353562702501</v>
+        <v>0.137150112610852</v>
       </c>
       <c r="AH123" s="6">
-        <v>0.109304686934985</v>
+        <v>0.113871410970105</v>
       </c>
       <c r="AI123" s="6">
-        <v>9.78371542150204E-2</v>
+        <v>9.9919471890529105E-2</v>
       </c>
       <c r="AJ123" s="6">
-        <v>4.9553405540664397E-2</v>
+        <v>4.8553070124690102E-2</v>
       </c>
       <c r="AK123" s="6">
-        <v>0.10282911510044999</v>
+        <v>0.106221871860068</v>
       </c>
       <c r="AL123" s="6"/>
       <c r="AM123" s="6"/>
@@ -14948,22 +14940,22 @@
         <v>3.5854223537917562</v>
       </c>
       <c r="AF124" s="6">
-        <v>0.10070595624614399</v>
+        <v>0.101677313090203</v>
       </c>
       <c r="AG124" s="6">
-        <v>0.13388127759295099</v>
+        <v>0.14124334095310001</v>
       </c>
       <c r="AH124" s="6">
-        <v>0.104827414390517</v>
+        <v>0.10896271349513199</v>
       </c>
       <c r="AI124" s="6">
-        <v>9.5501685069572698E-2</v>
+        <v>9.7371702783722994E-2</v>
       </c>
       <c r="AJ124" s="6">
-        <v>4.9183107814065499E-2</v>
+        <v>4.8147566195355103E-2</v>
       </c>
       <c r="AK124" s="6">
-        <v>0.10211697047035</v>
+        <v>0.105404844689896</v>
       </c>
       <c r="AL124" s="6"/>
       <c r="AM124" s="6"/>
@@ -15064,22 +15056,22 @@
         <v>3.1347841205434435</v>
       </c>
       <c r="AF125" s="6">
-        <v>0.10154809235352801</v>
+        <v>0.10250060879730701</v>
       </c>
       <c r="AG125" s="6">
-        <v>0.13835481296105501</v>
+        <v>0.14579785147933799</v>
       </c>
       <c r="AH125" s="6">
-        <v>0.113405349050879</v>
+        <v>0.118243738969333</v>
       </c>
       <c r="AI125" s="6">
-        <v>9.4859561564528794E-2</v>
+        <v>9.6763625521857993E-2</v>
       </c>
       <c r="AJ125" s="6">
-        <v>4.8813751270877503E-2</v>
+        <v>4.7755617116956001E-2</v>
       </c>
       <c r="AK125" s="6">
-        <v>0.105391055669579</v>
+        <v>0.108881449114712</v>
       </c>
       <c r="AL125" s="6"/>
       <c r="AM125" s="6"/>
@@ -15180,22 +15172,22 @@
         <v>3.0498152476294393</v>
       </c>
       <c r="AF126" s="6">
-        <v>0.10244559880084</v>
+        <v>0.103363155270899</v>
       </c>
       <c r="AG126" s="6">
-        <v>0.141350027010547</v>
+        <v>0.14898223905254099</v>
       </c>
       <c r="AH126" s="6">
-        <v>0.105209803643383</v>
+        <v>0.10900545243962401</v>
       </c>
       <c r="AI126" s="6">
-        <v>9.2413132911057502E-2</v>
+        <v>9.4192001539465803E-2</v>
       </c>
       <c r="AJ126" s="6">
-        <v>4.84231317911707E-2</v>
+        <v>4.7355850864450197E-2</v>
       </c>
       <c r="AK126" s="6">
-        <v>0.103469528952669</v>
+        <v>0.106693174548771</v>
       </c>
       <c r="AL126" s="6"/>
       <c r="AM126" s="6"/>
@@ -15296,22 +15288,22 @@
         <v>2.8130785086869281</v>
       </c>
       <c r="AF127" s="6">
-        <v>0.10310803433601599</v>
+        <v>0.103958233088025</v>
       </c>
       <c r="AG127" s="6">
-        <v>0.145132335530401</v>
+        <v>0.152491597589751</v>
       </c>
       <c r="AH127" s="6">
-        <v>0.103836789362226</v>
+        <v>0.10681085898858</v>
       </c>
       <c r="AI127" s="6">
-        <v>9.0669715261726097E-2</v>
+        <v>9.2498464626074806E-2</v>
       </c>
       <c r="AJ127" s="6">
-        <v>4.8178800123797903E-2</v>
+        <v>4.7116077600468299E-2</v>
       </c>
       <c r="AK127" s="6">
-        <v>0.103677913922595</v>
+        <v>0.10661303921840599</v>
       </c>
       <c r="AL127" s="6"/>
       <c r="AM127" s="6"/>
@@ -15412,22 +15404,22 @@
         <v>2.3625618204203391</v>
       </c>
       <c r="AF128" s="6">
-        <v>0.10358282880019</v>
+        <v>0.104344517163534</v>
       </c>
       <c r="AG128" s="6">
-        <v>0.14703540922011599</v>
+        <v>0.15387127181083801</v>
       </c>
       <c r="AH128" s="6">
-        <v>0.10071188868393301</v>
+        <v>0.103335705220555</v>
       </c>
       <c r="AI128" s="6">
-        <v>8.9940452060552803E-2</v>
+        <v>9.1871977121461598E-2</v>
       </c>
       <c r="AJ128" s="6">
-        <v>4.8043643286706801E-2</v>
+        <v>4.6993095522294102E-2</v>
       </c>
       <c r="AK128" s="6">
-        <v>0.10316820071378099</v>
+        <v>0.105890144148238</v>
       </c>
       <c r="AL128" s="6"/>
       <c r="AM128" s="6"/>
@@ -15528,22 +15520,22 @@
         <v>2.9204035567993003</v>
       </c>
       <c r="AF129" s="6">
-        <v>0.103913683374264</v>
+        <v>0.104575087982353</v>
       </c>
       <c r="AG129" s="6">
-        <v>0.14543156107518301</v>
+        <v>0.15176328342280701</v>
       </c>
       <c r="AH129" s="6">
-        <v>9.8005700475030003E-2</v>
+        <v>0.100418298568603</v>
       </c>
       <c r="AI129" s="6">
-        <v>8.9802491894653794E-2</v>
+        <v>9.1879196915805497E-2</v>
       </c>
       <c r="AJ129" s="6">
-        <v>4.7984824220919098E-2</v>
+        <v>4.6950067304691298E-2</v>
       </c>
       <c r="AK129" s="6">
-        <v>0.102048352551237</v>
+        <v>0.104611659538007</v>
       </c>
       <c r="AL129" s="6"/>
       <c r="AM129" s="6"/>
@@ -15644,22 +15636,22 @@
         <v>2.7487730323958459</v>
       </c>
       <c r="AF130" s="6">
-        <v>0.104088794972828</v>
+        <v>0.104642965024558</v>
       </c>
       <c r="AG130" s="6">
-        <v>0.14647305362073201</v>
+        <v>0.152259169703932</v>
       </c>
       <c r="AH130" s="6">
-        <v>0.100938100172971</v>
+        <v>0.10363086737406201</v>
       </c>
       <c r="AI130" s="6">
-        <v>9.0249643618001002E-2</v>
+        <v>9.2434056401113907E-2</v>
       </c>
       <c r="AJ130" s="6">
-        <v>4.8005180815208999E-2</v>
+        <v>4.6987888964398601E-2</v>
       </c>
       <c r="AK130" s="6">
-        <v>0.103226362262283</v>
+        <v>0.105750911365662</v>
       </c>
       <c r="AL130" s="6"/>
       <c r="AM130" s="6"/>
@@ -15760,22 +15752,22 @@
         <v>3.0247997236873658</v>
       </c>
       <c r="AF131" s="6">
-        <v>0.10444135210076801</v>
+        <v>0.104901944461872</v>
       </c>
       <c r="AG131" s="6">
-        <v>0.14838552462517299</v>
+        <v>0.15372815721549901</v>
       </c>
       <c r="AH131" s="6">
-        <v>9.9354462117242304E-2</v>
+        <v>0.10193773231705899</v>
       </c>
       <c r="AI131" s="6">
-        <v>8.9699320833563204E-2</v>
+        <v>9.1962463918586701E-2</v>
       </c>
       <c r="AJ131" s="6">
-        <v>4.79184223100508E-2</v>
+        <v>4.6913725425051102E-2</v>
       </c>
       <c r="AK131" s="6">
-        <v>0.103162215973988</v>
+        <v>0.105554923005777</v>
       </c>
       <c r="AL131" s="6"/>
       <c r="AM131" s="6"/>
@@ -15876,22 +15868,22 @@
         <v>2.2300999718893877</v>
       </c>
       <c r="AF132" s="6">
-        <v>0.104813133278905</v>
+        <v>0.105180232491576</v>
       </c>
       <c r="AG132" s="6">
-        <v>0.150811961003321</v>
+        <v>0.155737115797453</v>
       </c>
       <c r="AH132" s="6">
-        <v>0.10430498536916</v>
+        <v>0.10739228611127</v>
       </c>
       <c r="AI132" s="6">
-        <v>8.9603560334207702E-2</v>
+        <v>9.1976468102728401E-2</v>
       </c>
       <c r="AJ132" s="6">
-        <v>4.7813801035243401E-2</v>
+        <v>4.6822273899797699E-2</v>
       </c>
       <c r="AK132" s="6">
-        <v>0.105105908036305</v>
+        <v>0.107553179635302</v>
       </c>
       <c r="AL132" s="6"/>
       <c r="AM132" s="6"/>
@@ -15992,22 +15984,22 @@
         <v>2.0520308764275796</v>
       </c>
       <c r="AF133" s="6">
-        <v>0.104735127817858</v>
+        <v>0.104981260186891</v>
       </c>
       <c r="AG133" s="6">
-        <v>0.139866048749481</v>
+        <v>0.14327572733364899</v>
       </c>
       <c r="AH133" s="6">
-        <v>9.9968028707321896E-2</v>
+        <v>0.102574363501876</v>
       </c>
       <c r="AI133" s="6">
-        <v>8.8925558234820901E-2</v>
+        <v>9.1362621441441097E-2</v>
       </c>
       <c r="AJ133" s="6">
-        <v>4.7676463092910598E-2</v>
+        <v>4.6698451235863199E-2</v>
       </c>
       <c r="AK133" s="6">
-        <v>0.101122771590601</v>
+        <v>0.103081961611492</v>
       </c>
       <c r="AL133" s="6"/>
       <c r="AM133" s="6"/>
@@ -16108,22 +16100,22 @@
         <v>1.8110351478739517</v>
       </c>
       <c r="AF134" s="6">
-        <v>0.104925497382776</v>
+        <v>0.105082073281673</v>
       </c>
       <c r="AG134" s="6">
-        <v>0.141081601399907</v>
+        <v>0.14434285803014099</v>
       </c>
       <c r="AH134" s="6">
-        <v>9.8534693017819003E-2</v>
+        <v>0.101074854053519</v>
       </c>
       <c r="AI134" s="6">
-        <v>8.8988338049312596E-2</v>
+        <v>9.1547133292614102E-2</v>
       </c>
       <c r="AJ134" s="6">
-        <v>4.7680262493807801E-2</v>
+        <v>4.6721238558880801E-2</v>
       </c>
       <c r="AK134" s="6">
-        <v>0.101065670241171</v>
+        <v>0.102987019750786</v>
       </c>
       <c r="AL134" s="6"/>
       <c r="AM134" s="6"/>
@@ -16224,22 +16216,22 @@
         <v>2.6825128643984897</v>
       </c>
       <c r="AF135" s="6">
-        <v>0.10500964945147399</v>
+        <v>0.105076330768352</v>
       </c>
       <c r="AG135" s="6">
-        <v>0.14099144621607401</v>
+        <v>0.14400011250398601</v>
       </c>
       <c r="AH135" s="6">
-        <v>9.7610405576466205E-2</v>
+        <v>0.10016446090719699</v>
       </c>
       <c r="AI135" s="6">
-        <v>8.9411549167740106E-2</v>
+        <v>9.2104771293474802E-2</v>
       </c>
       <c r="AJ135" s="6">
-        <v>4.77357829780303E-2</v>
+        <v>4.6795068109754201E-2</v>
       </c>
       <c r="AK135" s="6">
-        <v>0.100903032340699</v>
+        <v>0.102786422477913</v>
       </c>
       <c r="AL135" s="6"/>
       <c r="AM135" s="6"/>
@@ -16340,22 +16332,22 @@
         <v>2.2270029244918277</v>
       </c>
       <c r="AF136" s="6">
-        <v>0.104852598681929</v>
+        <v>0.104827732161455</v>
       </c>
       <c r="AG136" s="6">
-        <v>0.14070969017283699</v>
+        <v>0.143485677346923</v>
       </c>
       <c r="AH136" s="6">
-        <v>9.8420250178667706E-2</v>
+        <v>0.101153732499562</v>
       </c>
       <c r="AI136" s="6">
-        <v>9.0062928244813406E-2</v>
+        <v>9.2883125120917495E-2</v>
       </c>
       <c r="AJ136" s="6">
-        <v>4.7897826252133499E-2</v>
+        <v>4.6974627687470197E-2</v>
       </c>
       <c r="AK136" s="6">
-        <v>0.101202192897725</v>
+        <v>0.10309662291124699</v>
       </c>
       <c r="AL136" s="6"/>
       <c r="AM136" s="6"/>
@@ -16456,22 +16448,22 @@
         <v>2.027165358505556</v>
       </c>
       <c r="AF137" s="6">
-        <v>0.104754952593492</v>
+        <v>0.104653149799024</v>
       </c>
       <c r="AG137" s="6">
-        <v>0.14055721923709799</v>
+        <v>0.14312018134177901</v>
       </c>
       <c r="AH137" s="6">
-        <v>9.9277755771488799E-2</v>
+        <v>0.102162325835287</v>
       </c>
       <c r="AI137" s="6">
-        <v>9.1000524542930297E-2</v>
+        <v>9.3945413064828398E-2</v>
       </c>
       <c r="AJ137" s="6">
-        <v>4.80424349766422E-2</v>
+        <v>4.7131046315010097E-2</v>
       </c>
       <c r="AK137" s="6">
-        <v>0.101613132736316</v>
+        <v>0.103515374725584</v>
       </c>
       <c r="AL137" s="6"/>
       <c r="AM137" s="6"/>
@@ -16572,22 +16564,22 @@
         <v>2.0908024736979058</v>
       </c>
       <c r="AF138" s="6">
-        <v>0.104510449906521</v>
+        <v>0.104337913104917</v>
       </c>
       <c r="AG138" s="6">
-        <v>0.13999304468705601</v>
+        <v>0.14230390154567699</v>
       </c>
       <c r="AH138" s="6">
-        <v>0.10140981055647701</v>
+        <v>0.10446065487335</v>
       </c>
       <c r="AI138" s="6">
-        <v>9.2411919198905096E-2</v>
+        <v>9.5496811419210501E-2</v>
       </c>
       <c r="AJ138" s="6">
-        <v>4.8265409762780001E-2</v>
+        <v>4.73633801859243E-2</v>
       </c>
       <c r="AK138" s="6">
-        <v>0.10236732815128</v>
+        <v>0.104275254975693</v>
       </c>
       <c r="AL138" s="6"/>
       <c r="AM138" s="6"/>
@@ -16688,22 +16680,22 @@
         <v>2.3679027430318911</v>
       </c>
       <c r="AF139" s="6">
-        <v>0.104419397722222</v>
+        <v>0.104193931335853</v>
       </c>
       <c r="AG139" s="6">
-        <v>0.139968571612334</v>
+        <v>0.14215543730396599</v>
       </c>
       <c r="AH139" s="6">
-        <v>0.102239345589026</v>
+        <v>0.105345822547736</v>
       </c>
       <c r="AI139" s="6">
-        <v>9.3269070234468496E-2</v>
+        <v>9.6396392421842905E-2</v>
       </c>
       <c r="AJ139" s="6">
-        <v>4.8395710652815602E-2</v>
+        <v>4.7493737774526298E-2</v>
       </c>
       <c r="AK139" s="6">
-        <v>0.102781476684187</v>
+        <v>0.104675771176647</v>
       </c>
       <c r="AL139" s="6"/>
       <c r="AM139" s="6"/>
@@ -16804,22 +16796,22 @@
         <v>1.9023562292566965</v>
       </c>
       <c r="AF140" s="6">
-        <v>0.104492059989408</v>
+        <v>0.104225614578282</v>
       </c>
       <c r="AG140" s="6">
-        <v>0.14090916197304801</v>
+        <v>0.14303411355930101</v>
       </c>
       <c r="AH140" s="6">
-        <v>0.10373096618126899</v>
+        <v>0.106923668119103</v>
       </c>
       <c r="AI140" s="6">
-        <v>9.34002459776241E-2</v>
+        <v>9.6488458802474503E-2</v>
       </c>
       <c r="AJ140" s="6">
-        <v>4.8425373259626099E-2</v>
+        <v>4.7517086896365697E-2</v>
       </c>
       <c r="AK140" s="6">
-        <v>0.103455636451261</v>
+        <v>0.10534325241642201</v>
       </c>
       <c r="AL140" s="6"/>
       <c r="AM140" s="6"/>
@@ -16920,22 +16912,22 @@
         <v>2.0005076522497944</v>
       </c>
       <c r="AF141" s="6">
-        <v>0.10451719303477899</v>
+        <v>0.10421053560280601</v>
       </c>
       <c r="AG141" s="6">
-        <v>0.140629831047246</v>
+        <v>0.14260945074672099</v>
       </c>
       <c r="AH141" s="6">
-        <v>0.10322974193711799</v>
+        <v>0.106296552996703</v>
       </c>
       <c r="AI141" s="6">
-        <v>9.3796064763463097E-2</v>
+        <v>9.6866072365306297E-2</v>
       </c>
       <c r="AJ141" s="6">
-        <v>4.8477983521818299E-2</v>
+        <v>4.7563938325159302E-2</v>
       </c>
       <c r="AK141" s="6">
-        <v>0.103350345514547</v>
+        <v>0.105158157864505</v>
       </c>
       <c r="AL141" s="6"/>
       <c r="AM141" s="6"/>
@@ -17036,22 +17028,22 @@
         <v>1.5696029305924952</v>
       </c>
       <c r="AF142" s="6">
-        <v>0.104564796389648</v>
+        <v>0.10422168039850201</v>
       </c>
       <c r="AG142" s="6">
-        <v>0.141400663015459</v>
+        <v>0.143311022156104</v>
       </c>
       <c r="AH142" s="6">
-        <v>0.10354919693124701</v>
+        <v>0.106576819028562</v>
       </c>
       <c r="AI142" s="6">
-        <v>9.3963048086620704E-2</v>
+        <v>9.6991226480334494E-2</v>
       </c>
       <c r="AJ142" s="6">
-        <v>4.8512659605288097E-2</v>
+        <v>4.7591537408532003E-2</v>
       </c>
       <c r="AK142" s="6">
-        <v>0.103671075773396</v>
+        <v>0.10543630489721</v>
       </c>
       <c r="AL142" s="6"/>
       <c r="AM142" s="6"/>
@@ -17152,22 +17144,22 @@
         <v>1.8974321429318763</v>
       </c>
       <c r="AF143" s="6">
-        <v>0.10461189441903999</v>
+        <v>0.10423454195954</v>
       </c>
       <c r="AG143" s="6">
-        <v>0.140899242347823</v>
+        <v>0.14280487079322501</v>
       </c>
       <c r="AH143" s="6">
-        <v>0.102777006078263</v>
+        <v>0.10567814230889901</v>
       </c>
       <c r="AI143" s="6">
-        <v>9.4228388109155806E-2</v>
+        <v>9.72212442285217E-2</v>
       </c>
       <c r="AJ143" s="6">
-        <v>4.8543373828911801E-2</v>
+        <v>4.7614871340660801E-2</v>
       </c>
       <c r="AK143" s="6">
-        <v>0.103409115466445</v>
+        <v>0.10512523797526301</v>
       </c>
       <c r="AL143" s="6"/>
       <c r="AM143" s="6"/>
@@ -17268,22 +17260,22 @@
         <v>1.820507471401811</v>
       </c>
       <c r="AF144" s="6">
-        <v>0.10433871971316599</v>
+        <v>0.103921596479276</v>
       </c>
       <c r="AG144" s="6">
-        <v>0.13973429018786401</v>
+        <v>0.14147874618426401</v>
       </c>
       <c r="AH144" s="6">
-        <v>0.10273121004038401</v>
+        <v>0.10580212191652801</v>
       </c>
       <c r="AI144" s="6">
-        <v>9.5760518399189101E-2</v>
+        <v>9.8837955348761303E-2</v>
       </c>
       <c r="AJ144" s="6">
-        <v>4.87580445826966E-2</v>
+        <v>4.7827417837293398E-2</v>
       </c>
       <c r="AK144" s="6">
-        <v>0.103444482335949</v>
+        <v>0.105178877392022</v>
       </c>
       <c r="AL144" s="6"/>
       <c r="AM144" s="6"/>
@@ -17384,22 +17376,22 @@
         <v>2.2706152643269917</v>
       </c>
       <c r="AF145" s="6">
-        <v>0.104065265043189</v>
+        <v>0.10361955463901799</v>
       </c>
       <c r="AG145" s="6">
-        <v>0.138699137152408</v>
+        <v>0.140338037546791</v>
       </c>
       <c r="AH145" s="6">
-        <v>0.104703596066684</v>
+        <v>0.107908235675995</v>
       </c>
       <c r="AI145" s="6">
-        <v>9.7234847488104695E-2</v>
+        <v>0.10032548333228999</v>
       </c>
       <c r="AJ145" s="6">
-        <v>4.8972000669482998E-2</v>
+        <v>4.8033936771511798E-2</v>
       </c>
       <c r="AK145" s="6">
-        <v>0.104046685987846</v>
+        <v>0.105787770120522</v>
       </c>
       <c r="AL145" s="6"/>
       <c r="AM145" s="6"/>
@@ -17500,22 +17492,22 @@
         <v>1.5683318643308297</v>
       </c>
       <c r="AF146" s="6">
-        <v>0.103756119415051</v>
+        <v>0.10329107347245001</v>
       </c>
       <c r="AG146" s="6">
-        <v>0.13726869160791699</v>
+        <v>0.13882002006079899</v>
       </c>
       <c r="AH146" s="6">
-        <v>0.102329793705248</v>
+        <v>0.105182921980617</v>
       </c>
       <c r="AI146" s="6">
-        <v>9.7783563543039506E-2</v>
+        <v>0.10060542973000799</v>
       </c>
       <c r="AJ146" s="6">
-        <v>4.9208418810094801E-2</v>
+        <v>4.8258591986078403E-2</v>
       </c>
       <c r="AK146" s="6">
-        <v>0.10316613660968101</v>
+        <v>0.104728425567331</v>
       </c>
       <c r="AL146" s="6"/>
       <c r="AM146" s="6"/>
@@ -17616,22 +17608,22 @@
         <v>2.0815893879536418</v>
       </c>
       <c r="AF147" s="6">
-        <v>0.104659583105145</v>
+        <v>0.10395454896831401</v>
       </c>
       <c r="AG147" s="6">
-        <v>0.141176327538799</v>
+        <v>0.142904129983178</v>
       </c>
       <c r="AH147" s="6">
-        <v>0.104302332056787</v>
+        <v>0.107312654188118</v>
       </c>
       <c r="AI147" s="6">
-        <v>9.8865113388278497E-2</v>
+        <v>0.10164364116666399</v>
       </c>
       <c r="AJ147" s="6">
-        <v>4.9368057234990499E-2</v>
+        <v>4.8399279371740003E-2</v>
       </c>
       <c r="AK147" s="6">
-        <v>0.105026040612984</v>
+        <v>0.106628651921574</v>
       </c>
       <c r="AL147" s="6"/>
       <c r="AM147" s="6"/>
@@ -17732,22 +17724,22 @@
         <v>0.93282150971987221</v>
       </c>
       <c r="AF148" s="6">
-        <v>0.104144109660426</v>
+        <v>0.103426936683489</v>
       </c>
       <c r="AG148" s="6">
-        <v>0.13855048259388</v>
+        <v>0.140068605376058</v>
       </c>
       <c r="AH148" s="6">
-        <v>0.10016112635452</v>
+        <v>0.102956121402452</v>
       </c>
       <c r="AI148" s="6">
-        <v>9.9586339983679203E-2</v>
+        <v>0.102698109914811</v>
       </c>
       <c r="AJ148" s="6">
-        <v>4.9679937805093999E-2</v>
+        <v>4.8693639088997202E-2</v>
       </c>
       <c r="AK148" s="6">
-        <v>0.103383639249589</v>
+        <v>0.104944294507248</v>
       </c>
       <c r="AL148" s="6"/>
       <c r="AM148" s="6"/>
@@ -17848,22 +17840,22 @@
         <v>1.2638241161472052</v>
       </c>
       <c r="AF149" s="6">
-        <v>0.11309475548534299</v>
+        <v>0.11253721571116899</v>
       </c>
       <c r="AG149" s="6">
-        <v>0.151559894537245</v>
+        <v>0.153583394826735</v>
       </c>
       <c r="AH149" s="6">
-        <v>0.105094582327591</v>
+        <v>0.108388843039147</v>
       </c>
       <c r="AI149" s="6">
-        <v>0.10190454377896201</v>
+        <v>0.10499550194320401</v>
       </c>
       <c r="AJ149" s="6">
-        <v>5.0036068493322601E-2</v>
+        <v>4.9027323967408401E-2</v>
       </c>
       <c r="AK149" s="6">
-        <v>0.109607194560487</v>
+        <v>0.111441484329628</v>
       </c>
       <c r="AL149" s="6"/>
       <c r="AM149" s="6"/>
@@ -17964,22 +17956,22 @@
         <v>1.1768382139329958</v>
       </c>
       <c r="AF150" s="6">
-        <v>0.111842114241808</v>
+        <v>0.111014393912307</v>
       </c>
       <c r="AG150" s="6">
-        <v>0.14923910384959499</v>
+        <v>0.15078380174021999</v>
       </c>
       <c r="AH150" s="6">
-        <v>0.110669323677261</v>
+        <v>0.114343567294374</v>
       </c>
       <c r="AI150" s="6">
-        <v>0.10403779319716901</v>
+        <v>0.107040119136477</v>
       </c>
       <c r="AJ150" s="6">
-        <v>5.0338367710147602E-2</v>
+        <v>4.9298153665753797E-2</v>
       </c>
       <c r="AK150" s="6">
-        <v>0.110923667830546</v>
+        <v>0.11268187939622699</v>
       </c>
       <c r="AL150" s="6"/>
       <c r="AM150" s="6"/>
@@ -18080,22 +18072,22 @@
         <v>1.2230453941256769</v>
       </c>
       <c r="AF151" s="6">
-        <v>0.110702867031773</v>
+        <v>0.109672609583306</v>
       </c>
       <c r="AG151" s="6">
-        <v>0.14610478297704199</v>
+        <v>0.14725150492170799</v>
       </c>
       <c r="AH151" s="6">
-        <v>0.11490913773188099</v>
+        <v>0.118706928633616</v>
       </c>
       <c r="AI151" s="6">
-        <v>0.106301217810042</v>
+        <v>0.109167452715799</v>
       </c>
       <c r="AJ151" s="6">
-        <v>5.0619791309464299E-2</v>
+        <v>4.9542138045638603E-2</v>
       </c>
       <c r="AK151" s="6">
-        <v>0.111695162850482</v>
+        <v>0.11332185498444899</v>
       </c>
       <c r="AL151" s="6"/>
       <c r="AM151" s="6"/>
@@ -18196,22 +18188,22 @@
         <v>1.4172889011298651</v>
       </c>
       <c r="AF152" s="6">
-        <v>0.10970618790683601</v>
+        <v>0.10852957848962599</v>
       </c>
       <c r="AG152" s="6">
-        <v>0.14297011106225799</v>
+        <v>0.14383416758023901</v>
       </c>
       <c r="AH152" s="6">
-        <v>0.116354250710909</v>
+        <v>0.11997843261098499</v>
       </c>
       <c r="AI152" s="6">
-        <v>0.108540398425477</v>
+        <v>0.11119128982644701</v>
       </c>
       <c r="AJ152" s="6">
-        <v>5.0858488203259902E-2</v>
+        <v>4.9738026348393201E-2</v>
       </c>
       <c r="AK152" s="6">
-        <v>0.111708745472912</v>
+        <v>0.11314358418103</v>
       </c>
       <c r="AL152" s="6"/>
       <c r="AM152" s="6"/>
@@ -18312,22 +18304,22 @@
         <v>1.2734727038456128</v>
       </c>
       <c r="AF153" s="6">
-        <v>0.108707574888497</v>
+        <v>0.107428507123323</v>
       </c>
       <c r="AG153" s="6">
-        <v>0.139591299524843</v>
+        <v>0.14027075470418601</v>
       </c>
       <c r="AH153" s="6">
-        <v>0.11595184615482999</v>
+        <v>0.11929379213152801</v>
       </c>
       <c r="AI153" s="6">
-        <v>0.111290879878888</v>
+        <v>0.113680891873678</v>
       </c>
       <c r="AJ153" s="6">
-        <v>5.1136389926716097E-2</v>
+        <v>4.9971135886121898E-2</v>
       </c>
       <c r="AK153" s="6">
-        <v>0.11127730312008299</v>
+        <v>0.112512952472578</v>
       </c>
       <c r="AL153" s="6"/>
       <c r="AM153" s="6"/>
@@ -18428,22 +18420,22 @@
         <v>1.0016539814294845</v>
       </c>
       <c r="AF154" s="6">
-        <v>0.107577644010903</v>
+        <v>0.106234299388844</v>
       </c>
       <c r="AG154" s="6">
-        <v>0.136129707062982</v>
+        <v>0.13675887328403899</v>
       </c>
       <c r="AH154" s="6">
-        <v>0.122023825088932</v>
+        <v>0.12555611778409301</v>
       </c>
       <c r="AI154" s="6">
-        <v>0.11472178293966701</v>
+        <v>0.116858181106789</v>
       </c>
       <c r="AJ154" s="6">
-        <v>5.15386736680013E-2</v>
+        <v>5.0327074369312497E-2</v>
       </c>
       <c r="AK154" s="6">
-        <v>0.11269920166007601</v>
+        <v>0.11389316513523599</v>
       </c>
       <c r="AL154" s="6"/>
       <c r="AM154" s="6"/>
@@ -18544,22 +18536,22 @@
         <v>1.3861300951614197</v>
       </c>
       <c r="AF155" s="6">
-        <v>0.106596903760796</v>
+        <v>0.105228222658837</v>
       </c>
       <c r="AG155" s="6">
-        <v>0.137686345698631</v>
+        <v>0.138555684422589</v>
       </c>
       <c r="AH155" s="6">
-        <v>0.13063763633938599</v>
+        <v>0.13413342720431001</v>
       </c>
       <c r="AI155" s="6">
-        <v>0.11752202000300201</v>
+        <v>0.11935382597387199</v>
       </c>
       <c r="AJ155" s="6">
-        <v>5.1888738810674101E-2</v>
+        <v>5.0622389738913802E-2</v>
       </c>
       <c r="AK155" s="6">
-        <v>0.115881957614328</v>
+        <v>0.117038179648822</v>
       </c>
       <c r="AL155" s="6"/>
       <c r="AM155" s="6"/>
@@ -18660,22 +18652,22 @@
         <v>1.4700067976651354</v>
       </c>
       <c r="AF156" s="6">
-        <v>0.10578385310384</v>
+        <v>0.104419758625547</v>
       </c>
       <c r="AG156" s="6">
-        <v>0.13445593413975801</v>
+        <v>0.1353236833176</v>
       </c>
       <c r="AH156" s="6">
-        <v>0.122337223427609</v>
+        <v>0.12394684765925899</v>
       </c>
       <c r="AI156" s="6">
-        <v>0.119291396828255</v>
+        <v>0.12045654020237299</v>
       </c>
       <c r="AJ156" s="6">
-        <v>5.2161914212206999E-2</v>
+        <v>5.0835059561478199E-2</v>
       </c>
       <c r="AK156" s="6">
-        <v>0.113214843072956</v>
+        <v>0.113726993322927</v>
       </c>
       <c r="AL156" s="6"/>
       <c r="AM156" s="6"/>
@@ -18776,22 +18768,22 @@
         <v>1.8772174071937542</v>
       </c>
       <c r="AF157" s="6">
-        <v>0.104941463632701</v>
+        <v>0.10360299151682301</v>
       </c>
       <c r="AG157" s="6">
-        <v>0.13108674433436299</v>
+        <v>0.13198569465395699</v>
       </c>
       <c r="AH157" s="6">
-        <v>0.123266404354664</v>
+        <v>0.124705990901482</v>
       </c>
       <c r="AI157" s="6">
-        <v>0.122960229916678</v>
+        <v>0.12364324950969301</v>
       </c>
       <c r="AJ157" s="6">
-        <v>5.24911949283937E-2</v>
+        <v>5.1101223972963197E-2</v>
       </c>
       <c r="AK157" s="6">
-        <v>0.113351313634663</v>
+        <v>0.113715296852888</v>
       </c>
       <c r="AL157" s="6"/>
       <c r="AM157" s="6"/>
@@ -18892,22 +18884,22 @@
         <v>2.0906440296744933</v>
       </c>
       <c r="AF158" s="6">
-        <v>0.103962744248514</v>
+        <v>0.10266869315103599</v>
       </c>
       <c r="AG158" s="6">
-        <v>0.12698141384659001</v>
+        <v>0.12797762461558199</v>
       </c>
       <c r="AH158" s="6">
-        <v>0.11153046812911201</v>
+        <v>0.10913782034451699</v>
       </c>
       <c r="AI158" s="6">
-        <v>0.111276658011249</v>
+        <v>0.12108323366262</v>
       </c>
       <c r="AJ158" s="6">
-        <v>5.2809129633973398E-2</v>
+        <v>5.1506058731417399E-2</v>
       </c>
       <c r="AK158" s="6">
-        <v>0.106610724245101</v>
+        <v>0.108191838757278</v>
       </c>
       <c r="AL158" s="6"/>
       <c r="AM158" s="6"/>
@@ -19008,22 +19000,22 @@
         <v>1.3930722664508011</v>
       </c>
       <c r="AF159" s="6">
-        <v>0.10331949849437699</v>
+        <v>0.10209246490490299</v>
       </c>
       <c r="AG159" s="6">
-        <v>0.12514439055587301</v>
+        <v>0.126037823222172</v>
       </c>
       <c r="AH159" s="6">
-        <v>0.116116598329582</v>
+        <v>0.112266184454864</v>
       </c>
       <c r="AI159" s="6">
-        <v>0.114410485901749</v>
+        <v>0.12344966942209</v>
       </c>
       <c r="AJ159" s="6">
-        <v>5.3062142983976497E-2</v>
+        <v>5.16841248658821E-2</v>
       </c>
       <c r="AK159" s="6">
-        <v>0.108009940448913</v>
+        <v>0.108996104483295</v>
       </c>
       <c r="AL159" s="6"/>
       <c r="AM159" s="6"/>
@@ -19124,22 +19116,22 @@
         <v>1.9251312156534084</v>
       </c>
       <c r="AF160" s="6">
-        <v>0.103002309394189</v>
+        <v>0.101861192788123</v>
       </c>
       <c r="AG160" s="6">
-        <v>0.13866763243072699</v>
+        <v>0.14039548523958001</v>
       </c>
       <c r="AH160" s="6">
-        <v>0.12724729143635199</v>
+        <v>0.122297509342546</v>
       </c>
       <c r="AI160" s="6">
-        <v>0.118504667047287</v>
+        <v>0.12774696388671999</v>
       </c>
       <c r="AJ160" s="6">
-        <v>5.3518011417627499E-2</v>
+        <v>5.2070176946124397E-2</v>
       </c>
       <c r="AK160" s="6">
-        <v>0.115229342528541</v>
+        <v>0.116051332294836</v>
       </c>
       <c r="AL160" s="6"/>
       <c r="AM160" s="6"/>
@@ -19240,22 +19232,22 @@
         <v>1.9760215457679919</v>
       </c>
       <c r="AF161" s="6">
-        <v>0.102458641705906</v>
+        <v>0.101393390292386</v>
       </c>
       <c r="AG161" s="6">
-        <v>0.13532041289444399</v>
+        <v>0.13685345594928999</v>
       </c>
       <c r="AH161" s="6">
-        <v>0.116682194337544</v>
+        <v>0.1142621941313</v>
       </c>
       <c r="AI161" s="6">
-        <v>0.115644839670437</v>
+        <v>0.118905742481016</v>
       </c>
       <c r="AJ161" s="6">
-        <v>5.3693487363496099E-2</v>
+        <v>5.2078077613652102E-2</v>
       </c>
       <c r="AK161" s="6">
-        <v>0.110927575313022</v>
+        <v>0.11106082011780199</v>
       </c>
       <c r="AL161" s="6"/>
       <c r="AM161" s="6"/>
@@ -19356,22 +19348,22 @@
         <v>2.5920852647836057</v>
       </c>
       <c r="AF162" s="6">
-        <v>0.102076536206018</v>
+        <v>0.10109551788266399</v>
       </c>
       <c r="AG162" s="6">
-        <v>0.133166005140709</v>
+        <v>0.134902255263114</v>
       </c>
       <c r="AH162" s="6">
-        <v>0.118809374636341</v>
+        <v>0.11795860195421801</v>
       </c>
       <c r="AI162" s="6">
-        <v>0.117926859247535</v>
+        <v>0.120397932396984</v>
       </c>
       <c r="AJ162" s="6">
-        <v>5.3781321650543001E-2</v>
+        <v>5.2085560999291999E-2</v>
       </c>
       <c r="AK162" s="6">
-        <v>0.111422666456353</v>
+        <v>0.11181478081487101</v>
       </c>
       <c r="AL162" s="6"/>
       <c r="AM162" s="6"/>
@@ -19472,22 +19464,22 @@
         <v>1.50943244568289</v>
       </c>
       <c r="AF163" s="6">
-        <v>0.102143739659731</v>
+        <v>0.10125435024099801</v>
       </c>
       <c r="AG163" s="6">
-        <v>0.133539243239647</v>
+        <v>0.13539163163342699</v>
       </c>
       <c r="AH163" s="6">
-        <v>0.118351992506743</v>
+        <v>0.117385923030444</v>
       </c>
       <c r="AI163" s="6">
-        <v>0.116612249589163</v>
+        <v>0.11843569751804101</v>
       </c>
       <c r="AJ163" s="6">
-        <v>5.3446286045831799E-2</v>
+        <v>5.1673134931687098E-2</v>
       </c>
       <c r="AK163" s="6">
-        <v>0.111068047775486</v>
+        <v>0.111289436198322</v>
       </c>
       <c r="AL163" s="6"/>
       <c r="AM163" s="6"/>
@@ -19588,22 +19580,22 @@
         <v>1.031059022288261</v>
       </c>
       <c r="AF164" s="6">
-        <v>0.10161958156062099</v>
+        <v>0.100802925422672</v>
       </c>
       <c r="AG164" s="6">
-        <v>0.13274281420091799</v>
+        <v>0.134641957677335</v>
       </c>
       <c r="AH164" s="6">
-        <v>0.11745463770212</v>
+        <v>0.116526764876732</v>
       </c>
       <c r="AI164" s="6">
-        <v>0.115498870121792</v>
+        <v>0.11671564962421201</v>
       </c>
       <c r="AJ164" s="6">
-        <v>5.3168575214657898E-2</v>
+        <v>5.1336001895861703E-2</v>
       </c>
       <c r="AK164" s="6">
-        <v>0.110281635212178</v>
+        <v>0.110377310711805</v>
       </c>
       <c r="AL164" s="6"/>
       <c r="AM164" s="6"/>
@@ -19704,22 +19696,22 @@
         <v>1.9256671894165578</v>
       </c>
       <c r="AF165" s="6">
-        <v>0.101780461484669</v>
+        <v>0.101048155245898</v>
       </c>
       <c r="AG165" s="6">
-        <v>0.12593013849771501</v>
+        <v>0.12761179901115399</v>
       </c>
       <c r="AH165" s="6">
-        <v>0.111574956262571</v>
+        <v>0.111181882816343</v>
       </c>
       <c r="AI165" s="6">
-        <v>0.112340491066747</v>
+        <v>0.11267209155766</v>
       </c>
       <c r="AJ165" s="6">
-        <v>5.2606164464058199E-2</v>
+        <v>5.0729818896797098E-2</v>
       </c>
       <c r="AK165" s="6">
-        <v>0.106296238440832</v>
+        <v>0.106315062598642</v>
       </c>
       <c r="AL165" s="6"/>
       <c r="AM165" s="6"/>
@@ -19820,22 +19812,22 @@
         <v>1.2261250335935614</v>
       </c>
       <c r="AF166" s="6">
-        <v>0.102469178361729</v>
+        <v>0.101823780883573</v>
       </c>
       <c r="AG166" s="6">
-        <v>0.130065674409855</v>
+        <v>0.13221063161174099</v>
       </c>
       <c r="AH166" s="6">
-        <v>0.117302293425518</v>
+        <v>0.117160723543969</v>
       </c>
       <c r="AI166" s="6">
-        <v>0.12550656316304601</v>
+        <v>0.12577009244720799</v>
       </c>
       <c r="AJ166" s="6">
-        <v>5.4059928039486498E-2</v>
+        <v>5.2157220460619297E-2</v>
       </c>
       <c r="AK166" s="6">
-        <v>0.112139906854013</v>
+        <v>0.112316477441586</v>
       </c>
       <c r="AL166" s="6"/>
       <c r="AM166" s="6"/>
@@ -19936,22 +19928,22 @@
         <v>2.1948426317724312</v>
       </c>
       <c r="AF167" s="6">
-        <v>0.103027687938856</v>
+        <v>0.102418753850876</v>
       </c>
       <c r="AG167" s="6">
-        <v>0.126636051736255</v>
+        <v>0.128112069598914</v>
       </c>
       <c r="AH167" s="6">
-        <v>0.11061998648919499</v>
+        <v>0.110251818840858</v>
       </c>
       <c r="AI167" s="6">
-        <v>0.120195234998621</v>
+        <v>0.119749808825105</v>
       </c>
       <c r="AJ167" s="6">
-        <v>5.33465763108774E-2</v>
+        <v>5.1384381039613798E-2</v>
       </c>
       <c r="AK167" s="6">
-        <v>0.108353960233622</v>
+        <v>0.108142798044565</v>
       </c>
       <c r="AL167" s="6"/>
       <c r="AM167" s="6"/>
@@ -20052,22 +20044,22 @@
         <v>2.1280528703382373</v>
       </c>
       <c r="AF168" s="6">
-        <v>0.10358270728048501</v>
+        <v>0.10301515674782</v>
       </c>
       <c r="AG168" s="6">
-        <v>0.13042708972688599</v>
+        <v>0.13234387873894399</v>
       </c>
       <c r="AH168" s="6">
-        <v>0.115880271501383</v>
+        <v>0.11576645545954101</v>
       </c>
       <c r="AI168" s="6">
-        <v>0.13254594073551099</v>
+        <v>0.13169841624902201</v>
       </c>
       <c r="AJ168" s="6">
-        <v>5.4275694860445201E-2</v>
+        <v>5.2272792432603597E-2</v>
       </c>
       <c r="AK168" s="6">
-        <v>0.113683954589613</v>
+        <v>0.113544012001805</v>
       </c>
       <c r="AL168" s="6"/>
       <c r="AM168" s="6"/>
@@ -20168,22 +20160,22 @@
         <v>1.4192658654465617</v>
       </c>
       <c r="AF169" s="6">
-        <v>0.10417315131218401</v>
+        <v>0.10363010674491099</v>
       </c>
       <c r="AG169" s="6">
-        <v>0.13450647721775699</v>
+        <v>0.13676598067329401</v>
       </c>
       <c r="AH169" s="6">
-        <v>0.11412704832196099</v>
+        <v>0.113938838062666</v>
       </c>
       <c r="AI169" s="6">
-        <v>0.125773854738504</v>
+        <v>0.124183584186507</v>
       </c>
       <c r="AJ169" s="6">
-        <v>5.3482727511855802E-2</v>
+        <v>5.1427725270594603E-2</v>
       </c>
       <c r="AK169" s="6">
-        <v>0.112636893026411</v>
+        <v>0.112382990885777</v>
       </c>
       <c r="AL169" s="6"/>
       <c r="AM169" s="6"/>
@@ -20284,22 +20276,22 @@
         <v>1.2322096829791462</v>
       </c>
       <c r="AF170" s="6">
-        <v>0.104849611611618</v>
+        <v>0.104315055620168</v>
       </c>
       <c r="AG170" s="6">
-        <v>0.12877648920780299</v>
+        <v>0.13074132491389201</v>
       </c>
       <c r="AH170" s="6">
-        <v>0.105431233714496</v>
+        <v>0.10502618284389401</v>
       </c>
       <c r="AI170" s="6">
-        <v>0.118903671595103</v>
+        <v>0.11692250477055401</v>
       </c>
       <c r="AJ170" s="6">
-        <v>5.2644989251930799E-2</v>
+        <v>5.0569720365732998E-2</v>
       </c>
       <c r="AK170" s="6">
-        <v>0.10740782240774099</v>
+        <v>0.106939280291214</v>
       </c>
       <c r="AL170" s="6"/>
       <c r="AM170" s="6"/>
@@ -20400,22 +20392,22 @@
         <v>1.5133294061204339</v>
       </c>
       <c r="AF171" s="6">
-        <v>0.10554700535662601</v>
+        <v>0.105003482985856</v>
       </c>
       <c r="AG171" s="6">
-        <v>0.13329226390416901</v>
+        <v>0.13566490911434301</v>
       </c>
       <c r="AH171" s="6">
-        <v>0.10062287048118</v>
+        <v>0.100367900565258</v>
       </c>
       <c r="AI171" s="6">
-        <v>0.113004663623076</v>
+        <v>0.11090307947344</v>
       </c>
       <c r="AJ171" s="6">
-        <v>5.1878501200049401E-2</v>
+        <v>4.9809614606911697E-2</v>
       </c>
       <c r="AK171" s="6">
-        <v>0.105893030820367</v>
+        <v>0.10552744903064699</v>
       </c>
       <c r="AL171" s="6"/>
       <c r="AM171" s="6"/>
@@ -20516,22 +20508,22 @@
         <v>1.8266957194658318</v>
       </c>
       <c r="AF172" s="6">
-        <v>0.10610397525387801</v>
+        <v>0.10553121198963999</v>
       </c>
       <c r="AG172" s="6">
-        <v>0.13774068363540101</v>
+        <v>0.14038339655954901</v>
       </c>
       <c r="AH172" s="6">
-        <v>0.101419489826098</v>
+        <v>0.102182812644806</v>
       </c>
       <c r="AI172" s="6">
-        <v>0.10856392130584</v>
+        <v>0.10651134268862</v>
       </c>
       <c r="AJ172" s="6">
-        <v>5.1262571048062901E-2</v>
+        <v>4.9218906935509697E-2</v>
       </c>
       <c r="AK172" s="6">
-        <v>0.106112338588777</v>
+        <v>0.106076778027841</v>
       </c>
       <c r="AL172" s="6"/>
       <c r="AM172" s="6"/>
@@ -20632,22 +20624,22 @@
         <v>1.7881526975653372</v>
       </c>
       <c r="AF173" s="6">
-        <v>0.106239991617348</v>
+        <v>0.105616718171386</v>
       </c>
       <c r="AG173" s="6">
-        <v>0.139834271201984</v>
+        <v>0.14249280150367299</v>
       </c>
       <c r="AH173" s="6">
-        <v>0.10513334685656001</v>
+        <v>0.106308146228352</v>
       </c>
       <c r="AI173" s="6">
-        <v>0.111664804872945</v>
+        <v>0.10896236266767199</v>
       </c>
       <c r="AJ173" s="6">
-        <v>5.10120129690457E-2</v>
+        <v>4.8970819498732901E-2</v>
       </c>
       <c r="AK173" s="6">
-        <v>0.108268069756813</v>
+        <v>0.108178744322764</v>
       </c>
       <c r="AL173" s="6"/>
       <c r="AM173" s="6"/>
@@ -20748,22 +20740,22 @@
         <v>2.1947699042637936</v>
       </c>
       <c r="AF174" s="6">
-        <v>0.106161920404967</v>
+        <v>0.10548478822214</v>
       </c>
       <c r="AG174" s="6">
-        <v>0.14049319433729501</v>
+        <v>0.14303505408702299</v>
       </c>
       <c r="AH174" s="6">
-        <v>0.104795266870979</v>
+        <v>0.106048855530214</v>
       </c>
       <c r="AI174" s="6">
-        <v>0.110512411986197</v>
+        <v>0.107894608371237</v>
       </c>
       <c r="AJ174" s="6">
-        <v>5.0864818330795099E-2</v>
+        <v>4.8860453116040502E-2</v>
       </c>
       <c r="AK174" s="6">
-        <v>0.10803825431616899</v>
+        <v>0.10795788374217</v>
       </c>
       <c r="AL174" s="6"/>
       <c r="AM174" s="6"/>
@@ -20864,22 +20856,22 @@
         <v>2.2791609796911416</v>
       </c>
       <c r="AF175" s="6">
-        <v>0.106110321699998</v>
+        <v>0.105387117584388</v>
       </c>
       <c r="AG175" s="6">
-        <v>0.141363390573958</v>
+        <v>0.14379361385903899</v>
       </c>
       <c r="AH175" s="6">
-        <v>0.10679898925741201</v>
+        <v>0.10824228647339899</v>
       </c>
       <c r="AI175" s="6">
-        <v>0.110242074679541</v>
+        <v>0.107716075530115</v>
       </c>
       <c r="AJ175" s="6">
-        <v>5.0715086360549201E-2</v>
+        <v>4.8748093913357E-2</v>
       </c>
       <c r="AK175" s="6">
-        <v>0.10866144801520999</v>
+        <v>0.108634046068548</v>
       </c>
       <c r="AL175" s="6"/>
       <c r="AM175" s="6"/>
@@ -20980,22 +20972,22 @@
         <v>1.4294968863346469</v>
       </c>
       <c r="AF176" s="6">
-        <v>0.10600881459082601</v>
+        <v>0.10524439398673099</v>
       </c>
       <c r="AG176" s="6">
-        <v>0.14186041952523901</v>
+        <v>0.14414781042025701</v>
       </c>
       <c r="AH176" s="6">
-        <v>0.107205025496784</v>
+        <v>0.108932056527739</v>
       </c>
       <c r="AI176" s="6">
-        <v>0.109377374924482</v>
+        <v>0.106824051640768</v>
       </c>
       <c r="AJ176" s="6">
-        <v>5.0611108147633602E-2</v>
+        <v>4.8680994926190303E-2</v>
       </c>
       <c r="AK176" s="6">
-        <v>0.108650569072976</v>
+        <v>0.10869207964397699</v>
       </c>
       <c r="AL176" s="6"/>
       <c r="AM176" s="6"/>
@@ -21096,22 +21088,22 @@
         <v>2.1627028623058209</v>
       </c>
       <c r="AF177" s="6">
-        <v>0.105831030036275</v>
+        <v>0.105030983267368</v>
       </c>
       <c r="AG177" s="6">
-        <v>0.14204606223564201</v>
+        <v>0.144175441895777</v>
       </c>
       <c r="AH177" s="6">
-        <v>0.107769763316932</v>
+        <v>0.109541488769791</v>
       </c>
       <c r="AI177" s="6">
-        <v>0.10916657691918701</v>
+        <v>0.106710326661731</v>
       </c>
       <c r="AJ177" s="6">
-        <v>5.0588084169235298E-2</v>
+        <v>4.8692458209465703E-2</v>
       </c>
       <c r="AK177" s="6">
-        <v>0.108760693571599</v>
+        <v>0.10881574245591701</v>
       </c>
       <c r="AL177" s="6"/>
       <c r="AM177" s="6"/>
@@ -21212,22 +21204,22 @@
         <v>2.8366527901891203</v>
       </c>
       <c r="AF178" s="6">
-        <v>0.105498022319631</v>
+        <v>0.104667711882365</v>
       </c>
       <c r="AG178" s="6">
-        <v>0.14097485136537999</v>
+        <v>0.142896566668619</v>
       </c>
       <c r="AH178" s="6">
-        <v>0.106909703615017</v>
+        <v>0.109017990969332</v>
       </c>
       <c r="AI178" s="6">
-        <v>0.106201924440019</v>
+        <v>0.103641677823349</v>
       </c>
       <c r="AJ178" s="6">
-        <v>5.0363937363823101E-2</v>
+        <v>4.8434170014353399E-2</v>
       </c>
       <c r="AK178" s="6">
-        <v>0.107523794136692</v>
+        <v>0.107621850268556</v>
       </c>
       <c r="AL178" s="6"/>
       <c r="AM178" s="6"/>
@@ -21328,22 +21320,22 @@
         <v>1.9765206556776604</v>
       </c>
       <c r="AF179" s="6">
-        <v>0.105015949890887</v>
+        <v>0.10416493934497</v>
       </c>
       <c r="AG179" s="6">
-        <v>0.13895019627942501</v>
+        <v>0.14066983723363899</v>
       </c>
       <c r="AH179" s="6">
-        <v>0.10502026951594901</v>
+        <v>0.10682667588120701</v>
       </c>
       <c r="AI179" s="6">
-        <v>0.10136965681575499</v>
+        <v>9.9208357880613995E-2</v>
       </c>
       <c r="AJ179" s="6">
-        <v>5.0320147419351799E-2</v>
+        <v>4.84320218106861E-2</v>
       </c>
       <c r="AK179" s="6">
-        <v>0.10541166570417899</v>
+        <v>0.10546349832087901</v>
       </c>
       <c r="AL179" s="6"/>
       <c r="AM179" s="6"/>
@@ -21444,22 +21436,22 @@
         <v>1.5554177048553441</v>
       </c>
       <c r="AF180" s="6">
-        <v>0.106120776824028</v>
+        <v>0.105292013644224</v>
       </c>
       <c r="AG180" s="6">
-        <v>0.145749534144473</v>
+        <v>0.147717505238042</v>
       </c>
       <c r="AH180" s="6">
-        <v>0.10786835857456099</v>
+        <v>0.10983674602176501</v>
       </c>
       <c r="AI180" s="6">
-        <v>0.102717753068715</v>
+        <v>0.10083306038208401</v>
       </c>
       <c r="AJ180" s="6">
-        <v>5.0482828632075302E-2</v>
+        <v>4.86293959746643E-2</v>
       </c>
       <c r="AK180" s="6">
-        <v>0.108293191020902</v>
+        <v>0.10851383999719499</v>
       </c>
       <c r="AL180" s="6"/>
       <c r="AM180" s="6"/>
@@ -21560,22 +21552,22 @@
         <v>2.6648568901471492</v>
       </c>
       <c r="AF181" s="6">
-        <v>0.105578810589933</v>
+        <v>0.1047283107693</v>
       </c>
       <c r="AG181" s="6">
-        <v>0.147550921770527</v>
+        <v>0.150296935428538</v>
       </c>
       <c r="AH181" s="6">
-        <v>0.11225143750225999</v>
+        <v>0.114353933238369</v>
       </c>
       <c r="AI181" s="6">
-        <v>0.104261198195963</v>
+        <v>0.10259596091065699</v>
       </c>
       <c r="AJ181" s="6">
-        <v>5.0675914568426003E-2</v>
+        <v>4.8849042768526398E-2</v>
       </c>
       <c r="AK181" s="6">
-        <v>0.110212690836378</v>
+        <v>0.11069824107514201</v>
       </c>
       <c r="AL181" s="6"/>
       <c r="AM181" s="6"/>
@@ -21676,22 +21668,22 @@
         <v>2.3096726271411683</v>
       </c>
       <c r="AF182" s="6">
-        <v>0.105090219800305</v>
+        <v>0.104218501326861</v>
       </c>
       <c r="AG182" s="6">
-        <v>0.14490152421003899</v>
+        <v>0.14715220170208901</v>
       </c>
       <c r="AH182" s="6">
-        <v>0.110292898485623</v>
+        <v>0.1119617188936</v>
       </c>
       <c r="AI182" s="6">
-        <v>9.8397461980715903E-2</v>
+        <v>9.7043729687596197E-2</v>
       </c>
       <c r="AJ182" s="6">
-        <v>4.7411623102624499E-2</v>
+        <v>4.5667165420573801E-2</v>
       </c>
       <c r="AK182" s="6">
-        <v>0.107220918323553</v>
+        <v>0.107543749559405</v>
       </c>
       <c r="AL182" s="6"/>
       <c r="AM182" s="6"/>
@@ -21792,22 +21784,22 @@
         <v>3.1738291117644479</v>
       </c>
       <c r="AF183" s="6">
-        <v>0.104358188429117</v>
+        <v>0.103476698143151</v>
       </c>
       <c r="AG183" s="6">
-        <v>0.141356531992609</v>
+        <v>0.143197169447319</v>
       </c>
       <c r="AH183" s="6">
-        <v>0.115392733476419</v>
+        <v>0.117308512606979</v>
       </c>
       <c r="AI183" s="6">
-        <v>0.101451973859983</v>
+        <v>0.10035135337288401</v>
       </c>
       <c r="AJ183" s="6">
-        <v>4.7936493984922203E-2</v>
+        <v>4.6287146373142199E-2</v>
       </c>
       <c r="AK183" s="6">
-        <v>0.10836996872579201</v>
+        <v>0.10872270731049299</v>
       </c>
       <c r="AL183" s="6"/>
       <c r="AM183" s="6"/>
@@ -21908,22 +21900,22 @@
         <v>2.1488358405154173</v>
       </c>
       <c r="AF184" s="6">
-        <v>0.103802679359248</v>
+        <v>0.102934689218348</v>
       </c>
       <c r="AG184" s="6">
-        <v>0.138309562124519</v>
+        <v>0.139909915765451</v>
       </c>
       <c r="AH184" s="6">
-        <v>0.111568590524645</v>
+        <v>0.112899641983011</v>
       </c>
       <c r="AI184" s="6">
-        <v>9.3763616706930494E-2</v>
+        <v>9.2937402017035001E-2</v>
       </c>
       <c r="AJ184" s="6">
-        <v>4.7347254969049603E-2</v>
+        <v>4.5779718844170501E-2</v>
       </c>
       <c r="AK184" s="6">
-        <v>0.104741898013635</v>
+        <v>0.104956720631471</v>
       </c>
       <c r="AL184" s="6"/>
       <c r="AM184" s="6"/>
@@ -22024,22 +22016,22 @@
         <v>1.7192872763967415</v>
       </c>
       <c r="AF185" s="6">
-        <v>0.10453327888564</v>
+        <v>0.103716964241256</v>
       </c>
       <c r="AG185" s="6">
-        <v>0.14634192647353</v>
+        <v>0.148261836865063</v>
       </c>
       <c r="AH185" s="6">
-        <v>0.11474830804684</v>
+        <v>0.116150391816969</v>
       </c>
       <c r="AI185" s="6">
-        <v>9.5768602777015599E-2</v>
+        <v>9.5298580117279194E-2</v>
       </c>
       <c r="AJ185" s="6">
-        <v>4.7724469695091302E-2</v>
+        <v>4.6241609800351503E-2</v>
       </c>
       <c r="AK185" s="6">
-        <v>0.10814268576059601</v>
+        <v>0.108550147534572</v>
       </c>
       <c r="AL185" s="6"/>
       <c r="AM185" s="6"/>
@@ -22140,22 +22132,22 @@
         <v>2.7486993518014202</v>
       </c>
       <c r="AF186" s="6">
-        <v>0.103977980391737</v>
+        <v>0.103163627871005</v>
       </c>
       <c r="AG186" s="6">
-        <v>0.14695273515073201</v>
+        <v>0.14867283771162099</v>
       </c>
       <c r="AH186" s="6">
-        <v>0.120491250865675</v>
+        <v>0.122003039974797</v>
       </c>
       <c r="AI186" s="6">
-        <v>9.8182235837423804E-2</v>
+        <v>9.8001550927511893E-2</v>
       </c>
       <c r="AJ186" s="6">
-        <v>4.81526394383801E-2</v>
+        <v>4.6737632015465699E-2</v>
       </c>
       <c r="AK186" s="6">
-        <v>0.110324566358216</v>
+        <v>0.110784125725812</v>
       </c>
       <c r="AL186" s="6"/>
       <c r="AM186" s="6"/>
@@ -22256,22 +22248,22 @@
         <v>1.6613507142512418</v>
       </c>
       <c r="AF187" s="6">
-        <v>0.103544289570751</v>
+        <v>0.102748292316047</v>
       </c>
       <c r="AG187" s="6">
-        <v>0.143923623370211</v>
+        <v>0.14528056115049201</v>
       </c>
       <c r="AH187" s="6">
-        <v>0.11646361962665799</v>
+        <v>0.117408424084681</v>
       </c>
       <c r="AI187" s="6">
-        <v>9.2864294385810495E-2</v>
+        <v>9.2808016905620502E-2</v>
       </c>
       <c r="AJ187" s="6">
-        <v>4.7867478514824403E-2</v>
+        <v>4.6498399092339597E-2</v>
       </c>
       <c r="AK187" s="6">
-        <v>0.10722589058149599</v>
+        <v>0.10749048524759</v>
       </c>
       <c r="AL187" s="6"/>
       <c r="AM187" s="6"/>
@@ -22372,22 +22364,22 @@
         <v>1.9594839504094352</v>
       </c>
       <c r="AF188" s="6">
-        <v>0.1045023661895</v>
+        <v>0.10376275378076399</v>
       </c>
       <c r="AG188" s="6">
-        <v>0.15434571965753999</v>
+        <v>0.15594916318552199</v>
       </c>
       <c r="AH188" s="6">
-        <v>0.120323771165067</v>
+        <v>0.121277512187958</v>
       </c>
       <c r="AI188" s="6">
-        <v>9.5241950451970495E-2</v>
+        <v>9.5517445509033599E-2</v>
       </c>
       <c r="AJ188" s="6">
-        <v>4.8260120715205697E-2</v>
+        <v>4.6946207787335902E-2</v>
       </c>
       <c r="AK188" s="6">
-        <v>0.11149808575556901</v>
+        <v>0.111911834812174</v>
       </c>
       <c r="AL188" s="6"/>
       <c r="AM188" s="6"/>
@@ -22488,22 +22480,22 @@
         <v>2.7561479170152836</v>
       </c>
       <c r="AF189" s="6">
-        <v>0.10396467371712</v>
+        <v>0.103220236043516</v>
       </c>
       <c r="AG189" s="6">
-        <v>0.149930129860253</v>
+        <v>0.15094176062116299</v>
       </c>
       <c r="AH189" s="6">
-        <v>0.12052829931965101</v>
+        <v>0.12123658763068799</v>
       </c>
       <c r="AI189" s="6">
-        <v>9.7885163142824805E-2</v>
+        <v>9.8420323238535404E-2</v>
       </c>
       <c r="AJ189" s="6">
-        <v>4.8644477623594903E-2</v>
+        <v>4.7371167798343897E-2</v>
       </c>
       <c r="AK189" s="6">
-        <v>0.11106244537498899</v>
+        <v>0.111332112175207</v>
       </c>
       <c r="AL189" s="6"/>
       <c r="AM189" s="6"/>
@@ -22604,22 +22596,22 @@
         <v>2.1124407643469567</v>
       </c>
       <c r="AF190" s="6">
-        <v>0.10342593839464299</v>
+        <v>0.102691581181356</v>
       </c>
       <c r="AG190" s="6">
-        <v>0.145884771393437</v>
+        <v>0.14651925679164801</v>
       </c>
       <c r="AH190" s="6">
-        <v>0.11554901943585601</v>
+        <v>0.115812276087148</v>
       </c>
       <c r="AI190" s="6">
-        <v>9.1102541054804906E-2</v>
+        <v>9.1578702938471701E-2</v>
       </c>
       <c r="AJ190" s="6">
-        <v>4.8206438593470902E-2</v>
+        <v>4.69455217578107E-2</v>
       </c>
       <c r="AK190" s="6">
-        <v>0.10709457869344501</v>
+        <v>0.107153273207618</v>
       </c>
       <c r="AL190" s="6"/>
       <c r="AM190" s="6"/>
@@ -22720,22 +22712,22 @@
         <v>1.6767802651994401</v>
       </c>
       <c r="AF191" s="6">
-        <v>0.103267755029561</v>
+        <v>0.102562838368919</v>
       </c>
       <c r="AG191" s="6">
-        <v>0.145815000325551</v>
+        <v>0.14633723300118701</v>
       </c>
       <c r="AH191" s="6">
-        <v>0.11723038553470699</v>
+        <v>0.11748073386107299</v>
       </c>
       <c r="AI191" s="6">
-        <v>9.2553218241661697E-2</v>
+        <v>9.3344291001860799E-2</v>
       </c>
       <c r="AJ191" s="6">
-        <v>4.8422956286286699E-2</v>
+        <v>4.7198225150144699E-2</v>
       </c>
       <c r="AK191" s="6">
-        <v>0.10785588301535</v>
+        <v>0.107964513571082</v>
       </c>
       <c r="AL191" s="6"/>
       <c r="AM191" s="6"/>
@@ -22836,22 +22828,22 @@
         <v>2.0365320511899654</v>
       </c>
       <c r="AF192" s="6">
-        <v>0.103077671513314</v>
+        <v>0.102402878957007</v>
       </c>
       <c r="AG192" s="6">
-        <v>0.14516438836945</v>
+        <v>0.14557096109348799</v>
       </c>
       <c r="AH192" s="6">
-        <v>0.11933821076534</v>
+        <v>0.119548991698066</v>
       </c>
       <c r="AI192" s="6">
-        <v>9.4100018351454401E-2</v>
+        <v>9.5151090405571404E-2</v>
       </c>
       <c r="AJ192" s="6">
-        <v>4.8651358900965898E-2</v>
+        <v>4.7454175568551901E-2</v>
       </c>
       <c r="AK192" s="6">
-        <v>0.108602906054551</v>
+        <v>0.108740350007621</v>
       </c>
       <c r="AL192" s="6"/>
       <c r="AM192" s="6"/>
@@ -22952,22 +22944,22 @@
         <v>-0.31520406547045354</v>
       </c>
       <c r="AF193" s="6">
-        <v>0.10325067643048599</v>
+        <v>0.102614144258765</v>
       </c>
       <c r="AG193" s="6">
-        <v>0.145945223072205</v>
+        <v>0.14629658835690701</v>
       </c>
       <c r="AH193" s="6">
-        <v>0.118873235568692</v>
+        <v>0.118911195905937</v>
       </c>
       <c r="AI193" s="6">
-        <v>9.4147953549233498E-2</v>
+        <v>9.5346885208145202E-2</v>
       </c>
       <c r="AJ193" s="6">
-        <v>4.8658723942571397E-2</v>
+        <v>4.7477453907543897E-2</v>
       </c>
       <c r="AK193" s="6">
-        <v>0.108710103041627</v>
+        <v>0.108829666707627</v>
       </c>
       <c r="AL193" s="6"/>
       <c r="AM193" s="6"/>
@@ -23068,22 +23060,22 @@
         <v>-4.5480300396860684E-3</v>
       </c>
       <c r="AF194" s="6">
-        <v>7.64304726639915E-2</v>
+        <v>7.5473736608509007E-2</v>
       </c>
       <c r="AG194" s="6">
-        <v>0.119118568550038</v>
+        <v>0.118852623100555</v>
       </c>
       <c r="AH194" s="6">
-        <v>0.108621227857869</v>
+        <v>0.108165412997623</v>
       </c>
       <c r="AI194" s="6">
-        <v>9.0769742163595804E-2</v>
+        <v>9.1983088976109406E-2</v>
       </c>
       <c r="AJ194" s="6">
-        <v>4.8120258252298598E-2</v>
+        <v>4.6944324764623499E-2</v>
       </c>
       <c r="AK194" s="6">
-        <v>9.5025816623338102E-2</v>
+        <v>9.4824178655596503E-2</v>
       </c>
       <c r="AL194" s="6"/>
       <c r="AM194" s="6"/>
@@ -23184,22 +23176,22 @@
         <v>1.5629895948606531</v>
       </c>
       <c r="AF195" s="6">
-        <v>7.8949899432089202E-2</v>
+        <v>7.8690708090131303E-2</v>
       </c>
       <c r="AG195" s="6">
-        <v>0.11962315964841699</v>
+        <v>0.120003097054178</v>
       </c>
       <c r="AH195" s="6">
-        <v>9.3738578867923902E-2</v>
+        <v>9.3048839338468803E-2</v>
       </c>
       <c r="AI195" s="6">
-        <v>8.6001307462379106E-2</v>
+        <v>8.7252141913592401E-2</v>
       </c>
       <c r="AJ195" s="6">
-        <v>4.7332863414777E-2</v>
+        <v>4.6171363659451597E-2</v>
       </c>
       <c r="AK195" s="6">
-        <v>9.0411862680629798E-2</v>
+        <v>9.0392342910564402E-2</v>
       </c>
       <c r="AL195" s="6"/>
       <c r="AM195" s="6"/>
@@ -23300,22 +23292,22 @@
         <v>1.4169872215187951</v>
       </c>
       <c r="AF196" s="6">
-        <v>8.1509239479097606E-2</v>
+        <v>8.1868400454952805E-2</v>
       </c>
       <c r="AG196" s="6">
-        <v>0.129203695840934</v>
+        <v>0.130422003473112</v>
       </c>
       <c r="AH196" s="6">
-        <v>0.10367404942620601</v>
+        <v>0.10341305224217399</v>
       </c>
       <c r="AI196" s="6">
-        <v>0.115789687389187</v>
+        <v>0.11898431573849801</v>
       </c>
       <c r="AJ196" s="6">
-        <v>5.4178203446836902E-2</v>
+        <v>5.3207247456808902E-2</v>
       </c>
       <c r="AK196" s="6">
-        <v>0.10346209461184</v>
+        <v>0.104332103986647</v>
       </c>
       <c r="AL196" s="6"/>
       <c r="AM196" s="6"/>
@@ -23416,22 +23408,22 @@
         <v>2.4841632440153916</v>
       </c>
       <c r="AF197" s="6">
-        <v>8.4008180881055397E-2</v>
+        <v>8.4903056850118605E-2</v>
       </c>
       <c r="AG197" s="6">
-        <v>0.13947336729231699</v>
+        <v>0.14135887639546199</v>
       </c>
       <c r="AH197" s="6">
-        <v>0.120774516391744</v>
+        <v>0.12191408726639</v>
       </c>
       <c r="AI197" s="6">
-        <v>0.10925734590464101</v>
+        <v>0.112314653867451</v>
       </c>
       <c r="AJ197" s="6">
-        <v>5.2528545836638803E-2</v>
+        <v>5.1356274046623303E-2</v>
       </c>
       <c r="AK197" s="6">
-        <v>0.108969652940896</v>
+        <v>0.11034689165354999</v>
       </c>
       <c r="AL197" s="6"/>
       <c r="AM197" s="6"/>
@@ -23532,22 +23524,22 @@
         <v>1.366001726903221</v>
       </c>
       <c r="AF198" s="6">
-        <v>8.6268598540529706E-2</v>
+        <v>8.7606751755618203E-2</v>
       </c>
       <c r="AG198" s="6">
-        <v>0.14889267318496699</v>
+        <v>0.151184511267664</v>
       </c>
       <c r="AH198" s="6">
-        <v>0.133823342465654</v>
+        <v>0.13554237436248101</v>
       </c>
       <c r="AI198" s="6">
-        <v>0.145074324826477</v>
+        <v>0.14893148596887701</v>
       </c>
       <c r="AJ198" s="6">
-        <v>5.5301382949273399E-2</v>
+        <v>5.3306674588712799E-2</v>
       </c>
       <c r="AK198" s="6">
-        <v>0.1233655812236</v>
+        <v>0.12509396770891801</v>
       </c>
       <c r="AL198" s="6"/>
       <c r="AM198" s="6"/>
@@ -23648,22 +23640,22 @@
         <v>1.0760756542293137</v>
       </c>
       <c r="AF199" s="6">
-        <v>8.8422675234230794E-2</v>
+        <v>9.0123472013088707E-2</v>
       </c>
       <c r="AG199" s="6">
-        <v>0.15115606301548201</v>
+        <v>0.152016020606628</v>
       </c>
       <c r="AH199" s="6">
-        <v>0.112002170931869</v>
+        <v>0.111709437746952</v>
       </c>
       <c r="AI199" s="6">
-        <v>0.12917356762460599</v>
+        <v>0.13060401053957499</v>
       </c>
       <c r="AJ199" s="6">
-        <v>5.3706810433077803E-2</v>
+        <v>5.1629002177833498E-2</v>
       </c>
       <c r="AK199" s="6">
-        <v>0.11476847804394801</v>
+        <v>0.115135890312951</v>
       </c>
       <c r="AL199" s="6"/>
       <c r="AM199" s="6"/>
@@ -23764,22 +23756,22 @@
         <v>0.6148751967291588</v>
       </c>
       <c r="AF200" s="6">
-        <v>9.0334480897383607E-2</v>
+        <v>9.2309110663289895E-2</v>
       </c>
       <c r="AG200" s="6">
-        <v>0.156218244878638</v>
+        <v>0.157551134488332</v>
       </c>
       <c r="AH200" s="6">
-        <v>0.100574259717851</v>
+        <v>0.10060004616014701</v>
       </c>
       <c r="AI200" s="6">
-        <v>0.11865599395588999</v>
+        <v>0.118941980350614</v>
       </c>
       <c r="AJ200" s="6">
-        <v>5.2493760027116303E-2</v>
+        <v>5.0393264369268297E-2</v>
       </c>
       <c r="AK200" s="6">
-        <v>0.110635101353453</v>
+        <v>0.11097136495751</v>
       </c>
       <c r="AL200" s="6"/>
       <c r="AM200" s="6"/>
@@ -23880,22 +23872,22 @@
         <v>1.2624289991201465</v>
       </c>
       <c r="AF201" s="6">
-        <v>9.2055884132332705E-2</v>
+        <v>9.4230718057434298E-2</v>
       </c>
       <c r="AG201" s="6">
-        <v>0.149806441963071</v>
+        <v>0.15189692111136899</v>
       </c>
       <c r="AH201" s="6">
-        <v>9.1411307344941004E-2</v>
+        <v>9.1447927071897597E-2</v>
       </c>
       <c r="AI201" s="6">
-        <v>0.111135149706433</v>
+        <v>0.110880034909385</v>
       </c>
       <c r="AJ201" s="6">
-        <v>5.15336307923085E-2</v>
+        <v>4.9447669340966997E-2</v>
       </c>
       <c r="AK201" s="6">
-        <v>0.105101074818143</v>
+        <v>0.105521065850958</v>
       </c>
       <c r="AL201" s="6"/>
       <c r="AM201" s="6"/>
@@ -23996,22 +23988,22 @@
         <v>1.7521907302608497</v>
       </c>
       <c r="AF202" s="6">
-        <v>9.3645985509698895E-2</v>
+        <v>9.5957517142309504E-2</v>
       </c>
       <c r="AG202" s="6">
-        <v>0.156180044131255</v>
+        <v>0.158225900341599</v>
       </c>
       <c r="AH202" s="6">
-        <v>9.8483841449753903E-2</v>
+        <v>9.92807058032497E-2</v>
       </c>
       <c r="AI202" s="6">
-        <v>0.10601409443734799</v>
+        <v>0.10555911975827501</v>
       </c>
       <c r="AJ202" s="6">
-        <v>5.0720621495196697E-2</v>
+        <v>4.8673738962674899E-2</v>
       </c>
       <c r="AK202" s="6">
-        <v>0.10733426970894901</v>
+        <v>0.10792471740911</v>
       </c>
       <c r="AL202" s="6"/>
       <c r="AM202" s="6"/>
@@ -24112,22 +24104,22 @@
         <v>2.3321882907563207</v>
       </c>
       <c r="AF203" s="6">
-        <v>9.5353104806050207E-2</v>
+        <v>9.7763455566038701E-2</v>
       </c>
       <c r="AG203" s="6">
-        <v>0.164302433715242</v>
+        <v>0.16620753151051601</v>
       </c>
       <c r="AH203" s="6">
-        <v>0.110811828954211</v>
+        <v>0.112466432489851</v>
       </c>
       <c r="AI203" s="6">
-        <v>0.11595764781006</v>
+        <v>0.115646116000596</v>
       </c>
       <c r="AJ203" s="6">
-        <v>4.9923889273876601E-2</v>
+        <v>4.7936918481280497E-2</v>
       </c>
       <c r="AK203" s="6">
-        <v>0.114852579233455</v>
+        <v>0.11567999804910201</v>
       </c>
       <c r="AL203" s="6"/>
       <c r="AM203" s="6"/>
@@ -24228,22 +24220,22 @@
         <v>1.8219006186775744</v>
       </c>
       <c r="AF204" s="6">
-        <v>9.6903240410701794E-2</v>
+        <v>9.9351824403986003E-2</v>
       </c>
       <c r="AG204" s="6">
-        <v>0.17190486668553301</v>
+        <v>0.17340453000130501</v>
       </c>
       <c r="AH204" s="6">
-        <v>0.12372346801567</v>
+        <v>0.12612014315829501</v>
       </c>
       <c r="AI204" s="6">
-        <v>0.13069299255745501</v>
+        <v>0.12877920863613301</v>
       </c>
       <c r="AJ204" s="6">
-        <v>4.9451272237456302E-2</v>
+        <v>4.7452323632863801E-2</v>
       </c>
       <c r="AK204" s="6">
-        <v>0.12349641243418701</v>
+        <v>0.124041247843173</v>
       </c>
       <c r="AL204" s="6"/>
       <c r="AM204" s="6"/>
@@ -24344,22 +24336,22 @@
         <v>1.4231006705795579</v>
       </c>
       <c r="AF205" s="6">
-        <v>9.8524789473531396E-2</v>
+        <v>0.100976099858543</v>
       </c>
       <c r="AG205" s="6">
-        <v>0.17915405933031001</v>
+        <v>0.179995830677142</v>
       </c>
       <c r="AH205" s="6">
-        <v>0.110817843535698</v>
+        <v>0.111985189097391</v>
       </c>
       <c r="AI205" s="6">
-        <v>0.119590991775212</v>
+        <v>0.117242199081874</v>
       </c>
       <c r="AJ205" s="6">
-        <v>4.86452332658713E-2</v>
+        <v>4.6736603010519601E-2</v>
       </c>
       <c r="AK205" s="6">
-        <v>0.119370004673975</v>
+        <v>0.119374468894191</v>
       </c>
       <c r="AL205" s="6"/>
       <c r="AM205" s="6"/>
@@ -24460,22 +24452,22 @@
         <v>2.5165602770652384</v>
       </c>
       <c r="AF206" s="6">
-        <v>9.9845660558206498E-2</v>
+        <v>0.102235652990257</v>
       </c>
       <c r="AG206" s="6">
-        <v>0.18408496731843901</v>
+        <v>0.18397958051924601</v>
       </c>
       <c r="AH206" s="6">
-        <v>0.102365952092518</v>
+        <v>0.103119466096219</v>
       </c>
       <c r="AI206" s="6">
-        <v>0.112260977087954</v>
+        <v>0.10985963845520499</v>
       </c>
       <c r="AJ206" s="6">
-        <v>4.80935024980612E-2</v>
+        <v>4.6282417674157E-2</v>
       </c>
       <c r="AK206" s="6">
-        <v>0.11666824627216001</v>
+        <v>0.11635119299407</v>
       </c>
       <c r="AL206" s="6"/>
       <c r="AM206" s="6"/>
@@ -24576,22 +24568,22 @@
         <v>1.6507461498299847</v>
       </c>
       <c r="AF207" s="6">
-        <v>0.100961337141265</v>
+        <v>0.103245679971112</v>
       </c>
       <c r="AG207" s="6">
-        <v>0.18946736750474899</v>
+        <v>0.18829804154907001</v>
       </c>
       <c r="AH207" s="6">
-        <v>0.111365882310121</v>
+        <v>0.11268252666035899</v>
       </c>
       <c r="AI207" s="6">
-        <v>0.12587551267720801</v>
+        <v>0.123143911922967</v>
       </c>
       <c r="AJ207" s="6">
-        <v>4.8187386602674097E-2</v>
+        <v>4.6470865198111999E-2</v>
       </c>
       <c r="AK207" s="6">
-        <v>0.123587383902293</v>
+        <v>0.123098891326526</v>
       </c>
       <c r="AL207" s="6"/>
       <c r="AM207" s="6"/>
@@ -24692,22 +24684,22 @@
         <v>1.1540622643664733</v>
       </c>
       <c r="AF208" s="6">
-        <v>0.102015369425039</v>
+        <v>0.104168882188653</v>
       </c>
       <c r="AG208" s="6">
-        <v>0.182575618313077</v>
+        <v>0.18014860793951901</v>
       </c>
       <c r="AH208" s="6">
-        <v>0.101454257743325</v>
+        <v>0.102280785203474</v>
       </c>
       <c r="AI208" s="6">
-        <v>0.11848230676751501</v>
+        <v>0.115570620900947</v>
       </c>
       <c r="AJ208" s="6">
-        <v>4.7766933149784099E-2</v>
+        <v>4.6136423232734002E-2</v>
       </c>
       <c r="AK208" s="6">
-        <v>0.11778295101344601</v>
+        <v>0.116835210274694</v>
       </c>
       <c r="AL208" s="6"/>
       <c r="AM208" s="6"/>
@@ -24808,22 +24800,22 @@
         <v>1.7648328335621244</v>
       </c>
       <c r="AF209" s="6">
-        <v>0.103111626367432</v>
+        <v>0.10511922211442599</v>
       </c>
       <c r="AG209" s="6">
-        <v>0.17634028496812301</v>
+        <v>0.17307004837204301</v>
       </c>
       <c r="AH209" s="6">
-        <v>9.2765281084887699E-2</v>
+        <v>9.3487476684680201E-2</v>
       </c>
       <c r="AI209" s="6">
-        <v>0.11173285570979501</v>
+        <v>0.10889470641881401</v>
       </c>
       <c r="AJ209" s="6">
-        <v>4.73295783174962E-2</v>
+        <v>4.5787347016707197E-2</v>
       </c>
       <c r="AK209" s="6">
-        <v>0.11257802265935</v>
+        <v>0.11142241867406701</v>
       </c>
       <c r="AL209" s="6"/>
       <c r="AM209" s="6"/>
@@ -24924,22 +24916,22 @@
         <v>1.5595450080951423</v>
       </c>
       <c r="AF210" s="6">
-        <v>0.104262876304133</v>
+        <v>0.10610982806467301</v>
       </c>
       <c r="AG210" s="6">
-        <v>0.18365831646026501</v>
+        <v>0.17965124946945499</v>
       </c>
       <c r="AH210" s="6">
-        <v>0.10277163632535601</v>
+        <v>0.104309617405317</v>
       </c>
       <c r="AI210" s="6">
-        <v>0.10903437405142</v>
+        <v>0.106381901900862</v>
       </c>
       <c r="AJ210" s="6">
-        <v>4.6872434328914699E-2</v>
+        <v>4.5420442329995703E-2</v>
       </c>
       <c r="AK210" s="6">
-        <v>0.11637727128302899</v>
+        <v>0.115287804480522</v>
       </c>
       <c r="AL210" s="6"/>
       <c r="AM210" s="6"/>
@@ -25040,22 +25032,22 @@
         <v>1.1270571978375443</v>
       </c>
       <c r="AF211" s="6">
-        <v>0.105160881621917</v>
+        <v>0.106814559203572</v>
       </c>
       <c r="AG211" s="6">
-        <v>0.18887622862557299</v>
+        <v>0.18394882560861101</v>
       </c>
       <c r="AH211" s="6">
-        <v>9.9393704534268004E-2</v>
+        <v>0.100847669660336</v>
       </c>
       <c r="AI211" s="6">
-        <v>0.104154796950606</v>
+        <v>0.101754729697746</v>
       </c>
       <c r="AJ211" s="6">
-        <v>4.6570383954446598E-2</v>
+        <v>4.5209284155867002E-2</v>
       </c>
       <c r="AK211" s="6">
-        <v>0.115602332988752</v>
+        <v>0.114339225050595</v>
       </c>
       <c r="AL211" s="6"/>
       <c r="AM211" s="6"/>
@@ -25156,22 +25148,22 @@
         <v>1.570304901288111</v>
       </c>
       <c r="AF212" s="6">
-        <v>0.106088890153871</v>
+        <v>0.107541822928395</v>
       </c>
       <c r="AG212" s="6">
-        <v>0.189871709385911</v>
+        <v>0.18397571546581601</v>
       </c>
       <c r="AH212" s="6">
-        <v>9.1894023527111304E-2</v>
+        <v>9.32005828241846E-2</v>
       </c>
       <c r="AI212" s="6">
-        <v>9.9692182648804903E-2</v>
+        <v>9.7628226833570905E-2</v>
       </c>
       <c r="AJ212" s="6">
-        <v>4.62632257062809E-2</v>
+        <v>4.4990695735032601E-2</v>
       </c>
       <c r="AK212" s="6">
-        <v>0.112857119628422</v>
+        <v>0.111417122532268</v>
       </c>
       <c r="AL212" s="6"/>
       <c r="AM212" s="6"/>
@@ -25272,22 +25264,22 @@
         <v>1.7202449082450499</v>
       </c>
       <c r="AF213" s="6">
-        <v>0.106813900570182</v>
+        <v>0.108047293290724</v>
       </c>
       <c r="AG213" s="6">
-        <v>0.19459631993203699</v>
+        <v>0.187666650062316</v>
       </c>
       <c r="AH213" s="6">
-        <v>9.7285899415356203E-2</v>
+        <v>9.9623634425681007E-2</v>
       </c>
       <c r="AI213" s="6">
-        <v>9.6793538076291902E-2</v>
+        <v>9.5214099504560404E-2</v>
       </c>
       <c r="AJ213" s="6">
-        <v>4.60641905359103E-2</v>
+        <v>4.48781457852672E-2</v>
       </c>
       <c r="AK213" s="6">
-        <v>0.114766935354973</v>
+        <v>0.11357834006206199</v>
       </c>
       <c r="AL213" s="6"/>
       <c r="AM213" s="6"/>
@@ -25388,22 +25380,22 @@
         <v>1.2618727644106542</v>
       </c>
       <c r="AF214" s="6">
-        <v>0.107337900456438</v>
+        <v>0.108341692238189</v>
       </c>
       <c r="AG214" s="6">
-        <v>0.19770208050785601</v>
+        <v>0.189721082490586</v>
       </c>
       <c r="AH214" s="6">
-        <v>0.100169891821595</v>
+        <v>0.10263262311405399</v>
       </c>
       <c r="AI214" s="6">
-        <v>9.3713377061061795E-2</v>
+        <v>9.2597946091709599E-2</v>
       </c>
       <c r="AJ214" s="6">
-        <v>4.5963802758234099E-2</v>
+        <v>4.4861096848526801E-2</v>
       </c>
       <c r="AK214" s="6">
-        <v>0.11574964716132199</v>
+        <v>0.114416351603238</v>
       </c>
       <c r="AL214" s="6"/>
       <c r="AM214" s="6"/>
@@ -25504,22 +25496,22 @@
         <v>1.7423798552176351</v>
       </c>
       <c r="AF215" s="6">
-        <v>0.108167288057875</v>
+        <v>0.108956577553387</v>
       </c>
       <c r="AG215" s="6">
-        <v>0.202159662781913</v>
+        <v>0.19292877242307699</v>
       </c>
       <c r="AH215" s="6">
-        <v>9.41444366331987E-2</v>
+        <v>9.6222954334810096E-2</v>
       </c>
       <c r="AI215" s="6">
-        <v>9.0779282504550696E-2</v>
+        <v>9.0049915981148407E-2</v>
       </c>
       <c r="AJ215" s="6">
-        <v>4.5721723430819303E-2</v>
+        <v>4.4694826108704198E-2</v>
       </c>
       <c r="AK215" s="6">
-        <v>0.114424351200418</v>
+        <v>0.11279750317887299</v>
       </c>
       <c r="AL215" s="6"/>
       <c r="AM215" s="6"/>
@@ -25620,22 +25612,22 @@
         <v>1.4999625873922895</v>
       </c>
       <c r="AF216" s="6">
-        <v>0.108621751171498</v>
+        <v>0.10917922590324999</v>
       </c>
       <c r="AG216" s="6">
-        <v>0.20512631645813301</v>
+        <v>0.19470359241858201</v>
       </c>
       <c r="AH216" s="6">
-        <v>0.102858396623718</v>
+        <v>0.105599330218747</v>
       </c>
       <c r="AI216" s="6">
-        <v>9.2806573632466194E-2</v>
+        <v>9.2593732422368902E-2</v>
       </c>
       <c r="AJ216" s="6">
-        <v>4.5652709628189903E-2</v>
+        <v>4.4699078985276898E-2</v>
       </c>
       <c r="AK216" s="6">
-        <v>0.118159694352357</v>
+        <v>0.116500987648941</v>
       </c>
       <c r="AL216" s="6"/>
       <c r="AM216" s="6"/>
@@ -25736,22 +25728,22 @@
         <v>1.082822661978966</v>
       </c>
       <c r="AF217" s="6">
-        <v>0.108744244642747</v>
+        <v>0.109069149966715</v>
       </c>
       <c r="AG217" s="6">
-        <v>0.203986303650003</v>
+        <v>0.19236147655306801</v>
       </c>
       <c r="AH217" s="6">
-        <v>0.100310479532356</v>
+        <v>0.10252184769622601</v>
       </c>
       <c r="AI217" s="6">
-        <v>9.2012219635539502E-2</v>
+        <v>9.2134179038372302E-2</v>
       </c>
       <c r="AJ217" s="6">
-        <v>4.5725411061304497E-2</v>
+        <v>4.4842607480636003E-2</v>
       </c>
       <c r="AK217" s="6">
-        <v>0.117015653757685</v>
+        <v>0.11498835538329601</v>
       </c>
       <c r="AL217" s="6"/>
       <c r="AM217" s="6"/>
@@ -25852,22 +25844,22 @@
         <v>0.66766647422866754</v>
       </c>
       <c r="AF218" s="6">
-        <v>0.108700768854105</v>
+        <v>0.10889995851885099</v>
       </c>
       <c r="AG218" s="6">
-        <v>0.188472656369573</v>
+        <v>0.17920918093028901</v>
       </c>
       <c r="AH218" s="6">
-        <v>9.6553146256221703E-2</v>
+        <v>9.8632171849306005E-2</v>
       </c>
       <c r="AI218" s="6">
-        <v>9.1595179995945394E-2</v>
+        <v>9.1964372059759297E-2</v>
       </c>
       <c r="AJ218" s="6">
-        <v>4.57952076479098E-2</v>
+        <v>4.4974021151971598E-2</v>
       </c>
       <c r="AK218" s="6">
-        <v>0.112335504903969</v>
+        <v>0.110821357591396</v>
       </c>
       <c r="AL218" s="6"/>
       <c r="AM218" s="6"/>
@@ -25968,22 +25960,22 @@
         <v>1.7786890783948905</v>
       </c>
       <c r="AF219" s="6">
-        <v>0.108638234219209</v>
+        <v>0.108633507760775</v>
       </c>
       <c r="AG219" s="6">
-        <v>0.18465371041630099</v>
+        <v>0.17429195396517799</v>
       </c>
       <c r="AH219" s="6">
-        <v>9.4699914662808901E-2</v>
+        <v>9.6894320842565204E-2</v>
       </c>
       <c r="AI219" s="6">
-        <v>9.1637740215801206E-2</v>
+        <v>9.2267354444889399E-2</v>
       </c>
       <c r="AJ219" s="6">
-        <v>4.5935098151412598E-2</v>
+        <v>4.5169218384245299E-2</v>
       </c>
       <c r="AK219" s="6">
-        <v>0.11094443166953</v>
+        <v>0.109244149226738</v>
       </c>
       <c r="AL219" s="6"/>
       <c r="AM219" s="6"/>
@@ -26084,22 +26076,22 @@
         <v>1.2848963631856947</v>
       </c>
       <c r="AF220" s="6">
-        <v>0.10853152325014399</v>
+        <v>0.108343260748838</v>
       </c>
       <c r="AG220" s="6">
-        <v>0.183503465818387</v>
+        <v>0.17293096120725601</v>
       </c>
       <c r="AH220" s="6">
-        <v>9.7057920469292694E-2</v>
+        <v>9.9665642810932598E-2</v>
       </c>
       <c r="AI220" s="6">
-        <v>9.6251109514944894E-2</v>
+        <v>9.7257444218840097E-2</v>
       </c>
       <c r="AJ220" s="6">
-        <v>4.6819739951833E-2</v>
+        <v>4.6325019188809803E-2</v>
       </c>
       <c r="AK220" s="6">
-        <v>0.112449278913132</v>
+        <v>0.11090576266727099</v>
       </c>
       <c r="AL220" s="6"/>
       <c r="AM220" s="6"/>
@@ -26200,22 +26192,22 @@
         <v>0.99590919540268885</v>
       </c>
       <c r="AF221" s="6">
-        <v>0.10847604525980301</v>
+        <v>0.108125464975448</v>
       </c>
       <c r="AG221" s="6">
-        <v>0.18083538522030901</v>
+        <v>0.16990063751944601</v>
       </c>
       <c r="AH221" s="6">
-        <v>9.5250954444801694E-2</v>
+        <v>9.7859559073978503E-2</v>
       </c>
       <c r="AI221" s="6">
-        <v>9.5918172545541594E-2</v>
+        <v>9.7003093426994605E-2</v>
       </c>
       <c r="AJ221" s="6">
-        <v>4.6886723111152898E-2</v>
+        <v>4.6387547869697801E-2</v>
       </c>
       <c r="AK221" s="6">
-        <v>0.11126379333478099</v>
+        <v>0.10960932535802199</v>
       </c>
       <c r="AL221" s="6"/>
       <c r="AM221" s="6"/>
@@ -26316,22 +26308,22 @@
         <v>1.6720951998170364</v>
       </c>
       <c r="AF222" s="6">
-        <v>0.108557470686082</v>
+        <v>0.108062383651161</v>
       </c>
       <c r="AG222" s="6">
-        <v>0.17983089530669</v>
+        <v>0.16908268192541501</v>
       </c>
       <c r="AH222" s="6">
-        <v>9.3292507622618495E-2</v>
+        <v>9.57580013557148E-2</v>
       </c>
       <c r="AI222" s="6">
-        <v>9.4919082401003496E-2</v>
+        <v>9.6234480054382995E-2</v>
       </c>
       <c r="AJ222" s="6">
-        <v>4.6883214368024298E-2</v>
+        <v>4.6375439556960399E-2</v>
       </c>
       <c r="AK222" s="6">
-        <v>0.11029101059122</v>
+        <v>0.108653186493257</v>
       </c>
       <c r="AL222" s="6"/>
       <c r="AM222" s="6"/>
@@ -26432,22 +26424,22 @@
         <v>2.1878870669183925</v>
       </c>
       <c r="AF223" s="6">
-        <v>0.108606202612489</v>
+        <v>0.107977860074497</v>
       </c>
       <c r="AG223" s="6">
-        <v>0.18024836962643101</v>
+        <v>0.16935174840936401</v>
       </c>
       <c r="AH223" s="6">
-        <v>9.7464101981978093E-2</v>
+        <v>0.100459160557762</v>
       </c>
       <c r="AI223" s="6">
-        <v>9.8847497113117494E-2</v>
+        <v>0.100459376401245</v>
       </c>
       <c r="AJ223" s="6">
-        <v>4.6960840975373598E-2</v>
+        <v>4.6449598833845002E-2</v>
       </c>
       <c r="AK223" s="6">
-        <v>0.112439181465449</v>
+        <v>0.110941315994601</v>
       </c>
       <c r="AL223" s="6"/>
       <c r="AM223" s="6"/>
@@ -26548,22 +26540,22 @@
         <v>1.7317363171024169</v>
       </c>
       <c r="AF224" s="6">
-        <v>0.108729783677273</v>
+        <v>0.10797938020659199</v>
       </c>
       <c r="AG224" s="6">
-        <v>0.18131600364745301</v>
+        <v>0.17021256373784999</v>
       </c>
       <c r="AH224" s="6">
-        <v>0.102294740316254</v>
+        <v>0.105759152756719</v>
       </c>
       <c r="AI224" s="6">
-        <v>0.10227661710803</v>
+        <v>0.104057867343592</v>
       </c>
       <c r="AJ224" s="6">
-        <v>4.6946104513897302E-2</v>
+        <v>4.6425229853317103E-2</v>
       </c>
       <c r="AK224" s="6">
-        <v>0.114778911621328</v>
+        <v>0.113409654978057</v>
       </c>
       <c r="AL224" s="6"/>
       <c r="AM224" s="6"/>
@@ -26664,22 +26656,22 @@
         <v>1.3757026939757111</v>
       </c>
       <c r="AF225" s="6">
-        <v>0.108762151684714</v>
+        <v>0.10789747911565201</v>
       </c>
       <c r="AG225" s="6">
-        <v>0.178109726576893</v>
+        <v>0.166154158931972</v>
       </c>
       <c r="AH225" s="6">
-        <v>9.8798531957090804E-2</v>
+        <v>0.101972071794867</v>
       </c>
       <c r="AI225" s="6">
-        <v>0.10112492163046501</v>
+        <v>0.10269498994524399</v>
       </c>
       <c r="AJ225" s="6">
-        <v>4.6950866474331103E-2</v>
+        <v>4.6422200004011697E-2</v>
       </c>
       <c r="AK225" s="6">
-        <v>0.112861899273132</v>
+        <v>0.111105802288279</v>
       </c>
       <c r="AL225" s="6"/>
       <c r="AM225" s="6"/>
@@ -26780,22 +26772,22 @@
         <v>1.8524055397911354</v>
       </c>
       <c r="AF226" s="6">
-        <v>0.108769169225053</v>
+        <v>0.10779964155503299</v>
       </c>
       <c r="AG226" s="6">
-        <v>0.17471547567318499</v>
+        <v>0.16354518103124299</v>
       </c>
       <c r="AH226" s="6">
-        <v>9.6494703663268996E-2</v>
+        <v>9.95777156101227E-2</v>
       </c>
       <c r="AI226" s="6">
-        <v>9.9832870099977003E-2</v>
+        <v>0.10126244366056</v>
       </c>
       <c r="AJ226" s="6">
-        <v>4.6966547705174999E-2</v>
+        <v>4.6431087463674699E-2</v>
       </c>
       <c r="AK226" s="6">
-        <v>0.11117787086297801</v>
+        <v>0.10952909746674901</v>
       </c>
       <c r="AL226" s="6"/>
       <c r="AM226" s="6"/>
@@ -26896,22 +26888,22 @@
         <v>1.3352790660718483</v>
       </c>
       <c r="AF227" s="6">
-        <v>0.108779060071042</v>
+        <v>0.107714737896415</v>
       </c>
       <c r="AG227" s="6">
-        <v>0.17522899005213499</v>
+        <v>0.164102962141571</v>
       </c>
       <c r="AH227" s="6">
-        <v>0.100577462577652</v>
+        <v>0.104098170055635</v>
       </c>
       <c r="AI227" s="6">
-        <v>0.10040311203786501</v>
+        <v>0.102344482450863</v>
       </c>
       <c r="AJ227" s="6">
-        <v>4.6979189480862403E-2</v>
+        <v>4.6437173710156897E-2</v>
       </c>
       <c r="AK227" s="6">
-        <v>0.112509243027111</v>
+        <v>0.111121148967002</v>
       </c>
       <c r="AL227" s="6"/>
       <c r="AM227" s="6"/>
@@ -27012,22 +27004,22 @@
         <v>1.2070075560622229</v>
       </c>
       <c r="AF228" s="6">
-        <v>0.10855373451339401</v>
+        <v>0.107248576612741</v>
       </c>
       <c r="AG228" s="6">
-        <v>0.16523461619719201</v>
+        <v>0.15403579959031199</v>
       </c>
       <c r="AH228" s="6">
-        <v>9.7974589281577998E-2</v>
+        <v>0.10145600561957401</v>
       </c>
       <c r="AI228" s="6">
-        <v>9.9555401574445396E-2</v>
+        <v>0.101324599177777</v>
       </c>
       <c r="AJ228" s="6">
-        <v>4.7003750182784798E-2</v>
+        <v>4.64559362213703E-2</v>
       </c>
       <c r="AK228" s="6">
-        <v>0.10929149220659801</v>
+        <v>0.107733302120308</v>
       </c>
       <c r="AL228" s="6"/>
       <c r="AM228" s="6"/>
@@ -27128,22 +27120,22 @@
         <v>1.7752058794531678</v>
       </c>
       <c r="AF229" s="6">
-        <v>0.108430314052449</v>
+        <v>0.107069444663713</v>
       </c>
       <c r="AG229" s="6">
-        <v>0.165151583845255</v>
+        <v>0.15436976640716901</v>
       </c>
       <c r="AH229" s="6">
-        <v>9.8295161061214706E-2</v>
+        <v>0.102331178529495</v>
       </c>
       <c r="AI229" s="6">
-        <v>9.8947691921965897E-2</v>
+        <v>0.100408809829654</v>
       </c>
       <c r="AJ229" s="6">
-        <v>4.7086142972853802E-2</v>
+        <v>4.6534728300330397E-2</v>
       </c>
       <c r="AK229" s="6">
-        <v>0.109206909456126</v>
+        <v>0.107856106449922</v>
       </c>
       <c r="AL229" s="6"/>
       <c r="AM229" s="6"/>
@@ -27244,22 +27236,22 @@
         <v>2.5374757999355069</v>
       </c>
       <c r="AF230" s="6">
-        <v>0.108063610055684</v>
+        <v>0.10665884452213301</v>
       </c>
       <c r="AG230" s="6">
-        <v>0.163266101986101</v>
+        <v>0.15302600132410099</v>
       </c>
       <c r="AH230" s="6">
-        <v>9.9301377030844601E-2</v>
+        <v>0.103391943129752</v>
       </c>
       <c r="AI230" s="6">
-        <v>9.9380356117227203E-2</v>
+        <v>0.100849071445933</v>
       </c>
       <c r="AJ230" s="6">
-        <v>4.7291679032298001E-2</v>
+        <v>4.6739877785473498E-2</v>
       </c>
       <c r="AK230" s="6">
-        <v>0.10911275846492099</v>
+        <v>0.107905116900799</v>
       </c>
       <c r="AL230" s="6"/>
       <c r="AM230" s="6"/>
@@ -27360,22 +27352,22 @@
         <v>2.1416492550333288</v>
       </c>
       <c r="AF231" s="6">
-        <v>0.107600610769413</v>
+        <v>0.106167934969763</v>
       </c>
       <c r="AG231" s="6">
-        <v>0.160647699632332</v>
+        <v>0.15101670971575201</v>
       </c>
       <c r="AH231" s="6">
-        <v>9.9343014255118101E-2</v>
+        <v>0.103466162031566</v>
       </c>
       <c r="AI231" s="6">
-        <v>9.8473654188815193E-2</v>
+        <v>9.9820731776693594E-2</v>
       </c>
       <c r="AJ231" s="6">
-        <v>4.7492705034352899E-2</v>
+        <v>4.6934645906065602E-2</v>
       </c>
       <c r="AK231" s="6">
-        <v>0.108289872761059</v>
+        <v>0.107195392734781</v>
       </c>
       <c r="AL231" s="6"/>
       <c r="AM231" s="6"/>
@@ -27476,22 +27468,22 @@
         <v>1.2729760319036387</v>
       </c>
       <c r="AF232" s="6">
-        <v>0.10717368753456</v>
+        <v>0.105728328976726</v>
       </c>
       <c r="AG232" s="6">
-        <v>0.16039146137920099</v>
+        <v>0.15118237437947399</v>
       </c>
       <c r="AH232" s="6">
-        <v>0.101546312250669</v>
+        <v>0.10577162579867599</v>
       </c>
       <c r="AI232" s="6">
-        <v>9.9347944433776106E-2</v>
+        <v>0.10075937449714099</v>
       </c>
       <c r="AJ232" s="6">
-        <v>4.7739858056654497E-2</v>
+        <v>4.7173302293727203E-2</v>
       </c>
       <c r="AK232" s="6">
-        <v>0.109020800856253</v>
+        <v>0.108052789515133</v>
       </c>
       <c r="AL232" s="6"/>
       <c r="AM232" s="6"/>
@@ -27592,22 +27584,22 @@
         <v>1.8635476233541226</v>
       </c>
       <c r="AF233" s="6">
-        <v>0.107943640187524</v>
+        <v>0.10648310414249</v>
       </c>
       <c r="AG233" s="6">
-        <v>0.16380806703064099</v>
+        <v>0.15470263808835</v>
       </c>
       <c r="AH233" s="6">
-        <v>0.103630358885103</v>
+        <v>0.107904543407359</v>
       </c>
       <c r="AI233" s="6">
-        <v>0.100321034141319</v>
+        <v>0.101779634012498</v>
       </c>
       <c r="AJ233" s="6">
-        <v>4.7994570683851899E-2</v>
+        <v>4.7414296384839898E-2</v>
       </c>
       <c r="AK233" s="6">
-        <v>0.110760594729036</v>
+        <v>0.10983725833516</v>
       </c>
       <c r="AL233" s="6"/>
       <c r="AM233" s="6"/>
@@ -27708,22 +27700,22 @@
         <v>1.6011751205105895</v>
       </c>
       <c r="AF234" s="6">
-        <v>0.10759069728800499</v>
+        <v>0.106109968641381</v>
       </c>
       <c r="AG234" s="6">
-        <v>0.16187292370526701</v>
+        <v>0.153178779005154</v>
       </c>
       <c r="AH234" s="6">
-        <v>0.104123244405208</v>
+        <v>0.10825946440584</v>
       </c>
       <c r="AI234" s="6">
-        <v>0.100482778526451</v>
+        <v>0.101902929033306</v>
       </c>
       <c r="AJ234" s="6">
-        <v>4.8148162259308097E-2</v>
+        <v>4.75452297817626E-2</v>
       </c>
       <c r="AK234" s="6">
-        <v>0.11045571606259801</v>
+        <v>0.109568319810458</v>
       </c>
       <c r="AL234" s="6"/>
       <c r="AM234" s="6"/>
@@ -27824,22 +27816,22 @@
         <v>1.6863567581214767</v>
       </c>
       <c r="AF235" s="6">
-        <v>0.107225889731875</v>
+        <v>0.105737099020764</v>
       </c>
       <c r="AG235" s="6">
-        <v>0.15992637618122299</v>
+        <v>0.151665375218142</v>
       </c>
       <c r="AH235" s="6">
-        <v>0.10521613730929601</v>
+        <v>0.10927542072878001</v>
       </c>
       <c r="AI235" s="6">
-        <v>0.101040297836267</v>
+        <v>0.102440704845561</v>
       </c>
       <c r="AJ235" s="6">
-        <v>4.8315701814233197E-2</v>
+        <v>4.7688837193891803E-2</v>
       </c>
       <c r="AK235" s="6">
-        <v>0.110399665189098</v>
+        <v>0.109573600595725</v>
       </c>
       <c r="AL235" s="6"/>
       <c r="AM235" s="6"/>
@@ -27940,22 +27932,22 @@
         <v>1.4827607624205541</v>
       </c>
       <c r="AF236" s="6">
-        <v>0.106767843243743</v>
+        <v>0.105283000109081</v>
       </c>
       <c r="AG236" s="6">
-        <v>0.15718671404908799</v>
+        <v>0.14941774495441301</v>
       </c>
       <c r="AH236" s="6">
-        <v>0.105649416343298</v>
+        <v>0.10964149660657101</v>
       </c>
       <c r="AI236" s="6">
-        <v>0.102252469022085</v>
+        <v>0.10361749863172399</v>
       </c>
       <c r="AJ236" s="6">
-        <v>4.8538850413922703E-2</v>
+        <v>4.7887884708321803E-2</v>
       </c>
       <c r="AK236" s="6">
-        <v>0.11010287491012299</v>
+        <v>0.109356766471275</v>
       </c>
       <c r="AL236" s="6"/>
       <c r="AM236" s="6"/>
@@ -28056,22 +28048,22 @@
         <v>1.4030377167227215</v>
       </c>
       <c r="AF237" s="6">
-        <v>0.106094914138796</v>
+        <v>0.10462840597209</v>
       </c>
       <c r="AG237" s="6">
-        <v>0.15342486490902599</v>
+        <v>0.14626597126559299</v>
       </c>
       <c r="AH237" s="6">
-        <v>0.10911562348364801</v>
+        <v>0.113292764556627</v>
       </c>
       <c r="AI237" s="6">
-        <v>0.10435234668014</v>
+        <v>0.105709031130426</v>
       </c>
       <c r="AJ237" s="6">
-        <v>4.8890556021020097E-2</v>
+        <v>4.8216206705009999E-2</v>
       </c>
       <c r="AK237" s="6">
-        <v>0.110584597752566</v>
+        <v>0.11000574704386901</v>
       </c>
       <c r="AL237" s="6"/>
       <c r="AM237" s="6"/>
@@ -28172,22 +28164,22 @@
         <v>1.7985251251584344</v>
       </c>
       <c r="AF238" s="6">
-        <v>0.105411439031145</v>
+        <v>0.103979860211362</v>
       </c>
       <c r="AG238" s="6">
-        <v>0.149687872047752</v>
+        <v>0.14317336580012099</v>
       </c>
       <c r="AH238" s="6">
-        <v>0.11305967326177099</v>
+        <v>0.117392486200026</v>
       </c>
       <c r="AI238" s="6">
-        <v>0.106688369477745</v>
+        <v>0.10798606894667</v>
       </c>
       <c r="AJ238" s="6">
-        <v>4.9261569970108103E-2</v>
+        <v>4.8557283233177199E-2</v>
       </c>
       <c r="AK238" s="6">
-        <v>0.111238497338238</v>
+        <v>0.11081688968735399</v>
       </c>
       <c r="AL238" s="6"/>
       <c r="AM238" s="6"/>
@@ -28288,22 +28280,22 @@
         <v>-0.75265924520984129</v>
       </c>
       <c r="AF239" s="6">
-        <v>0.105471754504169</v>
+        <v>0.104084553134399</v>
       </c>
       <c r="AG239" s="6">
-        <v>0.1504043822235</v>
+        <v>0.144299439750252</v>
       </c>
       <c r="AH239" s="6">
-        <v>0.115661628187543</v>
+        <v>0.11981058183992099</v>
       </c>
       <c r="AI239" s="6">
-        <v>0.106026989102066</v>
+        <v>0.107123591037787</v>
       </c>
       <c r="AJ239" s="6">
-        <v>4.91941740936764E-2</v>
+        <v>4.8438880277604297E-2</v>
       </c>
       <c r="AK239" s="6">
-        <v>0.11197421841702</v>
+        <v>0.111544798937389</v>
       </c>
       <c r="AL239" s="6"/>
       <c r="AM239" s="6"/>
@@ -28404,22 +28396,22 @@
         <v>2.9641544564512401</v>
       </c>
       <c r="AF240" s="6">
-        <v>4.3323228461134899E-2</v>
+        <v>4.2319117345536797E-2</v>
       </c>
       <c r="AG240" s="6">
-        <v>8.2634937857699597E-2</v>
+        <v>8.0056332306531294E-2</v>
       </c>
       <c r="AH240" s="6">
-        <v>8.8024371025721304E-2</v>
+        <v>9.0212225622513201E-2</v>
       </c>
       <c r="AI240" s="6">
-        <v>9.2692123728196504E-2</v>
+        <v>9.2775794293208397E-2</v>
       </c>
       <c r="AJ240" s="6">
-        <v>4.7299488500184797E-2</v>
+        <v>4.6451089186720702E-2</v>
       </c>
       <c r="AK240" s="6">
-        <v>7.6675823302368398E-2</v>
+        <v>7.6414320166981298E-2</v>
       </c>
       <c r="AL240" s="6"/>
       <c r="AM240" s="6"/>
@@ -28520,22 +28512,22 @@
         <v>1.793242944103568</v>
       </c>
       <c r="AF241" s="6">
-        <v>4.6115845995379198E-2</v>
+        <v>4.6201630578651801E-2</v>
       </c>
       <c r="AG241" s="6">
-        <v>8.7291830763055703E-2</v>
+        <v>8.6139893765714196E-2</v>
       </c>
       <c r="AH241" s="6">
-        <v>9.4128362518056299E-2</v>
+        <v>9.6879174378316599E-2</v>
       </c>
       <c r="AI241" s="6">
-        <v>0.106036747619479</v>
+        <v>0.106795735325226</v>
       </c>
       <c r="AJ241" s="6">
-        <v>6.1690446544020297E-2</v>
+        <v>6.1248083126938399E-2</v>
       </c>
       <c r="AK241" s="6">
-        <v>8.4976050788264701E-2</v>
+        <v>8.5568714424029899E-2</v>
       </c>
       <c r="AL241" s="6"/>
       <c r="AM241" s="6"/>
@@ -28636,22 +28628,22 @@
         <v>3.4011855199125307</v>
       </c>
       <c r="AF242" s="6">
-        <v>4.8845956223843301E-2</v>
+        <v>4.9994593359108601E-2</v>
       </c>
       <c r="AG242" s="6">
-        <v>9.1503356206325603E-2</v>
+        <v>9.1652194609376694E-2</v>
       </c>
       <c r="AH242" s="6">
-        <v>9.8455880180805297E-2</v>
+        <v>0.10185918352257101</v>
       </c>
       <c r="AI242" s="6">
-        <v>0.103542712867151</v>
+        <v>0.104073668112033</v>
       </c>
       <c r="AJ242" s="6">
-        <v>6.0277835773850597E-2</v>
+        <v>5.9349110844386599E-2</v>
       </c>
       <c r="AK242" s="6">
-        <v>8.6641496424046699E-2</v>
+        <v>8.77159733458069E-2</v>
       </c>
       <c r="AL242" s="6"/>
       <c r="AM242" s="6"/>
@@ -28752,22 +28744,22 @@
         <v>5.6462756680954129</v>
       </c>
       <c r="AF243" s="6">
-        <v>5.1470391530728202E-2</v>
+        <v>5.3629237146077098E-2</v>
       </c>
       <c r="AG243" s="6">
-        <v>9.4799149518532702E-2</v>
+        <v>9.6145191487408493E-2</v>
       </c>
       <c r="AH243" s="6">
-        <v>0.101009015654123</v>
+        <v>0.10458524692577199</v>
       </c>
       <c r="AI243" s="6">
-        <v>0.108133165516063</v>
+        <v>0.108781079922508</v>
       </c>
       <c r="AJ243" s="6">
-        <v>6.5596392482302895E-2</v>
+        <v>6.4438963935547502E-2</v>
       </c>
       <c r="AK243" s="6">
-        <v>9.0276685462775605E-2</v>
+        <v>9.1811039941398803E-2</v>
       </c>
       <c r="AL243" s="6"/>
       <c r="AM243" s="6"/>
@@ -28868,22 +28860,22 @@
         <v>4.7188637431982983</v>
       </c>
       <c r="AF244" s="6">
-        <v>5.3936880499844297E-2</v>
+        <v>5.70281136674953E-2</v>
       </c>
       <c r="AG244" s="6">
-        <v>9.6866700407973405E-2</v>
+        <v>9.9198608168489702E-2</v>
       </c>
       <c r="AH244" s="6">
-        <v>0.100399681988697</v>
+        <v>0.10391365544624601</v>
       </c>
       <c r="AI244" s="6">
-        <v>0.103809283971892</v>
+        <v>0.104164196348643</v>
       </c>
       <c r="AJ244" s="6">
-        <v>5.8663459351756E-2</v>
+        <v>5.69277821412656E-2</v>
       </c>
       <c r="AK244" s="6">
-        <v>8.8910855758704901E-2</v>
+        <v>9.0624842184074697E-2</v>
       </c>
       <c r="AL244" s="6"/>
       <c r="AM244" s="6"/>
@@ -28984,22 +28976,22 @@
         <v>5.1696142914430254</v>
       </c>
       <c r="AF245" s="6">
-        <v>5.6310500500468402E-2</v>
+        <v>6.0252004264205301E-2</v>
       </c>
       <c r="AG245" s="6">
-        <v>9.8526103093137293E-2</v>
+        <v>0.10169294608816901</v>
       </c>
       <c r="AH245" s="6">
-        <v>9.89697903360445E-2</v>
+        <v>0.10249516180113501</v>
       </c>
       <c r="AI245" s="6">
-        <v>9.8650609692160898E-2</v>
+        <v>9.8804490170353698E-2</v>
       </c>
       <c r="AJ245" s="6">
-        <v>5.7548498136789798E-2</v>
+        <v>5.5588209896865803E-2</v>
       </c>
       <c r="AK245" s="6">
-        <v>8.7844434083819006E-2</v>
+        <v>8.9852293249979606E-2</v>
       </c>
       <c r="AL245" s="6"/>
       <c r="AM245" s="6"/>
@@ -29100,22 +29092,22 @@
         <v>5.9511291308389502</v>
       </c>
       <c r="AF246" s="6">
-        <v>5.84835225516789E-2</v>
+        <v>6.3166571211386802E-2</v>
       </c>
       <c r="AG246" s="6">
-        <v>9.88577015467524E-2</v>
+        <v>0.102648483632425</v>
       </c>
       <c r="AH246" s="6">
-        <v>9.4998459995158602E-2</v>
+        <v>9.7952284425972494E-2</v>
       </c>
       <c r="AI246" s="6">
-        <v>8.9787126726770403E-2</v>
+        <v>8.9967259438338207E-2</v>
       </c>
       <c r="AJ246" s="6">
-        <v>5.6983349162772402E-2</v>
+        <v>5.4854588199509599E-2</v>
       </c>
       <c r="AK246" s="6">
-        <v>8.5103703672684106E-2</v>
+        <v>8.7190375314166402E-2</v>
       </c>
       <c r="AL246" s="6"/>
       <c r="AM246" s="6"/>
@@ -29216,22 +29208,22 @@
         <v>4.7476483472724595</v>
       </c>
       <c r="AF247" s="6">
-        <v>6.0677462595118997E-2</v>
+        <v>6.6034551163505706E-2</v>
       </c>
       <c r="AG247" s="6">
-        <v>0.10001061471595001</v>
+        <v>0.104453449747164</v>
       </c>
       <c r="AH247" s="6">
-        <v>9.4096089335198196E-2</v>
+        <v>9.6944356072680704E-2</v>
       </c>
       <c r="AI247" s="6">
-        <v>8.4958312103919506E-2</v>
+        <v>8.5437054483197203E-2</v>
       </c>
       <c r="AJ247" s="6">
-        <v>5.5913105925562298E-2</v>
+        <v>5.3659880402899103E-2</v>
       </c>
       <c r="AK247" s="6">
-        <v>8.4193803475832593E-2</v>
+        <v>8.6555026692020406E-2</v>
       </c>
       <c r="AL247" s="6"/>
       <c r="AM247" s="6"/>
@@ -29332,22 +29324,22 @@
         <v>5.0137613215522236</v>
       </c>
       <c r="AF248" s="6">
-        <v>6.2848459090122197E-2</v>
+        <v>6.8803501379162996E-2</v>
       </c>
       <c r="AG248" s="6">
-        <v>0.102467229785453</v>
+        <v>0.107910171016211</v>
       </c>
       <c r="AH248" s="6">
-        <v>9.7355464618240906E-2</v>
+        <v>0.100673572977774</v>
       </c>
       <c r="AI248" s="6">
-        <v>8.7093941536360603E-2</v>
+        <v>8.80469889443454E-2</v>
       </c>
       <c r="AJ248" s="6">
-        <v>5.56876017121044E-2</v>
+        <v>5.33493810509637E-2</v>
       </c>
       <c r="AK248" s="6">
-        <v>8.6395924456535697E-2</v>
+        <v>8.9299684349132297E-2</v>
       </c>
       <c r="AL248" s="6"/>
       <c r="AM248" s="6"/>
@@ -29448,22 +29440,22 @@
         <v>4.6052563158959003</v>
       </c>
       <c r="AF249" s="6">
-        <v>6.4924235871472696E-2</v>
+        <v>7.1385643377497102E-2</v>
       </c>
       <c r="AG249" s="6">
-        <v>0.103751606122927</v>
+        <v>0.109645114723632</v>
       </c>
       <c r="AH249" s="6">
-        <v>9.5596760332738895E-2</v>
+        <v>9.8812743653476504E-2</v>
       </c>
       <c r="AI249" s="6">
-        <v>8.8603294022788603E-2</v>
+        <v>8.9907843561730094E-2</v>
       </c>
       <c r="AJ249" s="6">
-        <v>5.5511311692476098E-2</v>
+        <v>5.3103481961341001E-2</v>
       </c>
       <c r="AK249" s="6">
-        <v>8.6869503510982299E-2</v>
+        <v>8.9993413598166205E-2</v>
       </c>
       <c r="AL249" s="6"/>
       <c r="AM249" s="6"/>
@@ -29564,22 +29556,22 @@
         <v>4.6105104403611818</v>
       </c>
       <c r="AF250" s="6">
-        <v>6.6908641172503405E-2</v>
+        <v>7.3789140118424704E-2</v>
       </c>
       <c r="AG250" s="6">
-        <v>0.104888318849513</v>
+        <v>0.111124554447733</v>
       </c>
       <c r="AH250" s="6">
-        <v>9.8137380513041494E-2</v>
+        <v>0.101508127055378</v>
       </c>
       <c r="AI250" s="6">
-        <v>9.0859347641228994E-2</v>
+        <v>9.2523963679479196E-2</v>
       </c>
       <c r="AJ250" s="6">
-        <v>5.5357583211121601E-2</v>
+        <v>5.2891032208874797E-2</v>
       </c>
       <c r="AK250" s="6">
-        <v>8.8574185150011905E-2</v>
+        <v>9.1948522774801797E-2</v>
       </c>
       <c r="AL250" s="6"/>
       <c r="AM250" s="6"/>
@@ -29680,22 +29672,22 @@
         <v>3.8911294306007704</v>
       </c>
       <c r="AF251" s="6">
-        <v>6.8797494728115305E-2</v>
+        <v>7.6013218506734301E-2</v>
       </c>
       <c r="AG251" s="6">
-        <v>0.105737982305945</v>
+        <v>0.112263847146052</v>
       </c>
       <c r="AH251" s="6">
-        <v>9.9028326996905502E-2</v>
+        <v>0.102442308515667</v>
       </c>
       <c r="AI251" s="6">
-        <v>9.3163885696015206E-2</v>
+        <v>9.5120005725384399E-2</v>
       </c>
       <c r="AJ251" s="6">
-        <v>5.5234411866709798E-2</v>
+        <v>5.27189379481523E-2</v>
       </c>
       <c r="AK251" s="6">
-        <v>8.9779711948985305E-2</v>
+        <v>9.3334634204940106E-2</v>
       </c>
       <c r="AL251" s="6"/>
       <c r="AM251" s="6"/>
@@ -29796,22 +29788,22 @@
         <v>2.34023919135673</v>
       </c>
       <c r="AF252" s="6">
-        <v>7.0750662878875895E-2</v>
+        <v>7.8260442479644698E-2</v>
       </c>
       <c r="AG252" s="6">
-        <v>0.111187855078763</v>
+        <v>0.11868646508754301</v>
       </c>
       <c r="AH252" s="6">
-        <v>0.102651148772212</v>
+        <v>0.10646214691419301</v>
       </c>
       <c r="AI252" s="6">
-        <v>9.5204649867097396E-2</v>
+        <v>9.7340997721245701E-2</v>
       </c>
       <c r="AJ252" s="6">
-        <v>5.5110466172897603E-2</v>
+        <v>5.2554732119832998E-2</v>
       </c>
       <c r="AK252" s="6">
-        <v>9.2764386897902798E-2</v>
+        <v>9.6734442339068999E-2</v>
       </c>
       <c r="AL252" s="6"/>
       <c r="AM252" s="6"/>
@@ -29912,22 +29904,22 @@
         <v>2.1140630187133524</v>
       </c>
       <c r="AF253" s="6">
-        <v>7.6739991370623206E-2</v>
+        <v>8.5579916687215998E-2</v>
       </c>
       <c r="AG253" s="6">
-        <v>0.120871475240774</v>
+        <v>0.13000695766334799</v>
       </c>
       <c r="AH253" s="6">
-        <v>0.10716648549476999</v>
+        <v>0.111354971569558</v>
       </c>
       <c r="AI253" s="6">
-        <v>9.7872784666604498E-2</v>
+        <v>0.100158180958644</v>
       </c>
       <c r="AJ253" s="6">
-        <v>5.5128630723156803E-2</v>
+        <v>5.2536260669293899E-2</v>
       </c>
       <c r="AK253" s="6">
-        <v>9.7724775332169098E-2</v>
+        <v>0.102396453202021</v>
       </c>
       <c r="AL253" s="6"/>
       <c r="AM253" s="6"/>
@@ -30028,22 +30020,22 @@
         <v>3.9186505670670613</v>
       </c>
       <c r="AF254" s="6">
-        <v>7.8695422769037196E-2</v>
+        <v>8.7228708018963805E-2</v>
       </c>
       <c r="AG254" s="6">
-        <v>0.131329146915664</v>
+        <v>0.14080922784471001</v>
       </c>
       <c r="AH254" s="6">
-        <v>0.11279619058729901</v>
+        <v>0.117709979804721</v>
       </c>
       <c r="AI254" s="6">
-        <v>0.100726889276701</v>
+        <v>0.103092960751859</v>
       </c>
       <c r="AJ254" s="6">
-        <v>5.5196068265600202E-2</v>
+        <v>5.2568501086375397E-2</v>
       </c>
       <c r="AK254" s="6">
-        <v>0.10264851633769401</v>
+        <v>0.10756658632534601</v>
       </c>
       <c r="AL254" s="6"/>
       <c r="AM254" s="6"/>
@@ -30144,22 +30136,22 @@
         <v>2.8421418063750536</v>
       </c>
       <c r="AF255" s="6">
-        <v>7.9949503970223199E-2</v>
+        <v>8.8331998451185403E-2</v>
       </c>
       <c r="AG255" s="6">
-        <v>0.12981385328149</v>
+        <v>0.13836718856508001</v>
       </c>
       <c r="AH255" s="6">
-        <v>0.11009729625004</v>
+        <v>0.114115827435952</v>
       </c>
       <c r="AI255" s="6">
-        <v>9.3879135409318804E-2</v>
+        <v>9.5802942241376504E-2</v>
       </c>
       <c r="AJ255" s="6">
-        <v>5.2364172859205901E-2</v>
+        <v>4.97953552760627E-2</v>
       </c>
       <c r="AK255" s="6">
-        <v>9.9798832261187201E-2</v>
+        <v>0.104148426871745</v>
       </c>
       <c r="AL255" s="6"/>
       <c r="AM255" s="6"/>
@@ -30260,22 +30252,22 @@
         <v>2.3244359851286589</v>
       </c>
       <c r="AF256" s="6">
-        <v>8.10814021315623E-2</v>
+        <v>8.9274886407282206E-2</v>
       </c>
       <c r="AG256" s="6">
-        <v>0.12786642287236699</v>
+        <v>0.135586699129841</v>
       </c>
       <c r="AH256" s="6">
-        <v>0.11141639071262199</v>
+        <v>0.11520194753274</v>
       </c>
       <c r="AI256" s="6">
-        <v>9.6730768446071203E-2</v>
+        <v>9.8886830451168098E-2</v>
       </c>
       <c r="AJ256" s="6">
-        <v>5.2535417829899102E-2</v>
+        <v>5.0006401149437503E-2</v>
       </c>
       <c r="AK256" s="6">
-        <v>0.100502412426117</v>
+        <v>0.10461488199911401</v>
       </c>
       <c r="AL256" s="6"/>
       <c r="AM256" s="6"/>
@@ -30376,22 +30368,22 @@
         <v>2.6810800379859501</v>
       </c>
       <c r="AF257" s="6">
-        <v>8.2145364649880703E-2</v>
+        <v>9.0130232557249904E-2</v>
       </c>
       <c r="AG257" s="6">
-        <v>0.13342992731988301</v>
+        <v>0.14154170153183901</v>
       </c>
       <c r="AH257" s="6">
-        <v>0.1177941266261</v>
+        <v>0.121982674312668</v>
       </c>
       <c r="AI257" s="6">
-        <v>9.9552193201759495E-2</v>
+        <v>0.10182549311366899</v>
       </c>
       <c r="AJ257" s="6">
-        <v>5.2744747628181703E-2</v>
+        <v>5.0246348053325E-2</v>
       </c>
       <c r="AK257" s="6">
-        <v>0.104322150403446</v>
+        <v>0.10863976416644699</v>
       </c>
       <c r="AL257" s="6"/>
       <c r="AM257" s="6"/>
@@ -30492,22 +30484,22 @@
         <v>3.2225548435167894</v>
       </c>
       <c r="AF258" s="6">
-        <v>8.3140445862120896E-2</v>
+        <v>9.0902681401677302E-2</v>
       </c>
       <c r="AG258" s="6">
-        <v>0.13121002147574901</v>
+        <v>0.138416481324525</v>
       </c>
       <c r="AH258" s="6">
-        <v>0.111644835853937</v>
+        <v>0.115010418399044</v>
       </c>
       <c r="AI258" s="6">
-        <v>0.10119005823017101</v>
+        <v>0.10361244804579101</v>
       </c>
       <c r="AJ258" s="6">
-        <v>5.2908607207946802E-2</v>
+        <v>5.04326234395088E-2</v>
       </c>
       <c r="AK258" s="6">
-        <v>0.102713470560488</v>
+        <v>0.10658825570085501</v>
       </c>
       <c r="AL258" s="6"/>
       <c r="AM258" s="6"/>
@@ -30599,22 +30591,22 @@
         <v>2.5666877007683553</v>
       </c>
       <c r="AF259" s="6">
-        <v>8.4262341251246806E-2</v>
+        <v>9.1833685964660794E-2</v>
       </c>
       <c r="AG259" s="6">
-        <v>0.13070973271580999</v>
+        <v>0.137425109939389</v>
       </c>
       <c r="AH259" s="6">
-        <v>0.109108017618969</v>
+        <v>0.112027305026053</v>
       </c>
       <c r="AI259" s="6">
-        <v>0.100801987266273</v>
+        <v>0.10281187207645499</v>
       </c>
       <c r="AJ259" s="6">
-        <v>5.2858166340310299E-2</v>
+        <v>5.0402835019006602E-2</v>
       </c>
       <c r="AK259" s="6">
-        <v>0.101981543753686</v>
+        <v>0.105500698049526</v>
       </c>
       <c r="AL259" s="6"/>
       <c r="AM259" s="6"/>
@@ -30706,22 +30698,22 @@
         <v>2.8356142624129901</v>
       </c>
       <c r="AF260" s="6">
-        <v>8.5227189214983207E-2</v>
+        <v>9.2570295295396204E-2</v>
       </c>
       <c r="AG260" s="6">
-        <v>0.13145246185128301</v>
+        <v>0.13788557052766101</v>
       </c>
       <c r="AH260" s="6">
-        <v>0.113338834934684</v>
+        <v>0.116481471341742</v>
       </c>
       <c r="AI260" s="6">
-        <v>0.102552674141834</v>
+        <v>0.10453146404548599</v>
       </c>
       <c r="AJ260" s="6">
-        <v>5.29062052368659E-2</v>
+        <v>5.0470332992127602E-2</v>
       </c>
       <c r="AK260" s="6">
-        <v>0.10380875532878001</v>
+        <v>0.107284535550349</v>
       </c>
       <c r="AL260" s="6"/>
       <c r="AM260" s="6"/>
@@ -30813,22 +30805,22 @@
         <v>2.6222861571262999</v>
       </c>
       <c r="AF261" s="6">
-        <v>8.6003282910575102E-2</v>
+        <v>9.3082473982945904E-2</v>
       </c>
       <c r="AG261" s="6">
-        <v>0.129148480370432</v>
+        <v>0.13494377827123999</v>
       </c>
       <c r="AH261" s="6">
-        <v>0.10975815589537501</v>
+        <v>0.112658717493083</v>
       </c>
       <c r="AI261" s="6">
-        <v>0.10522892891027701</v>
+        <v>0.107263367032117</v>
       </c>
       <c r="AJ261" s="6">
-        <v>5.3086100191529803E-2</v>
+        <v>5.06628229133139E-2</v>
       </c>
       <c r="AK261" s="6">
-        <v>0.103022956567039</v>
+        <v>0.106247136538115</v>
       </c>
       <c r="AL261" s="6"/>
       <c r="AM261" s="6"/>
@@ -30920,22 +30912,22 @@
         <v>4.32677217130255</v>
       </c>
       <c r="AF262" s="6">
-        <v>8.6840901806339799E-2</v>
+        <v>9.3679605130116597E-2</v>
       </c>
       <c r="AG262" s="6">
-        <v>0.12821135459413299</v>
+        <v>0.13366034948907299</v>
       </c>
       <c r="AH262" s="6">
-        <v>0.112725841763213</v>
+        <v>0.115698727914283</v>
       </c>
       <c r="AI262" s="6">
-        <v>0.107137234505155</v>
+        <v>0.10903563735311</v>
       </c>
       <c r="AJ262" s="6">
-        <v>5.3144036123707099E-2</v>
+        <v>5.0730487484824303E-2</v>
       </c>
       <c r="AK262" s="6">
-        <v>0.104127083878422</v>
+        <v>0.107223487079128</v>
       </c>
       <c r="AL262" s="6"/>
       <c r="AM262" s="6"/>
@@ -31027,22 +31019,22 @@
         <v>3.5082118242694804</v>
       </c>
       <c r="AF263" s="6">
-        <v>8.7637696225598097E-2</v>
+        <v>9.4234934746928997E-2</v>
       </c>
       <c r="AG263" s="6">
-        <v>0.12718112679320001</v>
+        <v>0.13233797946974499</v>
       </c>
       <c r="AH263" s="6">
-        <v>0.11057443947703099</v>
+        <v>0.11301531839368199</v>
       </c>
       <c r="AI263" s="6">
-        <v>9.9880864677710998E-2</v>
+        <v>0.10126949110298999</v>
       </c>
       <c r="AJ263" s="6">
-        <v>5.0855800982847803E-2</v>
+        <v>4.8513247996218298E-2</v>
       </c>
       <c r="AK263" s="6">
-        <v>0.101479060591586</v>
+        <v>0.104233668557658</v>
       </c>
       <c r="AL263" s="6"/>
       <c r="AM263" s="6"/>
@@ -31055,15 +31047,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76C54D9-CA56-4CB0-A579-57FD6B646278}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DD3CA9B-7A94-4772-8273-147065CB6EBA}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -31090,28 +31073,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8D75A12-56FE-494F-95BC-F47763DA8D7F}">
-  <sheetPr>
-    <tabColor theme="5" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="B3:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>